--- a/attached_assets/May_Deals_1780695126872_Call_Analysis.xlsx
+++ b/attached_assets/May_Deals_1780695126872_Call_Analysis.xlsx
@@ -51,12 +51,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF9C3"/>
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,11 +102,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -652,21 +652,25 @@
       <c r="N2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention calls where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All retention calls were either outgoing or incoming without Aspire/Resync involvement.</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+          <t>Incoming call on Onboarding line: Marcus says, 'I have Raymond with me here on the line, Raymond Roberts. Got the file?' indicating a partner representative is transferring the client.</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Marcus via Onboarding line</t>
+        </is>
+      </c>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Raymond Roberts requested cancellation of his debt consolidation program. Multiple outbound calls were made to confirm and discuss the cancellation, and one brief incoming retention call occurred, but no Aspire/Resync warm transfer was detected. Raymond confirmed he had already canceled and was not interested in continuing due to financial hardship and garnishments. The account was canceled, and no retention was achieved.</t>
+          <t>Raymond was initially onboarded via a live transfer from Marcus, who handed him off to Cassie on the Onboarding line. The onboarding process was completed, payment dates were set, and Raymond's concerns were addressed. Later, Raymond requested cancellation, which was confirmed in a completed outbound call with the Retention team. Multiple outbound attempts were made, and the client was ultimately canceled, with no retention achieved.</t>
         </is>
       </c>
     </row>
@@ -725,25 +729,25 @@
       <c r="N3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>The only incoming completed call on the Retention line (2026-06-03 19:47) was from Dean Lewis, a compliance manager at Mitsubishi, not from an Aspire or Resync representative with a client on the line. The transcript shows Paul called back after receiving a call, and there is no mention of Aspire/Resync transferring a cancelling client.</t>
+          <t>On 2026-05-29 22:57, incoming Onboarding line: Charlie Waybins says, 'I have here mister Paul. He's ready to go. Are you ready for the phone number?' and confirms details for a handoff. This is a clear partner transfer.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Compliance Manager (Dean Lewis, Mitsubishi)</t>
+          <t>Charlie Waybins via Onboarding line</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Paul Maag began onboarding but soon expressed dissatisfaction and requested cancellation, citing misleading information and pressure during the sales process. Multiple departments, including onboarding and customer service, attempted to clarify the program and address concerns. Ultimately, Paul confirmed his desire to cancel during a call with compliance, and no evidence of retention success or a live transfer from Aspire/Resync was found. Several outbound attempts and voicemails were made, but the cancellation request remained unresolved in favor of retention.</t>
+          <t>Paul Maag was live-transferred in by a partner (Charlie Waybins) on the Onboarding line to start the program. Multiple calls followed, including a lengthy CS Team call where Paul expressed discomfort and requested cancellation, and a completed Retention line call where Paul confirmed his wish to cancel due to feeling misled. Outbound attempts and voicemails were made, but ultimately Paul was not retained and pursued cancellation.</t>
         </is>
       </c>
     </row>
@@ -802,25 +806,29 @@
       <c r="N4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line. The only completed incoming call was to Onboarding, and the only completed outbound call was to NSF. No transcript or summary indicates a representative from Aspire or Resync stating they have a client who wants to cancel on an incoming Retention call.</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr">
+          <t>"This is Jason. I'm with Eugene here. You ready for the phone number?" — Incoming call on Onboarding line, Jason (Aspire/partner) is on the line with the client and hands off to Devon Smith.</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Eugene was onboarded into the program and given payment details, but later informed an agent during an outbound NSF call that he had canceled his enrollment, citing participation in other debt resolution programs. Multiple outbound retention calls were attempted, all resulting in voicemails with no completed incoming retention calls. No live transfer from Aspire or Resync to the Retention line occurred, and the cancellation was not processed via a retention-line conversation.</t>
+          <t>The customer was live-transferred in by a partner (Aspire) on the Onboarding line, where onboarding and payment details were discussed and confirmed. Afterward, multiple outbound attempts were made by your agents, mostly to the Retention line, but none were answered or completed. The only completed outbound call reached the customer, who stated he had canceled his enrollment and was already in other debt programs; a callback was scheduled to review his contract. No completed incoming calls occurred on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -879,21 +887,25 @@
       <c r="N5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-06-03 17:44 was a warm transfer from Patrick, who stated he had a mutual client requesting cancellation and transferred the call to Abdulrhman. The transcript shows Patrick introducing himself and the client, and asking for cancellation assistance, matching the definition of a live call.</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>On 2026-05-28 16:04, incoming on the Onboarding line, George (partner rep) says: 'I got Kimmy here on the line. She did enroll with us today into the resolution program along with a graduation loan.' and 'I'll leave you with Donna right now.' This is a clear live transfer from a partner rep.</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (George) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>The customer requested cancellation of their debt relief program, and this was communicated via a live transfer from an Aspire representative. Multiple outbound calls were made by retention agents to discuss the program and confirm cancellation, with the customer repeatedly expressing dissatisfaction and requesting to cancel. The agents agreed to process the cancellation and promised follow-up and confirmation. No retention was achieved; the customer was not retained and cancellation was processed.</t>
+          <t>The customer was live-transferred in by a partner rep for onboarding and enrolled in the debt resolution program. Later, the customer requested cancellation, which was handled through both inbound and outbound calls, including a completed incoming call on the Retention line where the cancellation request was confirmed. Multiple outbound attempts were made to follow up and finalize the cancellation, and the customer was promised a confirmation email. The process included some confusion and dissatisfaction from the customer regarding the program details.</t>
         </is>
       </c>
     </row>
@@ -959,18 +971,18 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line; all calls were outbound attempts and voicemails. No transcript or summary indicates a representative from Aspire or Resync transferring a cancelling client.</t>
+          <t>No incoming calls; all calls were outbound attempts with no transcribable conversations and no mention of Aspire/Resync.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>All calls to Linda Howard were outbound attempts, resulting in voicemails with no completed conversations. No incoming retention-line calls were received, and no evidence of cancellation processing or retention efforts via live interaction. The customer did not answer any calls, and no further action was documented.</t>
+          <t>All calls to Linda Howard were outbound attempts, resulting in voicemails or brief messages with no completed conversations. No incoming calls were received on any line, including Retention. The customer did not answer, and no live contact was made regarding the cancellation request.</t>
         </is>
       </c>
     </row>
@@ -1029,25 +1041,29 @@
       <c r="N7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls where a representative stated they were from Aspire or Resync and had a client wanting to cancel. All retention calls were either outbound or resulted in voicemail.</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr">
+          <t>The incoming call on the Onboarding line opened with a representative (Olivia) providing Robert's file number and then handing off the client to Cassie from the onboarding team, indicating a live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Partner representative (Olivia) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Robert Mittleman was onboarded into a debt relief program and confirmed his payment setup. Outbound calls were made to discuss his debt and cancellation request, but he expressed hesitance and ultimately declined further assistance, stating he never received a loan and cannot pay off the accounts. No incoming retention-line calls were completed; only outbound attempts and voicemails occurred.</t>
+          <t>Robert Mittleman was live-transferred in by a partner rep (Olivia) to the onboarding team, where his program was explained and his payment details were set up. Subsequent outbound calls discussed his debt status and options, but Robert expressed hesitance and ultimately declined further assistance, stating he never received a loan and could not pay off the accounts. No completed incoming calls occurred on the Retention line, and several outbound attempts were made to reach him.</t>
         </is>
       </c>
     </row>
@@ -1106,25 +1122,29 @@
       <c r="N8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. No such transcript or summary is present.</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr">
+          <t>Incoming call on Onboarding line: The caller says, 'I have Ivan here. His file number is 121 7158526... Ivan, I have Xavier here, one of our best. He's going to take good care of you.' This is a clear handoff/transfer of the client to the onboarding agent.</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Unknown partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>Ivan Camacho completed one onboarding call with the Better Lending team, where the debt management program and payment schedule were explained. No incoming calls were received on the Retention line, but multiple outbound attempts and voicemails were made by retention agents with no successful contact. No cancellation or retention conversation occurred, and the customer's cancellation request remains unresolved.</t>
+          <t>The only completed call was an incoming transfer on the Onboarding line, where Ivan was handed off to the onboarding agent for program setup and first payment scheduling. No completed calls occurred on the Retention line, despite numerous outbound attempts and voicemails from agents trying to reach Ivan after a cancellation request. There is no evidence of Aspire or Resync involvement in any call. The customer was onboarded but did not engage further, and the cancellation request was not resolved via a completed retention call.</t>
         </is>
       </c>
     </row>
@@ -1183,25 +1203,29 @@
       <c r="N9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative from Aspire or Resync states they have a client who wants to cancel. All completed calls were either to or from Onboarding, and all Retention calls were outbound voicemails.</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr">
+          <t>The incoming call on the Onboarding line opened with: 'This is Tom Miller. I have Gwen on the other line here. Her file is ready to go.' This is a clear live transfer from a partner representative.</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Tom Miller via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>All completed calls were with the Onboarding department, where the customer discussed payment schedules and the debt relief process, expressing gratitude and understanding. There were several outbound attempts to the Retention line, but none were answered or completed. No incoming Retention calls occurred, and no cancellation was processed through Retention. The customer appears to have been onboarded and informed, but no further action was completed regarding cancellation.</t>
+          <t>A partner representative (Tom Miller) from Resync transferred Gwendolyn Downs to your company via a live call on the Onboarding line, where her onboarding and payment details were discussed and confirmed. No completed incoming calls occurred on the Retention line, though several outbound attempts were made without answer. The customer was successfully onboarded and expressed gratitude for the support, but later requested cancellation. No retention conversation was completed.</t>
         </is>
       </c>
     </row>
@@ -1267,18 +1291,18 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. No transcript or summary indicates a warm transfer from Aspire/Resync.</t>
+          <t>No incoming call transcript or summary mentions Aspire or Resync, nor any indication of a partner representative handing off or transferring the client. The only completed incoming call (Onboarding line) is from Devon Smith of the Federal Lending onboarding team, directly assisting the client.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>The only completed call was an incoming onboarding call where the agent explained the debt reduction process and scheduled the client's first payment. All other calls were outbound attempts or voicemails from the retention team, with no completed incoming retention calls. The customer did not answer any retention calls, and there is no evidence of a live transfer or cancellation discussion. No retention outcome was achieved.</t>
+          <t>There was one completed incoming call on the Onboarding line, where the agent finalized the client's onboarding and explained the debt reduction process. All other calls were outbound attempts or voicemails, primarily from the Retention team, with no completed incoming calls on the Retention line. No evidence of a live transfer or partner handoff was found. The client did not answer any retention calls, and the cancellation request status remains unresolved.</t>
         </is>
       </c>
     </row>
@@ -1337,25 +1361,29 @@
       <c r="N11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. The only completed incoming call was to Onboarding, not Retention, and it was an onboarding discussion.</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr">
+          <t>Incoming call on Onboarding line: Gabriela (partner rep) calls in, provides file number, and is present on the line to hand off Cheryl to Dana Mohamed. Gabriela is explicitly identified as a partner, and Dana refers to the process involving Resync.</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Gabriela (Resync) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>Cheryl Austel completed onboarding in a call with Dana Mohamed, where her questions about the debt relief process and payment schedule were addressed. Multiple outbound attempts were made by the retention team to reach Cheryl after a cancellation request, but all resulted in voicemails with no completed retention-line conversations. No live transfer from Aspire or Resync occurred, and no retention agent spoke directly with Cheryl. The cancellation request remains unresolved as no direct contact was made on the retention line.</t>
+          <t>Cheryl was live-transferred in by Gabriela from Resync on the Onboarding line, where onboarding details and the debt relief process were explained. Cheryl expressed some nervousness, which was addressed by Dana. No completed incoming calls occurred on the Retention line, though there were multiple outbound retention call attempts, all resulting in voicemails. The customer’s request for cancellation was not resolved via a completed retention call.</t>
         </is>
       </c>
     </row>
@@ -1414,25 +1442,25 @@
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was transferred internally by Jackson to Michael (cancellation manager), with no mention of Aspire or Resync. The transcript shows an internal warm transfer, not an Aspire/Resync live transfer.</t>
+          <t>Opening transcript shows an incoming caller (Jackson) saying, 'I'm gonna unhold the line... Corey, can you hear me?... I have Michael here on the line with me. He's my cancellation manager. He's gonna take care of you.' This indicates a live transfer/handoff. Call came in on the Retention line.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Jackson (internal agent)</t>
+          <t>Live transfer via Retention line (from Jackson)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Corey Blackman requested cancellation due to dissatisfaction and confusion about the debt consolidation loan. The only completed call was an incoming retention call, where Michael (cancellation manager) explained the process and offered a refund, but Corey remained firm on cancelling and planned to investigate further. Several outbound attempts and voicemails were made, but no outbound calls were completed. No Aspire or Resync live transfer was detected.</t>
+          <t>The customer, Corey Blackman, requested cancellation and was live-transferred to a cancellation manager via the Retention line. During the call, Corey expressed dissatisfaction with the service and remained firm on his decision to cancel, despite the manager's attempts to explain the process and offer a refund. Several outbound attempts and voicemails were made, but no further contact was completed. The main outcome was a cancellation request with the client planning to follow up after further investigation.</t>
         </is>
       </c>
     </row>
@@ -1491,25 +1519,29 @@
       <c r="N13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. The only completed incoming calls were to Onboarding and CS, not Retention.</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr">
+          <t>The incoming call on the Onboarding line opened with a representative introducing themselves and stating, 'He’s already, like he’s all good to go, and he’s now ready, like, to basically become debt free... Xavier with him today... you can basically proceed here with him, and then you can take it from there.' This indicates a live transfer/hand-off with the client already on the line.</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (possibly Aspire) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>The customer, Keith Hayes, completed onboarding with an agent who explained the debt relief process and provided support information. Multiple outbound calls and voicemails were made from the Retention line and related departments, but there were no completed incoming calls to Retention. The only completed incoming calls were to Onboarding and CS, with no evidence of a live transfer for cancellation. Ultimately, no retention conversation occurred and the customer's cancellation request was not handled via a live Retention call.</t>
+          <t>The customer, Keith Hayes, was live-transferred in by a partner rep (likely Aspire) to the Onboarding line, where the onboarding process and program details were reviewed. Multiple outbound attempts were made by your agents (mostly voicemails) to reach Keith, especially on the Retention line, but no completed incoming calls occurred on Retention. No retention conversation was completed, and the customer’s cancellation request status remains unresolved in the call history.</t>
         </is>
       </c>
     </row>
@@ -1568,25 +1600,29 @@
       <c r="N14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. The only completed incoming call was to Onboarding, not Retention, and did not involve a warm transfer for cancellation.</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr">
+          <t>The incoming Onboarding call opens with Cassie from the onboarding team greeting Joshua, and another party (likely a partner rep) present at the start says, 'Can you transfer me to do my auto I'm still here.' This indicates a live transfer. The call came in on the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (likely Resync) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>Joshua Hing received a detailed onboarding call explaining the debt-relief process and payment schedule, but there were no completed incoming calls to the Retention line. Multiple outbound calls and voicemails were attempted by retention agents, but none were answered or completed. No cancellation or retention conversation occurred, and the customer did not engage with the retention team.</t>
+          <t>Joshua Hing had one completed incoming call, which was a live transfer from a partner (likely Resync) to the Onboarding team, where the onboarding process and payment schedule were explained. There were no completed calls on the Retention line, but multiple outbound attempts were made, all resulting in voicemails. The customer requested cancellation, but no retention conversation was completed. The only substantive interaction was the initial onboarding call.</t>
         </is>
       </c>
     </row>
@@ -1652,18 +1688,18 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>There were zero completed incoming calls on the Retention line, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel. All calls were outbound attempts or voicemails.</t>
+          <t>No incoming calls mention Aspire or Resync, nor any partner handoff; the only incoming call was a brief voicemail with no transcript.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>The company made 20 outbound attempts to reach Lindsay Tripp, all of which resulted in voicemails or brief messages, with no completed conversations. There were no completed incoming calls to the Retention line, and no evidence of a live transfer from Aspire or Resync. The customer's cancellation request was not resolved via phone, as no direct contact was made.</t>
+          <t>There were 21 total calls, all but one were outbound attempts to reach the customer, resulting in voicemails. No completed incoming calls occurred on the Retention line or any other line. The only incoming call was a brief voicemail with no conversation. The customer did not connect with an agent, and no live transfer or partner handoff was detected.</t>
         </is>
       </c>
     </row>
@@ -1722,25 +1758,29 @@
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. All retention-related calls are outbound, and no transcript or summary indicates a warm transfer from Aspire or Resync.</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr">
+          <t>On 2026-05-19 18:54, an incoming call on the Onboarding line began with: 'Hi, sir. It's Harvey Washington. I have Don Gilbert here on the other line. Are you ready for the phone number?' This is a clear live transfer from a partner representative.</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Harvey Washington (Aspire/Resync) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>All retention activity consisted of outbound calls and voicemails to the customer, with no incoming retention-line calls. The customer, Don Gilbert, discussed his debt management and consolidation options with several agents, expressing concerns about loan terms and his credit rating. Despite multiple attempts to reach him and provide program updates, there is no evidence of a completed cancellation or retention via an incoming retention call. The process remains unresolved, with a follow-up scheduled.</t>
+          <t>There was one completed live transfer from a partner (Harvey Washington) to the Onboarding line, where Don Gilbert was handed off for onboarding and debt review. Multiple outbound attempts were made by your agents, but there were no completed incoming calls on the Retention line. Most outbound calls resulted in voicemails or brief updates, with one lengthy discussion about program options and client concerns. The client expressed confusion and hesitancy about the program, and a follow-up was scheduled, but no final resolution or retention was achieved.</t>
         </is>
       </c>
     </row>
@@ -1806,18 +1846,18 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. All retention-related calls were outbound, and incoming retention calls were only voicemails.</t>
+          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, or a partner handoff/transfer. All completed calls were outbound, and all incoming calls were either missed or went to voicemail.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>Brian Vanloan requested cancellation of his debt consolidation program, prompting several outbound calls from retention agents to discuss his concerns and clarify loan terms. No incoming retention-line calls were completed; only voicemails were left. Brian was dissatisfied with the contract terms and requested time to consult with his advisor before finalizing cancellation. The case remains unresolved, with Brian planning to call back when ready.</t>
+          <t>All completed calls with Brian Vanloan were outbound, with no completed incoming calls on the Retention line. The customer requested cancellation due to dissatisfaction with loan terms, and agents provided clarification and agreed to hold the cancellation request while Brian consulted an advisor. No live transfer from Aspire or Resync occurred, and all incoming calls were missed or went to voicemail.</t>
         </is>
       </c>
     </row>
@@ -1876,25 +1916,29 @@
       <c r="N18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. All completed calls were on the Onboarding line, and all Retention line calls were outbound and went to voicemail.</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr">
+          <t>On 2026-05-18 20:21, incoming on Onboarding: The caller says, 'I have Corey here with me... File number 1215 4358 76... Mister Corey Parks.' The agent responds, 'I'll be taking it from here. Thank you, Max.' This is a clear live transfer from a partner (likely Aspire or Resync) handing off the client to your onboarding agent.</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Partner (likely Aspire/Resync) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>Corey Parks completed two onboarding calls, during which he expressed concerns about affordability and ultimately requested to cancel the service. No incoming calls were completed on the Retention line; all retention-related calls were outbound attempts that reached voicemail. The cancellation request was made during onboarding, and follow-up attempts to reach Corey for retention were unsuccessful.</t>
+          <t>The customer, Corey Parks, was live transferred in by a partner (likely Aspire/Resync) to the onboarding team, where he discussed his debt situation and ultimately requested to cancel due to unaffordable payment terms. No completed calls occurred on the Retention line, though multiple outbound attempts were made to reach Corey for follow-up, all resulting in voicemails. The cancellation request was not resolved on a Retention call, and no further customer contact was completed after the initial onboarding calls.</t>
         </is>
       </c>
     </row>
@@ -1953,25 +1997,29 @@
       <c r="N19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel. All retention activity is outbound and consists of voicemails or brief attempts.</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr">
+          <t>The incoming Onboarding line call begins with a representative saying, 'I have here Tamron with me. Are you ready for the file ID?' and then hands off the client, indicating a live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Partner representative via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>The customer completed onboarding in a single, lengthy incoming call, where the debt relief program and payment schedule were discussed. After onboarding, agents made numerous outbound calls and left multiple voicemails, primarily from the retention team, but there were no completed incoming calls to the Retention line. No contact was made regarding cancellation or retention, and there is no evidence of a live transfer from Aspire or Resync. The customer's request for cancellation was not addressed in a live conversation.</t>
+          <t>There was one completed incoming call on the Onboarding line, which was a live transfer from a partner representative handing off Tamara Nicklas to the onboarding agent. No completed calls occurred on the Retention line, despite 31 outbound attempts (mostly voicemails) to reach the customer regarding her cancellation request. The only successful contact was during onboarding, where the program was explained and first payment confirmed. No further live contact was made after onboarding.</t>
         </is>
       </c>
     </row>
@@ -2030,21 +2078,25 @@
       <c r="N20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Both incoming retention calls (2026-06-02 18:48 and 18:53) feature a representative named Maya stating she is from Better Path Lending, affiliated with Resync, and that she has Kathleen on the line to cancel. The transcript shows a warm transfer from an Aspire/Resync affiliate with the client present.</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>In the 2026-06-02 18:48 incoming Retention call, Maya (from a partner) says: 'I do have with me on the line Kathleen. She wants to cancel.' and in the 18:53 call, Maya again states: 'I have Kathleen with me on.' Both are clear live transfers from a partner representative on the Retention line.</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (Maya) via Retention line</t>
+        </is>
+      </c>
       <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Kathleen Downen requested to cancel her program, and her case was handled via two incoming retention calls where a Resync affiliate (Maya) warm-transferred her to the retention team. The retention agent confirmed her intent to cancel due to financial hardship and bankruptcy. After some document issues, Kathleen successfully signed the necessary forms to complete her cancellation. Several outbound attempts were made for follow-up, but the main outcome was a completed cancellation process.</t>
+          <t>The customer, Kathleen Downen, was live-transferred in by a partner representative (Maya) on the Retention line to request cancellation. Two completed incoming Retention calls involved the partner and your agents discussing the cancellation and file details. Afterward, your agent completed an outbound call with Kathleen, confirming her cancellation due to financial hardship and assisting with the necessary paperwork. The process was completed after resolving document delivery issues.</t>
         </is>
       </c>
     </row>
@@ -2103,25 +2155,29 @@
       <c r="N21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>There are zero completed incoming calls on the Retention line. No transcript or summary shows a representative stating they are from Aspire or Resync with a client wanting to cancel, nor any warm transfer from those sources.</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr">
+          <t>The incoming call on the Onboarding line (2026-05-14) opened with Gabriela stating, 'I have Michelle on the line. Are you ready for the file number?' This is a clear live transfer from a partner representative, likely Aspire or Resync, handing off the client.</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Michelle Brooks received several outbound calls and voicemails from retention and customer service agents regarding her debt consolidation program, but did not answer any of them. There were no completed incoming retention-line calls, and no evidence of a live transfer from Aspire or Resync. The onboarding call confirmed Michelle's enrollment and first payment, but subsequent calls focused on updates and cancellation requests were unanswered. The outcome is that outbound efforts were made, but no retention conversation occurred.</t>
+          <t>Michelle Brooks was live-transferred by a partner rep (Aspire/Resync) to the onboarding agent, who discussed her debt resolution process and scheduled her first payment. Multiple outbound calls and voicemails were made by company agents, mostly to follow up or address cancellation requests, but no completed incoming calls occurred on the Retention line. The client requested cancellation, but no retention agent was able to reach her directly; most calls resulted in voicemails.</t>
         </is>
       </c>
     </row>
@@ -2180,25 +2236,29 @@
       <c r="N22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls completed, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client wishing to cancel. All incoming calls were to Onboarding or CCB (other), not the Retention line.</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr">
+          <t>On 2026-05-14, an incoming call on the Onboarding line began with a representative saying, 'I have a customer on the line, Gregory. His file is good to go. Are you ready for the file number?' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Partner (unnamed) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Gregory Hoppe completed onboarding in mid-May and was scheduled to begin payments. In early June, he called a general support line (CCB) to request cancellation and a refund, as he could not reach his previous contact. Multiple outbound attempts were made by retention and other departments, but none were answered or resulted in a completed incoming retention call. No cancellation was confirmed on the retention line, and the customer did not connect with retention directly.</t>
+          <t>Gregory Hoppe was live-transferred by a partner to the onboarding team, where his enrollment and first payment were set up. Later, Gregory called in directly to request cancellation and a refund, but there were no completed calls on the Retention line. Multiple outbound attempts were made to reach him, all resulting in voicemail. The customer was not retained and is seeking cancellation and a refund.</t>
         </is>
       </c>
     </row>
@@ -2257,25 +2317,29 @@
       <c r="N23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>There were zero completed incoming calls to the Retention line. No transcript or summary shows a representative from Aspire or Resync stating they have a client who wants to cancel via a warm transfer.</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="4" t="inlineStr">
+          <t>Incoming call on Onboarding line: Caller (+12254053487) says, 'I have customer Patricia with me. The file should be good to go.' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Partner (likely Aspire) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Patricia Calfee requested cancellation, but no completed incoming retention calls occurred. The only completed calls were an onboarding discussion and a brief incoming call from CCB. Multiple outbound retention attempts were made, all resulting in voicemails with no customer response. The onboarding call explained the debt-relief process involving Aspire and Better Lending, but no cancellation or retention outcome was achieved.</t>
+          <t>Patricia Calfee was live-transferred in by a partner (likely Aspire) on the Onboarding line, where her onboarding process and payment schedule were discussed. There were no completed incoming calls on the Retention line, despite multiple outbound retention attempts (all went to voicemail). The customer requested cancellation, but no retention conversation was completed. Most outbound calls were unanswered, and only onboarding and a brief other call were completed.</t>
         </is>
       </c>
     </row>
@@ -2334,25 +2398,29 @@
       <c r="N24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. The only incoming calls were voicemails or from other departments (Onboarding, CS), and none fit the live transfer definition.</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="4" t="inlineStr">
+          <t>"I have Norma Garcia with me on the other line" and "They're going to take it from here, and that's all yours" from the opening transcript of the 2026-05-12 incoming Onboarding line call.</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (Aspire/Resync) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Norma Garcia had extensive outbound call attempts from the retention team, but none were answered or completed. The only completed calls were with the onboarding and CS teams, where she discussed starting the debt relief program and payment details. No incoming retention calls were completed, and no cancellation was processed through a live transfer. The outcome is that the retention team was unable to reach Norma, and her cancellation request remains unresolved.</t>
+          <t>The customer was live-transferred in by a partner representative (likely Aspire or Resync) via the Onboarding line, where the onboarding process and payment details were completed. Numerous outbound attempts were made by your agents, primarily on the Retention line, but none were answered or completed. No completed incoming calls occurred on the Retention line. The customer's initial request was cancellation, but the only substantive contact was the onboarding call; all other attempts resulted in voicemails or no answer.</t>
         </is>
       </c>
     </row>
@@ -2411,25 +2479,29 @@
       <c r="N25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. All retention calls are outbound, and the only incoming calls are to other departments or result in voicemail/no-answer.</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="4" t="inlineStr">
+          <t>On 2026-05-12, an incoming call on the Onboarding line opened with: 'My name is Jenny Gonzales. I have here Stephanie with me. Are you ready for the file number?' This indicates a partner representative (Jenny Gonzales) was transferring Stephanie to onboarding.</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (Jenny Gonzales) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>All contact attempts to Stephanie Roy Hussey were outbound, with no completed incoming calls to the Retention line. Multiple outbound calls and voicemails were made by retention and customer service agents, referencing Resync and program updates, but there is no evidence of a successful retention conversation or cancellation processing. The customer did not answer or return calls, and the cancellation request remains unresolved.</t>
+          <t>The customer, Stephanie Roy Hussey, was initially live-transferred by a partner rep (Jenny Gonzales) to onboarding, where her program details were discussed and onboarding was completed. Afterward, numerous outbound attempts were made by various agents to reach Stephanie regarding her account and possible cancellation, but no completed incoming calls occurred on the Retention line. All retention efforts were outbound, with most resulting in voicemails or brief conversations, and the customer did not re-engage. The account status remains as cancellation requested, with no evidence of retention success.</t>
         </is>
       </c>
     </row>
@@ -2495,18 +2567,18 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>There are no completed incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants to cancel. All retention-line incoming calls were either voicemails or had no answer.</t>
+          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, or any partner, was on the line or transferring the client. The only completed incoming call (CS Team) was initiated by the customer herself.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="4" t="inlineStr">
+      <c r="R26" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Eileen Fletcher was onboarded into a debt reduction program involving Resync and Better Lending, with payments scheduled. She later called customer service to clarify her account and was advised to cancel her DebtBlue account and request a refund. Multiple outbound retention calls were made, mostly resulting in voicemails, but there were no completed incoming retention-line calls. No cancellation was processed via a live retention call.</t>
+          <t>The customer, Eileen Fletcher, was onboarded into a debt resolution program via an outbound call. She later called in on the CS Team line to clarify her account and was advised to cancel with her previous provider (DebtBlue). There were numerous outbound attempts from the Retention line, but no completed incoming calls on Retention. No evidence of a live transfer from Aspire or Resync was found.</t>
         </is>
       </c>
     </row>
@@ -2565,21 +2637,25 @@
       <c r="N27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>There is no mention in the transcripts or summaries of a representative stating they are from Aspire or Resync, nor any indication that the incoming retention call was a warm transfer from those sources. The only completed incoming retention call was initiated directly by the customer.</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr"/>
+          <t>On 2026-05-08, an incoming call on the Onboarding line began with a representative (Sam) saying, 'I have Kenneth with me. You ready for the account number?' and then transferring Kenneth to agent Xavier Lookman.</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Partner representative (Sam) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R27" s="2" t="inlineStr"/>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Kenneth Gifford initially completed onboarding and later called the retention line himself to discuss cancellation due to financial hardship. The agent offered to postpone his payment and provided instructions for next steps, but there is no evidence of a warm transfer or Aspire/Resync involvement. Numerous outbound retention calls were made to Kenneth, but none were answered. The outcome was a payment postponement and a pending decision on cancellation.</t>
+          <t>Kenneth Gifford was initially live-transferred by a partner representative to the onboarding agent, where his account was set up and payment details confirmed. Later, Kenneth called the Retention line to discuss cancellation due to financial hardship, resulting in his payment being postponed and instructions to sign a document to formalize changes. Multiple outbound attempts were made by agents to reach Kenneth, but none were completed. Ultimately, the client was retained for now with a postponed payment, pending further updates.</t>
         </is>
       </c>
     </row>
@@ -2645,18 +2721,18 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls completed, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client wishing to cancel. All activity consists of outbound calls and voicemails.</t>
+          <t>No incoming calls had a transcribable conversation or opening transcript indicating a partner (Aspire/Resync) or a live transfer; all incoming calls were either voicemails or no-answer.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="4" t="inlineStr">
+      <c r="R28" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>The retention team made numerous outbound call attempts to Sharon Pullen, leaving multiple voicemails, but did not reach the customer. There were no completed incoming calls on the retention line, and no live conversations took place. No evidence of a live transfer from Aspire or Resync was found. The customer's cancellation request remains unresolved due to lack of contact.</t>
+          <t>There were 28 total calls for this customer, all of which were either outbound attempts or incomplete incoming calls (voicemails or no-answer). No completed calls occurred on the Retention line or any other line, and there is no evidence of a live transfer or partner handoff. Multiple outbound calls were made, all resulting in voicemail or no answer, so no customer contact was achieved.</t>
         </is>
       </c>
     </row>
@@ -2715,21 +2791,25 @@
       <c r="N29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-06-03 at 17:19 features Jacob from Aspire Law Group stating he has a mutual client (Therese) on the line who wants to cancel, clearly matching the definition of a live call.</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr"/>
+          <t>On 2026-05-07, Melina from Aspire called in on the Onboarding line and said, 'I have Teresa on the line. You ready for the file number?' On 2026-06-03, Jacob from Aspire Law Group called in on the Retention line and said, 'I have a mutual client with me on the line, Therese.' Both are clear live transfers from Aspire.</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line and Aspire via Retention line</t>
+        </is>
+      </c>
       <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>The customer, Terese Vincent, was onboarded into a debt relief program involving Aspire and Better Lending, but soon experienced payment issues and confusion about the process. On June 3rd, Aspire Law Group live-transferred Terese to the Retention line to request cancellation. Despite the retention agent's efforts to retain her, Terese insisted on canceling due to her self-employed status and preference to negotiate debts herself. Multiple outbound follow-ups and voicemails were made, but the outcome was a confirmed cancellation request.</t>
+          <t>The customer, Terese Vincent, was live transferred in by Aspire representatives on both the Onboarding and Retention lines. The initial onboarding call set up her debt reduction program, but later, Aspire transferred her to the Retention team to request cancellation. Terese confirmed she wanted to cancel, declining all retention offers. Multiple outbound attempts and voicemails were made, but the cancellation request was clear and handled during the live transfer.</t>
         </is>
       </c>
     </row>
@@ -2788,25 +2868,29 @@
       <c r="N30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All retention calls were outbound, and the only incoming calls were to Onboarding and CS Team.</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="4" t="inlineStr">
+          <t>"So I have here with me, Catherine, on the line. Let me just send you the file number." (incoming Onboarding line, 2026-05-07 03:30). This is a clear live transfer from a partner representative handing off the client.</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Catherine Rios completed onboarding and discussed payment scheduling, including a change to her loan start date with the CS Team. Several outbound calls and voicemails were made from the Retention line, but Catherine did not answer or call the Retention line herself. No cancellation was processed via a live transfer, and no incoming retention calls occurred. The account shows outbound retention activity but no incoming retention engagement.</t>
+          <t>Catherine Rios was live-transferred in by a partner (Aspire/Resync) on the Onboarding line, where her onboarding and payment schedule were discussed. She later called the CS Team to request a payment date change, which was accommodated. Multiple outbound attempts were made by the Retention team, but no incoming calls were completed on the Retention line. The account status is cancellation requested, but no retention-line conversation occurred; most contact was via onboarding and CS.</t>
         </is>
       </c>
     </row>
@@ -2865,21 +2949,25 @@
       <c r="N31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>The only incoming retention call (2026-05-23) was from the customer directly, not a representative from Aspire or Resync. The transcript and summary do not indicate a warm transfer or mention of an Aspire/Resync rep stating they have a client wishing to cancel.</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr"/>
+          <t>On 2026-05-07, the incoming Onboarding call opened with: 'This is Leon at the lending department. I have mister Floyd Hook here with me ready with the file number.' This indicates a live transfer from a partner (likely Resync) to your onboarding agent.</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
       <c r="R31" s="2" t="inlineStr"/>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Floyd Hook completed onboarding and was scheduled to start the debt reduction process. After multiple outbound attempts and voicemails from retention and NSF agents, Floyd called the retention line directly to request cancellation due to financial and family medical issues. He was informed the cancellation process takes time and did not continue the conversation. No Aspire/Resync warm transfer occurred; the cancellation request came from Floyd himself.</t>
+          <t>Floyd Hook was live-transferred in by a partner (Resync) to begin onboarding and had his debt reduction process explained. Later, he called in on the Retention line to request cancellation due to financial and family issues, and was informed cancellation is a process. Numerous outbound attempts were made by your agents, but none were answered. Ultimately, the client requested cancellation and did not proceed further.</t>
         </is>
       </c>
     </row>
@@ -2945,18 +3033,18 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls on the Retention line; all calls were outbound. No transcript or summary indicates an incoming call where a representative from Aspire or Resync stated they had a client wishing to cancel.</t>
+          <t>No incoming calls were completed; all calls in the log are outbound attempts or completed outbound calls. No transcript evidence of an incoming call with a partner handoff or mention of Aspire/Resync by an inbound caller.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="4" t="inlineStr">
+      <c r="R32" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>All contact attempts to James Crookshank were outbound, with no incoming retention-line calls. Multiple voicemails were left regarding his cancellation request and program updates, but James was only reached once, where he confirmed he no longer needed assistance and requested not to be contacted further. The majority of calls resulted in voicemails or no answer, and the account was not retained.</t>
+          <t>All contact attempts to James Crookshank were outbound, with no completed incoming calls on the Retention line. Agents repeatedly attempted to reach James regarding his cancellation request and program updates, leaving multiple voicemails and callback numbers. In one outbound call, James confirmed he no longer needed assistance, having resolved his debt independently, and requested no further contact. No live transfer or partner handoff occurred.</t>
         </is>
       </c>
     </row>
@@ -3015,21 +3103,25 @@
       <c r="N33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>There are two incoming retention calls (2026-06-01 and 2026-06-03) where representatives from Resync clearly state they are calling with a mutual client who wants to cancel, and the transcript shows a warm transfer to the retention agent.</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr"/>
+          <t>On 2026-06-01 18:07 (Retention line), the incoming caller introduced himself as Justin from Resync and stated, 'I have a mutual client that's requesting cancellation.' On 2026-06-03 21:18 (Retention line), the incoming caller introduced himself as Jacob from Resync and said, 'I have a mutual client that wants to cancel the program.' Both are clear live transfers from Resync.</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R33" s="2" t="inlineStr"/>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Johnny Watson initially enrolled in a debt consolidation program, but soon requested cancellation, claiming he never fully agreed to the contract and was unhappy with unauthorized withdrawals. Multiple incoming retention calls were warm-transferred from Resync, and retention agents processed Johnny's cancellation and refund requests. Johnny signed the necessary documents to finalize the cancellation and refund, and the account was closed. Several outbound calls and voicemails supported the process, with no retention achieved.</t>
+          <t>The customer, Johnny Watson, was onboarded and initially set up for a debt consolidation program, but soon after requested cancellation, stating he never enrolled and was unhappy with the process. Multiple live transfers from Resync brought cancellation requests to the Retention team, who worked with Johnny to process his refund and required documents. Several outbound and inbound calls occurred, including document signing and confirmation. Ultimately, the account was cancelled and a refund was processed for Johnny.</t>
         </is>
       </c>
     </row>
@@ -3088,21 +3180,25 @@
       <c r="N34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-20 was initiated by Brandon from Aspire Law Group, who clearly stated he was reaching out for a mutual client's cancellation request and transferred Nicholas Pitt to Talia Morgan for assistance. This matches the definition of a 'live call' from Aspire.</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr"/>
+          <t>2026-05-20 16:15 incoming on Retention: Caller introduces as Brandon from Aspire Law Group, states he is reaching out for a mutual client's cancellation request, and asks to transfer the client. Line: Retention.</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Retention line</t>
+        </is>
+      </c>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Pitt initially engaged with onboarding and discussed debt management and payment setup. On 2026-05-20, Aspire Law Group transferred Nicholas to the retention line to request cancellation due to a denied secured loan. Multiple outbound calls and voicemails followed, but no further retention-line incoming calls occurred. The primary outcome was a cancellation request handled via a live transfer from Aspire.</t>
+          <t>The customer, Nicholas Pitt, was transferred in via a live call from Aspire Law Group on the Retention line to request cancellation due to a denied secured loan. The Retention agent handled the cancellation request. There were multiple outbound attempts to reach Nicholas, with only one outbound and one inbound Retention call completed. The process included onboarding and follow-up, but ultimately the account moved to cancellation at the customer's request.</t>
         </is>
       </c>
     </row>
@@ -3161,25 +3257,29 @@
       <c r="N35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. The only incoming retention-line call was a voicemail, not a live transfer.</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="4" t="inlineStr">
+          <t>On 2026-05-05, an incoming call on the Onboarding line included Leah Tanner stating, 'I just have this file here, Benjamin m Majama, and his file is ready to go. Are you ready for the account number?' This indicates a partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Leah Tanner (Aspire/Resync) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Benjamin Marjamaa had two completed incoming calls: onboarding and customer service. The onboarding call confirmed account setup and payment details, mentioning Aspire as part of the debt reduction process. The CS call resulted in Benjamin deciding not to proceed, and the agent agreed to terminate the file. There were no completed incoming retention-line calls; all retention attempts were outbound and resulted in voicemails. The account was cancelled, and no retention conversation occurred.</t>
+          <t>There were two completed incoming calls: one on the Onboarding line where the partner (Leah Tanner) transferred Benjamin to your team, and one on the CS line where the customer called to cancel after a failed consolidation. No completed calls occurred on the Retention line despite numerous outbound attempts and voicemails. The customer ultimately requested cancellation, and the file was terminated without written confirmation.</t>
         </is>
       </c>
     </row>
@@ -3238,21 +3338,25 @@
       <c r="N36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-15, two incoming retention calls were warm transfers from Resync representatives (Connor and Daniel) stating they had a client (Anthony McGriff) who wanted to cancel, and they transferred Anthony to Talia Morgan for cancellation assistance.</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr"/>
+          <t>On 2026-05-15 18:06 and 2026-05-15 18:22, incoming calls on the Retention line began with: 'This is Connor calling from Resync on a recorded line. I have a client on the line, Anthony, who requests cancellation.' and 'This is Daniel speaking on a recorded line from Resync's client care department. I have an Anthony McGriff.'</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Anthony McGriff initially completed onboarding and later requested cancellation. Two incoming retention calls were warm transfers from Resync, with both Connor and Daniel facilitating the transfer to the compliance department for cancellation. After a dropped call, the process was completed, and Talia Morgan confirmed the account would be cancelled per Anthony's request. Multiple outbound attempts and voicemails were made, but the outcome was a confirmed cancellation.</t>
+          <t>Anthony McGriff was live-transferred twice by Resync representatives to the Retention line for cancellation requests. Talia Morgan from compliance handled the calls, confirmed the cancellation, and promised a confirmation email. Numerous outbound attempts and voicemails were made before and after, but the key outcome was the successful processing of Anthony's cancellation request after the live transfer. No retention was achieved; the client insisted on canceling.</t>
         </is>
       </c>
     </row>
@@ -3307,21 +3411,25 @@
       <c r="N37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-11 was initiated by Emily from Resync, who stated she had a cancellation request for Christina and transferred the call to Ryan Henderson. The transcript confirms Emily identified herself as being from Resync and was facilitating a warm transfer for a client wanting to cancel.</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr"/>
+          <t>On 2026-05-05, Elena called in on the Onboarding line and introduced herself, stating 'I have Christina Biron with me on the line.' On 2026-05-11, Emily from Resync called in on the Retention line and said, 'Hi, Ryan. This is Emily with Resync. I have a cancellation request for you.'</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Elena (Aspire) via Onboarding line; Emily (Resync) via Retention line</t>
+        </is>
+      </c>
       <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Cristina Bito On was onboarded and later requested cancellation. An incoming retention call was warm-transferred from Resync, where Cristina confirmed her desire to cancel. Multiple outbound calls and voicemails were made to follow up, but Cristina remained firm on her decision to cancel and did not provide a reason. The account was not retained, and the cancellation process was initiated.</t>
+          <t>The customer was initially live-transferred by a partner (Aspire) for onboarding, then later live-transferred by Resync for a cancellation request. The customer spoke with a retention agent and insisted on canceling the program, expressing distrust and refusing to discuss further. Numerous outbound attempts were made by agents, but only one incoming retention call was completed. The outcome was a firm cancellation request from the customer, with no retention achieved.</t>
         </is>
       </c>
     </row>
@@ -3380,25 +3488,29 @@
       <c r="N38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All retention calls were outbound, and no Aspire/Resync keywords were detected in transcripts.</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="4" t="inlineStr">
+          <t>The incoming call on the Onboarding line opened with the caller saying, 'So I have here Janine Platt with me on the line. The file is good to go. Are you ready for the phone number?' This indicates a partner representative was transferring the client.</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>Unknown partner via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Janine Platt was onboarded and made aware of her payment schedule. She later requested cancellation due to her son paying off her debts and concerns about her monthly income. Retention agents made multiple outbound calls to discuss options, including pausing the account, but Janine insisted on canceling. No incoming retention calls were completed, and most outbound attempts resulted in voicemails or brief conversations.</t>
+          <t>The customer was initially transferred in by a partner on the Onboarding line and completed onboarding with your agent. Later, the customer requested cancellation, prompting multiple outbound retention calls and voicemails, but no completed incoming calls on the Retention line. The customer expressed financial hardship and insisted on canceling, with agents offering to pause the account or reschedule payments. Ultimately, the customer was not retained, and all retention efforts were outbound only.</t>
         </is>
       </c>
     </row>
@@ -3457,21 +3569,25 @@
       <c r="N39" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-12 20:18, Jesse from Aspire Law Group called the Retention line and stated they had Maria Watson on the line who wanted to cancel the program. The transcript confirms this was a warm transfer from Aspire for a cancellation request.</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr"/>
+          <t>"Hi, Catherine. My name is Jesse. I'm calling from Aspire Law Group customer service. I have here on the line miss Maria Watson who has requested to cancel the program." (2026-05-12 incoming on Retention line)</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Retention line</t>
+        </is>
+      </c>
       <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Maria Watson made multiple attempts to cancel her debt-relief program, expressing confusion and distrust in several calls. The only completed incoming retention-line call was a live transfer from Aspire Law Group, where Maria's cancellation request was communicated but required a Spanish-speaking agent. Outbound retention agents also spoke with Maria, who insisted on canceling, and her cancellation was confirmed. Most other calls were voicemails or involved attempts to reach the correct department.</t>
+          <t>Maria Watson had multiple interactions with the company, including several inbound calls where she repeatedly requested to cancel her contract and expressed frustration about lack of response. A live transfer from Aspire Law Group to the Retention line confirmed her cancellation request. There were also several outbound attempts and completed calls from company agents, including one where cancellation was confirmed. The outcome is that Maria requested cancellation multiple times, was transferred in by a partner (Aspire), and the company acknowledged her cancellation request.</t>
         </is>
       </c>
     </row>
@@ -3530,25 +3646,29 @@
       <c r="N40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. All retention-related calls are outbound, and the only incoming call is to Onboarding, not Retention.</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="4" t="inlineStr">
+          <t>The incoming call on the Onboarding line opened with the caller saying, 'I do have here with me Kathleen Cohen. She is she's all ready. Are you ready for her file number?' indicating a live transfer of the client.</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>Partner (likely Aspire/Resync) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>The customer, Cathleen Cohen, completed onboarding and discussed her debt relief plan in detail. Multiple outbound calls were made by retention agents to follow up, but there were no incoming calls to the Retention line. Mr. Cohen (presumably Cathleen's husband) made it clear during an outbound call that they wished to stop the program and did not want further contact, even threatening legal action if calls continued. Ultimately, the customer requested cancellation and did not engage with retention efforts.</t>
+          <t>The customer was live-transferred in via the Onboarding line, where her debt relief plan was set up and explained. Multiple outbound attempts were made by various agents, but there were no completed incoming calls on the Retention line. The customer later expressed a desire to cancel the program and requested no further contact, even threatening legal action if calls continued. Ultimately, the account status is cancellation requested, with no successful retention intervention.</t>
         </is>
       </c>
     </row>
@@ -3614,18 +3734,18 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>There were zero incoming retention-line calls completed, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel. All calls were outbound attempts or voicemails.</t>
+          <t>No incoming calls were completed; all calls were outbound attempts or voicemails. No mention of Aspire or Resync in any transcript or call intro.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="4" t="inlineStr">
+      <c r="R41" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>The company made numerous outbound calls and left multiple voicemails for Chuck Westerman regarding his cancellation request, but there were no incoming retention-line calls or live conversations. No evidence of a warm transfer from Aspire or Resync was found. The customer did not answer or return any calls, and no cancellation or retention outcome was confirmed.</t>
+          <t>All contact attempts to the customer were outbound, with agents leaving multiple voicemails but never reaching the customer live. There were no completed incoming calls on any line, including Retention. The customer's request for cancellation was not resolved via a live conversation, and no partner transfer or live handoff occurred.</t>
         </is>
       </c>
     </row>
@@ -3684,25 +3804,29 @@
       <c r="N42" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls on the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. The only incoming completed calls were on 'CCB (other)' and 'CS Team (cs)' lines, and none fit the definition of a live transfer from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="4" t="inlineStr">
+          <t>On 2026-05-07 17:11, incoming on CS Team (cs): The agent introduces as 'Tammy Morgan with the compliance department' and, when asked, confirms 'With Resync.' The customer is handed off from Resync to your company to process a cancellation request.</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>Resync via CS Team (cs) line</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Theresa Wiedman made several incoming calls to clarify and correct issues with her account, specifically regarding the inclusion of Suncoast in her program. She expressed dissatisfaction and a desire to cancel during both inbound and outbound calls, citing miscommunication and lack of consent. Multiple outbound retention attempts were made, but there were no incoming calls to the Retention line. Ultimately, the customer requested cancellation, and the account was flagged for follow-up, but no retention-line live transfer occurred.</t>
+          <t>Theresa Weidman made several incoming calls to resolve an account issue and ultimately requested cancellation, citing dissatisfaction and a mistaken account inclusion. The only live transfer was from Resync via the CS Team line, where Theresa formally requested to cancel her program. Multiple outbound attempts were made by your agents, but none were completed on the Retention line. The customer was not retained and pursued cancellation after expressing frustration with the process.</t>
         </is>
       </c>
     </row>
@@ -3768,14 +3892,14 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>There is no evidence in the transcripts or summaries that an incoming retention call involved a representative stating they were from Aspire or Resync with a client wanting to cancel. The only incoming retention call was a direct call answered by Dean Lewis, who identified as a compliance manager at Mister Gacy.</t>
+          <t>No incoming call had an Aspire or Resync representative, nor any mention of a partner handoff or transfer. The only completed incoming call (Retention line, 2026-06-01) was a direct client call, with Dean Lewis introducing himself as a compliance manager and no mention of Aspire/Resync or a transfer.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr"/>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>The customer received numerous outbound calls and voicemails from various agents, mostly from the retention team, with only one incoming call to the retention line. The single incoming retention call did not involve Aspire or Resync and appeared to be a direct call, but there was no meaningful conversation as the agent repeatedly greeted the caller without response. No successful cancellation or retention conversation is documented, and most contact attempts resulted in voicemails or no answer.</t>
+          <t>There were 23 total calls, mostly outbound attempts with only three completed calls: one incoming on the Retention line and two outbound. The only completed incoming call was a direct client call, not a partner transfer. Most outbound calls went to voicemail. The client requested cancellation, and the team made repeated attempts to reach them, but there was no evidence of a live transfer or partner involvement.</t>
         </is>
       </c>
     </row>
@@ -3841,18 +3965,14 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>There is no evidence in the transcripts or summaries that an incoming retention call involved a representative stating they were from Aspire or Resync with a client wanting to cancel. The only completed incoming retention call was from an internal accounts manager (Dean Lewis from Better Path Lending), not Aspire or Resync.</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>Better Path Lending (Dean Lewis, accounts manager)</t>
-        </is>
-      </c>
+          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there any mention of a partner company or a handoff/transfer. The only completed incoming call (Retention line, 2026-05-25) was directly from a Better Path Lending accounts manager, not a partner.</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr"/>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>The customer, Jesus Portillo, received multiple outbound calls and voicemails from retention agents regarding a cancellation request, but did not answer those calls. One incoming retention call was completed, during which the customer denied knowledge of the contract and insisted on cancellation. There is no evidence of a live transfer from Aspire or Resync. The overall outcome is that the customer was reached once, expressed confusion, and requested cancellation.</t>
+          <t>The customer, Jesus Portillo, requested cancellation. Numerous outbound calls and voicemails were made by agents, mostly on the Retention line, with only one completed incoming call on the Retention line. In that call, the agent attempted to discuss a contract, but the customer denied any agreement and insisted on cancellation. There is no evidence of a live transfer or partner handoff; all contact was direct between the company and the customer.</t>
         </is>
       </c>
     </row>
@@ -3918,14 +4038,14 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention calls where a representative stated they were from Aspire or Resync and had a client who wants/needs to cancel. The only incoming retention call was from Grace Turner herself, not a warm transfer from Aspire/Resync.</t>
+          <t>No incoming call transcript mentions Aspire or Resync, nor does any caller indicate they are a partner handing off or transferring the client. Both completed incoming calls are directly from the customer (Grace Turner) to the Retention line and a follow-up from the same agent, with no evidence of a partner transfer.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Grace Turner called the retention line directly to request cancellation due to lack of communication from her representatives. She was informed by Katherine Adams that her contract was past the three-day cancellation grace period and could not be cancelled. Multiple outbound calls and voicemails were made to Grace, but none were completed. Grace expressed frustration and a desire to stop dealing with the company.</t>
+          <t>Grace Turner repeatedly attempted to contact her original representatives to cancel her transaction but was unsuccessful. She called the Retention line directly and spoke with Katherine Adams, who confirmed the communication issues and explained that the cancellation grace period had expired. Multiple outbound calls and voicemails were made by various agents to follow up, but there were no further completed calls. Ultimately, Grace was not able to cancel due to being outside the allowed period, and her frustration with the lack of communication remained unresolved.</t>
         </is>
       </c>
     </row>
@@ -3991,14 +4111,14 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>There was one incoming completed call to the Retention line, but no evidence in the transcript or summary that a representative stated they were from Aspire or Resync or that it was a warm transfer of a cancelling client. No Aspire/Resync keywords detected.</t>
+          <t>Neither incoming call mentions Aspire or Resync, nor does the caller indicate they are a partner transferring a client. The first call is in a foreign language and ends abruptly. The second call is a customer trying to reach someone named Travis, with no mention of a partner handoff.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr"/>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>The customer had one completed incoming call to the Retention line, but it was not a live transfer from Aspire or Resync. There were many outbound call attempts (mostly voicemails) but none were completed. Two other incoming calls were unrelated to retention and had communication issues. Overall, the cancellation request was not resolved via a live transfer, and the customer was not reached successfully by outbound calls.</t>
+          <t>There were 36 total calls, with the majority being outbound attempts (mostly voicemails) from your agents to the customer. Only three calls were completed, including one on the Retention line. The two completed incoming calls were from the customer directly, not a partner, and involved communication issues or requests to reach a specific person. No evidence of a live transfer or partner handoff was found. The customer's cancellation request status remains unresolved due to lack of successful engagement.</t>
         </is>
       </c>
     </row>
@@ -4057,21 +4177,25 @@
       <c r="N47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-21 was from Caleb at Aspire Law Group, who stated he had Terry Bell on the line and she wanted to cancel. This matches the definition of a live call from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr"/>
+          <t>Incoming call on Retention line opened with 'This is Caleb from Aspire Law Group on a recorded line... I do have miss Terry Bell here. She just wants to go ahead and cancel.'</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Retention line</t>
+        </is>
+      </c>
       <c r="R47" s="2" t="inlineStr"/>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Terri Bell's only completed call was an incoming retention-line call where an Aspire Law Group representative transferred her to compliance to process her cancellation request, citing a misunderstanding about the program being a loan. All subsequent 28 outbound calls were unsuccessful, resulting in voicemails or brief attempts, with no further contact or retention achieved. The customer was not retained and proceeded with cancellation. No other departments or internal transfers were involved.</t>
+          <t>There was one completed incoming call on the Retention line, which was a live transfer from Aspire Law Group where the client, Terri Bell, requested cancellation due to misunderstanding the program. All other 28 calls were outbound attempts or voicemails from various agents, with no additional completed conversations. The outcome was that the client was transferred in for cancellation, and no further contact was made despite multiple outbound attempts.</t>
         </is>
       </c>
     </row>
@@ -4130,21 +4254,25 @@
       <c r="N48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>The 2026-05-15 18:17 incoming retention call transcript shows Alexander from Resync stating, 'I have Heidi that's requested to cancel,' and transferring the call to Levi Miller, confirming this was a live transfer from Resync regarding a cancellation request.</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr"/>
+          <t>Incoming call on Retention line opened with: 'Hello, Levi. This is Alexander with Resync. I have Heidi that's requested to cancel.' (2026-05-15 18:17, Retention line).</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R48" s="2" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Heidi Terrazas requested cancellation of her debt relief program, with the initial incoming retention call being a live transfer from Resync. Multiple outbound calls followed, during which Heidi cited loss of disability income and inability to afford payments. Representatives discussed postponing payments and holding the account, but Heidi remained firm on cancellation. Several voicemails were left after the initial calls, with no evidence of retention success; the account appears to remain on hold or pending cancellation.</t>
+          <t>A live transfer from Resync was received on the Retention line, with the partner representative handing off Heidi for a cancellation request. Multiple outbound calls and voicemails followed, with agents discussing cancellation, financial hardship, and postponement of payments. The customer repeatedly requested cancellation due to loss of income, and agents confirmed the account was on hold and no payments would be deducted. There was one completed incoming Retention call and several outbound attempts, with no evidence of retention success.</t>
         </is>
       </c>
     </row>
@@ -4210,18 +4338,18 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>There were zero completed incoming retention-line calls, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel. All calls were outbound attempts or voicemails, with no live transfer or conversation detected.</t>
+          <t>No incoming calls with transcribable conversations; no mention of Aspire or Resync in any transcript or call log entry.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="4" t="inlineStr">
+      <c r="R49" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>The company made 26 outbound call attempts to Anne Marie Bryant, mostly leaving voicemails, but none of the calls were answered or resulted in a completed conversation. There were no incoming retention-line calls, and no evidence of a live transfer from Aspire or Resync. The customer did not engage, and the cancellation request was not processed via a live call.</t>
+          <t>All calls to this customer were outbound attempts, primarily voicemails left by various agents across Retention, CS, and NSF departments. There were no completed incoming calls on any line, including Retention, and no conversations took place. The customer did not answer any calls, and no live transfer from Aspire or Resync occurred. The cancellation request remains unresolved due to lack of contact.</t>
         </is>
       </c>
     </row>
@@ -4280,21 +4408,25 @@
       <c r="N50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-08, an incoming retention call transcript shows Alexander from Resync stating he is transferring Karen, who wants to cancel, to Rick from Mitigately. Alexander clearly identifies himself as from Resync and states the client wishes to cancel.</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr"/>
+          <t>Alexander with Resync called in on the Retention line and stated: 'I've got Karen Tushton that's requested to cancel the program due to not being able to afford the payments. Whenever you're ready for the transfer, let me know.'</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Karen Touchton requested cancellation due to unaffordable payments. An Aspire/Resync representative (Alexander) live-transferred her to the retention line, where the compliance manager discussed her options and explained the cancellation process. Multiple outbound follow-ups and voicemails were made, but no further incoming retention calls occurred. The account was set to remain active until June 8, with no payments drafted, pending final cancellation confirmation.</t>
+          <t>Karen Touchton's cancellation request was live-transferred by Resync to the Retention line, where the compliance manager discussed her affordability concerns. Multiple outbound attempts were made to follow up, with some completed outbound calls and several voicemails left. The account was set to remain active until June 8, with no payments drafted, pending a final decision. The process involved both inbound and outbound retention efforts, with the main issue being the customer's inability to afford the program.</t>
         </is>
       </c>
     </row>
@@ -4360,14 +4492,14 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming retention calls included a representative stating they were from Aspire or Resync and that they had a client who wanted to cancel. The only incoming retention call (2026-06-04 13:29) was from the customer herself, not a warm transfer from Aspire or Resync.</t>
+          <t>None of the incoming calls on any line (CS Team or Retention) include an introduction or statement from a representative indicating they are from Aspire or Resync, nor do they mention a partner handing off or transferring the client. All incoming calls are directly from the customer or someone calling on their behalf, asking for specific agents or support.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr"/>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>The customer, Canita Crader, had multiple interactions with customer service regarding document submission issues and ultimately requested to cancel her debt relief program due to affordability concerns. After several outbound and inbound calls, a compliance agent from Aspire confirmed the cancellation request, paused payments, and set a 30-day hold period with no deductions. The customer was informed that a follow-up would occur after 30 days to confirm her final decision. No live transfer from Aspire or Resync was detected; all retention calls were direct between the customer and the company.</t>
+          <t>The customer, Kenita Crader, made multiple calls to customer support regarding document submission issues and later requested to cancel her debt relief program. Several outbound and inbound calls occurred, including one completed call on the Retention line where the cancellation process was discussed and a payment pause was arranged. Ultimately, the account was placed on hold for thirty days with no payments deducted, and a follow-up was scheduled to confirm the cancellation.</t>
         </is>
       </c>
     </row>
@@ -4433,18 +4565,18 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls on the Retention line, and none of the incoming calls mention Aspire or Resync or involve a representative stating they have a client who wants to cancel. All incoming calls are on the 'CCB (other)' line and are general requests to speak with Joey Heckman.</t>
+          <t>None of the incoming calls mention Aspire or Resync, nor do they indicate a partner or representative is transferring the client. All incoming calls are direct from the customer or a family member, requesting to speak with a specific agent (Joey Hackman).</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="4" t="inlineStr">
+      <c r="R52" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>There were 32 total calls, with 28 outbound attempts and 3 completed incoming calls, all on a non-retention line. The incoming calls were from the customer or their representative seeking to reach Joey Heckman, with no mention of cancellation or Aspire/Resync. Numerous outbound voicemails were left by various agents, but there was no successful contact on the Retention line and no evidence of a retention or cancellation conversation. The customer did not connect with the Retention department.</t>
+          <t>There were 32 total calls, with 3 completed incoming calls, all on the 'CCB (other)' line, and 28 outbound attempts, mostly resulting in voicemails. No completed calls occurred on the Retention line, and no live transfers from Aspire or Resync were detected. The incoming calls were direct requests from the customer or a family member to speak with agent Joey Hackman, with no evidence of partner handoff or live transfer. The customer's cancellation request was not resolved via a completed retention call.</t>
         </is>
       </c>
     </row>
@@ -4510,18 +4642,18 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>There are zero completed incoming calls on the Retention line. All completed retention calls are outbound, and none of the call summaries or transcripts indicate an incoming call where a representative from Aspire or Resync states they have a client who wants to cancel.</t>
+          <t>There are no completed incoming calls on any line where the opening transcript or summary indicates a partner (Aspire/Resync) representative was on the line or transferring the client. The only completed incoming call (2026-05-07 21:04 on CS Team) does not mention Aspire/Resync or a partner transfer in its summary or transcript.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="4" t="inlineStr">
+      <c r="R53" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>The customer, Sheri Kunz, received numerous outbound calls from the Retention team, with several voicemails left and four completed outbound retention calls. Sheri repeatedly expressed confusion about the debt program, cited possible identity theft, and ultimately wanted to cancel due to already having another program and receiving government assistance. No incoming retention calls were completed, and the deal was ultimately cancelled after multiple unsuccessful retention attempts.</t>
+          <t>All completed calls were outbound, with no completed incoming calls on the Retention line. The customer, Sheri Kunz, repeatedly expressed confusion and concern about the debt consolidation program, citing identity theft and a preference to cancel. Multiple agents attempted to clarify the situation, provide documentation, and offer to postpone payments, but Sheri remained intent on cancellation. Numerous outbound attempts resulted in voicemails, and ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -4580,25 +4712,29 @@
       <c r="N54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. All retention calls were outbound and/or voicemails.</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="4" t="inlineStr">
+          <t>The incoming call on the Onboarding line opened with 'This is Jackson. I have Athena here with me. Her file is good to go. Are you ready for the file number?' indicating a partner (Jackson) was transferring Athena to your company.</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>Athena Taylor completed onboarding with an agent, confirming her understanding of the debt relief process and payment schedule. After onboarding, there were multiple outbound attempts from the Retention team, all resulting in voicemails except for one completed outbound call. No incoming calls were received on the Retention line, and there is no evidence of a live transfer or cancellation request. The customer has not engaged with Retention beyond receiving voicemails.</t>
+          <t>Athena Taylor was live transferred by a partner (Aspire) on the Onboarding line, where her onboarding and payment details were confirmed. Multiple outbound attempts were made to reach her on the Retention line, but none were completed; only voicemails were left. There were no completed incoming calls on the Retention line. The only completed call was the initial onboarding transfer, and follow-up efforts did not reach the client directly.</t>
         </is>
       </c>
     </row>
@@ -4664,14 +4800,14 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>There is only one completed incoming call to the Retention line, and the transcript/summary does not indicate that the representative stated they were from Aspire or Resync, nor that it was a warm transfer of a cancelling client.</t>
+          <t>No mention of Aspire or Resync in any incoming call opening transcript. The only incoming calls were from internal company agents (Devon from onboarding, Rick Miller from retention), and there is no indication of a partner handoff or transfer.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
       <c r="R55" s="2" t="inlineStr"/>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>Lillian N. Raini had one completed incoming call to the Onboarding department and one brief completed incoming call to Retention, with no evidence of a warm transfer or cancellation request. The majority of outbound calls were attempts that resulted in voicemails, with no successful outbound contact. There is no indication of cancellation or retention actions, and the customer did not respond to multiple outbound retention efforts.</t>
+          <t>The customer had two completed incoming calls: one on the Onboarding line and one brief call on the Retention line. There were numerous outbound attempts (17), all resulting in voicemails or no answer, and no completed outbound conversations. No evidence of a partner (Aspire/Resync) live transfer was found. The overall outcome appears to be initial onboarding and attempted retention follow-up, but no successful retention or cancellation conversation.</t>
         </is>
       </c>
     </row>
@@ -4737,18 +4873,14 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line, and no transcripts or summaries indicate a representative from Aspire or Resync transferring a cancelling client.</t>
+          <t>No transcribable conversations; all incoming calls to Onboarding line were no-answer or voicemail with no transcript. No mention of Aspire/Resync or any partner transfer.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="4" t="inlineStr">
-        <is>
-          <t>OB done — no calls on retention line</t>
-        </is>
-      </c>
+      <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>All calls were incoming to the Onboarding line and either resulted in no answer or voicemail, with no completed conversations. No calls were made to or from the Retention line, and there were no outbound attempts. The deal status is cancelled, but no retention or cancellation discussions occurred in the call history.</t>
+          <t>There were four incoming calls to the Onboarding line, all of which were either not answered or resulted in a voicemail with no transcript. No completed calls occurred on any line, and there were no outbound call attempts. There is no evidence of a live transfer or partner handoff. The customer's deal status is cancelled, but no direct contact was made.</t>
         </is>
       </c>
     </row>
@@ -4807,21 +4939,25 @@
       <c r="N57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming retention calls show a representative stating they are from Aspire or Resync and have a client who wants/needs to cancel. All retention calls are direct from the customer (David) himself, not a warm transfer from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr"/>
+          <t>The opening transcript of the 2026-05-30 incoming Onboarding call shows Mark (likely from a partner, possibly Resync/Aspire) handing off David to Vera for onboarding, explicitly stating 'She's gonna onboard you to everything. I'm gonna hang up. You'll wait.' This is a clear live transfer. The call came in on the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>Partner (Mark, likely Resync/Aspire) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R57" s="2" t="inlineStr"/>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>David Vas Nunes completed onboarding and then requested cancellation of his debt consolidation program. Multiple calls occurred on the retention line, including confirmation of cancellation and discussion about email confirmation. The customer insisted on canceling despite reassurances about credit impact. The account was canceled and David was told to expect a confirmation email.</t>
+          <t>David was initially onboarded via a live transfer from a partner representative. He later requested cancellation, citing misinformation and being up to date on payments. Multiple retention-line calls confirmed his cancellation request and provided email confirmation. Despite reassurances about credit score impact, David insisted on canceling, and the file was closed. Outbound and inbound calls were made, including voicemails and follow-up confirmations.</t>
         </is>
       </c>
     </row>
@@ -4880,21 +5016,25 @@
       <c r="N58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line; the only completed call was to the Onboarding line, where Aspire was mentioned as a partner, but no representative stated they were from Aspire or Resync with a cancelling client.</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr"/>
+          <t>The incoming call on the Onboarding line involved a partner representative providing client files and discussing Aspire as the partner. The caller provided file numbers and asked the agent to handle both Francis Welch and Elizabeth Belcher, indicating a live transfer/partner handoff.</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>Partner representative via Onboarding line</t>
+        </is>
+      </c>
       <c r="R58" s="2" t="inlineStr"/>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>There were two calls: one brief voicemail to Compliance and one completed onboarding call. During onboarding, payment schedules and the debt reduction process were explained, and Aspire was mentioned as a partner. No calls were made to the Retention line, and there is no evidence of a cancellation call or retention attempt. The deal status is cancelled, but this was not handled via the Retention line.</t>
+          <t>There were two calls: one brief voicemail and one completed incoming call on the Onboarding line. The completed call involved a partner representative transferring files for both Francis Welch and Elizabeth Belcher, with Aspire mentioned as the debt-relief partner. Payment schedules and program details were discussed, but Elizabeth was not present on the call. Ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -4953,21 +5093,25 @@
       <c r="N59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line; the only completed call was to the Onboarding line, where Aspire was mentioned as a partner, but no representative stated they were from Aspire or Resync with a cancelling client.</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr"/>
+          <t>The incoming call on the Onboarding line involved a partner representative providing client files and discussing Aspire as the partner. The caller provided file numbers and asked the agent to handle both Francis Welch and Elizabeth Belcher, indicating a live transfer/partner handoff.</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>Partner representative via Onboarding line</t>
+        </is>
+      </c>
       <c r="R59" s="2" t="inlineStr"/>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>There were two calls: one brief voicemail to Compliance and one completed onboarding call. During onboarding, payment schedules and the debt reduction process were explained, and Aspire was mentioned as a partner. No calls were made to the Retention line, and there is no evidence of a cancellation call or retention attempt. The deal status is cancelled, but this was not handled via the Retention line.</t>
+          <t>There were two calls: one brief voicemail and one completed incoming call on the Onboarding line. The completed call involved a partner representative transferring files for both Francis Welch and Elizabeth Belcher, with Aspire mentioned as the debt-relief partner. Payment schedules and program details were discussed, but Elizabeth was not present on the call. Ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -5033,18 +5177,18 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants to cancel. All incoming calls were either onboarding or from the customer directly; no Aspire/Resync warm transfer is present.</t>
+          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there an explicit partner handoff or transfer. The incoming calls are from onboarding and account services, but no mention of Aspire/Resync or a partner transfer.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="4" t="inlineStr">
+      <c r="R60" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Richard Bosley initiated cancellation after expressing dissatisfaction with the debt relief terms during onboarding. Multiple outbound and inbound calls occurred, with Richard repeatedly requesting cancellation and clarifying his right to refuse the contract. Ultimately, a compliance manager confirmed the cancellation and assured Richard that follow-up would occur. No live transfer from Aspire or Resync was detected, and all retention interactions were direct or outbound.</t>
+          <t>Richard Bosley contacted the company to cancel his debt relief contract due to dissatisfaction with the terms and perceived misinformation about interest rates. He was advised on his right to cancel and directed to the compliance department. Outbound calls were made to confirm his cancellation, and Richard insisted on ending the agreement. The contract was ultimately cancelled, and Richard was told he would receive follow-up communication. No incoming calls were completed on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -5103,25 +5247,29 @@
       <c r="N61" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client wishing to cancel. All retention activity was outbound, and no transcript or summary mentions Aspire or Resync.</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="4" t="inlineStr">
+          <t>On 2026-05-29 at 21:25, an incoming call on the Onboarding line opened with Mike introducing Ronald to Cassie, stating, 'This is Mike, and I have Ronald with me on the line...' and 'I will be leaving you with Cassie.' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>Partner agent Mike via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R61" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>Ronald Martinez was onboarded but soon expressed he could not afford the loan and wanted to cancel. Multiple outbound calls were made, including a completed outbound retention call where Ronald confirmed his desire to cancel despite offers to reschedule payments. No incoming retention calls occurred, and Ronald's cancellation was processed, with confirmation promised within 24-48 hours.</t>
+          <t>Ronald was transferred in by a partner agent (Mike) for onboarding, and later called in again to request cancellation due to affordability issues. Multiple outbound attempts were made by your team, but there were no completed incoming calls on the Retention line. Ultimately, Ronald spoke with a compliance manager on an outbound retention call and confirmed his cancellation request, which was processed. No Aspire/Resync keywords were detected in any transcript.</t>
         </is>
       </c>
     </row>
@@ -5180,25 +5328,29 @@
       <c r="N62" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. The only mention of Resync was during an onboarding call, not a retention call.</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="4" t="inlineStr">
+          <t>On the 2026-05-28 incoming call on the Onboarding line, the transcript shows a handoff: '+19493157441: I'll take it from here, Catherine.' The summary confirms Resync was involved and the client was transferred to Better Lending.</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R62" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>The customer, Christopher Conlon, had several calls, including one completed onboarding call where the program and payment process were explained, and multiple voicemails left on other lines. No incoming calls were completed on the Retention line, and there were only outbound attempts with no answer. Ultimately, the deal was cancelled, but there was no evidence of a live cancellation transfer or retention interaction.</t>
+          <t>The only completed call was an incoming live transfer from Resync on the Onboarding line, where the onboarding process and payment plan were explained to the client. No completed calls occurred on the Retention line, and two outbound attempts to reach the client were unsuccessful (voicemails left). Ultimately, the deal was cancelled. No retention intervention was completed.</t>
         </is>
       </c>
     </row>
@@ -5257,25 +5409,29 @@
       <c r="N63" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All retention-related activity was outbound, and the only completed incoming call was to Onboarding.</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="4" t="inlineStr">
+          <t>The incoming Onboarding line call opened with the caller saying 'I got Bobby,' indicating a handoff/transfer. The call involved confirming the phone number and details for Bobby, and the process was explained as involving Resync.</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R63" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>The customer, Bobbi Rowland, was onboarded into a debt consolidation program and had their questions answered about payments and process. Later, an outbound retention call was made after the customer decided to cancel due to concerns about company legitimacy. The agent confirmed the cancellation and explained the next steps. No incoming retention calls were completed; all retention efforts were outbound.</t>
+          <t>The customer, Bobbi Rowland, was transferred in via a live call from Resync on the Onboarding line, where the program and payment details were explained and confirmed. Subsequent outbound attempts were made, but no completed calls occurred on the Retention line. Ultimately, the customer canceled the program due to concerns about company legitimacy, and the cancellation was processed and confirmed by an agent. No retention intervention was completed, and the customer will receive a cancellation letter.</t>
         </is>
       </c>
     </row>
@@ -5341,18 +5497,18 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. All incoming calls are from internal departments (CS Team, Onboarding, CCB, Compliance BL), and no transcript mentions Aspire or Resync or a warm transfer for cancellation.</t>
+          <t>No incoming call transcript contains an introduction from Aspire or Resync, nor any explicit mention of a partner handing off or transferring the client. All introductions are from Better Lending or its agents, and the only onboarding call is from a Better Lending team member.</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
-      <c r="R64" s="4" t="inlineStr">
+      <c r="R64" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>Evelyn Saguid repeatedly contacted Better Lending to cancel her debt-relief program, facing delays and communication issues. She spoke with multiple customer service agents and was assured her cancellation was being processed, but experienced frustration due to lack of confirmation and repeated hang-ups. One outbound retention call confirmed her cancellation and deletion of personal information. No incoming retention-line calls were completed; the deal was ultimately cancelled.</t>
+          <t>Evelyn Saguid enrolled in a debt resolution program but quickly requested cancellation, citing issues with her previous provider and a desire to avoid further payments. She made multiple inbound calls to customer service and other lines, expressing frustration with delays and lack of confirmation. Despite several outbound attempts by agents, no completed calls occurred on the Retention line. Ultimately, her cancellation was processed after repeated follow-ups, but the experience was marked by communication issues and customer dissatisfaction.</t>
         </is>
       </c>
     </row>
@@ -5411,25 +5567,25 @@
       <c r="N65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client wishing to cancel. The only completed call was to the Onboarding line, and Aspire/Resync were mentioned as part of the process explanation, not as a warm transfer for cancellation.</t>
+          <t>Incoming call on Onboarding line: Jason Todd says, 'This is Jason Todd. I'm here with Renee.' Owen (your agent) responds, 'I'll be taking it from here, Jason.' This is a clear live transfer/hand-off.</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Jason Todd via Onboarding line</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr"/>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>Renea Lee had three incoming calls, two of which were brief voicemails to Compliance BL and one completed onboarding call. During the onboarding call, the process involving Resync and Better Lending was explained, and Renee's questions about the program were answered. No retention-line calls or outbound calls occurred, and there was no evidence of a cancellation request via a live transfer. The deal status is cancelled, but no retention activity was recorded.</t>
+          <t>The only completed call was an incoming live transfer on the Onboarding line, where Jason Todd (likely from a partner such as Resync) handed off Renee Lee to your onboarding agent. Renee was onboarded, had her questions answered, and was given next steps and contact info. There were no completed calls on the Retention line, and no outbound calls or attempts. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -5495,18 +5651,18 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client wishing to cancel. All retention activity was outbound.</t>
+          <t>No incoming calls mention Aspire or Resync, nor any partner handoff; all completed calls are outbound, and the only incoming call was a brief voicemail with no transcript.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
-      <c r="R66" s="4" t="inlineStr">
+      <c r="R66" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>All contact attempts to George McDowell Jr were outbound, with no incoming calls to the Retention line. The agent reached George on an outbound retention call, where he firmly requested to cancel his agreement due to dissatisfaction with the debt repayment process. The agent processed the cancellation and confirmed follow-up via email. No Aspire/Resync live transfer or internal transfer source was involved.</t>
+          <t>All completed contact with George McDowell Jr was via outbound calls. The agent reached George on an outbound Retention line call, during which George insisted on canceling his agreement due to dissatisfaction with the debt repayment process. The agent processed the cancellation and confirmed follow-up by email. No incoming Retention line calls were completed, and there was no evidence of a live transfer from Aspire or Resync.</t>
         </is>
       </c>
     </row>
@@ -5565,21 +5721,25 @@
       <c r="N67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O67" s="5" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-28 was a warm transfer from Andrew at Resync, who stated he had a client requesting cancellation and provided the client ID and reason before passing Ada Clay to Dean Lewis for processing.</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr"/>
+          <t>"Hello, Devon. This is David. I have my customer, Ada, in here." (incoming Onboarding line); "Hello, Dean. This is Andrew from Resync on a recorded line. I have a client requesting to cancel." (incoming Retention line)</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line and Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R67" s="2" t="inlineStr"/>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>Ada Clay was onboarded into a debt management program, with initial payments and support explained by the onboarding team. On 2026-05-28, a live cancellation request was transferred from Resync to the retention department, where Ada confirmed she wanted to cancel due to family assistance with her debts. Despite retention efforts, Ada insisted on cancellation, which was processed and confirmed. No further retention calls or payment activity occurred after cancellation.</t>
+          <t>Ada Clay was onboarded through a live transfer from Resync, with her payment plan and program details confirmed. Later, another live transfer from Resync on the Retention line was made to request cancellation, as Ada's family would help pay her debts. Despite an outbound retention call attempting to retain her, Ada insisted on canceling, and the cancellation was processed. There were both inbound and outbound calls, with the deal ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -5645,18 +5805,18 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls where a representative stated they were from Aspire or Resync and had a client wanting to cancel. The only completed retention call was outbound.</t>
+          <t>No incoming calls featured an Aspire or Resync representative, nor any explicit partner handoff/transfer. All incoming calls were either voicemails, in-progress with no transcript, or no-answer, and none mentioned Aspire/Resync or a transfer.</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="4" t="inlineStr">
+      <c r="R68" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>Marcelle Bobo was contacted by an account manager via an outbound retention call, during which she requested cancellation for both her and her husband's accounts due to dissatisfaction with the program and concerns about fees and credit impact. No incoming retention-line calls were completed, and there were no Aspire/Resync warm transfers. The account manager confirmed the cancellation process would be initiated and a supervisor would follow up. The deal status is cancelled.</t>
+          <t>The only completed call was an outbound retention call where Marcelle Bobo requested cancellation for both her and her husband's accounts, citing dissatisfaction with the program and concerns about fees and credit impact. The agent confirmed the cancellation process would be started. No incoming retention-line calls were completed, and no live transfers from Aspire or Resync occurred. Other incoming calls were either voicemails or unanswered.</t>
         </is>
       </c>
     </row>
@@ -5722,18 +5882,18 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls where a representative stated they were from Aspire or Resync and had a client wanting to cancel. The only completed retention call was outbound.</t>
+          <t>No incoming calls featured an Aspire or Resync representative, nor any explicit partner handoff/transfer. All incoming calls were either voicemails, in-progress with no transcript, or no-answer, and none mentioned Aspire/Resync or a transfer.</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="4" t="inlineStr">
+      <c r="R69" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>Marcelle Bobo was contacted by an account manager via an outbound retention call, during which she requested cancellation for both her and her husband's accounts due to dissatisfaction with the program and concerns about fees and credit impact. No incoming retention-line calls were completed, and there were no Aspire/Resync warm transfers. The account manager confirmed the cancellation process would be initiated and a supervisor would follow up. The deal status is cancelled.</t>
+          <t>The only completed call was an outbound retention call where Marcelle Bobo requested cancellation for both her and her husband's accounts, citing dissatisfaction with the program and concerns about fees and credit impact. The agent confirmed the cancellation process would be started. No incoming retention-line calls were completed, and no live transfers from Aspire or Resync occurred. Other incoming calls were either voicemails or unanswered.</t>
         </is>
       </c>
     </row>
@@ -5792,21 +5952,29 @@
       <c r="N70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync with a client wanting to cancel. The only call was an incoming onboarding call.</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
+          <t>Owen Saxe (Onboarding) explains the onboarding process involving two steps: debt reduction by Resync and payoff by Better Lending. The incoming call was on the Onboarding line, and Resync is referenced as part of the process.</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line (Resync referenced)</t>
+        </is>
+      </c>
+      <c r="R70" s="5" t="inlineStr">
+        <is>
+          <t>OB done — no calls on retention line</t>
+        </is>
+      </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>Gerald Havron had one incoming call to the onboarding department, where the agent explained the debt relief process and addressed Gerald's concerns about identity theft and creditor communications. No retention calls or outbound calls occurred. The onboarding process was completed, but there is no evidence of cancellation or retention activity in the call history.</t>
+          <t>Gerald Havron had one completed incoming call on the Onboarding line with agent Owen Saxe. During the call, the onboarding process was explained, including Resync's role in debt reduction. No calls were completed on the Retention line, and there were no outbound attempts. The deal status is cancelled, but the only call involved onboarding and process explanation.</t>
         </is>
       </c>
     </row>
@@ -5865,25 +6033,25 @@
       <c r="N71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was transferred by Kyle Romaine, who did not state they were from Aspire or Resync, but instead referenced being a customer of Leanne Anderson and connected Deborah to Rick from the compliance team.</t>
+          <t>Incoming call on Retention line opened by Kyle Romaine: 'I do have here Deborah on the line...she wanted to cancel the service, so I just had to connect her over to you.'</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>Kyle Romaine</t>
+          <t>Kyle Romaine via Retention line</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr"/>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>Deborah Lawrence was transferred to the retention line by Kyle Romaine to discuss cancelling her service. Despite Rick's offers to adjust the payment terms, Deborah chose to proceed with cancellation, which was confirmed during the call. Multiple outbound calls were made to Deborah, all resulting in brief voicemails with no completed outbound conversations. The account was ultimately cancelled after the single completed incoming retention call.</t>
+          <t>Deborah Lawrence was transferred in on the Retention line by Kyle Romaine to discuss cancellation. Rick from compliance attempted to retain her by offering to include taxes and lower payments, but Deborah declined and the service was cancelled. Multiple outbound calls were made to Deborah, but all resulted in brief voicemails with no further contact. The account status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -5942,25 +6110,29 @@
       <c r="N72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client wanting to cancel. The only completed call was an incoming onboarding call, not a warm transfer for cancellation.</t>
+          <t>Incoming call on Onboarding line: Brian says, 'I have here Teresa Desiderio on the line with me.'</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Onboarding</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr"/>
+          <t>Aspire/Resync via Onboarding line (Brian)</t>
+        </is>
+      </c>
+      <c r="R72" s="5" t="inlineStr">
+        <is>
+          <t>OB done — no calls on retention line</t>
+        </is>
+      </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Teresa Desiderio had three incoming calls, two brief voicemails from Compliance BL and one completed onboarding call. During the onboarding call, Teresa expressed frustration about her debt, but Dana Mohamed explained the program steps and reassured her. No retention-line calls or outbound calls occurred, and the deal status is cancelled.</t>
+          <t>Teresa Desiderio was live transferred by Brian (likely from Aspire/Resync) to the onboarding team, where Dana Mohamed explained the debt reduction process and next steps. Teresa expressed frustration about her debt situation, and Dana provided reassurance and instructions. There were no completed calls on the Retention line, and no outbound calls or attempts. Ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -6019,25 +6191,25 @@
       <c r="N73" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>The only incoming retention-line call (#5, 2026-05-26 20:50) was transferred internally from Joseph Alexander (agent), not from Aspire or Resync. The transcript shows Joseph Alexander redirected Rosa to Dean Lewis for cancellation, but there is no evidence of a representative stating they are from Aspire or Resync during the transfer.</t>
+          <t>On 2026-05-25 19:35, incoming on Onboarding: The call opens with 'You have Alexandra from the lending department, and I got Rosa here.' This is a clear live transfer from a partner (Resync) to Better Lending's onboarding team.</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>Joseph Alexander (agent)</t>
+          <t>Resync via Onboarding line</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr"/>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>Rosa Mack initially enrolled in a debt resolution program but requested cancellation after her husband did not agree to the terms. Multiple calls were made to reach her agent, Joseph Alexander, and ultimately Rosa was transferred internally to the retention department, where her cancellation was processed and confirmed. No outbound calls were completed, but several outbound attempts and voicemails occurred. Rosa later called again to demand that unwanted notices about the canceled program stop, threatening legal action if they continued.</t>
+          <t>Rosa Mack was live-transferred in by a partner (Resync) to complete onboarding for a debt resolution program. After onboarding, she made multiple attempts to reach her agent, Alexander Joseph, through various incoming calls. Ultimately, Rosa requested cancellation of her program via a completed incoming call on the Retention line, citing her husband's lack of agreement. The cancellation was processed and confirmed, and subsequent calls involved her requesting that all notices about the program cease.</t>
         </is>
       </c>
     </row>
@@ -6096,25 +6268,29 @@
       <c r="N74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. The only completed retention call was outbound, and the incoming retention calls were voicemails with no transcript evidence of a live transfer.</t>
-        </is>
-      </c>
-      <c r="Q74" s="2" t="inlineStr"/>
-      <c r="R74" s="4" t="inlineStr">
+          <t>On 2026-05-25 18:48, an incoming call on the Onboarding line began with Sarah (partner rep) saying 'I have Peter here on the line. Are you ready for the file number?' and then transferring the client to Cassie from Better Lending.</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep Sarah via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R74" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Peter Nero completed onboarding with Cassie from Better Lending, who explained the debt reduction process involving Resync and set up his first payment. Later, Peter's cancellation request was confirmed by Henry Hart during an outbound retention call, with Peter expressing appreciation. All incoming retention calls were voicemails, and there were no live transfers from Aspire or Resync. The deal was ultimately cancelled.</t>
+          <t>Peter Nero was live-transferred in by a partner rep (Sarah) on the Onboarding line, where the onboarding process was completed and his payment schedule was set up. Multiple outbound attempts were made by the retention team, but no completed incoming calls occurred on the Retention line. Ultimately, Peter requested cancellation, which was confirmed by an outbound retention call. No retention-line inbound calls were completed; the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -6173,21 +6349,25 @@
       <c r="N75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O75" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was made directly by Sharon Jenkins herself, not transferred by a representative from Aspire or Resync. The transcript shows Sharon called to confirm her cancellation and did not mention being transferred by Aspire or Resync.</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="inlineStr"/>
+          <t>"This is Jamie Gonzalez. And I have here Sharon. And when you're ready, tell me to get the file number." (incoming Onboarding line)</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
       <c r="R75" s="2" t="inlineStr"/>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Sharon Jenkins completed onboarding with Better Lending and later called the retention line to confirm her account cancellation, expressing concern about not receiving a confirmation email. Dean Lewis confirmed the cancellation and advised Sharon to check her inbox, spam, or junk folder for the email. No outbound calls or attempts were made to Sharon, and the account was ultimately cancelled as requested.</t>
+          <t>Sharon Jenkins was live-transferred in by an Aspire representative via the Onboarding line, where she was welcomed and given an overview of the debt reduction process. Later, Sharon called the Retention line to confirm her cancellation and requested email confirmation, which the agent verified had been sent. There were no outbound calls or attempts to Sharon. Ultimately, the account was canceled as requested.</t>
         </is>
       </c>
     </row>
@@ -6246,21 +6426,25 @@
       <c r="N76" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>There is one completed incoming call on the Retention line, but the transcript does not show a representative stating they are from Aspire or Resync or that this was a warm transfer from those sources. No Aspire/Resync keywords were detected.</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr"/>
+          <t>On 2026-05-25 15:31, an incoming call on the Onboarding line opened with Floyd (likely a partner rep) saying, 'This is Floyd. I'm gonna go with me, mister Jimmy Rogers. Whenever you're ready for the phone number.' Donna (your agent) replied, and Floyd said, 'I'll hand it from here.' This is a clear live transfer handoff.</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep Floyd via Onboarding line</t>
+        </is>
+      </c>
       <c r="R76" s="2" t="inlineStr"/>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Jimmy Rogers initially onboarded for a debt consolidation program but soon decided to cancel, stating he could manage his debts independently. Multiple calls covered onboarding, tax assistance, and the cancellation process. The cancellation was confirmed by a retention agent after Jimmy declined offers to postpone or retain the service. No live transfer from Aspire or Resync occurred, and the deal was ultimately cancelled per the customer's request.</t>
+          <t>Jimmy Rogers was live-transferred in by a partner rep for onboarding, completed onboarding, but called back the next day to cancel his debt consolidation, stating he could manage his debts himself. He also discussed tax issues and was offered a tax program, but the main debt-relief deal was cancelled after a brief retention call. Multiple outbound attempts and completed calls occurred, including one completed incoming call on the Retention line, but the final outcome was cancellation.</t>
         </is>
       </c>
     </row>
@@ -6326,18 +6510,18 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync with a client wanting to cancel. All retention calls were either voicemails or outbound calls.</t>
+          <t>No incoming calls were completed; the only incoming call was a voicemail with no mention of Aspire or Resync. No transcript evidence of a partner transfer or handoff.</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
-      <c r="R77" s="4" t="inlineStr">
+      <c r="R77" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>The customer, Cody Schulte, made no incoming calls to the Retention line. There were two outbound attempts, one of which was completed. In the completed outbound call, Cody requested to cancel his consolidation loan, stating he had made other arrangements. The agent confirmed the cancellation and informed Cody he would receive a confirmation email. No Aspire or Resync warm transfer occurred.</t>
+          <t>There were three calls: one incoming voicemail on the Retention line, and two outbound calls. The only completed call was an outbound call where Cody requested to cancel his consolidation loan, which was confirmed by the agent. No live transfer or partner handoff occurred, and the deal was cancelled as requested by the customer.</t>
         </is>
       </c>
     </row>
@@ -6396,21 +6580,25 @@
       <c r="N78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O78" s="5" t="inlineStr">
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-23 was a warm transfer from Lana, who stated she was representing a client (John Martinez) and explicitly requested cancellation. The transcript shows Lana identifying herself and mentioning she has a client who wants to cancel, which matches the definition of a live call from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr"/>
+          <t>Both completed incoming calls (Onboarding and Retention) began with a partner representative introducing themselves and stating they have the client to transfer. For example, on the Onboarding line: 'I have with me on the line, John, John Martinez, with me.' On the Retention line: 'This is Lana. I have a client here. He want to cancel.'</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line and Retention line</t>
+        </is>
+      </c>
       <c r="R78" s="2" t="inlineStr"/>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>John Martinez initially engaged with the onboarding department and understood the debt-relief program, but later decided to cancel his application after his co-signer changed his mind. A representative (Lana) from Aspire/Resync called the retention line to request cancellation on John's behalf, and the process was confirmed and set to be completed with email confirmation. No outbound calls were completed, and the deal status is cancelled.</t>
+          <t>John Martinez was live-transferred in twice by partner representatives: first for onboarding, then for cancellation. The onboarding call confirmed his understanding of the debt program and set up payments, but a subsequent retention call was made by a partner to cancel his application due to a co-signer backing out. No outbound calls were completed; several outbound attempts and voicemails were left. The final outcome was cancellation, with confirmation to be sent via email.</t>
         </is>
       </c>
     </row>
@@ -6469,25 +6657,25 @@
       <c r="N79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O79" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>There is no evidence in the transcripts or summaries of any incoming retention call where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. The completed retention call was directly from the customer, Arthur Robertson, not a warm transfer from Aspire or Resync.</t>
+          <t>On 2026-05-22 at 22:19, an incoming call on the Onboarding line opened with a representative (not the customer) introducing Arthur and stating, 'I have Arthur on the line with me right now... This file is ready. He signed his agreement.' This is a clear partner handoff/live transfer.</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Partner rep via Onboarding line</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr"/>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>Arthur Robertson initially completed onboarding but later requested to cancel his application due to financial difficulties and hospitalization. Multiple outbound attempts were made, but only one completed outbound call and one completed incoming retention call occurred. The retention agent offered to pause the account, but Arthur insisted on cancellation. The account was cancelled, and Arthur requested confirmation via email.</t>
+          <t>Arthur was live-transferred in by a partner rep and completed onboarding. He later called in to cancel due to financial hardship and hospitalization, and despite offers to pause or adjust payments, insisted on cancellation. Multiple outbound attempts were made, and one completed incoming call on the Retention line confirmed his cancellation request. The deal was ultimately cancelled at Arthur's request.</t>
         </is>
       </c>
     </row>
@@ -6546,21 +6734,25 @@
       <c r="N80" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O80" s="5" t="inlineStr">
+      <c r="O80" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>The 2026-05-27 17:11 incoming retention call transcript shows Ralph from Aspire Law Group calling to cancel a client's program and performing a warm transfer to Dean Lewis for proper assistance.</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr"/>
+          <t>On the 2026-05-27 17:11 incoming Retention line call, the caller says: 'This is Ralph calling over with Aspire Law Group. I have a client on the line requesting to cancel.' This is a clear live transfer from Aspire on the Retention line.</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Retention line</t>
+        </is>
+      </c>
       <c r="R80" s="2" t="inlineStr"/>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>Gerardo's cancellation request was initiated via a live transfer from Aspire Law Group to the retention team. The retention agent discussed options with Gerardo, including postponing payments, but Gerardo ultimately insisted on canceling due to financial constraints. Multiple outbound calls were made to follow up, and Gerardo confirmed his desire to cancel, which was processed with a confirmation promised within 24-48 hours. No other departments were involved, and the deal was cancelled.</t>
+          <t>Gerardo's case involved a live transfer from Aspire Law Group to the Retention line, where he requested to cancel his program. The agent discussed options, including postponing payments, but Gerardo ultimately insisted on canceling. Multiple outbound attempts were made, and a final call confirmed his cancellation request, with the agent informing him of the process and possible fees. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -6619,25 +6811,25 @@
       <c r="N81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O81" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was a warm transfer from another internal agent (Kelly Morgan), not from an Aspire or Resync representative. There is no mention of Aspire or Resync in the transcript or summary.</t>
+          <t>Incoming call on Retention line: The caller says, 'I have here Reginald on the line. We just signed the contract and finished the compliance call, and he wanted to cancel everything.' The caller then transfers Reginald to the compliance manager, indicating a live transfer/handoff.</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>Kelly Morgan (internal agent)</t>
+          <t>Partner representative via Retention line</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr"/>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>Reginald Daniels called to cancel his debt consolidation program shortly after signing up. The only completed retention call was a warm transfer from internal agent Kelly Morgan, not Aspire/Resync. Reginald was informed that his account was not yet registered and could not be canceled immediately, but he was given instructions to call back if he wished to proceed. Multiple outbound attempts were made, but no outbound calls were completed. The account status is cancelled.</t>
+          <t>Reginald Daniels was transferred in by a partner representative immediately after signing the contract, expressing a desire to cancel the debt consolidation program. The compliance manager explained that cancellation could not occur until the account was registered and provided instructions for future cancellation. Multiple outbound attempts were made, but no outbound calls were completed. Ultimately, the deal was cancelled, with only one completed incoming call on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -6696,29 +6888,29 @@
       <c r="N82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O82" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O82" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming retention calls involved a representative stating they were from Aspire or Resync with a client wanting to cancel. The only mention of Aspire/Resync was in the onboarding call, not as a warm transfer to retention.</t>
+          <t>The 2026-05-22 19:46 incoming call on the Onboarding line begins with a representative (not the customer) stating, 'I have Christiana here,' and then handing off to Owen from onboarding, indicating a live transfer. The summary also mentions working with Resync.</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>CS Team</t>
-        </is>
-      </c>
-      <c r="R82" s="4" t="inlineStr">
+          <t>Partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R82" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>Christine Craig initially joined a debt resolution program but soon realized she could not afford the payments due to her Social Security income. She contacted customer service to cancel, and her file was transferred to retention, where multiple outbound calls were made to discuss options. Despite offers to lower payments or delay them, Christine insisted on cancellation, which was confirmed and processed. No incoming retention calls were completed; all retention conversations were outbound, and the deal was ultimately cancelled.</t>
+          <t>The customer was live-transferred in via the Onboarding line, with a partner representative present on the call. After onboarding, the customer expressed inability to afford the program and requested cancellation. Multiple outbound calls were made by retention agents to discuss options, but the customer insisted on canceling due to financial hardship. No completed incoming calls occurred on the Retention line; the account was ultimately canceled as requested.</t>
         </is>
       </c>
     </row>
@@ -6777,21 +6969,25 @@
       <c r="N83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O83" s="5" t="inlineStr">
+      <c r="O83" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-29 19:16, an incoming retention call was initiated by Caleb from Aspire Law Group, who stated he had a client (Toni Buxton) who wanted to cancel. Caleb clearly identified himself as from Aspire and performed a warm transfer to the retention agent.</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr"/>
+          <t>On 2026-05-22 at 16:05, an incoming call on the Onboarding line began with a representative (Sayan) stating, 'I have missus Tony Buxton here,' and then transferring the client to your agent. On 2026-05-29 at 19:16, an incoming call on the Retention line began with 'This is Caleb from Aspire Law Group on a recorded line,' and he transferred Toni to your agent for cancellation.</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line and Aspire via Retention line</t>
+        </is>
+      </c>
       <c r="R83" s="2" t="inlineStr"/>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Toni Buxton initially went through onboarding for a debt reduction program but later expressed dissatisfaction with the contract and process. An Aspire Law Group representative performed a live transfer to the retention team, where Toni insisted on canceling her agreement despite attempts by agents to address her concerns. Multiple outbound calls followed to discuss her cancellation, and ultimately, her request to cancel was confirmed and processed by a supervisor. No retention was achieved; the deal was cancelled.</t>
+          <t>Toni Buxton was live-transferred twice by Aspire representatives—first to onboarding for program setup, and later to retention for cancellation. Multiple outbound calls were made to discuss tax and debt consolidation options, but Toni ultimately expressed dissatisfaction with the contract and requested cancellation. Despite attempts to address her concerns, Toni insisted on canceling, and the cancellation was confirmed by a supervisor. The case ended with the client opting out of the service.</t>
         </is>
       </c>
     </row>
@@ -6850,25 +7046,29 @@
       <c r="N84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O84" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants to cancel. The only cancellation request was made directly by the customer on an incoming CS Team call.</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="inlineStr"/>
-      <c r="R84" s="4" t="inlineStr">
+          <t>On 2026-05-22, an incoming call on the Onboarding line began with Xavier from Better London onboarding team stating, 'I have Revlon with me. Are you ready for the file number?' This indicates a live transfer with the client already on the line, and Aspire was referenced in the call summary.</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R84" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>The customer completed onboarding and was informed about the debt management process and payment schedule. Later, the customer called the CS Team to request cancellation due to financial hardship, and the agent confirmed the cancellation process would proceed. There were also discussions about payment postponement and eligibility for future loans, but ultimately the customer cancelled the arrangement. No live transfer from Aspire or Resync to retention was detected.</t>
+          <t>The customer was live-transferred in by a partner (Aspire) on the Onboarding line, where the debt management program and payment details were explained. Later, the customer called in on the CS Team line to request cancellation due to financial hardship, and the cancellation process was confirmed. Outbound attempts were made, but there were no completed incoming calls on the Retention line. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -6927,25 +7127,29 @@
       <c r="N85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O85" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>No incoming calls to the Retention line were completed; all completed calls were on the Onboarding line. No mention of Aspire or Resync or a representative stating they are from those companies.</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr"/>
-      <c r="R85" s="4" t="inlineStr">
+          <t>"+19092240573: Hi, Xavier. This is Zara. I have Joe Bonita on the line." (incoming on Onboarding line)</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>Zara via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R85" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>All completed calls were with the Onboarding department, focusing on explaining the program and confirming enrollment details with Jo Bonita Rains. There were no incoming retention-line calls, and no evidence of Aspire or Resync involvement. The customer was provided with program information and support contacts, but ultimately the deal status is marked as cancelled. No retention efforts or cancellation discussions are documented in the call transcripts.</t>
+          <t>The customer was transferred in by Zara on the Onboarding line, where the onboarding process and program details were discussed. There were no completed incoming calls on the Retention line, but there was one outbound call attempt and completion from the Onboarding department. Ultimately, the deal was cancelled. No Aspire or Resync keywords were detected in the transcripts.</t>
         </is>
       </c>
     </row>
@@ -7004,21 +7208,25 @@
       <c r="N86" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O86" s="5" t="inlineStr">
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call transcript shows an agent stating, 'I do have Lisa Villa. She wants to cancel... Thank you for choosing Resync.' This indicates a warm transfer from Resync for a cancellation.</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="inlineStr"/>
+          <t>"And I do have Lisa Villa. She wants to cancel... And thank you for choosing Resync." — Incoming call on Retention line, caller explicitly states they are transferring the client from Resync.</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R86" s="2" t="inlineStr"/>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>Elisa Villa was transferred to the retention line by a Resync representative to request cancellation due to financial hardship. The retention agent, Ryan Henderson, confirmed her desire to cancel and processed the request after discussing her options. An outbound follow-up call was made to finalize the cancellation and provide contact information. The account was ultimately cancelled as requested by the customer.</t>
+          <t>A partner representative from Resync called in on the Retention line to transfer Elisa Villa for a cancellation request due to financial hardship. The agent, Ryan Henderson, handled the cancellation process and confirmed the client's desire to cancel rather than postpone payments. After discussing options, the cancellation was processed and the client was provided with contact information for future needs. There were both an incoming and an outbound completed call, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -7077,25 +7285,29 @@
       <c r="N87" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O87" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client wanting to cancel. All completed calls were either onboarding or customer service, and cancellation was requested by Gilbert directly to CS.</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr"/>
-      <c r="R87" s="4" t="inlineStr">
+          <t>Incoming call on the Onboarding line: The caller introduces themselves as Catherine from the lending department and says, 'I have Gilbert Martinez on the line.' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>Catherine (lending department) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R87" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>Gilbert Martinez completed onboarding with Better Lending and set up payment dates. He later contacted customer service to request cancellation of his enrollment, which was escalated to the cancellation department. No incoming retention-line calls occurred, and cancellation was handled via outbound and CS calls. No retention attempt or warm transfer from Aspire/Resync was documented.</t>
+          <t>Gilbert Martinez was transferred in by a partner (Catherine from the lending department) via a live call on the Onboarding line, where his onboarding and payment dates were finalized. Subsequent outbound calls from Better Lending confirmed Gilbert's enrollment and later addressed his request to cancel the program. No completed incoming calls occurred on the Retention line, and the deal was ultimately cancelled after Gilbert requested to withdraw from the program.</t>
         </is>
       </c>
     </row>
@@ -7154,21 +7366,25 @@
       <c r="N88" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O88" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>The only completed incoming retention call (2026-05-29) was from the client himself (Damon Robbie) directly, not from an Aspire or Resync representative stating they were transferring a cancelling client. The transcript shows the client called to cancel and discussed Resync, but there is no evidence of a warm transfer from Aspire/Resync staff.</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="inlineStr"/>
+          <t>On 2026-05-21, the incoming Onboarding call opened with Devon Smith introducing himself as 'with the family on the onboarding team' and the other party (Leon) stating 'I got Danny and Riley quickly. His first payment is on the June 22 for you to know.' This is a clear live transfer/hand-off scenario, with the partner agent present and transferring the client.</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>Partner agent (Leon) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R88" s="2" t="inlineStr"/>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>The customer had multiple interactions, including onboarding and customer service calls, with several outbound attempts from the retention team. The only completed incoming retention call was from the client directly, who called to cancel his program, citing misinformation and lack of proper cancellation confirmation. The agent explained the cancellation process and promised follow-up from compliance. Ultimately, the client’s program was cancelled after his direct request.</t>
+          <t>The customer was live-transferred in by a partner agent on the Onboarding line, with payment and program details confirmed. Multiple outbound attempts were made by your team, and one completed outbound call handled account changes. The customer later called in on the Retention line to request cancellation, citing misinformation and lack of confirmation. The agent processed the cancellation and advised the customer would receive compliance follow-up.</t>
         </is>
       </c>
     </row>
@@ -7227,21 +7443,25 @@
       <c r="N89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O89" s="5" t="inlineStr">
+      <c r="O89" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>The first incoming retention call (2026-05-26 22:48) was initiated by Jacob from Resync, who stated he had a mutual client (David Johns) who wanted to cancel, and he transferred the client to the retention agent Max Francis. The transcript clearly shows this was a warm transfer from Resync for a cancellation.</t>
-        </is>
-      </c>
-      <c r="Q89" s="2" t="inlineStr"/>
+          <t>Incoming call on Retention line: 'This is Jacob from Resync on a recorded line. I have a mutual client that wants to cancel the program. It should be for David Johns.'</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R89" s="2" t="inlineStr"/>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>David Johns was transferred to the retention department by a Resync representative to request cancellation of his debt relief program. During the calls, David expressed dissatisfaction with the program and confusion about its nature, ultimately insisting on cancellation. The retention agent explained the process and sent cancellation documents. Multiple outbound attempts and voicemails followed, but the deal was ultimately cancelled as requested by the client.</t>
+          <t>David Johns was transferred in by Jacob from Resync on the Retention line to request cancellation of his program. Max Francis handled the call, discussed the client's concerns, and initiated the cancellation process, sending required documents for signature. Multiple outbound attempts and voicemails were made, but only one outbound call was completed. Ultimately, the client proceeded with cancellation after expressing dissatisfaction with the program.</t>
         </is>
       </c>
     </row>
@@ -7307,18 +7527,18 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client wishing to cancel.</t>
+          <t>No incoming calls included any mention of Aspire or Resync, nor was there any indication of a partner representative transferring the client. All incoming calls were voicemails with no transcribable conversations.</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr"/>
-      <c r="R90" s="4" t="inlineStr">
+      <c r="R90" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>All calls were either voicemails or brief missed calls, with no completed conversations. There were two outbound attempts from the CS Team, but the customer did not answer. No incoming calls were completed on the Retention line, and there is no evidence of a live transfer or cancellation discussion. The deal status is marked as cancelled, but this was not handled via a live call.</t>
+          <t>There were a total of five calls, all of which resulted in voicemails with no completed conversations. Two outbound attempts were made to reach the customer, but no contact was established. No incoming calls were completed on the Retention line. The deal was ultimately cancelled, and there was no evidence of a live transfer or partner handoff.</t>
         </is>
       </c>
     </row>
@@ -7377,21 +7597,29 @@
       <c r="N91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line. The only call was an incoming onboarding call where the representative mentioned Resync, but it was not a warm transfer for cancellation.</t>
-        </is>
-      </c>
-      <c r="Q91" s="2" t="inlineStr"/>
-      <c r="R91" s="2" t="inlineStr"/>
+          <t>Julian Morris (partner rep) called in on the Onboarding line and stated, 'I have here Mary on the line,' indicating a live transfer. The call included both Julian and Mary, with Dana Mohamed from onboarding department receiving the transfer.</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>Julian Morris (Resync) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R91" s="5" t="inlineStr">
+        <is>
+          <t>OB done — no calls on retention line</t>
+        </is>
+      </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>Mary Scott participated in a single onboarding call with Dana Mohamed, where the debt-relief program and payment schedule were explained. The call focused on introducing the program, addressing Mary's concerns, and setting up her first payment. There were no calls to the Retention line, no outbound calls, and no cancellation or retention discussions occurred during this call.</t>
+          <t>Mary Scott was live-transferred by a Resync representative (Julian Morris) to the onboarding department, where Dana Mohamed explained the debt reduction program and scheduled her first payment. There were no outbound calls or completed calls on the Retention line. The deal status is cancelled, but the only call was an onboarding live transfer with no further follow-up or retention activity.</t>
         </is>
       </c>
     </row>
@@ -7450,21 +7678,25 @@
       <c r="N92" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O92" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All completed calls were to Onboarding and CS, not Retention.</t>
-        </is>
-      </c>
-      <c r="Q92" s="2" t="inlineStr"/>
+          <t>The opening transcript of the 2026-05-20 incoming call on the Onboarding line includes: 'This is Leah, and I have Sylvia here with me... she's all good to go. Now Sylvia, they'll take care of everything. So she's all yours, Donna.' This is a clear live transfer from a partner handing off the client.</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>Partner representative (Leah) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R92" s="2" t="inlineStr"/>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>Sylvia Ramos completed two incoming calls: one with Onboarding, where the debt relief process and Aspire's role were explained, and one with Customer Support, where she confirmed her program cancellation and was assured a confirmation email would be sent. There were no calls to the Retention line, and no outbound calls or attempts. The cancellation was processed smoothly, and Sylvia's concerns about a bank account were addressed.</t>
+          <t>Sylvia Ramos was live-transferred by a partner representative to the onboarding team, where her enrollment and program details were confirmed. Later, Sylvia called customer support to follow up on a cancellation notice after ending her program; the agent confirmed her cancellation and explained the notice would be sent by email. No completed calls occurred on the Retention line, and there were no outbound call attempts. The client was ultimately canceled and received confirmation of this status.</t>
         </is>
       </c>
     </row>
@@ -7523,21 +7755,25 @@
       <c r="N93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O93" s="5" t="inlineStr">
+      <c r="O93" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-27 17:13, Emily from Freesync called the retention line and stated, 'I have a cancellation request for you,' and transferred Michael Lambert to the representative. This matches the definition of a live call from an Aspire/Resync partner with a client wishing to cancel.</t>
-        </is>
-      </c>
-      <c r="Q93" s="2" t="inlineStr"/>
+          <t>On 2026-05-20, incoming Onboarding line: '+13343548248: I have Michael here with me. Are you ready for the file number?' and '+13343548248: We got Vera here. I told you she is my favorite. So now I make sure you're in great hands.' This is a clear live transfer from a partner handing off the client.</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>Partner (likely Aspire/Resync) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R93" s="2" t="inlineStr"/>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>Michael Lambert was onboarded on 5/20 but expressed concerns about the program. On 5/27, a live transfer from Freesync initiated his cancellation request, which was confirmed by the retention agent. Later that day, Michael called back (after being transferred from another help number) to ensure his cancellation was processed, expressing a preference to pay his own bills and requesting written confirmation. No outbound calls were completed; all outbound attempts went to voicemail. The account was ultimately cancelled as requested.</t>
+          <t>Michael Lambert was live-transferred in by a partner for onboarding, where he expressed concerns about the program. Later, a partner (Emily from Freesync) live-transferred him on the Retention line to request cancellation, which was confirmed by your agents. Michael called back to Retention to ensure cancellation, citing lack of written confirmation and a preference to handle payments himself. Multiple outbound attempts were made but only voicemails were left; ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -7596,21 +7832,29 @@
       <c r="N94" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line, and no transcripts or summaries mention a representative from Aspire or Resync transferring a cancelling client.</t>
-        </is>
-      </c>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
+          <t>"We have Robert here. So are you ready for the phone number?... He's gonna take it from here, Robert." — incoming Onboarding line. This is a clear live transfer with the client already on the line.</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>Unknown partner via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R94" s="5" t="inlineStr">
+        <is>
+          <t>OB done — no calls on retention line</t>
+        </is>
+      </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>Robert Lundgren had two completed incoming calls: one with Onboarding to discuss the debt consolidation program and another with Customer Service to express concerns after speaking with his wife. He was reassured about the process and offered a pause to consider his options. No calls were made to the Retention line, and there is no evidence of a live transfer or cancellation handled via retention.</t>
+          <t>Robert Lundgren was live-transferred in via the Onboarding line by a partner representative, then discussed the debt consolidation program with an agent. Later, he called the CS Team to request cancellation after discussing with his wife, expressing concerns about the program. There were no completed calls on the Retention line and no outbound attempts. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -7669,21 +7913,25 @@
       <c r="N95" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O95" s="5" t="inlineStr">
+      <c r="O95" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-27 14:25, an incoming retention call transcript shows Connor from Resync explicitly stating he is transferring a client (Mr. Robinson) who wants to cancel. Levi Miller, the compliance supervisor, confirms the cancellation request with Mr. Robinson. This matches the definition of a live call from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q95" s="2" t="inlineStr"/>
+          <t>On 2026-05-27 14:25, an incoming call on the Retention line opened with: 'Hello, Levi. This is Connor calling from Resync on a recorded line... I have mister Levi here on the line ready to assist you with your request.' This is a clear live transfer from Resync.</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R95" s="2" t="inlineStr"/>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>Scott Robinson initially engaged with onboarding and customer support regarding payment scheduling and program details. Later, a live transfer from Resync to the retention team was made for a cancellation request, which was confirmed by the agent. Multiple outbound retention calls followed to confirm the cancellation and address any remaining concerns, with Scott and his spouse both expressing frustration and confirming their desire to cancel. The account was ultimately cancelled, and no retention was achieved.</t>
+          <t>Scott Robinson had multiple interactions with the company, including onboarding, support, and retention. A live transfer from Resync led to a cancellation request, which was confirmed and processed after several follow-up calls. There were both inbound and outbound calls on the Retention line, including voicemails and confirmations. Ultimately, the account was cancelled per the client's request, with final confirmation provided.</t>
         </is>
       </c>
     </row>
@@ -7742,25 +7990,29 @@
       <c r="N96" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O96" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O96" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. The only completed call was an onboarding call, and no retention-line calls were completed.</t>
-        </is>
-      </c>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="4" t="inlineStr">
+          <t>The incoming Onboarding call opened with a partner representative on the line: '+14236051275: Rosita, I have here Owen. He's on the line. They're going to take good care of you.' This indicates a live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R96" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>Rosita Delgado had a single completed call with the onboarding department, where the program and payment process were explained and her concerns addressed. All other calls were either voicemails or brief missed calls, with no completed inbound retention-line calls. Although Aspire was mentioned during onboarding, there was no evidence of a live transfer for cancellation. Ultimately, the deal was cancelled, but no retention intervention occurred.</t>
+          <t>Rosita Delgado was live-transferred in by Aspire on the Onboarding line, where she completed her onboarding call and had her program details explained. No completed calls occurred on the Retention line, and there was one outbound attempt from the CS Team that resulted in voicemail. The deal was ultimately cancelled, and no further successful contact was made after onboarding. Multiple voicemails were left on the CS Team line, but no additional conversations took place.</t>
         </is>
       </c>
     </row>
@@ -7826,18 +8078,18 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All retention-related calls were outbound, and no incoming retention calls matched the live call definition.</t>
+          <t>No incoming call transcript shows a representative from Aspire or Resync, or any explicit partner handoff/transfer. The only incoming completed call (CCB) was from Faye David at Better Pest Funding, not Aspire/Resync, and was a message request for Amy.</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr"/>
-      <c r="R97" s="4" t="inlineStr">
+      <c r="R97" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>Martha Lowe received several outbound calls from retention agents regarding her debt consolidation program. She firmly stated her desire to cancel and not be contacted further, expressing confidence in managing her debts independently. No incoming retention-line calls were completed, and all cancellation discussions occurred during outbound calls. The account was ultimately cancelled per Martha's repeated requests.</t>
+          <t>All completed calls were outbound, with no completed incoming calls on the Retention line. Martha Lowe was repeatedly contacted by agents regarding her debt consolidation program but firmly requested cancellation and no further contact. She stated she would handle her debts independently and disputed the program's value. The deal was ultimately cancelled, and Martha requested to be removed from the call list.</t>
         </is>
       </c>
     </row>
@@ -7896,21 +8148,25 @@
       <c r="N98" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O98" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative from Aspire or Resync states they have a client wishing to cancel. The only cancellation occurred on a call to the CCB line, not Retention, and was initiated directly by the customer.</t>
-        </is>
-      </c>
-      <c r="Q98" s="2" t="inlineStr"/>
+          <t>On the 2026-05-19 23:33 incoming Onboarding line call, the caller (+12525616877) said: 'It's Joey. I do have live on file here with me... So, Lavrin, you do have here Devon on the line now... They're going to take care from here.' This is a clear live transfer from a partner (likely Resync) via the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
       <c r="R98" s="2" t="inlineStr"/>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>Lavern Albritton completed onboarding with Better Lending, where the program and payment schedule were explained. Shortly after, Lavern called the CCB line to cancel her application, stating her daughter would assist with her bills instead. The agent confirmed the cancellation and informed her that a supervisor would follow up. No calls were completed on the Retention line, and there were no outbound attempts.</t>
+          <t>The customer was live-transferred in from a partner (Resync) to the Onboarding line, where the onboarding process and program details were explained. Shortly after, the customer called in to cancel, stating her daughter would pay her bills instead, and the agent confirmed the cancellation and promised a supervisor callback. No completed calls occurred on the Retention line, and there were no outbound attempts. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -7969,25 +8225,29 @@
       <c r="N99" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O99" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O99" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. All retention-line calls were voicemails with no completed conversations, and no transcript or summary shows a warm transfer from Aspire or Resync.</t>
-        </is>
-      </c>
-      <c r="Q99" s="2" t="inlineStr"/>
-      <c r="R99" s="4" t="inlineStr">
+          <t>2026-05-19 22:52 incoming on Onboarding: Liano from the lending department says, 'Valerie Smith, she's here with us already on the line,' and introduces the client to Mohamed Mosad for handoff. This is a clear live transfer from a partner (Resync mentioned in call summary).</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R99" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>Valery Smith attempted to cancel her debt-relief program, expressing dissatisfaction with service and payment discomfort. Multiple calls were made to customer support and onboarding, but no completed incoming retention-line calls occurred. The cancellation was eventually processed and confirmed via onboarding, with a promise to send a confirmation email. No live retention transfer or direct retention conversation took place; all retention calls were voicemails.</t>
+          <t>Valerie Smith was live-transferred in by a partner (Resync) and onboarded, but soon after requested cancellation due to dissatisfaction with the service and communication issues. Multiple inbound and outbound calls occurred, but no completed calls were handled on the Retention line. Ultimately, the cancellation was processed and confirmed, with Valerie requesting written confirmation by email.</t>
         </is>
       </c>
     </row>
@@ -8046,21 +8306,25 @@
       <c r="N100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O100" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was initiated directly by the customer (Juan Maldonado) and handled by Dean Lewis, with no mention of Aspire or Resync, nor any evidence of a warm transfer from those sources in the transcript or summary.</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr"/>
+          <t>On 2026-05-19 21:28, incoming Onboarding line: '+15712370411: I have mister Maldonado on the line right now, and his phone number is 115088148.' This is a clear live transfer from a partner handing off the client.</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>Partner (unknown, likely Aspire) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R100" s="2" t="inlineStr"/>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>Juan Maldonado completed onboarding but soon became dissatisfied with the debt consolidation service, feeling misled and experiencing issues with his banks. After discussing his concerns with NSF and retention agents, he requested immediate cancellation of his account. The retention agent confirmed the cancellation and promised a confirmation email. Outbound calls included document signing and brief voicemails, but the main outcome was cancellation at the customer's request.</t>
+          <t>Juan Maldonado was live-transferred in by a partner (likely Aspire) and onboarded into the debt management program. He later had issues with the service, leading to multiple outbound attempts and a completed inbound call on the NSF line. Ultimately, Juan called the Retention line to request immediate cancellation due to dissatisfaction and confusion about the program, which was processed by the agent. The account was closed, and confirmation was promised.</t>
         </is>
       </c>
     </row>
@@ -8126,18 +8390,18 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>There were zero completed incoming calls on the Retention line, and no transcripts or summaries mention a representative from Aspire or Resync transferring a cancelling client. All retention-related conversations were outbound.</t>
+          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there any mention of a partner handoff or transfer. The only completed incoming call was from 'Liam with Better Lending onboarding team' on the Onboarding line, which does not match the partner transfer criteria.</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="4" t="inlineStr">
+      <c r="R101" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>Robbie Parras was onboarded and provided with program details, but subsequently requested to cancel his debt relief services. All retention efforts were outbound, with Dean Lewis confirming the cancellation after Robbie insisted on discontinuing due to concerns about payments and credit score. Several outbound calls and voicemails were made regarding tax issues, but there were no incoming retention calls or live transfers from Aspire/Resync. The account status is cancelled.</t>
+          <t>Robbie Parras was onboarded via an incoming call from the Better Lending team, where account setup and program details were discussed. Multiple outbound calls were made by various agents to discuss tax and debt relief, but most resulted in voicemails or brief conversations. Robbie requested cancellation during an outbound retention call, and the agent processed the cancellation after discussing the risks and benefits. No completed incoming calls occurred on the Retention line, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -8196,21 +8460,25 @@
       <c r="N102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync with a client wishing to cancel. The only completed incoming call was to Onboarding, not Retention.</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="inlineStr"/>
+          <t>The incoming call on the Onboarding line opened with 'This is Donna of your carding team,' and referenced Resync as the negotiating party, indicating a partner handoff.</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
       <c r="R102" s="2" t="inlineStr"/>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>Todd Fiske had two incoming calls: one brief voicemail to Compliance and one completed call to Onboarding. During the Onboarding call, the agent explained the debt reduction process involving Resync and Better Lending, and scheduled Todd's first payment. There were no calls to the Retention line, no outbound calls, and no evidence of a live cancellation transfer. The account status is cancelled, but no retention interaction occurred in these calls.</t>
+          <t>Todd Fiske had one completed incoming call on the Onboarding line, facilitated by Donna from the carding team, who referenced Resync and explained the debt reduction process. No calls were completed on the Retention line, and there were no outbound attempts. The outcome was that Todd was onboarded with a scheduled payment, but the deal status is now cancelled.</t>
         </is>
       </c>
     </row>
@@ -8269,21 +8537,25 @@
       <c r="N103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O103" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming calls were to the Retention line, and no representative stated they were from Aspire or Resync with a client wanting to cancel. The detected Aspire/Resync keywords were part of onboarding explanations, not a live transfer for cancellation.</t>
-        </is>
-      </c>
-      <c r="Q103" s="2" t="inlineStr"/>
+          <t>In the 2026-05-18 21:21 incoming Onboarding call, the transcript shows Daniel (likely from Aspire/Resync or a partner) calling in and handing off Gail to Xavier Lookman from Better Lending, saying 'I got it from here. Thank you, Daniel.' This is a classic live transfer.</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>Partner (Daniel) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R103" s="2" t="inlineStr"/>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>Gail Pettigrew Butler had two completed incoming calls: one with onboarding to review payment and process details, and one with customer support to clarify credit application questions. No calls were made to the Retention line, and there were no outbound calls or attempts. The deal was ultimately cancelled, but no retention-specific activity was recorded.</t>
+          <t>Gail Pettigrew Butler was live-transferred in by a partner (Daniel) to the Better Lending onboarding team, where her onboarding and payment schedule were explained. She later called the CS Team with questions about applying for new credit while enrolled, and was reassured this would not interfere with her plan. No calls were completed on the Retention line, and there were no outbound attempts. Ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -8342,25 +8614,29 @@
       <c r="N104" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O104" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>No incoming calls to the Retention line were completed, and no transcripts or summaries mention a representative from Aspire or Resync transferring a cancelling client.</t>
-        </is>
-      </c>
-      <c r="Q104" s="2" t="inlineStr"/>
-      <c r="R104" s="4" t="inlineStr">
+          <t>The incoming call on the Onboarding line opened with 'This is Lawson Pierce. I have Kim O'Donnell here. She her file is good to go.' This indicates a partner representative (Lawson Pierce) was transferring the client.</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>Lawson Pierce via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R104" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>All calls involved onboarding, with no completed incoming retention-line calls. The customer, Kim O'Donnell, received detailed onboarding information, payment scheduling, and support contacts. Despite the deal status being cancelled, there is no evidence of cancellation discussions or retention attempts in the call history. Outbound calls were made to provide payment and program details, but no retention activity occurred.</t>
+          <t>Kim O'Donnell was live transferred by Lawson Pierce to the onboarding team, where the onboarding process and program details were explained. There were no completed incoming calls on the Retention line, but an outbound onboarding call was completed to confirm payment details and next steps. The customer was successfully onboarded, but the deal status is now marked as cancelled.</t>
         </is>
       </c>
     </row>
@@ -8426,14 +8702,14 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls, and no transcripts indicate a representative from Aspire or Resync transferring a cancelling client.</t>
+          <t>No incoming calls with a representative mentioning Aspire/Resync or indicating a live transfer; only a brief voicemail on the Compliance BL line.</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr"/>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>There was only one incoming call to the Compliance BL line, which went to voicemail and had no transcribable conversation. No retention-line calls, outbound calls, or completed calls occurred. The customer's deal status is cancelled, but there is no evidence of any live interaction or cancellation conversation in the call records.</t>
+          <t>There was only one incoming call, which went to voicemail on the Compliance BL line and had no transcribable conversation. No completed calls occurred on any line, and there were no outbound attempts. The customer did not interact with an agent, and the deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -8492,25 +8768,29 @@
       <c r="N106" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O106" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. All incoming calls were either to CS Team or Onboarding, and the only completed retention call was outbound.</t>
-        </is>
-      </c>
-      <c r="Q106" s="2" t="inlineStr"/>
-      <c r="R106" s="4" t="inlineStr">
+          <t>"+12522029314: Hey. This is Zara. I have Denise with me on the line." (Onboarding line, incoming call, 2026-05-18 19:29). Zara is a partner rep transferring the client.</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R106" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>Denise Coleman completed onboarding and made her first payment, but had ongoing confusion and concerns about the debt-relief process, especially regarding her car loan and creditor notifications. Multiple calls to customer support addressed her questions, but Denise ultimately requested cancellation due to financial issues and a court threat from a creditor. No incoming retention-line calls were completed; only outbound retention calls and customer support interactions occurred.</t>
+          <t>Denise Coleman was live-transferred in by Aspire on the Onboarding line and completed onboarding for a debt-relief program. Multiple subsequent calls were made to customer service regarding payment status, creditor notifications, and confusion about the program. Denise ultimately requested cancellation due to ongoing creditor pressure and dissatisfaction with the timeline. No completed incoming calls occurred on the Retention line, and the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -8569,25 +8849,29 @@
       <c r="N107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O107" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync with a cancelling client. All completed incoming calls were to the Onboarding line, and none match the live call definition.</t>
-        </is>
-      </c>
-      <c r="Q107" s="2" t="inlineStr"/>
-      <c r="R107" s="4" t="inlineStr">
+          <t>In the 2026-05-17 00:12 incoming Onboarding call, David (likely from Aspire/Resync) says, 'This is David... I'm ready for the file ID whenever you are... Please take good care of him,' clearly handing off Carlos to the Better Lending onboarding agent.</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R107" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>Carlos completed onboarding calls, discussed debt management, and scheduled a payment, but later called the Onboarding line to cancel after deciding the program was not suitable. No incoming calls were made to the Retention line, and cancellation was handled directly by onboarding staff. Carlos stopped his payment with his bank, and the deal was ultimately cancelled.</t>
+          <t>Carlos was live-transferred by a partner (David, likely from Aspire/Resync) to the Better Lending onboarding team, where his onboarding was initiated. After further discussion in an outbound call, Carlos decided the program was not suitable and called back to cancel. No completed calls occurred on the Retention line, and the cancellation was confirmed on an incoming Onboarding call. No payments were processed, and Carlos stopped his scheduled payment with his bank.</t>
         </is>
       </c>
     </row>
@@ -8646,21 +8930,29 @@
       <c r="N108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O108" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client wanting to cancel. The only completed call was an onboarding call discussing the program and payment setup.</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr"/>
-      <c r="R108" s="2" t="inlineStr"/>
+          <t>Cassie (partner rep) on the Onboarding line says, 'I have Ingrid with me on the line. Are you ready for her phone number?' and hands off the client to Mohamed from Allego Boarding Team.</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>Cassie (partner rep) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R108" s="5" t="inlineStr">
+        <is>
+          <t>OB done — no calls on retention line</t>
+        </is>
+      </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>Ingrid Cotton had four calls, with only one completed: an onboarding call where the debt relief process and payment schedule were explained. No calls were completed on the Retention line, and there were no outbound calls or attempts. The deal status is cancelled, but there is no evidence of a cancellation conversation in the call logs provided.</t>
+          <t>The only completed call was an incoming live transfer on the Onboarding line, where Cassie from a partner company transferred Ingrid to the Allego Boarding Team for onboarding. No completed calls occurred on the Retention line, and there were no outbound attempts. Ingrid was onboarded, her payment plan was confirmed, but the deal ultimately ended in cancellation.</t>
         </is>
       </c>
     </row>
@@ -8719,21 +9011,25 @@
       <c r="N109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O109" s="5" t="inlineStr">
+      <c r="O109" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-27 at 20:19 was a warm transfer from Samuel, who stated he had a client (Monica Williams) wanting to cancel. The transcript shows Samuel introduced himself and requested to transfer Monica for cancellation, fitting the definition of a live call from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q109" s="2" t="inlineStr"/>
+          <t>On the 2026-05-16 17:56 incoming Onboarding call, the transcript shows: '+14787142524: I got miss Monica here. ... You're in good hands.' This indicates a partner representative (Charlie) is handing off Monica to the onboarding team on the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (Charlie) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R109" s="2" t="inlineStr"/>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>Monica Williams initially engaged with the onboarding team to start a debt resolution program, but later requested cancellation. A live retention call was received from Samuel (Aspire/Resync) to cancel Monica's program, citing her husband's decision to handle their finances. Retention agents confirmed the cancellation, discussed loan options, and informed Monica about possible fees and confirmation emails. The deal was ultimately cancelled, with no retention achieved.</t>
+          <t>Monica Williams was initially live-transferred by a partner rep to the onboarding team to start her debt resolution process. Later, a partner rep (Samuel) live-transferred Monica to the Retention line to request cancellation, which was processed after confirming her husband would handle their finances. Multiple outbound and inbound calls occurred, including voicemails and follow-ups, with the final outcome being a confirmed cancellation of Monica's program. Monica was informed about possible cancellation fees and will receive confirmation via email.</t>
         </is>
       </c>
     </row>
@@ -8799,18 +9095,18 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line, and no transcripts indicate a representative from Aspire or Resync stating they have a client who wants to cancel.</t>
+          <t>No incoming call transcript or summary indicates a caller from Aspire or Resync, or any explicit partner handoff/transfer. All incoming calls are either voicemails or have no transcribable conversation.</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr"/>
-      <c r="R110" s="4" t="inlineStr">
+      <c r="R110" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>There were three outbound attempts from the Onboarding department, all resulting in voicemails, and no completed calls. No incoming calls were completed on the Retention line, and no live transfer from Aspire or Resync occurred. The customer's deal was ultimately cancelled without any successful contact or retention attempt.</t>
+          <t>There were a total of five calls for this customer, all of which were either voicemails or had no completed conversations. Three outbound attempts were made by the agent, all resulting in voicemail. No incoming calls were completed on the Retention line, and there is no evidence of a live transfer from Aspire or Resync. The deal status is cancelled, and there was no successful contact with the customer.</t>
         </is>
       </c>
     </row>
@@ -8869,25 +9165,29 @@
       <c r="N111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O111" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>There are zero completed incoming calls on the Retention line. No transcript or summary shows a representative stating they are from Aspire or Resync with a client wanting to cancel via a warm transfer.</t>
-        </is>
-      </c>
-      <c r="Q111" s="2" t="inlineStr"/>
-      <c r="R111" s="4" t="inlineStr">
+          <t>On 2026-05-15, an incoming call on the Onboarding line opened with: 'I have Jerry with me here. You ready for the file number?' and 'So, Jerry, I have Vera on the line now. She's gonna take it from here.' This is a clear live transfer from a partner representative handing off the client.</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R111" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>Jerry and Marsha Kraft contacted customer support and onboarding regarding debt management and subsequently canceled their loan. Multiple calls focused on refund inquiries after cancellation, with agents confirming the refund process and providing contact numbers for Aspire. No retention-line calls occurred; all outbound attempts were handled by onboarding and CS teams. The account was ultimately canceled, and the refund is pending.</t>
+          <t>Jerry and Marsha Craft contacted the company to cancel their loan and resolve a refund for a payment withdrawn after cancellation. Multiple incoming calls were made to customer support and onboarding, but none were completed on the Retention line. The refund process was discussed and initiated, with agents providing updates and contact numbers for Aspire. The deal was ultimately cancelled, and the clients were awaiting their refund.</t>
         </is>
       </c>
     </row>
@@ -8946,21 +9246,25 @@
       <c r="N112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O112" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync with a client wanting to cancel. The only completed incoming call was to the Onboarding line, and no Aspire/Resync keywords were detected.</t>
-        </is>
-      </c>
-      <c r="Q112" s="2" t="inlineStr"/>
+          <t>Incoming call on Onboarding line: The caller (Elena) says, 'I have Chiyon with me' and provides the client's information to Xavier, indicating a live transfer/hand-off.</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>Elena via Onboarding line</t>
+        </is>
+      </c>
       <c r="R112" s="2" t="inlineStr"/>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>Chihyung Chang spoke with an onboarding agent about starting the debt management program, confirming payment details and understanding the process. No calls were completed on the Retention line, and there were no outbound calls or attempts. The deal status is cancelled, but no cancellation conversation occurred in the available call history.</t>
+          <t>The customer, Chihyung Chang, was transferred in via a live call on the Onboarding line by Elena, who handed off the client to agent Xavier Lookman. The call focused on explaining the debt management process and confirming payment details, with the customer expressing understanding. There were no completed calls on the Retention line and no outbound attempts. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -9026,18 +9330,18 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All incoming calls were to Onboarding or CS Team lines, and no Aspire/Resync keywords were detected.</t>
+          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, nor any mention of a partner transferring the client. All incoming calls are directly from the customer (Bessie/Betsy Wilson).</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr"/>
-      <c r="R113" s="4" t="inlineStr">
+      <c r="R113" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>Bessie Wilson initially completed onboarding and confirmed payment details, but soon called the onboarding department to request cancellation due to concerns about the company's legitimacy. Despite attempts to reassure her, she insisted on canceling. Later, she called the CS Team to confirm her cancellation, which was processed. No calls were made to the Retention line, and the deal was ultimately canceled.</t>
+          <t>Bessie Wilson called in to cancel her application, citing concerns from a family member and enrollment with another debt consolidation company. The company made outbound attempts and handled incoming calls on the Onboarding and CS lines, but there were no completed calls on the Retention line. Ultimately, the cancellation was confirmed and Bessie expressed gratitude. No live transfer or partner handoff occurred.</t>
         </is>
       </c>
     </row>
@@ -9096,25 +9400,29 @@
       <c r="N114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O114" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. All retention interactions were outbound, and the only incoming call was to Onboarding.</t>
-        </is>
-      </c>
-      <c r="Q114" s="2" t="inlineStr"/>
-      <c r="R114" s="4" t="inlineStr">
+          <t>The 2026-05-15 18:53 incoming call on the Onboarding line includes a handoff: the incoming caller says, 'I'll be taking it from here, and don't worry. Todd is in good hands,' and the transcript shows a partner representative transferring the client. The summary and transcript mention Aspire and a transfer.</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R114" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S114" s="2" t="inlineStr">
         <is>
-          <t>Todd Searle engaged with the company regarding his debt relief plan, initially speaking with Onboarding about the program and payment schedule. Subsequent outbound retention calls addressed his concerns about business funding and ultimately processed his cancellation request, with confirmation and refund details provided. No incoming retention-line calls occurred; all retention actions were handled via outbound calls. The deal was cancelled and Todd was assured of a refund.</t>
+          <t>Todd Searle was live-transferred in by Aspire on the Onboarding line. After onboarding, he had several outbound calls with agents to discuss his debt relief plan and business funding needs. Ultimately, Todd requested to cancel his program, and the cancellation was processed with confirmation and a refund timeline provided. No completed incoming calls occurred on the Retention line; all retention interactions were outbound.</t>
         </is>
       </c>
     </row>
@@ -9180,18 +9488,18 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync with a client wanting to cancel. All incoming retention calls were voicemails, and the only completed conversation was on the CS Team line.</t>
+          <t>No incoming call included an introduction from Aspire or Resync, nor did any caller indicate they were a partner handing off the client. The only completed incoming call (CS Team) was initiated directly by the customer, Bernie Schumacher.</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr"/>
-      <c r="R115" s="4" t="inlineStr">
+      <c r="R115" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S115" s="2" t="inlineStr">
         <is>
-          <t>The customer, Bernd Schumacher, contacted the CS Team to request immediate cancellation of his loan payoff program, citing dissatisfaction with the payment plan. The agent confirmed the cancellation request and discussed next steps, including a transfer to accounting, but there were no completed calls on the Retention line. Multiple outbound attempts and voicemails were made, but no further live conversations occurred. Ultimately, the deal was cancelled with no live retention intervention.</t>
+          <t>The customer, Bernd Schumacher, called in directly to request cancellation of his loan payoff program, stating the payment plan was not suitable. The agent confirmed the cancellation request and discussed next steps. Multiple outbound attempts and voicemails were made, but no calls were completed on the Retention line. The deal was ultimately cancelled after the customer's request.</t>
         </is>
       </c>
     </row>
@@ -9250,25 +9558,25 @@
       <c r="N116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O116" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>The only incoming retention call was transferred internally from Ethan to Adam, not from Aspire or Resync. The transcript shows Ethan (internal agent) transferring the client, and there is no mention of Aspire or Resync representatives initiating the call or stating they have a client who wants to cancel.</t>
+          <t>Incoming call on Retention line: Ethan (partner rep) transferred the client to Adam, stating, 'You can transfer the client over. I'll be able to help.' and 'I just transferred you over, and Adam will be able to assist you further in this call.'</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>Ethan (internal agent)</t>
+          <t>Partner rep Ethan via Retention line</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr"/>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>David Stout's case involved both incoming and outgoing calls on the retention line. The incoming retention call was an internal transfer from Ethan to Adam, who assisted with the file. In the outbound call, Adam discussed confusion about a loan offer from Aspire, clarified terms with another agent, and ultimately decided to cancel due to financial constraints and unclear communication. The deal was cancelled, and no live transfer from Aspire or Resync occurred.</t>
+          <t>A partner representative (Ethan) live-transferred David Stout to the Retention line, where Adam handled the call. The client discussed confusion over a loan offer from Aspire, received clarification, but ultimately chose to cancel due to dissatisfaction and financial concerns. There was one completed outbound call and one completed incoming call on Retention; voicemails were left on other lines. The deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -9323,29 +9631,29 @@
       <c r="N117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O117" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming retention calls involved a representative stating they were from Aspire or Resync with a client wanting to cancel. All retention calls were either direct from Felix or transferred internally (Henry Hart RT OB), not a warm transfer from Aspire/Resync.</t>
+          <t>On 2026-05-14, an incoming call on the Onboarding line opened with: 'This is Floyd in here, and I got with you mister Felix Gonzalez Corveto. Tell me when you're ready for the file number.' This is a clear live transfer from a partner (Resync) to the onboarding agent.</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>Henry Hart RT OB</t>
-        </is>
-      </c>
-      <c r="R117" s="4" t="inlineStr">
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R117" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t>Felix Gonzalez Quevedo initially onboarded with questions about his payment plan and eligibility. He had multiple discussions with Henry Hart about removing creditors, qualifying for the program, and adding medical bills. Felix ultimately decided to cancel due to personal and financial concerns, and Henry processed the cancellation, confirming no payments would be deducted and that Felix would receive a confirmation email. There were several outbound attempts and completed calls, but the cancellation was finalized after Felix insisted and Henry confirmed it.</t>
+          <t>Felix was live-transferred in by Resync for onboarding, where his program and payment plan were explained. He later requested cancellation due to personal and financial concerns, with multiple calls discussing removing accounts and qualifying for the program. Ultimately, Felix insisted on canceling, and the agent confirmed the cancellation would be processed with no payments taken. No completed incoming calls occurred on the Retention line; all retention interactions were via outbound or other lines.</t>
         </is>
       </c>
     </row>
@@ -9404,21 +9712,29 @@
       <c r="N118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O118" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O118" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync with a client wishing to cancel. The only completed call was to Onboarding, and no Retention line calls were completed.</t>
-        </is>
-      </c>
-      <c r="Q118" s="2" t="inlineStr"/>
-      <c r="R118" s="2" t="inlineStr"/>
+          <t>Owen Saxe from onboarding says, 'I'll be taking it from here. Thank you, Marcus.' This indicates a live transfer from a partner (likely Aspire or Resync) on the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R118" s="5" t="inlineStr">
+        <is>
+          <t>OB done — no calls on retention line</t>
+        </is>
+      </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>Dereje Aychiluhim had three incoming calls, with only one completed call to the Onboarding department. During this call, the onboarding agent explained the debt management process, mentioning Aspire as a partner for debt reduction and scheduled the first payment. There were no completed calls to the Retention line, and no outbound calls or attempts. Ultimately, the deal status is marked as cancelled, but there is no evidence of a live cancellation transfer or retention intervention.</t>
+          <t>The customer, Dereje Aychiluhim, was live-transferred in via the Onboarding line, with the partner representative present at the start of the call. The onboarding agent explained the debt relief process and scheduled the first payment. No completed calls occurred on the Retention line, and there were no outbound attempts. Ultimately, the deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -9477,25 +9793,25 @@
       <c r="N119" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O119" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was handled by Levi Miller from the compliance team. There is no mention in the transcript or summary of a representative from Aspire or Resync stating they have a client who wants to cancel. The transfer appears to be internal, not a warm transfer from Aspire/Resync.</t>
+          <t>On the 2026-05-18 18:04 incoming Retention line call, the caller says: 'I have here Rosie with me. She's basically in the process... So she's actually looking just to basically change her mind about the process. Alright? So I'll leave right now. You can take care of the device from now.' This is a clear live transfer/handoff.</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>Compliance team</t>
+          <t>Partner representative via Retention line</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr"/>
       <c r="S119" s="2" t="inlineStr">
         <is>
-          <t>Rosie Todorov called in to request a cancellation due to financial hardship. The compliance supervisor, Levi Miller, processed the cancellation after confirming no penalties would apply. Rosie declined an offer to skip her next payment and was informed she would receive a confirmation email. There were no outbound calls or attempts, and the cancellation was completed via an incoming retention call.</t>
+          <t>The customer, Rosie Todorov, called in with a partner representative who handed her off to the Retention team for a cancellation request due to financial hardship. The Retention agent processed the cancellation after confirming no penalties would apply and offered to help retain the client, but Rosie declined. There were no outbound calls or attempts, and the process was completed via incoming calls. No Aspire or Resync partner was mentioned by name, but a live transfer did occur.</t>
         </is>
       </c>
     </row>
@@ -9561,14 +9877,14 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>There were no completed incoming calls to the Retention line, and no evidence of a representative stating they were from Aspire or Resync.</t>
+          <t>No incoming call included an Aspire or Resync mention, nor was there any indication of a partner handoff. The only call was an unanswered inbound call to the CS Team line.</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr"/>
       <c r="R120" s="2" t="inlineStr"/>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>There was only one incoming call attempt from the CS Team, which was not answered and had no conversation. No calls were completed on the Retention line, and there were no outbound calls or attempts. No evidence of a live transfer or any interaction regarding cancellation was found.</t>
+          <t>There was a single incoming call attempt to the CS Team line, but the call was not answered and no conversation took place. No outbound calls were made to the customer. No evidence of a live transfer or partner handoff was found. The deal status is cancelled, but no further call activity occurred.</t>
         </is>
       </c>
     </row>
@@ -9627,21 +9943,25 @@
       <c r="N121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O121" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line; the only completed call was an incoming onboarding call where the representative explained the program and process to the customer.</t>
-        </is>
-      </c>
-      <c r="Q121" s="2" t="inlineStr"/>
+          <t>"This is Adam Jose with Randall Osborne. Are you ready for the file number?" (incoming on Onboarding line)</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line (Adam Jose)</t>
+        </is>
+      </c>
       <c r="R121" s="2" t="inlineStr"/>
       <c r="S121" s="2" t="inlineStr">
         <is>
-          <t>The customer, Randal Osborne, had two incoming calls: one brief voicemail and one completed onboarding call. During the onboarding call, the agent explained the debt-relief process, payment structure, and provided support contact information. There were no retention-line calls, cancellations, or outbound attempts. The customer was successfully onboarded but later marked as cancelled in the deal status.</t>
+          <t>The customer, Randall Osborne, was live transferred by Adam Jose from Aspire to the Better Lending onboarding team via the Onboarding line. The onboarding agent, Donya Alnasharty, explained the debt-relief process, confirmed Randall’s understanding, and provided contact details for future support. No calls were completed on the Retention line, and the deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -9707,18 +10027,18 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls completed; all completed calls were outbound. No transcript or summary indicates a representative from Aspire or Resync stating they have a client who wants to cancel.</t>
+          <t>No incoming call transcript or summary indicates a partner (Aspire/Resync) or any live transfer; all incoming calls were voicemails or had no transcribable content.</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr"/>
-      <c r="R122" s="4" t="inlineStr">
+      <c r="R122" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
         <is>
-          <t>The company made multiple outbound attempts to reach Cindy Ellett, with two outbound retention calls completed. All other calls were either voicemails or not answered, and there were no completed incoming calls to the retention line. Ultimately, the deal was cancelled, and there is no evidence of a live transfer or internal transfer initiating the cancellation.</t>
+          <t>The company made multiple outbound attempts to reach Cindy Ellett, leaving several voicemails. Two outbound calls were completed, but there were no completed incoming calls on the Retention line. No live transfer or partner handoff occurred. Ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -9777,21 +10097,25 @@
       <c r="N123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O123" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>The only completed incoming retention call (2026-05-14 14:49) was from the customer herself, not a representative from Aspire or Resync transferring a client. The transcript shows Gloria called directly to cancel, referencing a prior conversation with Ryan Henderson, but there is no evidence of a warm transfer from Aspire or Resync.</t>
-        </is>
-      </c>
-      <c r="Q123" s="2" t="inlineStr"/>
+          <t>"This is Daniel, and I have Gloria here." (Onboarding line, 2026-05-13 16:04) — Daniel is handing off the client, indicating a live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>Partner (Daniel) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R123" s="2" t="inlineStr"/>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>Gloria Miranda completed onboarding but soon decided to cancel her debt management program after discussing it with her daughter. She called the retention line directly to request cancellation, which was processed by the agent, and received confirmation that no payments would be withdrawn. There were also outbound attempts and a completed outbound call confirming the cancellation, with no indication of Aspire/Resync live transfer involvement.</t>
+          <t>Gloria Miranda was live-transferred by a partner (Daniel) for onboarding, where her debt management program was explained. Shortly after, Gloria called the Retention line to cancel her enrollment, citing a change of mind after discussing with her daughter. The cancellation was processed and confirmed by Henry Hart, with no payments withdrawn. Outbound follow-up confirmed the cancellation and that Gloria received her confirmation email.</t>
         </is>
       </c>
     </row>
@@ -9857,18 +10181,14 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was not a warm transfer from Aspire or Resync. The transcript shows Jessica Trebel was transferred internally to the compliance manager (Ryan Henderson) for cancellation, but there is no mention of Aspire or Resync, nor does a representative state they are from those companies.</t>
-        </is>
-      </c>
-      <c r="Q124" s="2" t="inlineStr">
-        <is>
-          <t>Compliance office</t>
-        </is>
-      </c>
+          <t>No incoming caller identified themselves as from Aspire or Resync, nor did any incoming caller explicitly state they were a partner handing off/transferring the client. The Onboarding and Retention calls were handled by internal agents (Vera Grayson, Ryan Henderson) and the opening lines do not mention Aspire/Resync or a partner transfer.</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr"/>
       <c r="R124" s="2" t="inlineStr"/>
       <c r="S124" s="2" t="inlineStr">
         <is>
-          <t>The customer (Jessica, on behalf of Barrett Chadwell) called to cancel their debt consolidation program shortly after onboarding. The retention call was an internal transfer to the compliance office, where the customer insisted on cancellation despite an offer to lower payments. No live transfer from Aspire or Resync occurred. Outbound calls were attempted by the CS team, but there were no successful outbound completions. The account was ultimately cancelled.</t>
+          <t>The customer had two completed incoming calls: one with onboarding to discuss program details and one with retention to request cancellation. The retention agent attempted to retain the client by offering lower payments, but the customer insisted on canceling both accounts. Outbound attempts were made but not completed. The deal was ultimately cancelled as requested by the customer.</t>
         </is>
       </c>
     </row>
@@ -9934,18 +10254,14 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was not a warm transfer from Aspire or Resync. The transcript shows Jessica Trebel was transferred internally to the compliance manager (Ryan Henderson) for cancellation, but there is no mention of Aspire or Resync, nor does a representative state they are from those companies.</t>
-        </is>
-      </c>
-      <c r="Q125" s="2" t="inlineStr">
-        <is>
-          <t>Compliance office</t>
-        </is>
-      </c>
+          <t>No incoming caller identified themselves as from Aspire or Resync, nor did any incoming caller explicitly state they were a partner handing off/transferring the client. The Onboarding and Retention calls were handled by internal agents (Vera Grayson, Ryan Henderson) and the opening lines do not mention Aspire/Resync or a partner transfer.</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr"/>
       <c r="R125" s="2" t="inlineStr"/>
       <c r="S125" s="2" t="inlineStr">
         <is>
-          <t>The customer (Jessica, on behalf of Barrett Chadwell) called to cancel their debt consolidation program shortly after onboarding. The retention call was an internal transfer to the compliance office, where the customer insisted on cancellation despite an offer to lower payments. No live transfer from Aspire or Resync occurred. Outbound calls were attempted by the CS team, but there were no successful outbound completions. The account was ultimately cancelled.</t>
+          <t>The customer had two completed incoming calls: one with onboarding to discuss program details and one with retention to request cancellation. The retention agent attempted to retain the client by offering lower payments, but the customer insisted on canceling both accounts. Outbound attempts were made but not completed. The deal was ultimately cancelled as requested by the customer.</t>
         </is>
       </c>
     </row>
@@ -10011,18 +10327,14 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was transferred from Jonathan Underwood, but there is no mention of Aspire or Resync, nor does the transcript indicate a representative from those companies was on the line or that it was a warm transfer from them.</t>
-        </is>
-      </c>
-      <c r="Q126" s="2" t="inlineStr">
-        <is>
-          <t>Jonathan Underwood</t>
-        </is>
-      </c>
+          <t>No mention of Aspire or Resync in any incoming call transcript or greeting. The only completed incoming call on the Retention line was initiated by the customer, Laura Mims, who referenced being transferred by Jonathan Underwood (an agent), not a partner company.</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr"/>
       <c r="R126" s="2" t="inlineStr"/>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t>Laura Mims called the Retention line after being transferred by Jonathan Underwood to cancel her contract due to upcoming surgery. The retention agent offered to postpone the contract, but Laura insisted on canceling. The agent agreed to process the cancellation and planned a follow-up call. There were also several voicemails left, but no further completed conversations occurred.</t>
+          <t>Laura Mims called in on the Retention line to request cancellation due to upcoming surgery. The agent offered to postpone, but Laura insisted on canceling. There were no live transfers from Aspire or Resync; all calls were either direct from the customer or outbound attempts from agents. The deal was ultimately cancelled after the customer's request.</t>
         </is>
       </c>
     </row>
@@ -10081,25 +10393,29 @@
       <c r="N127" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O127" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wants/needs to cancel. All completed incoming calls were to CS Team or Onboarding, not Retention.</t>
-        </is>
-      </c>
-      <c r="Q127" s="2" t="inlineStr"/>
-      <c r="R127" s="4" t="inlineStr">
+          <t>On 2026-05-12, an incoming call on the Onboarding line opened with a representative (Gabriella) stating, 'I have Kirk here. Are you ready?... I'll just give her your file number, and then I'll transfer you with her.' This indicates a live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (Gabriella) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R127" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S127" s="2" t="inlineStr">
         <is>
-          <t>Kirk Shelton initially completed onboarding and was informed about the debt reduction process involving Aspire. Later, Kirk contacted customer support to cancel his account but decided against it during the call. He subsequently called again to confirm the cancellation, and customer support verified that his account was already canceled. No incoming retention-line calls were completed, and all outbound attempts were handled by the CS Team.</t>
+          <t>The customer was live-transferred in by a partner rep on the Onboarding line and completed onboarding. Later, the customer attempted to cancel, with several inbound and outbound calls handled by the CS Team, but no completed calls occurred on the Retention line. Ultimately, the account was confirmed canceled by a CS agent. Multiple voicemails and missed calls occurred, and the customer was not retained.</t>
         </is>
       </c>
     </row>
@@ -10165,14 +10481,14 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>The only incoming retention call (2026-05-27 16:30) was a direct call with no mention of Aspire or Resync, and the transcript does not indicate a representative stating they are from those companies or a warm transfer.</t>
+          <t>No incoming call transcript or summary mentions Aspire or Resync, nor does any incoming caller explicitly state they are a partner handing off or transferring the client. The Onboarding line call was from 'Elena', but there is no indication she is from Aspire/Resync or a partner company.</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr"/>
       <c r="R128" s="2" t="inlineStr"/>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>Meredith Martin completed onboarding and was scheduled for a payment, but soon expressed financial hardship and postponed her first payment. She later called the retention line directly, and in a subsequent outbound retention call, confirmed her intent to cancel due to bankruptcy and her husband's illness. The agent processed her cancellation and clarified that no further payments would be drafted. No Aspire or Resync live transfer occurred.</t>
+          <t>Meredith Martin was onboarded through an incoming call with Elena and agent Xavier, where her program and payment schedule were set up. She later requested to postpone her payment due to financial difficulties. Ultimately, Meredith called the Retention line and then confirmed her cancellation in a follow-up outbound call, citing bankruptcy and her husband's illness. No evidence of a live transfer from Aspire or Resync was found, and the account was cancelled after several outbound and inbound interactions.</t>
         </is>
       </c>
     </row>
@@ -10231,21 +10547,25 @@
       <c r="N129" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O129" s="5" t="inlineStr">
+      <c r="O129" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>The 2026-05-22 17:07 incoming retention call transcript shows Lucas from Aspire Law Group calling with the client present, stating the client wants to cancel and offering to transfer the call to the representative. This matches the definition of a 'live call' as a warm transfer from Aspire.</t>
-        </is>
-      </c>
-      <c r="Q129" s="2" t="inlineStr"/>
+          <t>On 2026-05-12, an incoming call on the Onboarding line included a handoff where the caller (likely from Aspire) said, 'I'll take it from here,' and the agent Dana Mohamed introduced herself as from Better Lending onboarding. On 2026-05-22, an incoming call on the Retention line began with 'This is Lucas calling from Aspire Law Group. So, Sally, I have a client here with me,' clearly indicating a live transfer from Aspire.</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line and Aspire via Retention line</t>
+        </is>
+      </c>
       <c r="R129" s="2" t="inlineStr"/>
       <c r="S129" s="2" t="inlineStr">
         <is>
-          <t>The customer, Flossie Church, was onboarded and scheduled for a payment, but later an Aspire Law Group representative called the retention line to cancel her program, citing family assistance. The cancellation was confirmed in follow-up calls, with the customer stating she no longer needed the service. Multiple outbound attempts were made to reach her, and the cancellation was finalized, with confirmation to be sent by email. The deal status is cancelled.</t>
+          <t>The customer was live-transferred in twice: first for onboarding via Aspire, and later for cancellation via Aspire Law Group on the Retention line. After the cancellation request, agents confirmed the client wanted to cancel due to family assistance and processed the cancellation, with follow-up outbound calls to confirm and document the outcome. The deal was ultimately cancelled, and the customer declined to keep the loan as a backup. Multiple outbound attempts were made, and voicemails were left, but there was one completed incoming Retention call.</t>
         </is>
       </c>
     </row>
@@ -10304,25 +10624,29 @@
       <c r="N130" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O130" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O130" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. The only incoming retention call was a voicemail with no evidence of a live transfer from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q130" s="2" t="inlineStr"/>
-      <c r="R130" s="4" t="inlineStr">
+          <t>On 2026-05-12 01:46, incoming call on the Onboarding line: Owen from onboarding says, 'Thank you, Sarah,' and Sarah says, 'You're welcome,' indicating a handoff/transfer from Sarah (likely a partner rep) to Owen. The transcript shows Sarah on the line with the client and then handing off to Owen, which matches the definition of a live transfer. 'Resync' is also mentioned in the onboarding summary.</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R130" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>Alex Colantuono made multiple requests to cancel his debt relief program, primarily through the CS Team line. He was advised to contact the cancellation department and his bank to stop a pending payment. No incoming retention-line calls were completed; only one outbound retention call occurred, during which Alex reiterated his wish to cancel but was offered a hold and further follow-up. Ultimately, Alex's deal was cancelled after several outbound attempts and support interactions, with no live transfer from Aspire/Resync.</t>
+          <t>The customer, Alex, was live transferred in via a partner (Resync) and completed onboarding, expressing concerns about credit but proceeding. Multiple outbound attempts were made by agents, but there were no completed incoming calls on the Retention line. Alex repeatedly requested cancellation and to stop payments, with several completed inbound calls to CS but not Retention. Ultimately, Alex's deal was cancelled after discussions about his options and inability to proceed with payments.</t>
         </is>
       </c>
     </row>
@@ -10388,18 +10712,18 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line; the only call was an outbound call from Levi Miller to the customer, with no mention of Aspire or Resync or a warm transfer.</t>
+          <t>No incoming calls detected; only one outbound call was made by Levi Miller. No mention of Aspire or Resync, and no handoff/transfer occurred.</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr"/>
-      <c r="R131" s="4" t="inlineStr">
+      <c r="R131" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S131" s="2" t="inlineStr">
         <is>
-          <t>The only interaction was an outbound call from Levi Miller to the customer, during which the agent confirmed the file would be canceled and that a confirmation email would be sent. The customer was appreciative and there were no incoming retention calls or live transfers. The cancellation was completed without any retention intervention.</t>
+          <t>There was one outbound call made by agent Levi Miller to the customer. During the call, the agent confirmed the cancellation of the customer's file and informed him that a confirmation email would be sent. The customer thanked the agent for the assistance. No incoming or retention line calls occurred.</t>
         </is>
       </c>
     </row>
@@ -10465,18 +10789,18 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All retention-related activity was outbound, and no Aspire/Resync keywords were detected in transcripts.</t>
+          <t>No incoming calls had a representative identify as being from Aspire or Resync, nor did any incoming caller explicitly state they were transferring or handing off the client. The opening lines of the incoming Onboarding and CS Team calls show direct client contact, not a partner handoff.</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr"/>
-      <c r="R132" s="4" t="inlineStr">
+      <c r="R132" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>Johnny Smith completed onboarding and attempted to make payments, but experienced delays and issues with fund withdrawals and creditor notifications. He contacted support and ultimately requested cancellation during an outbound call from the Retention department. The cancellation was confirmed, and no further payment attempts will be made. No live transfer from Aspire or Resync occurred.</t>
+          <t>Johnny Smith completed onboarding and began the debt relief process, but experienced issues with payment processing and creditor notifications. Multiple outbound attempts were made to reach him, with only two outbound calls completed. No completed incoming calls occurred on the Retention line. Ultimately, Johnny requested to cancel his program during an outbound call with the Retention department, and the cancellation was confirmed.</t>
         </is>
       </c>
     </row>
@@ -10535,25 +10859,29 @@
       <c r="N133" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O133" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O133" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming calls were to the Retention line, and no transcript or summary shows a representative from Aspire or Resync stating they have a client who wants to cancel. All completed calls were to Onboarding or 'Other' lines.</t>
-        </is>
-      </c>
-      <c r="Q133" s="2" t="inlineStr"/>
-      <c r="R133" s="4" t="inlineStr">
+          <t>On the 2026-05-12 00:11 incoming Onboarding call, the caller said: 'Owen, I got Susan right here with me on the line. I want you to take good care of her, ma'am.' This indicates a live transfer from a partner (Aspire mentioned in summary) via the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R133" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S133" s="2" t="inlineStr">
         <is>
-          <t>Susan Dangleman had several incoming calls, mostly to Onboarding and 'Other' lines, discussing debt management and consolidation. There were no completed incoming calls to the Retention line, and only one outbound attempt resulted in a brief voicemail. Despite Aspire/Resync being mentioned in onboarding, no retention activity occurred, and the deal was ultimately cancelled.</t>
+          <t>Susan was live-transferred by an Aspire partner representative to the Onboarding team, where her debt management program was explained and initiated. No completed calls occurred on the Retention line, and there was one outbound attempt that resulted in a voicemail. Additional incoming calls were handled by other departments, but none resulted in retention activity. Ultimately, Susan's deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -10612,25 +10940,29 @@
       <c r="N134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O134" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. The only completed retention call (#4) is an outbound call where the agent identifies as Aspire and processes a cancellation request directly from the customer, not via a warm transfer from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr"/>
-      <c r="R134" s="4" t="inlineStr">
+          <t>"So I have Denise here with me... They're taking they're gonna be taking it from here... They're all yours." (incoming Onboarding line, 2026-05-11 22:13)</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R134" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S134" s="2" t="inlineStr">
         <is>
-          <t>Denise Adams initially engaged with onboarding calls to discuss and set up a debt repayment program. She later requested to cancel her enrollment, expressing frustration and feeling misled. Multiple voicemails were exchanged, and outbound retention calls were made, during which Denise insisted on cancellation and threatened legal action if not resolved. Ultimately, the cancellation was acknowledged and processed by the company, with no evidence of a live transfer from Aspire or Resync.</t>
+          <t>Denise Adams was live-transferred in by a partner (Aspire/Resync) on the Onboarding line, where her account was set up and program terms were explained. Subsequent calls included onboarding support and multiple outbound attempts from the Retention line, but no completed incoming calls on Retention. Denise ultimately requested cancellation, citing dissatisfaction and feeling misled, and her cancellation was processed after several outbound retention attempts. The deal was cancelled, with no retention save achieved.</t>
         </is>
       </c>
     </row>
@@ -10689,21 +11021,25 @@
       <c r="N135" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O135" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O135" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>The only incoming retention-line call (2026-05-18 18:15) was from the customer herself, Jennifer Lynch, confirming cancellation. There is no evidence in the transcript or summary that a representative from Aspire or Resync called in to transfer a cancelling client; all cancellation requests were initiated by Jennifer or outbound agents.</t>
-        </is>
-      </c>
-      <c r="Q135" s="2" t="inlineStr"/>
+          <t>On 2026-05-11 21:48, the incoming call on the Onboarding line began with the partner representative saying, 'This is Kyle, and I do have Jennifer on the line. Whenever you're ready for the file numbers.' This is a clear live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>Partner (Kyle) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R135" s="2" t="inlineStr"/>
       <c r="S135" s="2" t="inlineStr">
         <is>
-          <t>Jennifer Lynch initiated cancellation of her debt relief program after discussing it with her husband, who did not want to proceed. Multiple outbound calls were made to confirm and finalize the cancellation, and one incoming retention-line call was completed by Jennifer herself to confirm the process. There was some confusion about the cancellation status, but agents ultimately agreed to process the cancellation. No Aspire/Resync warm transfer occurred; the deal was cancelled per Jennifer's request.</t>
+          <t>The customer was live-transferred in by a partner (Kyle) for onboarding, where the debt relief program was explained and initial steps were set up. Subsequently, the customer and her husband decided to cancel, leading to multiple outbound and inbound calls, including one completed incoming call on the Retention line to confirm cancellation. The account was ultimately cancelled after the customer's repeated requests and confirmation with agents. Several outbound attempts were made to follow up, and the customer expressed frustration at ongoing calls after cancellation.</t>
         </is>
       </c>
     </row>
@@ -10762,21 +11098,25 @@
       <c r="N136" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O136" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O136" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>The only incoming retention-line call (2026-05-18 18:15) was from the customer herself, Jennifer Lynch, confirming cancellation. There is no evidence in the transcript or summary that a representative from Aspire or Resync called in to transfer a cancelling client; all cancellation requests were initiated by Jennifer or outbound agents.</t>
-        </is>
-      </c>
-      <c r="Q136" s="2" t="inlineStr"/>
+          <t>On 2026-05-11 21:48, the incoming call on the Onboarding line began with the partner representative saying, 'This is Kyle, and I do have Jennifer on the line. Whenever you're ready for the file numbers.' This is a clear live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>Partner (Kyle) via Onboarding line</t>
+        </is>
+      </c>
       <c r="R136" s="2" t="inlineStr"/>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>Jennifer Lynch initiated cancellation of her debt relief program after discussing it with her husband, who did not want to proceed. Multiple outbound calls were made to confirm and finalize the cancellation, and one incoming retention-line call was completed by Jennifer herself to confirm the process. There was some confusion about the cancellation status, but agents ultimately agreed to process the cancellation. No Aspire/Resync warm transfer occurred; the deal was cancelled per Jennifer's request.</t>
+          <t>The customer was live-transferred in by a partner (Kyle) for onboarding, where the debt relief program was explained and initial steps were set up. Subsequently, the customer and her husband decided to cancel, leading to multiple outbound and inbound calls, including one completed incoming call on the Retention line to confirm cancellation. The account was ultimately cancelled after the customer's repeated requests and confirmation with agents. Several outbound attempts were made to follow up, and the customer expressed frustration at ongoing calls after cancellation.</t>
         </is>
       </c>
     </row>
@@ -10835,25 +11175,29 @@
       <c r="N137" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O137" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O137" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants to cancel. All retention-related conversations occurred on outbound calls, and the only incoming retention call was a no-answer.</t>
-        </is>
-      </c>
-      <c r="Q137" s="2" t="inlineStr"/>
-      <c r="R137" s="4" t="inlineStr">
+          <t>Opening transcript of 2026-05-11 21:29 incoming Onboarding call: The caller (Iris) is transferring Patricia to Owen from onboarding, with explicit handoff language: 'I'll be taking it from you. Thank you, Iris.' This is a live transfer from a partner (Iris) to onboarding.</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R137" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t>Patricia Patton was onboarded into a debt relief program involving Aspire and Better Lending, but soon became confused about the program's nature, believing it to be a loan. After multiple outbound calls from retention agents clarifying the process and addressing her concerns, Patricia decided to cancel the program, citing miscommunication and advice from her lawyer. No incoming retention calls were completed; all retention discussions and the cancellation were handled via outbound calls. Several voicemails and support calls occurred, but ultimately the deal was cancelled.</t>
+          <t>Patricia was live-transferred in by a partner (Aspire) to the onboarding team, where her debt relief program was explained and initial steps were taken. She later called customer service to reach a specific representative, but no incoming retention-line calls were completed. Multiple outbound attempts were made by retention agents, and Patricia ultimately decided to cancel after clarifying program details and feeling misled. No payments were processed, and her cancellation was confirmed.</t>
         </is>
       </c>
     </row>
@@ -10912,25 +11256,29 @@
       <c r="N138" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O138" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls where a representative stated they were from 'Aspire' or 'Resync' and had a client who wanted to cancel. The only incoming retention call was a voicemail with no transcript evidence of a live transfer.</t>
-        </is>
-      </c>
-      <c r="Q138" s="2" t="inlineStr"/>
-      <c r="R138" s="4" t="inlineStr">
+          <t>On 2026-05-11, an incoming call on the Onboarding line opened with: 'I have Derek on the line. Are you ready for the file number?' indicating a partner representative was transferring the client.</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>Unknown partner via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R138" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S138" s="2" t="inlineStr">
         <is>
-          <t>Derrick Ellis had several interactions with the company, including onboarding and customer service calls, but no completed incoming calls to the Retention line. Outbound attempts were made to reach him on the Retention line, but only voicemails were left. The customer ultimately cancelled, citing affordability issues, and no retention intervention occurred. No evidence of Aspire/Resync live transfer was found.</t>
+          <t>The customer, Derrick Ellis, was transferred in by a partner representative for onboarding and discussed his financial situation and program details. Subsequent calls included an incoming call to the CS Team where the customer requested cancellation due to affordability, and another brief incoming call from a lending company. There were multiple outbound attempts to reach the customer on the Retention line, but no completed incoming calls on that line. Ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -10989,21 +11337,25 @@
       <c r="N139" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O139" s="5" t="inlineStr">
+      <c r="O139" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-15, an incoming call on the Retention line was received from Alexander with Resync, who stated he had Johnny Drake on the line requesting to cancel. The transcript confirms this was a warm transfer from Resync for a cancellation.</t>
-        </is>
-      </c>
-      <c r="Q139" s="2" t="inlineStr"/>
+          <t>On 2026-05-15, incoming on Retention line: Alexander with Resync says, 'I have Johnny Drake that's requested to cancel... Whenever you're ready for the transfer, let me know.' This is a clear live transfer from Resync via the Retention line.</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R139" s="2" t="inlineStr"/>
       <c r="S139" s="2" t="inlineStr">
         <is>
-          <t>Johnny Drake's account was cancelled after a live transfer from Resync, where he requested to cancel to pay creditors directly. Multiple outbound attempts and follow-up calls occurred, including a refund request and confirmation of cancellation. The customer was informed about the cancellation process and no further payments would be deducted. The account is now closed, with refund processing initiated.</t>
+          <t>Johnny Drake was live-transferred in by Resync to request cancellation, which was handled by the compliance manager. He also called in himself to the CS Team to confirm cancellation and request a refund for a payment taken in error. Multiple outbound attempts were made, and a Resync supervisor later confirmed the cancellation process and sent required documents. The account was ultimately cancelled, with refund and closure steps initiated.</t>
         </is>
       </c>
     </row>
@@ -11062,21 +11414,25 @@
       <c r="N140" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O140" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming retention calls show a representative stating they are from Aspire or Resync or indicate a warm transfer from those companies. All retention calls are direct from the customer or internal agents, and transcripts do not mention Aspire/Resync as the transfer source.</t>
-        </is>
-      </c>
-      <c r="Q140" s="2" t="inlineStr"/>
+          <t>On 2026-05-10, the incoming Onboarding call opens with '+15612946881: Rose, this is Jamie Gonzales. I have here Michelin. Are you ready for the file number?' indicating a partner (likely Aspire/Resync) is transferring the client to Better Lending via the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
       <c r="R140" s="2" t="inlineStr"/>
       <c r="S140" s="2" t="inlineStr">
         <is>
-          <t>Micheline Malerbranche had multiple interactions with Better Lending regarding debt consolidation, including onboarding and several retention calls. The customer was confused about program details and had trouble with technology, but agents repeatedly explained the process and sent documents. Ultimately, the account was cancelled and confirmation was provided. There were many outbound attempts and voicemails, but the customer did connect with agents on the retention line before cancellation was finalized.</t>
+          <t>The customer was live-transferred in by a partner (Aspire/Resync) and onboarded. Multiple completed incoming calls occurred on the Retention line, where the customer discussed their account, program details, and ultimately confirmed cancellation. There were numerous outbound attempts and voicemails, but the customer did connect with agents several times. The account was ultimately canceled and the customer received confirmation.</t>
         </is>
       </c>
     </row>
@@ -11142,18 +11498,18 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel. All calls were either voicemails, no-answer, or in-progress with the CS Team.</t>
+          <t>No incoming calls had a representative mention Aspire or Resync, nor did any indicate a partner was transferring the client. All incoming calls were voicemails, no-answers, or had no transcribable conversation.</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr"/>
-      <c r="R141" s="4" t="inlineStr">
+      <c r="R141" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S141" s="2" t="inlineStr">
         <is>
-          <t>All calls to Christopher Schaefer were either outbound attempts or incoming calls to the CS Team, none of which were completed or connected. No incoming retention-line calls occurred, and no conversations were transcribed. The deal was ultimately cancelled, with only voicemails and missed calls recorded.</t>
+          <t>There were a total of 12 calls, all involving the CS Team, with 6 outbound attempts made to the customer. All incoming calls resulted in voicemails or no answers, and no completed conversations occurred. No live transfers from Aspire or Resync were detected. The deal was ultimately cancelled, and no retention-line calls were completed.</t>
         </is>
       </c>
     </row>
@@ -11212,25 +11568,25 @@
       <c r="N142" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O142" s="5" t="inlineStr">
+      <c r="O142" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>The 2026-05-11 16:19 incoming retention call was a warm transfer from Landon at Resync, who stated he was transferring Maureen, a client who requested cancellation, to Michael Belfort for assistance.</t>
+          <t>On 2026-05-11 16:19, incoming on Retention line: 'This is Landon speaking on a recorded line from Resync... I have Maureen with Linda Line here... I'm just transferring her over.'</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>Resync</t>
+          <t>Resync via Retention line</t>
         </is>
       </c>
       <c r="R142" s="2" t="inlineStr"/>
       <c r="S142" s="2" t="inlineStr">
         <is>
-          <t>Maureen Redding initially completed onboarding but later requested cancellation. A live retention call was transferred from Resync, where Maureen confirmed her desire to cancel. The agent explained the contract and cancellation process, and Maureen insisted on immediate cancellation, which was ultimately agreed to pending email confirmation. Multiple outbound and inbound calls occurred, but the final outcome was cancellation of the deal.</t>
+          <t>Maureen Redding had several interactions with the company, including onboarding and multiple retention calls. There was a clear live transfer from Resync on the Retention line, where the client was handed off to discuss her cancellation request. Ultimately, Maureen insisted on canceling her contract, and the agent agreed to process the cancellation after requesting email confirmation. Outbound attempts and voicemails were also made, but the main outcome was the client's cancellation.</t>
         </is>
       </c>
     </row>
@@ -11289,25 +11645,29 @@
       <c r="N143" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O143" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync with a client wishing to cancel. All completed incoming calls were to Onboarding or CS Team, not Retention.</t>
-        </is>
-      </c>
-      <c r="Q143" s="2" t="inlineStr"/>
-      <c r="R143" s="4" t="inlineStr">
+          <t>The 2026-05-08 21:55 incoming call on the Onboarding line began with a representative ('Liam') stating 'I have here Helen' and handing off the client to the Better Lending onboarding agent, indicating a live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R143" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S143" s="2" t="inlineStr">
         <is>
-          <t>Helen Heyward was onboarded and informed about the debt-relief process, including payments and creditor negotiations. She later contacted the CS Team to request cancellation, which was confirmed by the agent, with a confirmation email promised. No incoming calls were completed on the Retention line, and all follow-up was handled via CS Team outbound calls and voicemails. The deal was ultimately cancelled per Helen's request.</t>
+          <t>Helen was live-transferred in by a partner rep for onboarding, where her file was confirmed and the debt-relief process explained. Subsequent calls included Helen requesting and confirming cancellation, with agents promising email confirmation within five to seven business days. There were several outbound attempts and voicemails, but no completed incoming calls on the Retention line. The deal was ultimately cancelled as requested by Helen.</t>
         </is>
       </c>
     </row>
@@ -11362,25 +11722,29 @@
       <c r="N144" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O144" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. The only retention call was outbound, initiated by Better Lending.</t>
-        </is>
-      </c>
-      <c r="Q144" s="2" t="inlineStr"/>
-      <c r="R144" s="4" t="inlineStr">
+          <t>Both incoming calls on the Onboarding line involved Floyd, a partner representative, transferring Carla Nash to Devon Smith. Floyd explicitly states he is with Carla Nash and hands her off to Devon, indicating a live transfer from a partner (Aspire/Resync).</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R144" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S144" s="2" t="inlineStr">
         <is>
-          <t>Carla Nash participated in two onboarding calls with Devon Smith, where the debt management process and payment details were explained. Later, Ryan Henderson from Better Lending made an outbound retention call to Carla, during which she requested to cancel her program due to concerns about her credit cards and credit score. Despite explanations, Carla insisted on cancellation, which was confirmed, and she asked for a confirmation letter and to be placed on a do not call list.</t>
+          <t>The customer, Karla Nash, was transferred in via a partner (Aspire/Resync) on the Onboarding line for initial setup and program explanation. After onboarding, an outbound call from the Retention team reached her, during which she requested cancellation due to concerns about her credit cards and credit score. The agent confirmed the cancellation, assured no further payments would be deducted, and agreed to send a confirmation letter and place her on a do not call list. No completed incoming calls occurred on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -11439,25 +11803,25 @@
       <c r="N145" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O145" s="5" t="inlineStr">
+      <c r="O145" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-23 at 16:25 was a warm transfer from Nolan at Resync, who stated he had a client (Linda Jean) wanting to cancel and transferred her to the retention agent.</t>
+          <t>Incoming Onboarding call: Julian Morris introduces himself and states, 'So I have here, okay, Linda Jean with me,' clearly indicating a live transfer of the client. Incoming Retention call: Nolan from Resync says, 'This is Nolan from Resync on a recorded line. So I have a client on the line who wants to cancel the program,' confirming a partner handoff.</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>Resync</t>
+          <t>Julian Morris via Onboarding line; Nolan from Resync via Retention line</t>
         </is>
       </c>
       <c r="R145" s="2" t="inlineStr"/>
       <c r="S145" s="2" t="inlineStr">
         <is>
-          <t>Linda Jean completed onboarding and later requested cancellation of her debt relief program. A live transfer from Resync brought her to the retention line, where she insisted on canceling despite offers to postpone payments. She acknowledged possible cancellation fees and requested a bill. The outcome was cancellation, with multiple retention calls and one outbound follow-up.</t>
+          <t>Linda Jean was transferred in by partner representatives (Julian from Aspire/Resync and Nolan from Resync) for onboarding and cancellation assistance. She completed onboarding and later requested cancellation due to financial and account issues, including IRS concerns and a Chase account problem. Retention agents discussed possible postponement, but Linda insisted on cancellation and acknowledged potential fees. The deal was ultimately cancelled after several completed calls, including both inbound and outbound attempts.</t>
         </is>
       </c>
     </row>
@@ -11516,25 +11880,29 @@
       <c r="N146" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O146" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming calls to the Retention line involved a representative stating they were from Aspire or Resync with a client wanting to cancel. All incoming calls were to Onboarding or CS Team, and no warm transfer from Aspire/Resync was documented.</t>
-        </is>
-      </c>
-      <c r="Q146" s="2" t="inlineStr"/>
-      <c r="R146" s="4" t="inlineStr">
+          <t>On the 2026-05-07 incoming Onboarding line call, the transcript shows: '+18314025314: I have with me Aaron Waters on the line. Whenever you're ready, I can give you the phone number.' This indicates a partner/third party was handing off the client.</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>Partner/third party via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R146" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S146" s="2" t="inlineStr">
         <is>
-          <t>Aaron Waters initially started a debt resolution program but quickly expressed concerns about its impact on his credit score and requested cancellation. The CS team attempted to address his concerns and offered references, but Aaron remained unconvinced. A supervisor was scheduled to follow up, and ultimately, the cancellation was confirmed with no payments withdrawn. There were outbound attempts to assist, but no incoming calls on the Retention line.</t>
+          <t>Aaron Waters was initially onboarded via a live transfer from a partner or third party. He later called in to the CS Team to cancel his enrollment, expressing concerns about credit impact and requesting confirmation of cancellation. An outbound call was made to him to coordinate with accounting, and a final incoming CS Team call confirmed his cancellation and that no payments would be withdrawn. No completed calls occurred on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -11593,21 +11961,25 @@
       <c r="N147" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O147" s="5" t="inlineStr">
+      <c r="O147" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>The 2026-05-18 21:01 incoming retention call transcript shows Caleb from Aspire Law Group stating he has Sasha on the line and is transferring her to opt out, which matches the definition of a live call from Aspire.</t>
-        </is>
-      </c>
-      <c r="Q147" s="2" t="inlineStr"/>
+          <t>On 2026-05-18, an incoming call on the Retention line began with 'This is Caleb from Aspire Law Group on a recorded line... I have miss Sasha here. She just wants to go ahead and opt out today.'</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Retention line</t>
+        </is>
+      </c>
       <c r="R147" s="2" t="inlineStr"/>
       <c r="S147" s="2" t="inlineStr">
         <is>
-          <t>The customer, Sasha Vanosten, completed onboarding and later requested to cancel her debt management program. An Aspire Law Group representative facilitated a live transfer to the retention line, where Sasha confirmed her wish to opt out. After a brief disconnection, the retention agent called Sasha back, discussed her reasons for leaving, and processed the cancellation. Sasha cited finding a better rate elsewhere, and the agent confirmed she would receive a cancellation email.</t>
+          <t>The customer was initially onboarded via a live transfer from a partner representative (Ray) on the Onboarding line. Later, Aspire Law Group called in on the Retention line to transfer Sasha for a cancellation request. After the transfer, the agent confirmed Sasha's identity and processed her cancellation after discussing her reasons for leaving. Outbound attempts were made but only one outbound call was completed, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -11673,18 +12045,18 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line; only one outbound call attempt was made, which resulted in a brief voicemail. No transcript or summary indicates a representative from Aspire or Resync transferring a cancelling client.</t>
+          <t>No incoming calls; only a single outbound call attempt to voicemail on the Retention line. No mention of Aspire/Resync or any partner transfer.</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr"/>
-      <c r="R148" s="4" t="inlineStr">
+      <c r="R148" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S148" s="2" t="inlineStr">
         <is>
-          <t>Only one outbound call attempt was made to Dwight Pullen on the Retention line, which resulted in a brief voicemail and no completed conversation. There were no incoming retention calls or live transfers from Aspire or Resync. The deal status is cancelled, and no further contact or retention activity occurred.</t>
+          <t>There was only one outbound call attempt made to the customer on the Retention line, which reached voicemail and was not completed. No incoming calls were received, and there is no evidence of a live transfer or partner involvement. The deal status is cancelled, and no further contact was made.</t>
         </is>
       </c>
     </row>
@@ -11743,21 +12115,25 @@
       <c r="N149" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O149" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line. The only call was an incoming onboarding call where the agent introduced themselves as part of the onboarding team, not as Aspire or Resync transferring a cancelling client.</t>
-        </is>
-      </c>
-      <c r="Q149" s="2" t="inlineStr"/>
+          <t>The incoming call on the Onboarding line began with Jason Powell introducing himself and providing the file ID for Pamela Garcia, indicating a live transfer from a partner (likely Aspire/Resync).</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
       <c r="R149" s="2" t="inlineStr"/>
       <c r="S149" s="2" t="inlineStr">
         <is>
-          <t>Pamela Garcia had a single incoming call with the onboarding department, where her questions about the debt relief process were addressed and program details were explained. There were no calls to the Retention line, and no outbound calls or attempts. Although Aspire/Resync was mentioned in the context of explaining the program, there was no cancellation or retention activity on record.</t>
+          <t>Pamela Garcia was live-transferred in by Jason Powell (Aspire/Resync) to the onboarding team. The agent, Vera Grayson, confirmed client details and explained the debt relief process, addressing Pamela's concerns about credit impact and payment schedules. No calls were completed on the Retention line, and the deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -11816,25 +12192,29 @@
       <c r="N150" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O150" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. All completed calls were either to CS or Onboarding, and all incoming retention calls were voicemails or ringing with no completed conversation.</t>
-        </is>
-      </c>
-      <c r="Q150" s="2" t="inlineStr"/>
-      <c r="R150" s="4" t="inlineStr">
+          <t>The 2026-05-07 incoming Onboarding call opens with 'This is Leon from Better Lending onboarding team' and 'I have my office here. Her file is good to go.' The transcript shows a partner representative (Leon/Better Lending) transferring Maria Lopez to your company for onboarding, mentioning Resync and the handoff process. This is a live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>Better Lending/Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R150" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S150" s="2" t="inlineStr">
         <is>
-          <t>Maria Lopez repeatedly contacted customer service to cancel her debt management program, citing confusion, stress, and a preference to handle debts independently. Despite multiple outbound attempts and voicemails from the company, there were no completed incoming calls on the Retention line. Ultimately, Maria confirmed her cancellation intentions with CS agents, and the deal was marked as cancelled. No live retention call or warm transfer from Aspire/Resync occurred.</t>
+          <t>Maria Lopez was transferred in via a live onboarding call from Better Lending/Resync, enrolled in a debt management program, but soon requested cancellation due to family concerns and dissatisfaction. Multiple inbound calls to the CS Team followed, with Maria repeatedly seeking cancellation and expressing frustration with transfers and wait times. No completed incoming calls occurred on the Retention line, despite several outbound attempts. Ultimately, Maria's deal was cancelled, and she was not retained.</t>
         </is>
       </c>
     </row>
@@ -11893,25 +12273,25 @@
       <c r="N151" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O151" s="5" t="inlineStr">
+      <c r="O151" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>The 2026-05-22 18:07 incoming retention call was a warm transfer from Grant at client care of Freesync, who stated he had a mutual client (Christine) requesting to cancel. The transcript confirms this was a live transfer from Freesync.</t>
+          <t>The opening transcript of the 2026-05-22 incoming Retention call shows Grant from the client care of Freesync explicitly stating, 'I have a mutual client that requested to cancel,' and transferring Christine to Talia Morgan. This is a clear live transfer from a partner (Freesync/Resync) on the Retention line.</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>Client care (Grant) from Freesync</t>
+          <t>Resync via Retention line</t>
         </is>
       </c>
       <c r="R151" s="2" t="inlineStr"/>
       <c r="S151" s="2" t="inlineStr">
         <is>
-          <t>Christine initially completed onboarding and scheduled her first payment. On May 22, a live transfer from Freesync client care to retention was made for Christine's cancellation request due to family issues. The retention agent attempted to retain her, but Christine insisted on canceling, and the process was completed. Outbound follow-up calls were made to confirm and finalize the cancellation.</t>
+          <t>Christine Bradich was initially onboarded via a live transfer from a partner on the Onboarding line, with her debt management plan set up. Later, a live transfer from Resync on the Retention line brought her cancellation request due to family issues, which was handled by Talia Morgan. Despite offers to pause payments, Christine insisted on cancellation, and the agent agreed to process it. Outbound calls were made for follow-up, including a voicemail, but the account was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -11970,21 +12350,25 @@
       <c r="N152" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O152" s="5" t="inlineStr">
+      <c r="O152" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-18 17:24, the incoming retention call includes a representative stating, 'So I have James here. He disconnect oh, so let me call him again and I'll transfer him again too.' This indicates a warm transfer of a cancelling client, and the transcript includes Aspire/Resync keywords.</t>
-        </is>
-      </c>
-      <c r="Q152" s="2" t="inlineStr"/>
+          <t>On 2026-05-07, the incoming Onboarding line call opened with: 'Devon, this is Wesley. I have James here on the line. His file is good to go. You ready for the number?' This is a clear live transfer from a partner handing off the client.</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
       <c r="R152" s="2" t="inlineStr"/>
       <c r="S152" s="2" t="inlineStr">
         <is>
-          <t>James Newcomb initially onboarded for a debt-relief program but soon expressed concerns and requested cancellation, citing confusion about the program and credit impact. Multiple outbound attempts and voicemails were made, and James ultimately confirmed his decision to cancel during calls with both CS and Retention. A live transfer from a partner (Aspire/Resync) to Retention occurred, and the file was processed for cancellation. No retention was achieved, and James's account was closed as requested.</t>
+          <t>James Newcomb was live-transferred in by a partner (Wesley) and onboarded. He later called in to the CS Team to request cancellation due to concerns about account closures and credit impact. Multiple outbound attempts were made, and there was one completed incoming call on the Retention line, where a transfer was attempted but ultimately the cancellation was processed. The deal was cancelled and the customer was not retained.</t>
         </is>
       </c>
     </row>
@@ -12043,21 +12427,25 @@
       <c r="N153" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O153" s="5" t="inlineStr">
+      <c r="O153" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-08 includes Nicholas stating he is calling from Resync with a mutual client who wants to be canceled, matching the definition of a live call.</t>
-        </is>
-      </c>
-      <c r="Q153" s="2" t="inlineStr"/>
+          <t>Incoming call on Retention line: Nicholas says, 'This is Nicholas on a recorded line calling from Resync who have a mutual client that wants to be canceled.'</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R153" s="2" t="inlineStr"/>
       <c r="S153" s="2" t="inlineStr">
         <is>
-          <t>Ricardo was contacted by a tax associate to discuss debt relief options but could not afford the services. The next day, a representative from Resync called the retention line to request cancellation on Ricardo's behalf due to financial hardship. Ricardo then spoke directly with the retention agent to confirm the cancellation and requested written confirmation. The account was set to be canceled, and a confirmation email was promised.</t>
+          <t>Ricardo was contacted by an agent to discuss tax debt relief options but could not afford the services. The next day, a Resync representative called in on the Retention line to request cancellation on Ricardo's behalf due to new financial difficulties. The cancellation process was initiated and confirmed, with Ricardo requesting written confirmation. The account was set to be canceled, and a confirmation email was promised.</t>
         </is>
       </c>
     </row>
@@ -12116,25 +12504,29 @@
       <c r="N154" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O154" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. No transcripts or summaries mention Aspire/Resync or a warm transfer for cancellation.</t>
-        </is>
-      </c>
-      <c r="Q154" s="2" t="inlineStr"/>
-      <c r="R154" s="4" t="inlineStr">
+          <t>"This is George. I got Cricket here. Her file is already in front of me... So, Cricket, I'm gonna leave you here." (incoming Onboarding line)</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>George (partner rep) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R154" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S154" s="2" t="inlineStr">
         <is>
-          <t>The customer, Crickett Schacht, completed onboarding and later contacted the company multiple times to cancel and request a refund after a payment was processed in error. All retention-related activity was handled via outbound calls or through other departments (CS, onboarding, other), with no completed incoming retention-line calls. The account was ultimately cancelled, and the customer was informed about the refund timeline, but no live retention save attempt occurred.</t>
+          <t>The customer was live-transferred in by George for onboarding, completed the onboarding process, and later called multiple times about a cancellation and refund issue. There were several incoming calls, but none were completed on the Retention line, despite outbound attempts. Ultimately, the customer canceled the program and was awaiting a refund, with customer service confirming the refund timeline. The deal ended as cancelled, with the customer expressing frustration over communication and refund delays.</t>
         </is>
       </c>
     </row>
@@ -12193,25 +12585,25 @@
       <c r="N155" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O155" s="5" t="inlineStr">
+      <c r="O155" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>The 2026-05-07 17:50 incoming retention call transcript shows Ethan from Aspire Law Group stating he has a client (Lawrence Hart) who wants to cancel and warm-transfers him to Henry Hart, the compliance manager, for cancellation assistance.</t>
+          <t>On 2026-05-07 17:50, incoming on Retention line: 'Hi, Henry. This is Ethan from Aspire Law Group on a recorded line. I have a client with me on the line. It's for Lawrence Hart. He called in to cancel out with the program.'</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
         <is>
-          <t>Aspire Law Group</t>
+          <t>Aspire via Retention line</t>
         </is>
       </c>
       <c r="R155" s="2" t="inlineStr"/>
       <c r="S155" s="2" t="inlineStr">
         <is>
-          <t>Lawrence Hart initially joined the debt management program but soon requested cancellation, citing dissatisfaction and confusion about the process and communication. An Aspire Law Group representative warm-transferred Lawrence to the retention line, where Henry Hart handled the cancellation request. Multiple outbound calls and voicemails were made to Lawrence, but ultimately the deal was cancelled, and Lawrence was not retained.</t>
+          <t>Lawrence Hart was transferred in by Aspire on both the Onboarding and Retention lines, with the Retention call specifically for a cancellation request. Multiple outbound calls and voicemails were made to the client, and two completed outbound calls occurred after the live transfer. Ultimately, the client expressed dissatisfaction and confusion, leading to a cancellation of the program. The process and payment plan were explained, but the client chose not to proceed.</t>
         </is>
       </c>
     </row>
@@ -12270,21 +12662,25 @@
       <c r="N156" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O156" s="5" t="inlineStr">
+      <c r="O156" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-29 22:10, the incoming retention call transcript shows Connor from Resync stating, 'I have Margaret on the line,' and discussing her cancellation and refund with the retention agent. Similarly, on 2026-06-01 and 2026-06-02, Marcus and Eric from Resync called the retention line with Margaret on the line to discuss her canceled account and refund, confirming these were live warm transfers from Resync.</t>
-        </is>
-      </c>
-      <c r="Q156" s="2" t="inlineStr"/>
+          <t>On 2026-05-06 02:44, an incoming call on the Onboarding line opened with a representative saying, 'That's Margaret Bernard. She's with me on the line here. She's ready to go. I'll be taking it from here.' This is a clear live transfer handoff. Additionally, on 2026-05-29 22:10, the Retention line call summary states Michael Belfort is on a call with Connor from Resync, who transfers Margaret to Michael.</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line (2026-05-06), Resync via Retention line (2026-05-29)</t>
+        </is>
+      </c>
       <c r="R156" s="2" t="inlineStr"/>
       <c r="S156" s="2" t="inlineStr">
         <is>
-          <t>Margaret Bernard initially enrolled in a debt relief program but soon requested cancellation, citing concerns about her credit score and preferring to work with her credit union. Multiple calls were made to customer support and onboarding to process her cancellation and request a refund. Several live incoming retention calls were warm-transferred from Resync, all focused on resolving her refund after cancellation. Ultimately, Margaret's account was canceled, and she was repeatedly assured her refund was being processed, though she expressed frustration with the delay.</t>
+          <t>Margaret Bernard was live-transferred in by a partner (Aspire/Resync) and completed onboarding, but soon requested to cancel her contract due to concerns about her credit score and a preference to work with her credit union. Multiple inbound calls were made to customer service and retention, including a live transfer from Resync to Retention, to process her cancellation and refund. Ultimately, her account was canceled and she was provided information about her refund, with several follow-ups to confirm the status.</t>
         </is>
       </c>
     </row>
@@ -12343,25 +12739,29 @@
       <c r="N157" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O157" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O157" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>There were zero completed incoming calls to the Retention line. No transcript or summary indicates an incoming call where a representative from Aspire or Resync stated they had a client wishing to cancel.</t>
-        </is>
-      </c>
-      <c r="Q157" s="2" t="inlineStr"/>
-      <c r="R157" s="4" t="inlineStr">
+          <t>The incoming Onboarding call opened with a representative on the line saying, 'I have here Anthony. His file is good to go... Sorry. It's not Anthony. It's Raymond, actually.' This indicates a live transfer/handoff from a partner (likely Aspire, as referenced in the onboarding summary).</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R157" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S157" s="2" t="inlineStr">
         <is>
-          <t>Raymond Johnson completed only one call, which was an onboarding session where the process and payment schedule were explained. All subsequent calls were outbound attempts or voicemails from the retention team, with no successful contact on the Retention line and no incoming retention calls completed. Despite multiple outreach attempts, there was no live retention conversation, and the deal was ultimately cancelled.</t>
+          <t>Raymond Johnson was live-transferred in by a partner (Aspire) to the onboarding team, where his onboarding process and payment schedule were explained. Numerous outbound attempts were made by your agents, mostly leaving voicemails, but there were no completed incoming calls on the Retention line. Ultimately, the deal was cancelled, and there was no successful retention contact with the customer.</t>
         </is>
       </c>
     </row>
@@ -12427,18 +12827,14 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was directly from the customer, Teresa Musick, who called herself to cancel. There is no mention of Aspire or Resync, nor evidence of a representative stating they were from those companies or a warm transfer.</t>
-        </is>
-      </c>
-      <c r="Q158" s="2" t="inlineStr">
-        <is>
-          <t>Onboarding</t>
-        </is>
-      </c>
+          <t>Neither incoming call mentions Aspire or Resync, nor does any representative indicate they are a partner handing off the client. The Onboarding call appears to be a direct transfer from another agent (Bruce), but there is no mention of Aspire/Resync or an external partner. The Retention call is a direct call from the customer.</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr"/>
       <c r="R158" s="2" t="inlineStr"/>
       <c r="S158" s="2" t="inlineStr">
         <is>
-          <t>Teresa Musick first completed onboarding, setting up her payment plan and learning about the debt reduction process. The next day, she called the retention line directly to cancel her loan consolidation, explaining her mother would pay off her credit card loans. The agent confirmed the cancellation and promised written confirmation. No outbound calls or attempts were made to Teresa.</t>
+          <t>Teresa Musick completed two incoming calls: one with onboarding to set up her debt relief plan and one with retention to request cancellation. The onboarding call involved a handoff from another internal agent (Bruce), but not from Aspire/Resync. Teresa decided to cancel her loan consolidation because her mother will pay off her debts. The cancellation was confirmed by the agent, and Teresa will receive written confirmation via email.</t>
         </is>
       </c>
     </row>
@@ -12497,29 +12893,29 @@
       <c r="N159" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O159" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O159" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. The only retention call was an outbound call following an internal transfer from onboarding.</t>
+          <t>"So I have Irene on the other line here. She's already ready to go. Let me give you the file number here." — Incoming Onboarding line, 2026-05-05 23:02. Caller is handing off the client to your agent.</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
         <is>
-          <t>Onboarding</t>
-        </is>
-      </c>
-      <c r="R159" s="4" t="inlineStr">
+          <t>Partner/unknown rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R159" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S159" s="2" t="inlineStr">
         <is>
-          <t>Irene initially engaged with onboarding to learn about the program but became uncomfortable with the debt consolidation process and decided to cancel, as she was seeking a personal loan instead. After expressing her intent to cancel during an onboarding call, she was transferred internally to the retention team, where her cancellation was processed and confirmed. Irene later called customer service to confirm her cancellation and was reassured that her request had been completed and no further charges would occur. No live transfer from Aspire or Resync occurred; all retention actions were handled internally.</t>
+          <t>The customer, Irene, was live-transferred in by a partner/unknown rep for onboarding, where she expressed concerns about the debt resolution process. Multiple outbound attempts were made, but no completed incoming calls occurred on the Retention line. Irene later called in to cancel after realizing the program was for debt consolidation, not a personal loan. Her cancellation was processed, and she received confirmation that her account was closed with no further deductions.</t>
         </is>
       </c>
     </row>
@@ -12585,18 +12981,18 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>There were zero completed incoming calls to the Retention line, and no transcripts or summaries mention a representative from Aspire or Resync transferring a cancelling client. All completed calls were to Onboarding and CS, not Retention.</t>
+          <t>No incoming caller identified themselves as from Aspire or Resync, nor did any incoming call mention a partner handoff or transfer. Both completed incoming calls (Onboarding and CS Team) were handled by internal agents (Donya Alnasharty and Levi Miller) and did not reference Aspire/Resync or a partner transfer in their greetings or transcripts.</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr"/>
-      <c r="R160" s="4" t="inlineStr">
+      <c r="R160" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S160" s="2" t="inlineStr">
         <is>
-          <t>The customer, Kyle Pasley, had two completed incoming calls: one with Onboarding for account setup and one with CS to discuss contract concerns. There were 23 outbound attempts to reach the customer on the Retention line, but none were answered, and only voicemails were left. No live retention conversation occurred, and the deal was ultimately cancelled.</t>
+          <t>There were two completed incoming calls: one with onboarding and one with the CS team, both handled internally with no partner transfer. The customer, Kyle Pasley, expressed concerns about contract discrepancies and requested a callback from a supervisor. Despite 23 outbound attempts (mostly voicemails) to reach the customer via the Retention line, there were zero completed incoming calls on Retention. Ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -12655,25 +13051,25 @@
       <c r="N161" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O161" s="5" t="inlineStr">
+      <c r="O161" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-21 23:02 involved Adam Maxwell, an account services manager with Better Path Lending, affiliated with Resync. The transcript shows Adam stating he has Mister Hunt on the line and is prepared to assist, indicating a warm transfer from Resync for a cancellation or loan inquiry.</t>
+          <t>"This is Devon from the onboarding team." ... '+16507718284: This is Marcus, and I have Robert Hunt here with us on the line, and the file is good to go.' (2026-05-05 incoming Onboarding line). Also, on 2026-05-21 incoming Retention line: '+16693337644: This is Adam Maxwell. I'm account services manager with Better Path Lending and the affiliate with Resync. I actually had a file here for you.'</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
         <is>
-          <t>Resync</t>
+          <t>Aspire via Onboarding line; Resync via Retention line</t>
         </is>
       </c>
       <c r="R161" s="2" t="inlineStr"/>
       <c r="S161" s="2" t="inlineStr">
         <is>
-          <t>Robert Hunt initially enrolled in a debt management program with Aspire and Better Lending, but later faced legal issues and considered bankruptcy. Multiple calls involved discussing his loan and debt reduction options, including a live transfer from Resync to the retention line. Ultimately, Robert decided to cancel his consolidation loan, citing bankruptcy and financial hardship, despite warnings about cancellation fees. The deal status is cancelled.</t>
+          <t>Robert Hunt was live transferred in by both Aspire (via the Onboarding line) and Resync (via the Retention line), with agents confirming the handoff and presence of the client. Multiple inbound and outbound calls occurred, including several customer support and retention discussions about legal notices, payment plans, and bankruptcy. Ultimately, Robert decided to cancel his loan after filing for bankruptcy, despite agents offering to delay payments or discuss alternatives. The deal was cancelled after the client insisted on ending the program.</t>
         </is>
       </c>
     </row>
@@ -12732,25 +13128,29 @@
       <c r="N162" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O162" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O162" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All completed retention conversations were outbound calls from internal agents to Olivia.</t>
-        </is>
-      </c>
-      <c r="Q162" s="2" t="inlineStr"/>
-      <c r="R162" s="4" t="inlineStr">
+          <t>The opening transcript of the 2026-05-05 incoming Onboarding call shows a handoff: '+19493157441: I'll take it from here. Thank you.' This indicates a partner (likely Aspire or Resync) was on the line to transfer Olivia to your agent, consistent with a live transfer.</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R162" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S162" s="2" t="inlineStr">
         <is>
-          <t>Olivia completed onboarding but soon decided to cancel her debt resolution plan, citing a family member's offer to pay off her debts. Multiple outbound calls from retention agents confirmed her intent to cancel, and she was provided instructions for cancellation with no penalties. No incoming retention-line calls were completed; all retention efforts were outbound, and the account was ultimately cancelled per Olivia's request.</t>
+          <t>Olivia was live-transferred in via the Onboarding line, completed onboarding, and was informed about the debt resolution process. Multiple outbound attempts were made by your agents, but no completed incoming calls occurred on the Retention line. Olivia requested cancellation soon after starting the plan, citing a family member's offer to pay off her debts, and the account was ultimately cancelled. No retention-line inbound calls were completed; all retention efforts were outbound.</t>
         </is>
       </c>
     </row>
@@ -12809,21 +13209,25 @@
       <c r="N163" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="O163" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O163" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming retention calls involved a representative stating they were from Aspire or Resync and transferring a client for cancellation. All retention calls were direct from Robert Ransom or Sid Ransom, with no mention of a warm transfer from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q163" s="2" t="inlineStr"/>
+          <t>On 2026-05-05, the incoming Onboarding line call opened with: 'This is Henry Hart. I have Robert Ransom here. His file is good to go.' This is a clear live transfer from a partner (Aspire/Resync) handing off the client.</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>Aspire/Resync via Onboarding line</t>
+        </is>
+      </c>
       <c r="R163" s="2" t="inlineStr"/>
       <c r="S163" s="2" t="inlineStr">
         <is>
-          <t>Robert Ransom repeatedly contacted the retention line to confirm and expedite the cancellation of his debt-relief contract, expressing concern about pending payments and lack of paperwork. Retention agents assured him the cancellation was processed and promised email confirmation and no further payments. Multiple incoming calls to retention occurred, but no outbound calls were completed and no warm transfers from Aspire/Resync were detected. The deal was ultimately cancelled, with the customer seeking confirmation throughout.</t>
+          <t>Robert Ransom was live transferred in by a partner (Aspire/Resync) and onboarded. He soon requested cancellation, calling multiple times to confirm it and to ensure no payments would be taken. Several incoming calls were made to the Retention line, where agents confirmed and finalized the cancellation, and promised email confirmation. No outbound calls were completed; all key actions occurred via incoming calls, and the deal was ultimately cancelled as requested.</t>
         </is>
       </c>
     </row>
@@ -12889,14 +13293,14 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming retention calls involved a representative stating they were from Aspire or Resync with a client wishing to cancel. All retention calls were directly between the customer and the company's own agents (Better Lending/Better Pass Lending), with no mention of Aspire/Resync or a warm transfer.</t>
+          <t>No incoming call transcript indicates the caller is from Aspire or Resync, nor does any caller explicitly state they are transferring or handing off the client from a partner. All incoming calls are either directly from the customer or from representatives of BetterPath/Better Back/Better Pass Lending.</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr"/>
       <c r="R164" s="2" t="inlineStr"/>
       <c r="S164" s="2" t="inlineStr">
         <is>
-          <t>Larry Linton contacted the company multiple times to request cancellation of his debt consolidation plan, citing receipt of a settlement check and choosing to handle finances independently. Retention agents confirmed and processed the cancellation, and Larry was assured no payments would be deducted and that he would receive confirmation. There were both incoming and outgoing calls, with some voicemails and follow-ups, but ultimately the account was cancelled as requested.</t>
+          <t>Larry Linton contacted the company to cancel his debt consolidation plan, citing that he received a settlement check and would handle his finances independently. Multiple calls occurred, including two completed incoming calls on the Retention line and one outbound call confirming the cancellation. No evidence of a partner live transfer was found. The cancellation was processed, and Larry was assured he would receive confirmation within 48 hours.</t>
         </is>
       </c>
     </row>
@@ -12951,25 +13355,25 @@
       <c r="N165" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O165" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O165" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>The only call was an incoming onboarding call where the agent explained the onboarding process and payment instructions. There was no mention of a representative from Aspire or Resync calling the retention line to transfer a cancelling client.</t>
+          <t>"We have Edward in call here right now." Incoming call on Onboarding line.</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Resync via Onboarding line</t>
         </is>
       </c>
       <c r="R165" s="2" t="inlineStr"/>
       <c r="S165" s="2" t="inlineStr">
         <is>
-          <t>Edward Samonte had a single incoming call with the onboarding department, where the process and payment schedule were explained. The agent discussed the involvement of Resync and Better Lending but did not address cancellation or retention. No retention line calls or outbound attempts were made. The onboarding was completed, and Edward confirmed his payment details.</t>
+          <t>Edward Samonte was transferred in via a live call from Resync on the Onboarding line, where agent Dana Mohamed took over the call. The onboarding process was explained, including payment instructions and the involvement of Resync and Better Lending. Edward confirmed his first payment date and banking details. No calls were completed on the Retention line, and there were no outbound calls or attempts.</t>
         </is>
       </c>
     </row>
@@ -13028,25 +13432,29 @@
       <c r="N166" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O166" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants to cancel. No such keywords or warm transfer evidence is present in any transcript.</t>
-        </is>
-      </c>
-      <c r="Q166" s="2" t="inlineStr"/>
-      <c r="R166" s="4" t="inlineStr">
+          <t>On the 2026-05-04 incoming Onboarding call, Jason Todd says, 'So are you ready for the file?' and 'So right now, I'm gonna be leaving you with Carmen,' clearly indicating a live transfer/hand-off to Donna on the onboarding team via the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>Jason Todd via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R166" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S166" s="2" t="inlineStr">
         <is>
-          <t>Carmen Rivera Oconnor completed onboarding with Donna, expressing relief at the new program and confirming understanding of the process. Later, a brief incoming call indicated Carmen considered withdrawing but ultimately decided to stay with the program and would notify customer service. Two outbound retention calls were made but only resulted in voicemails, with no incoming retention-line calls completed.</t>
+          <t>Carmen was live-transferred by Jason Todd to the onboarding team, where her onboarding was completed and the program explained. Later, Carmen called in to leave a message for Jason Todd, initially indicating she wanted to withdraw but then deciding to stay with her current program and promising to notify customer service. Two outbound retention calls were attempted but only reached voicemail. Ultimately, the deal was cancelled with no completed retention-line calls.</t>
         </is>
       </c>
     </row>
@@ -13105,25 +13513,29 @@
       <c r="N167" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O167" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O167" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>There were no completed incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client wanting to cancel. The only incoming Retention call was in-progress and not completed.</t>
-        </is>
-      </c>
-      <c r="Q167" s="2" t="inlineStr"/>
-      <c r="R167" s="4" t="inlineStr">
+          <t>The incoming Onboarding call opens with Ellie introducing herself and stating, 'I have with me Patricia Mullings,' and offering the customer ID to the agent. This is a clear live transfer/hand-off from a partner representative.</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (Ellie) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R167" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S167" s="2" t="inlineStr">
         <is>
-          <t>Patricia Mullings completed onboarding calls discussing the debt management process and payment instructions, with Resync mentioned as part of the process. No completed incoming retention calls occurred, and the deal was ultimately cancelled. Outbound attempts were made, but there was no evidence of retention intervention or live transfer for cancellation.</t>
+          <t>Patricia Mullings was live-transferred in by a partner rep (Ellie) on the Onboarding line, where her onboarding was completed and her customer ID was confirmed. An outbound call followed, explaining the debt management process and payment schedule, with instructions to contact support if needed. No completed calls occurred on the Retention line, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -13182,21 +13594,25 @@
       <c r="N168" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O168" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O168" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming retention calls indicate a representative from Aspire or Resync stating they are transferring a cancelling client. The transcripts and summaries show direct calls from the customer (Audrey/Irene Pierce) to the retention line, not a warm transfer from Aspire or Resync.</t>
-        </is>
-      </c>
-      <c r="Q168" s="2" t="inlineStr"/>
+          <t>On the 2026-05-04 incoming Onboarding line call, Xavier Lookman says: 'I believe you were with Daniel Cruz. Correct? He transferred you to me.' This indicates a live transfer from a partner/agent (Daniel Cruz) to the onboarding team.</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Cruz via Onboarding line</t>
+        </is>
+      </c>
       <c r="R168" s="2" t="inlineStr"/>
       <c r="S168" s="2" t="inlineStr">
         <is>
-          <t>Irene Pierce (sometimes referred to as Audrey) called multiple times to cancel her debt relief account, citing confusion and lack of consent from her daughter. Retention agents confirmed the cancellation and provided reassurance that her daughter would not be affected. Outbound follow-ups were made to confirm her wishes and offer reinstatement, but Irene declined further assistance. The account was ultimately cancelled after several completed calls and voicemails.</t>
+          <t>The customer was live-transferred in by Daniel Cruz to the onboarding team, where the onboarding process and debt relief steps were explained. Multiple calls followed, including two completed incoming calls on the Retention line, where the customer (and a relative) requested cancellation and confirmed the process. Outbound attempts were made for follow-up and confirmation, but ultimately the customer chose to cancel the program. No retention was achieved, and the deal was closed as cancelled.</t>
         </is>
       </c>
     </row>
@@ -13262,18 +13678,18 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention calls completed; all completed retention calls were outbound. No transcript or summary indicates a representative from Aspire or Resync stating they have a client who wants to cancel.</t>
+          <t>No incoming calls included any mention of Aspire or Resync, nor did any incoming call transcript indicate a partner handoff or transfer. All completed calls were outbound, and all incoming calls to the Retention line were voicemails with 0s duration.</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr"/>
-      <c r="R169" s="4" t="inlineStr">
+      <c r="R169" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S169" s="2" t="inlineStr">
         <is>
-          <t>All contact attempts to Graylin Robinson were outbound, with most resulting in voicemails and two completed outbound retention calls. During these calls, Mr. Robinson expressed his desire to cancel due to unemployment and financial hardship, and the agent offered a refund and to pause deductions. No incoming retention calls were completed, and the account was ultimately cancelled.</t>
+          <t>All completed calls were outbound attempts by company agents, with no completed incoming calls on the Retention line. The customer, Graylin Robinson, was reached twice by outbound calls, during which he stated he wanted to cancel due to unemployment and inability to pay. The agent offered a refund and to pause deductions, but ultimately the deal was cancelled. Most other calls were outbound voicemails or unanswered attempts.</t>
         </is>
       </c>
     </row>
@@ -13339,18 +13755,18 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync with a client wanting to cancel. The only completed incoming call was to Onboarding, not Retention.</t>
+          <t>The only completed incoming call was on the Onboarding line, but the opening transcript shows Mason introducing himself as from the onboarding team and does not mention Aspire, Resync, or indicate a partner transfer. There is no evidence of a partner handoff or live transfer.</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr"/>
-      <c r="R170" s="4" t="inlineStr">
+      <c r="R170" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S170" s="2" t="inlineStr">
         <is>
-          <t>All calls were either to or from the Onboarding department, with no completed incoming calls to the Retention line. The customer, Mr. Mooring, spoke with onboarding about the debt relief process and wanted to pause to review the agreement. Outbound attempts to Retention resulted in voicemails, and there was no evidence of a live transfer or retention intervention. The deal was ultimately cancelled.</t>
+          <t>There were four total calls for this customer: two incoming (one completed, one no-answer) and two outbound (both voicemails). The only completed call was an incoming Onboarding call where the agent explained the debt relief process and Aspire's role, but there was no partner transfer. No calls were completed on the Retention line, and all outbound attempts went to voicemail. The customer ultimately did not proceed and the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -13416,18 +13832,18 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All calls were outbound, and the only completed conversation was an outbound call.</t>
+          <t>There were no incoming calls where a partner (Aspire or Resync) representative called in to transfer the client. All calls were outbound attempts or voicemails, except for one completed outbound call. No incoming call transcript shows a partner handoff or transfer.</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr"/>
-      <c r="R171" s="4" t="inlineStr">
+      <c r="R171" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S171" s="2" t="inlineStr">
         <is>
-          <t>All contact attempts to the customer were outbound, with most resulting in voicemails and only one completed call. In the completed outbound call, the agent confirmed the customer had already canceled their program with Resync. There were no incoming retention-line calls or live transfers from Aspire/Resync. The customer's deal was ultimately canceled.</t>
+          <t>All calls to the customer were outbound, with most resulting in brief voicemails and only one completed outbound conversation. There were no completed incoming calls on the Retention line. The only completed call confirmed that the customer had already canceled their program with Resync, and the agent acknowledged the recent cancellation. The account status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -13493,14 +13909,14 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>There are no transcripts or summaries indicating that an Aspire or Resync representative stated they were transferring a client who wanted to cancel. The only incoming retention call (2026-05-29) has no evidence of a warm transfer from Aspire/Resync.</t>
+          <t>No incoming call transcript or summary mentions Aspire or Resync, nor any explicit partner handoff/transfer. Both completed incoming calls on 'CCB (other)' are from Better Pass Lending or a direct customer, not a partner transfer.</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr"/>
       <c r="R172" s="2" t="inlineStr"/>
       <c r="S172" s="2" t="inlineStr">
         <is>
-          <t>Samuel Vargas had two incoming calls from another company (Better Pass Lending) and one completed incoming retention call. The customer requested cancellation, which was confirmed and processed. There were two outbound retention calls, both resulting in voicemails. The deal status is cancelled, and no Aspire/Resync warm transfer was detected.</t>
+          <t>The customer (Samuel Vargas) had two completed incoming calls on the 'CCB (other)' line, one from Abby at Better Pass Lending and one from a caller wanting to cancel a claim related to Javier Gonzalez. There was one completed incoming call on the Retention line, but no outbound calls were completed—only two outbound attempts resulted in voicemails. Ultimately, the customer’s deal was cancelled, and there is no evidence of a live transfer from Aspire or Resync.</t>
         </is>
       </c>
     </row>
@@ -13566,18 +13982,18 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync and had a client wanting to cancel. The only completed call was outbound from the CS Team.</t>
+          <t>There were no incoming calls where the caller identified as being from Aspire or Resync, nor any explicit mention of a partner transferring the client on an inbound line. The only mention of Aspire was during an outbound call initiated by the company's agent.</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr"/>
-      <c r="R173" s="4" t="inlineStr">
+      <c r="R173" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S173" s="2" t="inlineStr">
         <is>
-          <t>All calls were outbound attempts or from the CS Team, with no incoming retention-line calls. The only completed call involved Jacob Zander from Aspire discussing cancellation with the client, who was dissatisfied and insisted on canceling. The contract was ultimately canceled as per the client's wishes.</t>
+          <t>Multiple outbound attempts were made to reach the customer, with voicemails left. One outbound call was completed, during which the agent spoke with Jacob Zander from Aspire about the client's desire to cancel. The client confirmed they wanted to cancel due to dissatisfaction with the debt consolidation offer. No incoming retention-line calls were completed, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -13643,18 +14059,18 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>There were zero incoming calls on the Retention line, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel. All calls were outbound attempts or voicemails.</t>
+          <t>No incoming calls were completed; all calls were outbound attempts with voicemails, and there are no transcripts indicating a partner transfer or mention of Aspire/Resync.</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr"/>
-      <c r="R174" s="4" t="inlineStr">
+      <c r="R174" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S174" s="2" t="inlineStr">
         <is>
-          <t>All 27 calls to the customer were outbound attempts, with no completed or answered calls. Agents left voicemails but never reached the customer live. There were no incoming calls to the Retention line, and no evidence of a live transfer from Aspire or Resync. Ultimately, the customer was not reached and the deal was cancelled.</t>
+          <t>All 27 calls to the customer were outbound attempts, resulting only in voicemails or brief messages. There were no completed incoming calls on any line, including Retention. No live conversations or partner transfers occurred. The customer did not answer, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -13716,18 +14132,18 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>There were zero incoming retention-line calls, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel.</t>
+          <t>All calls were outbound attempts or voicemails from company agents; there were no incoming calls, and no mention of Aspire or Resync in any transcript.</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr"/>
-      <c r="R175" s="4" t="inlineStr">
+      <c r="R175" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S175" s="2" t="inlineStr">
         <is>
-          <t>All calls to Kaiya Brooks were outbound attempts, mostly resulting in voicemails or brief messages, with no completed conversations. No incoming retention-line calls were received, and there is no evidence of a live transfer or cancellation discussion. The deal status is marked as cancelled, but this appears to have occurred without any direct phone interaction with the customer.</t>
+          <t>All contact attempts to Kaiya Brooks were outbound calls, mostly resulting in voicemails or no answer. There were no completed incoming calls on any line, including Retention. The customer did not engage in any conversations, and the deal status is marked as cancelled.</t>
         </is>
       </c>
     </row>
@@ -13866,14 +14282,14 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>Neither of the two completed incoming retention calls involved a representative stating they were from Aspire or Resync, nor was there any mention of a warm transfer from those companies in the transcripts or summaries.</t>
+          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there any mention of a partner transferring the client. All incoming calls are directly from the customer.</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr"/>
       <c r="R177" s="2" t="inlineStr"/>
       <c r="S177" s="2" t="inlineStr">
         <is>
-          <t>Tina Nosky made multiple attempts to cancel her debt-relief account, resulting in two completed incoming calls to the retention line where she reiterated her desire to cancel. Representatives confirmed her cancellation request and addressed confusion caused by erroneous text messages. Additional outbound calls and voicemails were made by agents to follow up, and Tina consistently stated she did not wish to continue with the program. Ultimately, her account was processed for cancellation and she was assured of confirmation.</t>
+          <t>The customer, Tina Nosky, made multiple requests to cancel her account, resulting in several completed calls with the Retention department. Agents confirmed the cancellation process, addressed confusion about account status, and assured no further payments would be taken. Numerous outbound attempts were made, but only one outbound call was completed. Ultimately, the account was confirmed as canceled, and the customer was not retained.</t>
         </is>
       </c>
     </row>
@@ -13939,18 +14355,18 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls on the Retention line; the only call was an outbound call from Henry Hart to Denise Bradley. No mention of Aspire or Resync, and no warm transfer from another company.</t>
+          <t>No incoming calls were completed; the only call was an outbound call made by agent Henry Hart. No mention of Aspire or Resync, and no evidence of a partner transfer.</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr"/>
-      <c r="R178" s="4" t="inlineStr">
+      <c r="R178" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S178" s="2" t="inlineStr">
         <is>
-          <t>Denise Bradley was contacted by Henry Hart via an outbound retention call, during which she withdrew her application due to personal and financial hardships. The agent confirmed the cancellation and provided information about possible future options. There were no incoming retention calls or live transfers from Aspire/Resync. The deal was cancelled as requested by the customer.</t>
+          <t>The only call was an outbound call from Henry Hart to Denise Bradley, during which Denise requested to withdraw from the debt consolidation program due to personal and financial hardships. The agent confirmed the cancellation and provided information about possible future options. There were no incoming calls, live transfers, or calls completed on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -14009,21 +14425,25 @@
       <c r="N179" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O179" s="5" t="inlineStr">
+      <c r="O179" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>The 2026-05-21 16:06 incoming retention call transcript shows Marcus from Resync stating he has a mutual client (Mary Hoffman) who wants to cancel, and he transfers Mary to Talia Morgan for cancellation assistance. This matches the definition of a live call.</t>
-        </is>
-      </c>
-      <c r="Q179" s="2" t="inlineStr"/>
+          <t>Incoming call on Retention line: Marcus from Resync called in and stated, 'This is Marcus with Resync. We do have a client, a mutual client that requests cancellation.' He then transferred Mary Hoffman to Talia Morgan for further assistance.</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R179" s="2" t="inlineStr"/>
       <c r="S179" s="2" t="inlineStr">
         <is>
-          <t>Mary Hoffman was transferred in by a Resync representative requesting cancellation. Multiple outbound calls were made by company agents to discuss her cancellation, payment options, and to confirm her intent to leave the program. Mary consistently expressed her desire to cancel due to financial hardship and prior scams, and ultimately confirmed her cancellation despite offers to postpone or split payments. The account was cancelled, and Mary planned to change her bank account to prevent further withdrawals.</t>
+          <t>Mary Hoffman's case involved multiple outbound attempts and a single completed incoming call on the Retention line, which was a live transfer from Resync regarding her cancellation request. After the transfer, agents discussed her desire to cancel due to financial hardship and previous scams. Despite offers to postpone payments or split them, Mary insisted on canceling and planned to change her bank account to prevent further withdrawals. The outcome was a confirmed cancellation after several follow-up calls and voicemails.</t>
         </is>
       </c>
     </row>
@@ -14078,25 +14498,25 @@
       <c r="N180" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O180" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O180" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>No incoming retention call transcript or summary indicates a representative stating they are from Aspire or Resync with a client wanting to cancel. All retention calls appear to be direct from the customer or internal transfers.</t>
+          <t>Incoming call on 'Katherine RT OB' (retention_ob) line, opening transcript: Caller (Mrs. Gomez) states she wants to remove herself from the 'resync repayment program' after consulting an attorney. Katherine Adams responds as the agent. The mention of 'resync' and the context of the call indicate a partner handoff or transfer from Resync.</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
         <is>
-          <t>Katherine RT OB (retention_ob)</t>
+          <t>Resync via Katherine RT OB (retention_ob) line</t>
         </is>
       </c>
       <c r="R180" s="2" t="inlineStr"/>
       <c r="S180" s="2" t="inlineStr">
         <is>
-          <t>The customer, Mrs. Gomez, made multiple attempts to reach her agent and discussed confusion about her debt consolidation program. She considered cancellation after consulting an attorney, and her payment deadline was extended while she reviewed documentation. Ultimately, her service was successfully canceled, and she was assured a cancellation confirmation would be sent. There were both inbound and outbound calls, including voicemails and follow-ups, with no evidence of a live transfer from Aspire or Resync.</t>
+          <t>The customer, Yenislecdys Gomez, made multiple calls seeking clarification about her debt program, including requests to speak with specific agents. She expressed confusion about the program terms and ultimately decided to cancel after consulting an attorney and discussing her concerns with agents. The cancellation was confirmed by Kevin Michael, who assured her a notification would be sent. Several outbound attempts were made, and at least one completed incoming call occurred on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -14162,22 +14582,18 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>No incoming retention call transcript or summary indicates a representative from Aspire or Resync stating they have a client who wants to cancel. The only incoming retention-related call was from 'Adam Maxwell RT OB' and does not mention Aspire/Resync or a warm transfer for cancellation.</t>
-        </is>
-      </c>
-      <c r="Q181" s="2" t="inlineStr">
-        <is>
-          <t>Adam Maxwell RT OB</t>
-        </is>
-      </c>
-      <c r="R181" s="4" t="inlineStr">
+          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there evidence of a partner handoff/transfer. The incoming calls are from customers or internal lines.</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr"/>
+      <c r="R181" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S181" s="2" t="inlineStr">
         <is>
-          <t>Multiple outbound attempts were made to reach Richard Holcombe regarding his debt program, but he declined to continue, citing disinterest and too many debt consolidation calls. An incoming call on the retention line involved a discussion about his contract and stress over the situation, but there was no clear cancellation request via a live transfer. Ultimately, the deal was cancelled after Richard expressed he did not want to proceed.</t>
+          <t>Multiple outbound attempts were made to reach Richard Holcombe, with only one outbound call completed. There were two incoming calls, but none were completed on the Retention line. The customer expressed disinterest in continuing with the debt program and ultimately cancelled. No evidence of a live transfer from Aspire or Resync was found, and the case was closed without retention.</t>
         </is>
       </c>
     </row>
@@ -14236,21 +14652,25 @@
       <c r="N182" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O182" s="5" t="inlineStr">
+      <c r="O182" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>The first incoming retention call included Jacob from Aspire Law Group stating he had a mutual client, Denise, who needed to cancel, and he transferred the call to the retention agent. This matches the definition of a live call from Aspire.</t>
-        </is>
-      </c>
-      <c r="Q182" s="2" t="inlineStr"/>
+          <t>Opening transcript of 2026-06-01 23:37 incoming Retention call: 'This is Jacob from Aspire Law Group... I have a mutual client, a Denise... I just authenticated the client and transferred the call.' Call came in on the Retention line.</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Retention line</t>
+        </is>
+      </c>
       <c r="R182" s="2" t="inlineStr"/>
       <c r="S182" s="2" t="inlineStr">
         <is>
-          <t>Denise's cancellation was processed after an Aspire Law Group representative live-transferred her to the retention team. Denise requested a refund and confirmation of her cancellation, which the agent processed and promised to confirm by email. There were no successful outbound contacts; both outbound attempts went to voicemail. Ultimately, Denise was cancelled and a refund was initiated.</t>
+          <t>Denise's case involved two completed incoming calls on the Retention line, both related to her cancellation and refund request. The first call was a live transfer from Jacob at Aspire Law Group, who handed Denise off to Michael Belfort for assistance. The second call continued the discussion, with Denise expressing frustration about a withdrawal after her cancellation attempt; Michael processed her refund and confirmed cancellation. No outbound calls were answered, only brief voicemails were left. The outcome was a confirmed cancellation and refund for Denise.</t>
         </is>
       </c>
     </row>
@@ -14312,14 +14732,14 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was handled by Katherine Adams from Better Path Lending, not Aspire or Resync, and there is no evidence in the transcript or summary of a representative stating they are from Aspire or Resync or that the call was a warm transfer from those companies.</t>
+          <t>No mention of Aspire or Resync, and no indication that the incoming call was a partner handoff or transfer. The call opened with the agent introducing herself as from Better Path Lending and speaking directly to the client.</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr"/>
       <c r="R183" s="2" t="inlineStr"/>
       <c r="S183" s="2" t="inlineStr">
         <is>
-          <t>Brenda Evans received one completed incoming call on the Retention line from Better Path Lending, during which she expressed her desire to cancel her debt consolidation program due to lack of communication and trust. The agent attempted to clarify and retain Brenda, but Brenda insisted on cancellation and mentioned involving her lawyer. There was also one outbound call attempt from customer service that resulted in a brief voicemail, with no further contact or retention efforts.</t>
+          <t>Brenda Evans received one completed incoming call on the Retention line, where she expressed her desire to cancel her debt consolidation program due to lack of communication and trust. The agent attempted to address her concerns, but Brenda remained firm about cancellation and mentioned involving her lawyer. There was also one outbound call attempt from the CS team that resulted in a brief voicemail. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -14385,18 +14805,14 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call involved a transfer from 'Kevin with client care' at Better Lending, not Aspire or Resync. The transcript does not mention Aspire or Resync, nor does it indicate a warm transfer from those companies.</t>
-        </is>
-      </c>
-      <c r="Q184" s="2" t="inlineStr">
-        <is>
-          <t>Client Care (Kevin)</t>
-        </is>
-      </c>
+          <t>The incoming call on the Retention line featured a representative named Kevin from 'client care,' but there was no mention of Aspire or Resync, nor was there an explicit statement that this was a partner handoff or live transfer from those companies.</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr"/>
       <c r="R184" s="2" t="inlineStr"/>
       <c r="S184" s="2" t="inlineStr">
         <is>
-          <t>Frank Saliture was transferred to the retention line by Kevin from client care because he wanted to cancel his debt relief program, citing affordability concerns and uncertainty about his account balance. Henry Hart, the compliance manager, discussed options with Frank, including lowering his monthly payment, but Frank insisted he could not afford any payment and chose to cancel. Henry assured Frank that any money withdrawn would be refunded and provided his contact information for future assistance.</t>
+          <t>Frank Saliture called in to cancel his debt relief program, expressing concerns about affordability and not recalling enrollment. The call was handled by Henry Hart, who discussed Frank's options and attempted to lower his payment, but Frank still decided to cancel. There was one completed incoming call on the Retention line and one outbound follow-up, with no evidence of a partner live transfer. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -14462,18 +14878,18 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>There were zero incoming calls on the Retention line; all completed calls were outbound. No transcript or summary indicates a representative from Aspire or Resync transferring a cancelling client.</t>
+          <t>No incoming calls were completed; all completed calls were outbound. No transcripts or summaries mention an incoming call from Aspire, Resync, or a partner representative handing off the client.</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr"/>
-      <c r="R185" s="4" t="inlineStr">
+      <c r="R185" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S185" s="2" t="inlineStr">
         <is>
-          <t>All calls to Noel Crockett were outbound, with no incoming retention-line calls. The customer expressed dissatisfaction with the debt program, requested cancellation, and sought confirmation of the cancellation policy. Multiple agents discussed her desire to cancel, and she confirmed she had already secured alternative arrangements. Ultimately, the customer insisted on cancellation and requested no further contact.</t>
+          <t>All completed calls to Noel Crockett were outbound, with no completed incoming calls on the Retention line. The customer expressed dissatisfaction with the program, requested cancellation, and repeatedly asked for confirmation that her account was closed. Agents discussed cancellation policies, attempted to resolve her concerns, and confirmed her request to cancel. Ultimately, the customer was not retained and requested no further contact.</t>
         </is>
       </c>
     </row>
@@ -14539,18 +14955,14 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>Neither of the completed incoming retention calls involved a representative stating they were from Aspire or Resync, nor was there a warm transfer from those companies. The first incoming call was from Colton at Sky Law Group, not Aspire or Resync.</t>
-        </is>
-      </c>
-      <c r="Q186" s="2" t="inlineStr">
-        <is>
-          <t>Sky Law Group</t>
-        </is>
-      </c>
+          <t>No incoming call transcript mentions Aspire or Resync, nor does any caller identify as a partner handing off the client. The only partner mentioned is 'Colton with the Sky Law Group,' which is not Aspire or Resync.</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr"/>
       <c r="R186" s="2" t="inlineStr"/>
       <c r="S186" s="2" t="inlineStr">
         <is>
-          <t>The customer, Timothy Langenberg, had multiple interactions with the retention team, including two completed incoming calls and one completed outbound call. The process involved a third-party (Sky Law Group) requesting cancellation on Timothy's behalf, with the client expressing dissatisfaction with the program's timeline and ultimately deciding to cancel. Several outbound attempts resulted in voicemails, and the account was cancelled due to unmet immediate financial needs and distrust in prior communications.</t>
+          <t>The customer, Timothy Langenberg, had multiple interactions with the retention team, including two completed incoming calls and one completed outbound call. The main issue was dissatisfaction with the program's timeline for debt payoff, leading to a cancellation request. The calls involved a representative from Sky Law Group assisting with the cancellation, but there were no Aspire or Resync live transfers. Ultimately, the client canceled due to unmet expectations and concerns about payment timing.</t>
         </is>
       </c>
     </row>
@@ -14612,18 +15024,18 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls on the Retention line; only one outbound call attempt was made, which reached voicemail. No transcript or summary indicates a live transfer from Aspire or Resync.</t>
+          <t>No incoming calls; only one outbound call attempt (voicemail) on the Retention line. No Aspire/Resync mention.</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr"/>
-      <c r="R187" s="4" t="inlineStr">
+      <c r="R187" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S187" s="2" t="inlineStr">
         <is>
-          <t>Only one outbound call attempt was made to the customer by the Retention department, which went to voicemail and was not completed. There were no incoming calls on the Retention line, and no conversations took place. The customer's deal status is cancelled, and no retention efforts were successful.</t>
+          <t>There was a single outbound call attempt to the customer on the Retention line, which went to voicemail and was not answered. No incoming calls were completed, and there is no evidence of a live transfer or partner handoff. The deal status is cancelled, and no conversation with the customer took place.</t>
         </is>
       </c>
     </row>
@@ -14689,18 +15101,14 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was transferred from 'Kevin with client care', not from Aspire or Resync. There is no mention of Aspire or Resync in the transcript or summaries.</t>
-        </is>
-      </c>
-      <c r="Q188" s="2" t="inlineStr">
-        <is>
-          <t>client care</t>
-        </is>
-      </c>
+          <t>The incoming call on the Retention line was from 'Kevin with client care,' but there is no mention of Aspire or Resync, nor is there any indication that Kevin is from a partner company handing off the client. The transcript only references internal staff.</t>
+        </is>
+      </c>
+      <c r="Q188" s="2" t="inlineStr"/>
       <c r="R188" s="2" t="inlineStr"/>
       <c r="S188" s="2" t="inlineStr">
         <is>
-          <t>Calvin Berryhill contacted the company to cancel his debt consolidation program, believing it was a loan. The incoming retention call was transferred from client care, and Calvin insisted on cancellation due to dissatisfaction and misunderstanding. An outbound follow-up call confirmed Calvin's desire to cancel, and he was reassured that no payments would be deducted. The deal was ultimately cancelled.</t>
+          <t>Calvin Berryhill contacted the company to cancel his program, believing it was a loan rather than debt consolidation. An internal client care representative transferred the call to a compliance agent, who confirmed Calvin's wish to cancel. The agent then called Calvin back to clarify the situation, but Calvin remained dissatisfied and insisted on cancellation. The account was ultimately cancelled, and no payments were taken.</t>
         </is>
       </c>
     </row>
@@ -14762,18 +15170,18 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. All retention calls are outbound, and no transcript indicates a warm transfer from Aspire or Resync.</t>
+          <t>All completed calls were outbound from company agents to the customer; there were no completed incoming calls where a partner (Aspire/Resync) or representative transferred or handed off the client. No incoming call transcript shows a partner introduction or transfer.</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr"/>
-      <c r="R189" s="4" t="inlineStr">
+      <c r="R189" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S189" s="2" t="inlineStr">
         <is>
-          <t>All calls to Gloria Mciver were outbound, with no incoming retention-line calls. Agents attempted to clarify program details and address confusion, but Gloria ultimately insisted on cancellation and claimed to have sent a cancellation form. Multiple voicemails were left, and the customer expressed dissatisfaction with the service. The deal status is cancelled, and no retention was achieved.</t>
+          <t>All contact attempts to Gloria Mciver were outbound, with no completed incoming calls on the Retention line. Agents discussed program details, clarified confusion about Aspire and Better Way, and addressed cancellation requests. Gloria ultimately insisted on canceling her enrollment, and the deal was marked as cancelled. Multiple voicemails were left, and no live transfer from Aspire or Resync occurred.</t>
         </is>
       </c>
     </row>
@@ -14835,18 +15243,18 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync with a client wanting to cancel. All calls were either outbound or incoming on a different line, and no Aspire/Resync keywords were detected.</t>
+          <t>No incoming call transcript or summary mentions Aspire, Resync, or a partner transfer. The only incoming call was from the customer returning a missed call.</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr"/>
-      <c r="R190" s="4" t="inlineStr">
+      <c r="R190" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S190" s="2" t="inlineStr">
         <is>
-          <t>Vilmar Are was contacted by the retention team to discuss cancellation due to concerns about credit impact and unaffordable payments. The agent explained the program but Vilmar decided to proceed with cancellation. A follow-up incoming call confirmed the cancellation was finalized, and the customer acknowledged this resolution. No live transfer from Aspire or Resync occurred.</t>
+          <t>The customer, Vilmar Are, requested to cancel their program due to credit concerns and unaffordable payments. An outbound retention call was completed to process the cancellation, and the agent explained the implications. Later, the customer called back after missing a call, and was informed that the cancellation had already been finalized. No live transfer or partner handoff occurred, and the account was successfully cancelled.</t>
         </is>
       </c>
     </row>
@@ -14905,21 +15313,25 @@
       <c r="N191" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O191" s="5" t="inlineStr">
+      <c r="O191" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-13 19:19 was from Emily with Resync, who clearly stated she had a cancellation request for the client. The transcript confirms this was a warm transfer from Resync for a client wanting to cancel.</t>
-        </is>
-      </c>
-      <c r="Q191" s="2" t="inlineStr"/>
+          <t>"This is Emily with Resync. I just have a cancellation request for you." — incoming on Retention line (retention_in)</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R191" s="2" t="inlineStr"/>
       <c r="S191" s="2" t="inlineStr">
         <is>
-          <t>The customer’s account was cancelled after a warm transfer from Resync, where a representative requested cancellation due to the client feeling misled about the program. Alan later called outbound to confirm the cancellation and dispute a payment, and the agent processed the cancellation and promised confirmation. Numerous outbound attempts and voicemails were made, but only one incoming retention call was completed. The deal was ultimately cancelled and the customer was assured of confirmation.</t>
+          <t>The customer was transferred in by a Resync representative on the Retention line to request a cancellation, citing being misled about the program. The compliance manager confirmed the cancellation and discussed related account details with the customer. Multiple outbound attempts were made before and after, but only one incoming Retention call was completed. The case ended with the customer's cancellation being processed and confirmation promised.</t>
         </is>
       </c>
     </row>
@@ -14981,14 +15393,14 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>The only incoming retention-line call (2026-05-28 16:17) was from Michael Belfort with Better Lending, not Aspire or Resync. The transcript does not indicate a representative stating they are from Aspire or Resync or that it was a warm transfer from those companies.</t>
+          <t>Neither incoming completed call (Rika NSF or Retention) includes any greeting or introduction from an Aspire or Resync representative, nor do they mention being a partner transferring the client. The Retention call opens with 'This is Michael with Better Lending,' not Aspire/Resync, and the other incoming call is a direct conversation between Rika Hart and Jennifer with no transfer or partner handoff.</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr"/>
       <c r="R192" s="2" t="inlineStr"/>
       <c r="S192" s="2" t="inlineStr">
         <is>
-          <t>Jennifer Blackmon received multiple outbound calls regarding missed payments, mostly resulting in voicemails. She disputed a March payment and insisted on canceling her account, threatening legal action. The only incoming retention-line call was handled by Michael Belfort, who confirmed the cancellation after Jennifer reiterated her desire to close the account. The deal was ultimately cancelled, and Jennifer was promised a confirmation email.</t>
+          <t>Jennifer Blackmon had multiple outbound call attempts from agents, mostly resulting in voicemails. She spoke with Rika Hart about payment issues and disputed charges, then called in to confirm her desire to cancel the account. Michael Belfort from Better Lending handled her cancellation request on the Retention line, confirmed the account would be canceled, and promised a confirmation email. The account was ultimately canceled after Jennifer insisted and threatened legal action.</t>
         </is>
       </c>
     </row>
@@ -15127,18 +15539,18 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls with a representative stating they were from Aspire or Resync and transferring a cancelling client. All calls were voicemails or voicemail attempts, and no relevant keywords were detected.</t>
+          <t>No incoming calls had transcribable conversations or any mention of Aspire/Resync or a partner transfer; all calls were either outbound voicemails or an incoming call that went to voicemail.</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr"/>
-      <c r="R194" s="4" t="inlineStr">
+      <c r="R194" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S194" s="2" t="inlineStr">
         <is>
-          <t>There were multiple outbound attempts to reach Rebecca Jones, all resulting in voicemails, and one brief incoming call that also resulted in a voicemail. No live conversations occurred, and there were no completed calls on the retention line. Ultimately, the deal was cancelled without any successful contact or retention discussion.</t>
+          <t>All calls were either outbound attempts that resulted in voicemail or a single incoming call to the Retention line that also went to voicemail. There were no completed conversations with the customer. No evidence of a live transfer or partner handoff was found. The customer's deal status is cancelled, and no retention was achieved.</t>
         </is>
       </c>
     </row>
@@ -15197,21 +15609,25 @@
       <c r="N195" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O195" s="5" t="inlineStr">
+      <c r="O195" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>The first incoming retention call involved Emily from Resync contacting Rick, the compliance team manager, to request a cancellation and transferring the client (Estebania) over for processing. This matches the definition of a live call from Resync.</t>
-        </is>
-      </c>
-      <c r="Q195" s="2" t="inlineStr"/>
+          <t>Call #1: Incoming on Retention line. The caller introduced herself as 'Emily with Resync' and stated, 'I just have a cancellation request for you.' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
       <c r="R195" s="2" t="inlineStr"/>
       <c r="S195" s="2" t="inlineStr">
         <is>
-          <t>Esteban Escobedo had two incoming retention calls, both completed. The first call was a live transfer from Resync requesting cancellation, and the second call involved Esteban directly contacting the retention line to confirm his cancellation request and discuss potential fees. No outbound calls or attempts were made. The outcome was a confirmed cancellation, with a waiver request for fees and confirmation to be sent by email.</t>
+          <t>Both calls were incoming on the Retention line. The first was a live transfer from Resync requesting cancellation, which was handled by Rick. The second call was a direct inquiry from the customer, Esteban, who confirmed his desire to cancel the consolidation loan service. Both calls resulted in the processing of the cancellation, with confirmation to be sent via email. No outbound calls or attempts were made.</t>
         </is>
       </c>
     </row>
@@ -15350,18 +15766,18 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line where a representative stated they were from Aspire or Resync with a client wishing to cancel. All incoming calls were to 'CCB (other)' or were voicemails; the only completed Retention call was outbound.</t>
+          <t>No incoming call transcript or summary mentions Aspire or Resync, nor any explicit partner handoff/transfer. All incoming calls are directly from the customer or unrelated parties.</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr"/>
-      <c r="R197" s="4" t="inlineStr">
+      <c r="R197" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S197" s="2" t="inlineStr">
         <is>
-          <t>The customer made several brief incoming calls to a general line requesting to speak with an agent, but did not reach the Retention line directly. The only completed Retention call was an outbound call, during which the customer confirmed their wish to cancel after discussing alternatives. The cancellation was processed and a confirmation was promised. No live transfer from Aspire/Resync or internal department occurred.</t>
+          <t>There were several incoming calls, but none on the Retention line and none involved a partner transfer. Outbound attempts were made, with one completed outbound Retention call where the customer confirmed cancellation after discussing options. No live transfer from Aspire or Resync occurred; the customer independently requested cancellation, which was processed and confirmed.</t>
         </is>
       </c>
     </row>
@@ -15420,25 +15836,29 @@
       <c r="N198" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O198" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O198" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming retention-line calls where a representative stated they were from Aspire or Resync and had a client who wanted to cancel. All completed calls were either outbound retention or incoming from CS, with no evidence of a warm transfer from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q198" s="2" t="inlineStr"/>
-      <c r="R198" s="4" t="inlineStr">
+          <t>The incoming call on the CS Team line opened with Talia Morgan stating, 'This is Talia Morgan with Resync, and this is about the debt consolidation program that you have with us.'</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>Resync via CS Team line</t>
+        </is>
+      </c>
+      <c r="R198" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S198" s="2" t="inlineStr">
         <is>
-          <t>Deborah Devincentz canceled her debt consolidation program, confirmed through both an incoming CS call and several outbound retention calls. She stated she had already paid off her credit cards and sent multiple cancellation requests. No incoming retention-line calls were completed, and the deal was ultimately cancelled after outbound follow-ups.</t>
+          <t>Deborah Devincentz canceled her debt consolidation program, stating she had already paid off her credit cards and no longer needed the service. There were multiple outbound retention calls, but no completed incoming calls on the Retention line. The only completed incoming call was on the CS Team line, where a Resync representative confirmed receipt of Deborah's cancellation request. Ultimately, the deal was canceled and no retention was achieved.</t>
         </is>
       </c>
     </row>
@@ -15504,14 +15924,14 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call was directly from the customer, Luis Sarango, who called after receiving voicemails. There is no evidence in the transcript or summary that a representative from Aspire or Resync initiated the call or stated they were transferring a client to cancel.</t>
+          <t>No mention of Aspire or Resync in the incoming retention call transcript. The caller was the customer, Luis Sarango, not a partner representative. The opening lines show Luis called in directly after receiving a voicemail.</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr"/>
       <c r="R199" s="2" t="inlineStr"/>
       <c r="S199" s="2" t="inlineStr">
         <is>
-          <t>Luis Sarango received two outbound retention calls, both resulting in voicemails. He then called the retention line to discuss cancellation, stating he found another debt solution with family support. The agent explained options, but Luis preferred to receive information by email and was not interested in retaining the program. The deal was cancelled.</t>
+          <t>Luis Sarango received two outbound retention calls, both resulting in voicemails. He then called in directly to the Retention line to request cancellation, citing family support and a new debt management option. The agent discussed alternatives but Luis remained firm on cancellation, requesting an email summary. No partner live transfer occurred; the deal was cancelled after the direct customer call.</t>
         </is>
       </c>
     </row>
@@ -15570,25 +15990,29 @@
       <c r="N200" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O200" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O200" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>There were zero completed incoming calls on the Retention line. No transcript or summary shows a representative from Aspire or Resync stating they have a client who wants to cancel via a warm transfer.</t>
-        </is>
-      </c>
-      <c r="Q200" s="2" t="inlineStr"/>
-      <c r="R200" s="4" t="inlineStr">
+          <t>The incoming completed call on the Onboarding line (2026-05-23) opened with Dana from the onboarding team welcoming Iris, the client, and referencing the Resync partner process. The transcript and summary indicate the client was handed off and the Resync process was explained, showing a partner transfer.</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R200" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S200" s="2" t="inlineStr">
         <is>
-          <t>All completed calls were outbound, with no completed incoming retention calls. The customer was onboarded and later contacted by retention agents regarding their consolidation loan, but chose to handle arrangements directly with creditors and declined further assistance. Multiple outbound attempts resulted in voicemails, and the customer was not retained in the program.</t>
+          <t>The customer was transferred in via the Onboarding line, with the Resync process explained and initial payment arrangements confirmed. Multiple outbound calls were made by retention agents, but no completed incoming calls occurred on the Retention line. The customer ultimately chose to handle their debt directly with creditors, declining further assistance from the company. Several outbound attempts resulted in voicemails or brief conversations, but no retention was achieved.</t>
         </is>
       </c>
     </row>
@@ -15647,25 +16071,29 @@
       <c r="N201" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O201" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O201" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming calls to the Retention line where a representative states they are from Aspire or Resync and have a client who wants to cancel. All retention interactions are outbound, and the only incoming call was an onboarding call from Better Lending.</t>
-        </is>
-      </c>
-      <c r="Q201" s="2" t="inlineStr"/>
-      <c r="R201" s="4" t="inlineStr">
+          <t>On the 2026-05-22 incoming Onboarding line call, the opening transcript shows: '+18158142724: This is Sarah assist you. Can I have Allison with me?' and 'Are you ready for the file number?' indicating a partner representative (Sarah) is transferring the client (Allison) to Better Lending for onboarding. This is a live transfer.</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R201" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S201" s="2" t="inlineStr">
         <is>
-          <t>Allison Schroeder completed onboarding with Better Lending and was informed about the debt reduction process involving Aspire. Multiple outbound calls and voicemails were made by retention agents to provide updates and request callbacks, but there were no incoming calls to the Retention line. No evidence of a cancellation or retention conversation occurred, and the customer did not respond to retention outreach. The account appears to remain in onboarding or early payment status with no confirmed cancellation.</t>
+          <t>Allison Schroeder was live-transferred by an Aspire representative to Better Lending for onboarding, where her debt reduction process and payment schedule were set up. Multiple outbound calls and voicemails were made by retention agents, but there were no completed incoming calls on the Retention line. The client did not connect with Retention, and the only completed inbound call was the initial onboarding transfer. No cancellation or retention resolution occurred.</t>
         </is>
       </c>
     </row>
@@ -15731,18 +16159,18 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>There were zero completed incoming calls on the Retention line, and no transcripts or summaries indicate a representative from Aspire or Resync stating they had a client wishing to cancel.</t>
+          <t>No mention of Aspire or Resync in any incoming call transcript. The only incoming call (Onboarding line) was from someone referencing a file for Brian Adams, but there is no indication this was a partner handoff or live transfer from Aspire/Resync.</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr"/>
-      <c r="R202" s="4" t="inlineStr">
+      <c r="R202" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S202" s="2" t="inlineStr">
         <is>
-          <t>The customer had two completed onboarding calls, including a discussion about the graduation loan and payment setup. There were numerous outbound attempts from retention and other departments, mostly resulting in voicemails, but no completed incoming retention calls. No cancellation or retention conversations occurred, and the customer did not answer any retention calls.</t>
+          <t>There was one completed incoming call on the Onboarding line, where a file was discussed, but no evidence of a partner live transfer. The majority of calls were outbound attempts, mostly resulting in voicemails, with only one outbound call completed. No completed incoming calls occurred on the Retention line. The customer did not connect with the Retention team, and most outreach attempts were unsuccessful.</t>
         </is>
       </c>
     </row>
@@ -15801,29 +16229,29 @@
       <c r="N203" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O203" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O203" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants to cancel. The only incoming calls were to Onboarding and NSF, and none match the live call definition.</t>
+          <t>On 2026-05-15 15:23, an incoming call on the Onboarding line opened with a representative saying, 'I got Don Mace here with me. Ready with the file number?' and then handed off to the Better Lending onboarding team, indicating a live transfer from a partner.</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
         <is>
-          <t>Jenny NSF</t>
-        </is>
-      </c>
-      <c r="R203" s="4" t="inlineStr">
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R203" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S203" s="2" t="inlineStr">
         <is>
-          <t>Dawn Mace had multiple outbound call attempts from various departments, with only a few calls completed. She spoke with onboarding about starting a debt reduction process through Aspire, but later contacted NSF to insist on cancellation due to financial hardship and lack of confirmation. No incoming calls were completed on the Retention line, and there is no evidence of a live transfer from Aspire or Resync. The outcome appears to be unresolved cancellation, with Dawn awaiting confirmation.</t>
+          <t>The customer was live transferred in from Aspire via the Onboarding line and began the onboarding process for debt reduction. Multiple outbound attempts were made to reach the customer, with only a few completed outbound calls and no completed incoming calls on the Retention line. The customer later attempted to cancel due to financial hardship, as discussed in an incoming NSF call, but did not connect with Retention directly. The case remains unresolved with cancellation requested but not confirmed.</t>
         </is>
       </c>
     </row>
@@ -15889,18 +16317,18 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>There were zero incoming retention-line calls completed, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel. All completed calls were outbound.</t>
+          <t>No incoming calls mention Aspire or Resync, nor any partner handoff/transfer. All completed calls are outbound; all incoming calls are voicemails or in-progress with no evidence of a live transfer.</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr"/>
-      <c r="R204" s="4" t="inlineStr">
+      <c r="R204" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S204" s="2" t="inlineStr">
         <is>
-          <t>All contact attempts to Stephanie Paige were outbound, with no incoming retention-line calls completed. Agents left multiple voicemails and messages, providing callback numbers and account updates, but there is no evidence Stephanie answered or engaged in a live conversation. No cancellation or retention discussion occurred, and the customer did not respond to any outreach.</t>
+          <t>All completed calls to this customer were outbound, with agents leaving messages or providing updates, but no incoming calls were completed on the Retention line. There were numerous outbound attempts, mostly resulting in voicemails. No evidence of a live transfer or partner handoff was found, and the customer did not connect on any inbound Retention call.</t>
         </is>
       </c>
     </row>
@@ -15959,25 +16387,29 @@
       <c r="N205" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O205" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O205" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>There were no incoming calls to the Retention line, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel.</t>
-        </is>
-      </c>
-      <c r="Q205" s="2" t="inlineStr"/>
-      <c r="R205" s="4" t="inlineStr">
+          <t>The incoming call on the Onboarding line began with Donna from the onboarding team greeting Melina, who then said, 'So I have Denise on the line. Let me provide you with the file number.' Melina then stated, 'I will leave the call now to care of the customer,' indicating a live transfer/hand-off.</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>Melina via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R205" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S205" s="2" t="inlineStr">
         <is>
-          <t>The customer, Dennis Splain, had one completed incoming call with the onboarding department where the debt relief process was explained and next steps were confirmed. All other calls were outbound attempts or voicemails from various departments (NSF, Retention, CS), with no completed incoming retention calls. There is no evidence of cancellation or retention discussions, and the customer did not answer any outbound calls. The account remains in onboarding/hold status with no further progress.</t>
+          <t>There was one completed incoming call, which was a live transfer from Melina via the Onboarding line, where the onboarding process and debt program were explained to the customer. All other calls were outbound attempts or voicemails, including several to the Retention line, but no completed incoming calls on Retention. No Aspire or Resync partner was mentioned. The customer was onboarded, but there was no further live contact; all subsequent outreach attempts were unsuccessful.</t>
         </is>
       </c>
     </row>
@@ -16036,25 +16468,29 @@
       <c r="N206" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O206" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O206" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>None of the incoming retention calls involved a representative stating they were from Aspire or Resync with a client wishing to cancel. All incoming retention calls were directly from the customer (Miss Daniels), not a warm transfer from Aspire/Resync.</t>
-        </is>
-      </c>
-      <c r="Q206" s="2" t="inlineStr"/>
-      <c r="R206" s="4" t="inlineStr">
+          <t>On 2026-05-05, an incoming call on the Onboarding line began with the caller saying, 'I have here Tony Daniels. Are you ready for the phone number?' indicating a partner was transferring the client. Additionally, the agent later referenced Aspire and Resync as partners in the process.</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>Partner (Aspire/Resync) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R206" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S206" s="2" t="inlineStr">
         <is>
-          <t>Miss Daniels initially onboarded and discussed her debt management options, with Aspire and Resync mentioned as partners. She later called the retention line expressing financial concerns and a desire to cancel, but was offered to postpone payments and gather more information. There were several outbound attempts and voicemails, but ultimately, the customer was not immediately cancelled and was reassured about no deductions and ongoing support. No live transfer from Aspire/Resync occurred; all retention interactions were direct with the customer.</t>
+          <t>The customer was live-transferred in by a partner (Aspire/Resync) on the Onboarding line and began the onboarding process, confirming a first payment date. Later, the customer expressed concerns about multiple debt programs and considered canceling, leading to several retention outbound attempts and two completed incoming calls on the retention line. The customer was reassured about no immediate payments and was advised to clarify her situation with other creditors. No completed incoming calls occurred on the Retention line itself; most retention activity was outbound or on other lines.</t>
         </is>
       </c>
     </row>
@@ -16113,21 +16549,25 @@
       <c r="N207" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O207" s="5" t="inlineStr">
+      <c r="O207" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>On 2026-05-14 16:09, an incoming retention call transcript shows Emily from Resync stating, 'I have a cancellation request for you,' and transferring the client (William) to the retention manager Rick. This matches the definition of a live call from Resync with a cancelling client.</t>
-        </is>
-      </c>
-      <c r="Q207" s="2" t="inlineStr"/>
+          <t>"Hi, Rick. This is Emily with Resync. I have a cancellation request for you." (2026-05-14 incoming on Retention line); also, 2026-05-04 incoming Onboarding line: "I have William Hill with me. Are you ready for the file number?"</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line (2026-05-04) and Resync via Retention line (2026-05-14)</t>
+        </is>
+      </c>
       <c r="R207" s="2" t="inlineStr"/>
       <c r="S207" s="2" t="inlineStr">
         <is>
-          <t>The customer, William Woodward, was onboarded for debt relief with Resync and Better Lending, with his first payment scheduled for May 14. On May 14, a live transfer from Resync brought a cancellation request to the retention team, and William confirmed his desire to cancel, though he was outside the three-day cancellation window. The retention agent kept the account active until June 15 with no further payments and processed a refund. Multiple outbound attempts and voicemails followed, with one additional outbound call discussing refund status but no further customer engagement.</t>
+          <t>The customer was live-transferred in twice: once for onboarding (from Resync) and once for a cancellation request (from Resync). After the cancellation request, the agent explained the account would remain active until June 15 with no further payments, and a refund would be processed. Multiple outbound attempts were made, with only one additional outbound call completed and many voicemails left. The customer was not retained, and the process moved toward cancellation and refund.</t>
         </is>
       </c>
     </row>
@@ -16186,25 +16626,25 @@
       <c r="N208" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O208" s="5" t="inlineStr">
+      <c r="O208" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>The incoming retention call on 2026-05-21 was a warm transfer from Connor at Resync, who stated he had Anthony on the line for a cancellation request and transferred him to Talia Morgan on the Retention line.</t>
+          <t>"Hello, Talia. This is Connor calling from Resync on a recorded line... I have Anthony here on the line. He's following up on his cancellation. Thank you, Talia. Transferring 321." (Retention line); also, Onboarding call opened with a handoff: 'I have here Anthony on the line. His file is good to go. So are you ready for the phone number?' (Onboarding line)</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
         <is>
-          <t>Resync</t>
+          <t>Resync via Retention line; partner handoff via Onboarding line</t>
         </is>
       </c>
       <c r="R208" s="2" t="inlineStr"/>
       <c r="S208" s="2" t="inlineStr">
         <is>
-          <t>Anthony Dzurka had multiple interactions regarding his debt-relief program, including onboarding and customer service calls. The key retention call was a live transfer from Resync, where Anthony requested cancellation and follow-up on a refund. Outbound calls were mostly voicemails attempting to reach Anthony, and there was confusion about the refund process. Ultimately, Anthony canceled his program and was awaiting a refund.</t>
+          <t>Anthony was live-transferred in twice: once via Onboarding for initial setup (with Resync mentioned as a partner), and once via Retention from Resync regarding a cancellation. He discussed removing a debt and ultimately requested cancellation and a refund, which was confirmed as in process. Multiple outbound attempts were made, but there was one completed inbound Retention call and one completed outbound Retention call. The account is on hold pending refund and cancellation resolution.</t>
         </is>
       </c>
     </row>
@@ -16263,25 +16703,29 @@
       <c r="N209" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O209" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="O209" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>There are no incoming retention-line calls where a representative states they are from Aspire or Resync and have a client who wants/needs to cancel. All retention-related calls are outbound, and the only incoming retention call is a voicemail with no transcript or evidence of a warm transfer.</t>
-        </is>
-      </c>
-      <c r="Q209" s="2" t="inlineStr"/>
-      <c r="R209" s="4" t="inlineStr">
+          <t>Incoming call on Onboarding line: Max said, 'I had a client on the line, but it seems that the call dropped with her. Let me just give you the file number.' This indicates a partner (Max) was transferring or handing off a client.</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>Max (partner) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="R209" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S209" s="2" t="inlineStr">
         <is>
-          <t>Adriane Hankerson attempted to cancel her debt consolidation program, with multiple outbound calls from retention and compliance agents to discuss her cancellation request. She confirmed her desire to cancel after comparing programs and chose another option. No incoming retention-line live calls or warm transfers were completed; most calls were outbound attempts, voicemails, or follow-ups regarding her cancellation paperwork.</t>
+          <t>The customer was transferred in via a live call from a partner (Max) on the Onboarding line. Multiple outbound attempts were made, with three completed outbound calls discussing the customer's desire to cancel their program. No completed incoming calls occurred on the Retention line, and the customer ultimately confirmed their wish to cancel after comparing programs. Most other calls were voicemails or brief attempts with no further live contact.</t>
         </is>
       </c>
     </row>
@@ -16347,18 +16791,18 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>There were zero incoming retention-line calls completed, and no transcripts or summaries indicate a representative from Aspire or Resync stating they have a client who wants to cancel. All calls were outbound attempts, mostly voicemails.</t>
+          <t>All calls were outbound attempts with no completed incoming calls. No mention of Aspire or Resync, and no evidence of a live transfer or partner handoff in any call transcript or log.</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr"/>
-      <c r="R210" s="4" t="inlineStr">
+      <c r="R210" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
       <c r="S210" s="2" t="inlineStr">
         <is>
-          <t>All calls to Frank Miller were outbound attempts, primarily leaving brief voicemails from various agents and departments. No incoming retention-line calls were completed, and there is no evidence of any live conversation or cancellation request. The customer did not answer or engage, so no progress was made regarding cancellation, retention, or onboarding.</t>
+          <t>All 20 calls to Frank Miller were outbound attempts, each resulting in brief voicemails with no completed conversations. There were no completed incoming calls on any line, including Retention. No live transfers or partner handoffs occurred, and the customer did not answer or return any calls. No progress was made on the account due to lack of contact.</t>
         </is>
       </c>
     </row>

--- a/attached_assets/May_Deals_1780695126872_Call_Analysis.xlsx
+++ b/attached_assets/May_Deals_1780695126872_Call_Analysis.xlsx
@@ -10,7 +10,7 @@
     <sheet name="May Deals - Call Analysis" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'May Deals - Call Analysis'!$A$1:$S$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'May Deals - Call Analysis'!$A$1:$U$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S210"/>
+  <dimension ref="A1:U210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,10 +494,12 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="38" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,20 +580,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Transferred From (Company)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Transferred By (Agent)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Live Call Evidence</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Transfer Source</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Outcome Summary</t>
         </is>
@@ -657,20 +669,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Onboarding line: Marcus says, 'I have Raymond with me here on the line, Raymond Roberts. Got the file?' indicating a partner representative is transferring the client.</t>
-        </is>
-      </c>
+      <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Marcus via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr"/>
+          <t>Marcus</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-30 incoming Onboarding line call, the transcript shows: 'This is Marcus. I have Raymond with me here on the line, Raymond Roberts.' Marcus is handing off the client to Cassie from onboarding, indicating a live transfer.</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Raymond was initially onboarded via a live transfer from Marcus, who handed him off to Cassie on the Onboarding line. The onboarding process was completed, payment dates were set, and Raymond's concerns were addressed. Later, Raymond requested cancellation, which was confirmed in a completed outbound call with the Retention team. Multiple outbound attempts were made, and the client was ultimately canceled, with no retention achieved.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Raymond was live-transferred in by Marcus to the onboarding team, where payment dates and program details were set. Later, Raymond requested cancellation, which was confirmed in a completed outbound Retention call. Multiple outbound attempts were made, and one brief incoming call was received on the Retention line. Ultimately, Raymond canceled his program due to financial hardship and garnishment issues.</t>
         </is>
       </c>
     </row>
@@ -734,20 +752,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-29 22:57, incoming Onboarding line: Charlie Waybins says, 'I have here mister Paul. He's ready to go. Are you ready for the phone number?' and confirms details for a handoff. This is a clear partner transfer.</t>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Charlie Waybins via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr"/>
+          <t>Charlie Waybins</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-29 22:57, incoming Onboarding line: Charlie Waybins says, 'I have here mister Paul. He's ready to go. Are you ready for the phone number?' and provides details to Vera Grayson, clearly transferring the client.</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Paul Maag was live-transferred in by a partner (Charlie Waybins) on the Onboarding line to start the program. Multiple calls followed, including a lengthy CS Team call where Paul expressed discomfort and requested cancellation, and a completed Retention line call where Paul confirmed his wish to cancel due to feeling misled. Outbound attempts and voicemails were made, but ultimately Paul was not retained and pursued cancellation.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Paul Maag was live-transferred in by a partner rep (Charlie Waybins) to complete onboarding. After onboarding, Paul expressed discomfort and requested cancellation, citing misinformation and pressure during the sales process. Multiple outbound and inbound calls occurred, including a completed Retention line call where Paul reiterated his wish to cancel. The account outcome is a requested cancellation, with no evidence of retention or payment continuation.</t>
         </is>
       </c>
     </row>
@@ -811,24 +839,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>"This is Jason. I'm with Eugene here. You ready for the phone number?" — Incoming call on Onboarding line, Jason (Aspire/partner) is on the line with the client and hands off to Devon Smith.</t>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
+          <t>Jason</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-29 incoming Onboarding line call, the caller says: 'This is Jason. I'm with Eugene here. You ready for the phone number?' indicating a partner rep (Jason) is transferring the client (Eugene) to Devon from Better New York onboarding.</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Onboarding line</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live-transferred in by a partner (Aspire) on the Onboarding line, where onboarding and payment details were discussed and confirmed. Afterward, multiple outbound attempts were made by your agents, mostly to the Retention line, but none were answered or completed. The only completed outbound call reached the customer, who stated he had canceled his enrollment and was already in other debt programs; a callback was scheduled to review his contract. No completed incoming calls occurred on the Retention line.</t>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Eugene, was live-transferred by Jason from Aspire to the Better New York onboarding team, where program details and payment information were discussed and confirmed. Later, an outbound call from Better Lending revealed Eugene had canceled his enrollment, citing participation in other debt resolution programs and confusion about contract terms; a callback was scheduled for further review. Multiple outbound attempts were made to the customer, primarily on the Retention line, but no completed incoming calls were received on Retention. The account status remains as cancellation requested.</t>
         </is>
       </c>
     </row>
@@ -892,20 +930,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-28 16:04, incoming on the Onboarding line, George (partner rep) says: 'I got Kimmy here on the line. She did enroll with us today into the resolution program along with a graduation loan.' and 'I'll leave you with Donna right now.' This is a clear live transfer from a partner rep.</t>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Partner rep (George) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr"/>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03 17:44 incoming on Retention: Patrick (partner rep) says, 'I have a mutual client on the line with me who requested cancellation. Can you please assist?' This is a clear partner live transfer on the Retention line.</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>The customer was live-transferred in by a partner rep for onboarding and enrolled in the debt resolution program. Later, the customer requested cancellation, which was handled through both inbound and outbound calls, including a completed incoming call on the Retention line where the cancellation request was confirmed. Multiple outbound attempts were made to follow up and finalize the cancellation, and the customer was promised a confirmation email. The process included some confusion and dissatisfaction from the customer regarding the program details.</t>
+          <t>Partner rep via Retention line</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Kimetha Spoon, was initially onboarded via a live transfer from a partner rep (George) on the Onboarding line, and later a cancellation request was live-transferred by another partner rep (Patrick) on the Retention line. Multiple outbound calls were made by your agents to discuss the program and process the cancellation, with the customer expressing dissatisfaction and ultimately confirming her wish to cancel. The process included clarifications, confirmation of cancellation, and promises of follow-up and email confirmation. Both onboarding and cancellation involved partner handoffs, and at least one completed incoming call occurred on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -969,20 +1017,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls; all calls were outbound attempts with no transcribable conversations and no mention of Aspire/Resync.</t>
-        </is>
-      </c>
+      <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls; all calls were outbound attempts with voicemails, and no mention of Aspire or Resync.</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>All calls to Linda Howard were outbound attempts, resulting in voicemails or brief messages with no completed conversations. No incoming calls were received on any line, including Retention. The customer did not answer, and no live contact was made regarding the cancellation request.</t>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>All calls to Linda Howard were outbound attempts, resulting in voicemails with no completed conversations. No incoming calls were received on any line, including Retention. There is no evidence of a live transfer or partner handoff. The customer's cancellation request remains unresolved due to lack of contact.</t>
         </is>
       </c>
     </row>
@@ -1046,24 +1096,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line opened with a representative (Olivia) providing Robert's file number and then handing off the client to Cassie from the onboarding team, indicating a live transfer from a partner.</t>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Partner representative (Olivia) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-27 03:28 incoming call on the Onboarding line, the transcript shows a handoff: '+17082672457: I'll give you his file's number...' and '+19493157441: Thank you, Olivia. I'll take it from here.' The caller (Olivia) is transferring Robert to Cassie from onboarding, indicating a live transfer.</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>Robert Mittleman was live-transferred in by a partner rep (Olivia) to the onboarding team, where his program was explained and his payment details were set up. Subsequent outbound calls discussed his debt status and options, but Robert expressed hesitance and ultimately declined further assistance, stating he never received a loan and could not pay off the accounts. No completed incoming calls occurred on the Retention line, and several outbound attempts were made to reach him.</t>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Robert Mittleman was live-transferred in on the Onboarding line by Olivia, who provided his file number before handing him off to Cassie. Robert was onboarded and his payment information was confirmed. Later, outbound calls were made to discuss his debt program and a cancellation request, but there were no completed incoming calls on the Retention line. Ultimately, Robert expressed hesitance about the program and declined further assistance.</t>
         </is>
       </c>
     </row>
@@ -1127,24 +1187,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Onboarding line: The caller says, 'I have Ivan here. His file number is 121 7158526... Ivan, I have Xavier here, one of our best. He's going to take good care of you.' This is a clear handoff/transfer of the client to the onboarding agent.</t>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Unknown partner rep via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R8" s="5" t="inlineStr">
+          <t>Eugene</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: the caller says 'I have Ivan here' and introduces the client to Xavier for a handoff, clearly indicating a live transfer.</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (Eugene) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>The only completed call was an incoming transfer on the Onboarding line, where Ivan was handed off to the onboarding agent for program setup and first payment scheduling. No completed calls occurred on the Retention line, despite numerous outbound attempts and voicemails from agents trying to reach Ivan after a cancellation request. There is no evidence of Aspire or Resync involvement in any call. The customer was onboarded but did not engage further, and the cancellation request was not resolved via a completed retention call.</t>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Ivan Camacho was live-transferred in by a partner representative (Eugene) to the Onboarding team, where he discussed his debt management program and next steps with Xavier. There were no completed incoming calls on the Retention line, but multiple outbound attempts were made to reach Ivan, all resulting in voicemails. Ivan's cancellation request was not directly addressed in any completed call, and there is no evidence of Aspire or Resync involvement.</t>
         </is>
       </c>
     </row>
@@ -1208,24 +1278,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line opened with: 'This is Tom Miller. I have Gwen on the other line here. Her file is ready to go.' This is a clear live transfer from a partner representative.</t>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Tom Miller via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R9" s="5" t="inlineStr">
+          <t>Tom Miller</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: 'This is Tom Miller. I have Gwen on the other line here. Her file is ready to go.'</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>A partner representative (Tom Miller) from Resync transferred Gwendolyn Downs to your company via a live call on the Onboarding line, where her onboarding and payment details were discussed and confirmed. No completed incoming calls occurred on the Retention line, though several outbound attempts were made without answer. The customer was successfully onboarded and expressed gratitude for the support, but later requested cancellation. No retention conversation was completed.</t>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>Gwendolyn Downs was live-transferred in by Tom Miller from Resync on the Onboarding line, where her file and payment details were discussed and set up. There were several outbound attempts to reach her on the Retention line, but no completed incoming calls on Retention. The client expressed gratitude for support and confirmed understanding of the debt relief process. No retention intervention occurred; the main completed calls were onboarding and setup related.</t>
         </is>
       </c>
     </row>
@@ -1289,20 +1369,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary mentions Aspire or Resync, nor any indication of a partner representative handing off or transferring the client. The only completed incoming call (Onboarding line) is from Devon Smith of the Federal Lending onboarding team, directly assisting the client.</t>
-        </is>
-      </c>
+      <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="5" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>The only completed incoming call was on the Onboarding line with Devon Smith, who introduced themselves as part of the Federal Lending onboarding team. There was no mention of Aspire or Resync, nor any indication of a partner transfer or handoff in the opening transcript.</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>There was one completed incoming call on the Onboarding line, where the agent finalized the client's onboarding and explained the debt reduction process. All other calls were outbound attempts or voicemails, primarily from the Retention team, with no completed incoming calls on the Retention line. No evidence of a live transfer or partner handoff was found. The client did not answer any retention calls, and the cancellation request status remains unresolved.</t>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Varlee Forch, had one completed incoming call with the onboarding team, where the debt relief process and payment schedule were explained. No live transfer or partner handoff occurred, and there were no completed calls on the Retention line. Multiple outbound attempts were made by various agents, all resulting in voicemails. The cancellation request was not addressed in a live conversation.</t>
         </is>
       </c>
     </row>
@@ -1366,24 +1448,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Onboarding line: Gabriela (partner rep) calls in, provides file number, and is present on the line to hand off Cheryl to Dana Mohamed. Gabriela is explicitly identified as a partner, and Dana refers to the process involving Resync.</t>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Gabriela (Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R11" s="5" t="inlineStr">
+          <t>Gabriela</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-22 23:15 incoming Onboarding line call, Gabriela (likely a partner rep) calls in, provides the file number, and then leaves the call, handing Cheryl over to Dana Mohamed. This is a classic live transfer scenario, with Gabriela introducing the client and then departing.</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>Cheryl was live-transferred in by Gabriela from Resync on the Onboarding line, where onboarding details and the debt relief process were explained. Cheryl expressed some nervousness, which was addressed by Dana. No completed incoming calls occurred on the Retention line, though there were multiple outbound retention call attempts, all resulting in voicemails. The customer’s request for cancellation was not resolved via a completed retention call.</t>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>Cheryl was live-transferred by Gabriela from Resync to the onboarding team, where her onboarding and payment schedule were confirmed. Multiple outbound attempts were made by the retention team after a cancellation request, but no completed calls occurred on the retention line. The only completed call was the initial onboarding transfer; all other calls were voicemails or brief messages. Cheryl's status remains as cancellation requested, with no evidence of retention team contact.</t>
         </is>
       </c>
     </row>
@@ -1447,20 +1539,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Opening transcript shows an incoming caller (Jackson) saying, 'I'm gonna unhold the line... Corey, can you hear me?... I have Michael here on the line with me. He's my cancellation manager. He's gonna take care of you.' This indicates a live transfer/handoff. Call came in on the Retention line.</t>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Live transfer via Retention line (from Jackson)</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr"/>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Opening transcript on Retention line: 'I have Michael here on the line with me. He's my cancellation manager. He's gonna take care of you.' This indicates a partner representative (Jackson) is handing off the client to the company's cancellation manager.</t>
+        </is>
+      </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>The customer, Corey Blackman, requested cancellation and was live-transferred to a cancellation manager via the Retention line. During the call, Corey expressed dissatisfaction with the service and remained firm on his decision to cancel, despite the manager's attempts to explain the process and offer a refund. Several outbound attempts and voicemails were made, but no further contact was completed. The main outcome was a cancellation request with the client planning to follow up after further investigation.</t>
+          <t>Retention line</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>Corey Blackman requested cancellation and was live-transferred by a partner representative (Jackson) to the company's cancellation manager, Michael, on the Retention line. Corey expressed dissatisfaction and confusion about the service and decided to cancel, with Michael offering a refund and further instructions. There were several outbound attempts and voicemails, but only one completed incoming call on the Retention line. No Aspire or Resync company was named in the transfer.</t>
         </is>
       </c>
     </row>
@@ -1524,24 +1626,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line opened with a representative introducing themselves and stating, 'He’s already, like he’s all good to go, and he’s now ready, like, to basically become debt free... Xavier with him today... you can basically proceed here with him, and then you can take it from there.' This indicates a live transfer/hand-off with the client already on the line.</t>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Partner rep (possibly Aspire) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R13" s="5" t="inlineStr">
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: The caller says, 'He's already, like he's all good to go, and he's now ready, like, to basically become a debt free... Xavier with him today... you have your already onboarding department agent. So, yeah, you can basically proceed here with him, and then you can take it from there.' This indicates a partner representative is handing off the client.</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Keith Hayes, was live-transferred in by a partner rep (likely Aspire) to the Onboarding line, where the onboarding process and program details were reviewed. Multiple outbound attempts were made by your agents (mostly voicemails) to reach Keith, especially on the Retention line, but no completed incoming calls occurred on Retention. No retention conversation was completed, and the customer’s cancellation request status remains unresolved in the call history.</t>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Keith Hayes, was live-transferred in on the Onboarding line by a partner representative named Xavier, who handed him off for onboarding. There were no completed incoming calls on the Retention line, despite multiple outbound retention attempts and voicemails. Only two calls were completed: one onboarding and one brief CS call. The customer's status remains 'Cancellation Requested,' but no retention conversation was completed.</t>
         </is>
       </c>
     </row>
@@ -1605,24 +1717,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>The incoming Onboarding call opens with Cassie from the onboarding team greeting Joshua, and another party (likely a partner rep) present at the start says, 'Can you transfer me to do my auto I'm still here.' This indicates a live transfer. The call came in on the Onboarding line.</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Partner rep (likely Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R14" s="5" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-20 incoming Onboarding line call, the transcript shows a handoff: a caller says 'Can you transfer me to do my auto I'm still here', and 'Have a good day, both of you', indicating a partner (likely Resync) was transferring Joshua to Cassie from Better Lending.</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>Joshua Hing had one completed incoming call, which was a live transfer from a partner (likely Resync) to the Onboarding team, where the onboarding process and payment schedule were explained. There were no completed calls on the Retention line, but multiple outbound attempts were made, all resulting in voicemails. The customer requested cancellation, but no retention conversation was completed. The only substantive interaction was the initial onboarding call.</t>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>Joshua Hing was live-transferred in by a Resync representative to the Better Lending onboarding team, where Cassie completed the onboarding and explained the program and payment schedule. Multiple outbound attempts were made by retention agents after Joshua requested cancellation, but none were answered and no completed calls occurred on the Retention line. No further contact was made, and the cancellation was not confirmed or processed via a completed call.</t>
         </is>
       </c>
     </row>
@@ -1686,20 +1804,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls mention Aspire or Resync, nor any partner handoff; the only incoming call was a brief voicemail with no transcript.</t>
-        </is>
-      </c>
+      <c r="P15" s="3" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="5" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript mentions Aspire or Resync, nor any partner representative handing off the client. All incoming calls were voicemails or not completed.</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>There were 21 total calls, all but one were outbound attempts to reach the customer, resulting in voicemails. No completed incoming calls occurred on the Retention line or any other line. The only incoming call was a brief voicemail with no conversation. The customer did not connect with an agent, and no live transfer or partner handoff was detected.</t>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>There were 21 total calls, all of which were either outbound attempts or brief voicemails. No completed incoming calls occurred on any line, including Retention. Multiple outbound calls and voicemails were made by various agents, but there was no successful contact with the customer. No evidence of a live transfer or partner handoff was found.</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1883,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-19 18:54, an incoming call on the Onboarding line began with: 'Hi, sir. It's Harvey Washington. I have Don Gilbert here on the other line. Are you ready for the phone number?' This is a clear live transfer from a partner representative.</t>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Harvey Washington (Aspire/Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="inlineStr">
+          <t>Harvey Washington</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:54 incoming on Onboarding line: Harvey Washington says, 'I have Don Gilbert here on the other line.' This is a clear live transfer from a partner rep.</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>There was one completed live transfer from a partner (Harvey Washington) to the Onboarding line, where Don Gilbert was handed off for onboarding and debt review. Multiple outbound attempts were made by your agents, but there were no completed incoming calls on the Retention line. Most outbound calls resulted in voicemails or brief updates, with one lengthy discussion about program options and client concerns. The client expressed confusion and hesitancy about the program, and a follow-up was scheduled, but no final resolution or retention was achieved.</t>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>There were multiple outbound attempts to reach Don Gilbert, but no completed incoming calls on the Retention line. The only live transfer occurred when Harvey Washington from Aspire transferred Don to the Onboarding department to finalize his file. Most subsequent calls were outbound, with agents leaving voicemails or discussing program details and cancellation concerns. The client expressed confusion and hesitancy about the program, and a follow-up was scheduled, but no retention-line inbound calls were completed.</t>
         </is>
       </c>
     </row>
@@ -1844,20 +1974,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, or a partner handoff/transfer. All completed calls were outbound, and all incoming calls were either missed or went to voicemail.</t>
-        </is>
-      </c>
+      <c r="P17" s="3" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="5" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript shows a representative from Aspire or Resync introducing themselves or handing off the client. All completed calls are outbound, and all incoming calls are voicemails or no-answer.</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>All completed calls with Brian Vanloan were outbound, with no completed incoming calls on the Retention line. The customer requested cancellation due to dissatisfaction with loan terms, and agents provided clarification and agreed to hold the cancellation request while Brian consulted an advisor. No live transfer from Aspire or Resync occurred, and all incoming calls were missed or went to voicemail.</t>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>All completed calls with Brian Vanloan were outbound, with no completed incoming calls on the Retention line. The customer requested cancellation due to dissatisfaction with loan terms, and agents provided clarification and agreed to hold the cancellation request while Brian consulted an advisor. No live transfer from Aspire or Resync occurred; all incoming calls were missed or voicemails.</t>
         </is>
       </c>
     </row>
@@ -1921,24 +2053,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-18 20:21, incoming on Onboarding: The caller says, 'I have Corey here with me... File number 1215 4358 76... Mister Corey Parks.' The agent responds, 'I'll be taking it from here. Thank you, Max.' This is a clear live transfer from a partner (likely Aspire or Resync) handing off the client to your onboarding agent.</t>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Partner (likely Aspire/Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="inlineStr">
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-18 20:21, incoming on Onboarding: The caller says, 'Hello, Owen. I have Corey here with me. File number 1215 4358 76.' Owen replies, 'I'll be taking it from here. Thank you, Max.' This is a clear live transfer from a partner rep (Max) handing off the client.</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Corey Parks, was live transferred in by a partner (likely Aspire/Resync) to the onboarding team, where he discussed his debt situation and ultimately requested to cancel due to unaffordable payment terms. No completed calls occurred on the Retention line, though multiple outbound attempts were made to reach Corey for follow-up, all resulting in voicemails. The cancellation request was not resolved on a Retention call, and no further customer contact was completed after the initial onboarding calls.</t>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>Corey Parks was live-transferred in by a Resync representative (Max) to the onboarding team, where he discussed his debt situation and ultimately requested to cancel due to an unaffordable payment amount. Multiple outbound attempts were made by your agents, but all went to voicemail and none were completed on the Retention line. No retention conversation occurred, and the cancellation request was not resolved during these calls.</t>
         </is>
       </c>
     </row>
@@ -2002,24 +2144,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>The incoming Onboarding line call begins with a representative saying, 'I have here Tamron with me. Are you ready for the file ID?' and then hands off the client, indicating a live transfer from a partner.</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Partner representative via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line opened with a representative introducing Tamara and saying 'I have here Tamron with me. Are you ready for the file ID?' and then handing off to the Better Lending agent.</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>There was one completed incoming call on the Onboarding line, which was a live transfer from a partner representative handing off Tamara Nicklas to the onboarding agent. No completed calls occurred on the Retention line, despite 31 outbound attempts (mostly voicemails) to reach the customer regarding her cancellation request. The only successful contact was during onboarding, where the program was explained and first payment confirmed. No further live contact was made after onboarding.</t>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>There was one completed incoming call on the Onboarding line, which was a live transfer from a partner rep who did not state their company name. The rest of the 33 calls were outbound attempts and voicemails, mostly from the Retention team, but none were answered or completed. No incoming calls were completed on the Retention line. The customer was onboarded, but later requested cancellation and could not be reached for further retention discussion.</t>
         </is>
       </c>
     </row>
@@ -2083,20 +2231,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>In the 2026-06-02 18:48 incoming Retention call, Maya (from a partner) says: 'I do have with me on the line Kathleen. She wants to cancel.' and in the 18:53 call, Maya again states: 'I have Kathleen with me on.' Both are clear live transfers from a partner representative on the Retention line.</t>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Partner rep (Maya) via Retention line</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr"/>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>On both incoming Retention line calls, the caller (Maya) states 'I do have with me on the line Kathleen' and 'I have Kathleen with me on', indicating a live transfer. Maya is the partner rep handing off the client to your company, and the call is handled by your Retention team.</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>The customer, Kathleen Downen, was live-transferred in by a partner representative (Maya) on the Retention line to request cancellation. Two completed incoming Retention calls involved the partner and your agents discussing the cancellation and file details. Afterward, your agent completed an outbound call with Kathleen, confirming her cancellation due to financial hardship and assisting with the necessary paperwork. The process was completed after resolving document delivery issues.</t>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>Kathleen Downen was live-transferred from Resync (by Maya) to your Retention team to request cancellation. Two incoming Retention calls were completed, both involving the partner rep and your agents confirming the cancellation process. Outbound attempts were made, and one outbound call was completed to finalize the cancellation and resolve document issues. The client was ultimately processed for cancellation due to financial hardship.</t>
         </is>
       </c>
     </row>
@@ -2160,24 +2318,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line (2026-05-14) opened with Gabriela stating, 'I have Michelle on the line. Are you ready for the file number?' This is a clear live transfer from a partner representative, likely Aspire or Resync, handing off the client.</t>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="inlineStr">
+          <t>Gabriela</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>"This is Gabriela. I have Michelle on the line. Are you ready for the file number?" — incoming Onboarding line</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>Michelle Brooks was live-transferred by a partner rep (Aspire/Resync) to the onboarding agent, who discussed her debt resolution process and scheduled her first payment. Multiple outbound calls and voicemails were made by company agents, mostly to follow up or address cancellation requests, but no completed incoming calls occurred on the Retention line. The client requested cancellation, but no retention agent was able to reach her directly; most calls resulted in voicemails.</t>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>Michelle Brooks was live-transferred in by Gabriela from Resync on the Onboarding line, where her debt resolution process was explained and her first payment scheduled. Multiple outbound calls and voicemails were made by your agents, but there were no completed incoming calls on the Retention line. The customer requested cancellation, but no retention conversation was completed. Most subsequent contact attempts resulted in voicemails or brief messages.</t>
         </is>
       </c>
     </row>
@@ -2241,24 +2409,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-14, an incoming call on the Onboarding line began with a representative saying, 'I have a customer on the line, Gregory. His file is good to go. Are you ready for the file number?' This is a clear partner handoff/transfer.</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>Partner (unnamed) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr">
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-14, incoming call on Onboarding line: '+19419613410: I have a customer on the line, Gregory. His file is good to go. Are you ready for the file number?' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>Gregory Hoppe was live-transferred by a partner to the onboarding team, where his enrollment and first payment were set up. Later, Gregory called in directly to request cancellation and a refund, but there were no completed calls on the Retention line. Multiple outbound attempts were made to reach him, all resulting in voicemail. The customer was not retained and is seeking cancellation and a refund.</t>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>Gregory Hoppe had two completed incoming calls: one via the Onboarding line, which was a partner handoff to start onboarding, and one direct customer call to the CCB line regarding payment status and a cancellation request. There were multiple outbound attempts from the Retention team, but no completed incoming calls on the Retention line. The customer ultimately requested cancellation and a refund, but no retention conversation was completed.</t>
         </is>
       </c>
     </row>
@@ -2322,24 +2496,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Onboarding line: Caller (+12254053487) says, 'I have customer Patricia with me. The file should be good to go.' This is a clear partner handoff/transfer.</t>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Partner (likely Aspire) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R23" s="5" t="inlineStr">
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: '+12254053487: Hello, Owen. This is Adam again. I have customer Patricia with me.' Adam is handing off Patricia, indicating a live transfer.</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>Patricia Calfee was live-transferred in by a partner (likely Aspire) on the Onboarding line, where her onboarding process and payment schedule were discussed. There were no completed incoming calls on the Retention line, despite multiple outbound retention attempts (all went to voicemail). The customer requested cancellation, but no retention conversation was completed. Most outbound calls were unanswered, and only onboarding and a brief other call were completed.</t>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>Patricia Calfee was live-transferred by Adam from Aspire to your company on the Onboarding line, where she discussed her onboarding and upcoming payment. Multiple outbound attempts were made to reach her, primarily via the Retention line, but none were successful and no incoming calls were completed on Retention. The customer requested cancellation, but there was no completed retention conversation; most calls resulted in voicemails or no answer.</t>
         </is>
       </c>
     </row>
@@ -2403,24 +2587,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>"I have Norma Garcia with me on the other line" and "They're going to take it from here, and that's all yours" from the opening transcript of the 2026-05-12 incoming Onboarding line call.</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>Partner rep (Aspire/Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="inlineStr">
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: The caller says, 'I have Norma Garcia with me on the other line... They're going to take it from here, and that's all yours.' This is a clear live transfer.</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live-transferred in by a partner representative (likely Aspire or Resync) via the Onboarding line, where the onboarding process and payment details were completed. Numerous outbound attempts were made by your agents, primarily on the Retention line, but none were answered or completed. No completed incoming calls occurred on the Retention line. The customer's initial request was cancellation, but the only substantive contact was the onboarding call; all other attempts resulted in voicemails or no answer.</t>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>Norma Garcia was live-transferred in by a representative from Aspire on the Onboarding line, where she completed her onboarding for the debt relief program. Multiple outbound attempts were made by your team, but there were no completed incoming calls on the Retention line. The client did not answer any retention calls, and no retention conversation was completed. The initial onboarding was successful, but subsequent contact attempts were unsuccessful.</t>
         </is>
       </c>
     </row>
@@ -2484,24 +2674,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-12, an incoming call on the Onboarding line opened with: 'My name is Jenny Gonzales. I have here Stephanie with me. Are you ready for the file number?' This indicates a partner representative (Jenny Gonzales) was transferring Stephanie to onboarding.</t>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Partner rep (Jenny Gonzales) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R25" s="5" t="inlineStr">
+          <t>Jenny Gonzales</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-12 00:48, incoming on Onboarding line: Jenny Gonzales says, 'My name is Jenny Gonzales. I have here Stephanie with me. Are you ready for the file number?' indicating a live transfer/hand-off with the client already on the line.</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Stephanie Roy Hussey, was initially live-transferred by a partner rep (Jenny Gonzales) to onboarding, where her program details were discussed and onboarding was completed. Afterward, numerous outbound attempts were made by various agents to reach Stephanie regarding her account and possible cancellation, but no completed incoming calls occurred on the Retention line. All retention efforts were outbound, with most resulting in voicemails or brief conversations, and the customer did not re-engage. The account status remains as cancellation requested, with no evidence of retention success.</t>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>Stephanie Roy Hussey was live-transferred in by Jenny Gonzales from Resync on the Onboarding line, where her onboarding and program details were confirmed. After onboarding, there were numerous outbound attempts and completed calls from various agents, mostly regarding program updates and retention, but no completed incoming calls on the Retention line. Most outbound calls resulted in voicemails or brief conversations, and the customer did not connect on the Retention line. The overall outcome is that the customer was onboarded via live transfer, but did not complete any retention calls despite multiple outreach attempts.</t>
         </is>
       </c>
     </row>
@@ -2565,20 +2765,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, or any partner, was on the line or transferring the client. The only completed incoming call (CS Team) was initiated by the customer herself.</t>
-        </is>
-      </c>
+      <c r="P26" s="3" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="5" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call had a representative introduce themselves as being from Aspire or Resync, nor did any incoming caller explicitly state they were transferring or handing off the client. The only completed incoming call (CS Team, 2026-05-13) was the customer herself calling in, not a partner transfer.</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Eileen Fletcher, was onboarded into a debt resolution program via an outbound call. She later called in on the CS Team line to clarify her account and was advised to cancel with her previous provider (DebtBlue). There were numerous outbound attempts from the Retention line, but no completed incoming calls on Retention. No evidence of a live transfer from Aspire or Resync was found.</t>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Eileen Fletcher, was onboarded into a debt reduction program via an outbound call. She later called in herself to the CS Team to clarify her enrollment and was advised to cancel with her previous provider, DebtBlue. Multiple outbound attempts were made by the Retention team, but there were no completed incoming calls on the Retention line. No live transfer from Aspire or Resync occurred; all partner mentions were informational only.</t>
         </is>
       </c>
     </row>
@@ -2642,20 +2844,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-08, an incoming call on the Onboarding line began with a representative (Sam) saying, 'I have Kenneth with me. You ready for the account number?' and then transferring Kenneth to agent Xavier Lookman.</t>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Partner representative (Sam) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr"/>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-08, incoming Onboarding line: '+15864896056: I have Kenneth with me. You ready for the account number?' and 'Kenneth, I will let you with Xavier right now.' This is a partner handing off the client.</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Kenneth Gifford was initially live-transferred by a partner representative to the onboarding agent, where his account was set up and payment details confirmed. Later, Kenneth called the Retention line to discuss cancellation due to financial hardship, resulting in his payment being postponed and instructions to sign a document to formalize changes. Multiple outbound attempts were made by agents to reach Kenneth, but none were completed. Ultimately, the client was retained for now with a postponed payment, pending further updates.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>Kenneth Gifford was live-transferred in on the Onboarding line by a partner representative named Sam, then onboarded by Xavier Lookman. Later, Kenneth called in directly to the Retention line to discuss cancellation due to financial hardship; Levi Miller offered to postpone his payment and sent a document to formalize changes. Numerous outbound attempts were made by retention agents, but none were answered. The client was not retained during these calls, and the cancellation process was discussed.</t>
         </is>
       </c>
     </row>
@@ -2719,20 +2931,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls had a transcribable conversation or opening transcript indicating a partner (Aspire/Resync) or a live transfer; all incoming calls were either voicemails or no-answer.</t>
-        </is>
-      </c>
+      <c r="P28" s="3" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="5" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls included a representative from Aspire or Resync, nor any indication of a partner transfer. All incoming calls were either voicemails or no-answer with no mention of a partner company.</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>There were 28 total calls for this customer, all of which were either outbound attempts or incomplete incoming calls (voicemails or no-answer). No completed calls occurred on the Retention line or any other line, and there is no evidence of a live transfer or partner handoff. Multiple outbound calls were made, all resulting in voicemail or no answer, so no customer contact was achieved.</t>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>There were 28 total calls for this customer, all of which were either outbound attempts or incomplete incoming calls (voicemails or no-answer). No completed incoming calls occurred on the Retention line, and no live transfers from Aspire or Resync were detected. The agents left multiple voicemails but did not reach the customer, and no conversation took place regarding the cancellation request.</t>
         </is>
       </c>
     </row>
@@ -2796,20 +3010,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-07, Melina from Aspire called in on the Onboarding line and said, 'I have Teresa on the line. You ready for the file number?' On 2026-06-03, Jacob from Aspire Law Group called in on the Retention line and said, 'I have a mutual client with me on the line, Therese.' Both are clear live transfers from Aspire.</t>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Aspire via Onboarding line and Aspire via Retention line</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr"/>
+          <t>Melina</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-07, an incoming call on the Onboarding line began with: 'This is Leon from Better Lending onboarding team.' Melina (the partner rep) said, 'I have Teresa on the line. You ready for the file number?' and then left the call, indicating a partner live transfer.</t>
+        </is>
+      </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>The customer, Terese Vincent, was live transferred in by Aspire representatives on both the Onboarding and Retention lines. The initial onboarding call set up her debt reduction program, but later, Aspire transferred her to the Retention team to request cancellation. Terese confirmed she wanted to cancel, declining all retention offers. Multiple outbound attempts and voicemails were made, but the cancellation request was clear and handled during the live transfer.</t>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Terese Vincent, was live-transferred in by Melina from Aspire on the Onboarding line, where her onboarding and payment schedule were set up. Later, Terese called in on the Retention line with Jacob from Aspire to request cancellation, which was handled by Dean Lewis. Multiple outbound attempts were made by retention agents, but only one incoming retention call was completed. Ultimately, Terese insisted on canceling her program, declining all retention offers.</t>
         </is>
       </c>
     </row>
@@ -2873,24 +3097,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>"So I have here with me, Catherine, on the line. Let me just send you the file number." (incoming Onboarding line, 2026-05-07 03:30). This is a clear live transfer from a partner representative handing off the client.</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R30" s="5" t="inlineStr">
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>"Hi. So I have here with me, Catherine, on the line. Let me just send you the the file number." (incoming Onboarding line)</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>Catherine Rios was live-transferred in by a partner (Aspire/Resync) on the Onboarding line, where her onboarding and payment schedule were discussed. She later called the CS Team to request a payment date change, which was accommodated. Multiple outbound attempts were made by the Retention team, but no incoming calls were completed on the Retention line. The account status is cancellation requested, but no retention-line conversation occurred; most contact was via onboarding and CS.</t>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>Catherine Rios was live-transferred in by an Aspire representative on the Onboarding line, where her onboarding and payment schedule were discussed. She later called the CS Team to request a change in her payment start date, which was accommodated. Multiple outbound attempts were made by the retention team, but no completed calls occurred on the Retention line. The customer’s main requests were handled via onboarding and CS, with no successful retention intervention.</t>
         </is>
       </c>
     </row>
@@ -2954,20 +3184,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-07, the incoming Onboarding call opened with: 'This is Leon at the lending department. I have mister Floyd Hook here with me ready with the file number.' This indicates a live transfer from a partner (likely Resync) to your onboarding agent.</t>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-07 01:07, incoming on Onboarding: The caller says, 'This is Leon at the lending department. I have mister Floyd Hook here with me ready with the file number.' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>Floyd Hook was live-transferred in by a partner (Resync) to begin onboarding and had his debt reduction process explained. Later, he called in on the Retention line to request cancellation due to financial and family issues, and was informed cancellation is a process. Numerous outbound attempts were made by your agents, but none were answered. Ultimately, the client requested cancellation and did not proceed further.</t>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>Floyd Hook was initially live-transferred by a Resync representative (Leon) to the onboarding team, where his debt reduction process was explained and his first payment scheduled. Later, Floyd called the retention line to request cancellation due to financial and family medical issues, but was informed that cancellation is a process and not immediate. Numerous outbound attempts were made by agents to reach Floyd, but none were answered or completed. Ultimately, the client requested cancellation and did not proceed further.</t>
         </is>
       </c>
     </row>
@@ -3031,20 +3271,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls were completed; all calls in the log are outbound attempts or completed outbound calls. No transcript evidence of an incoming call with a partner handoff or mention of Aspire/Resync by an inbound caller.</t>
-        </is>
-      </c>
+      <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="5" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>All completed calls were outbound from company agents to the customer; there are no completed incoming calls on any line. No transcript shows an incoming caller introducing themselves as from Aspire or Resync, or as a partner transferring the client.</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>All contact attempts to James Crookshank were outbound, with no completed incoming calls on the Retention line. Agents repeatedly attempted to reach James regarding his cancellation request and program updates, leaving multiple voicemails and callback numbers. In one outbound call, James confirmed he no longer needed assistance, having resolved his debt independently, and requested no further contact. No live transfer or partner handoff occurred.</t>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>All contact attempts to James Crookshank were outbound, with no completed incoming calls on the Retention line or any other department. Agents repeatedly called regarding his cancellation request and program status, often leaving voicemails. In one outbound call, James confirmed he resolved his debt independently and requested no further contact. No live transfer or partner handoff occurred.</t>
         </is>
       </c>
     </row>
@@ -3108,20 +3350,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-06-01 18:07 (Retention line), the incoming caller introduced himself as Justin from Resync and stated, 'I have a mutual client that's requesting cancellation.' On 2026-06-03 21:18 (Retention line), the incoming caller introduced himself as Jacob from Resync and said, 'I have a mutual client that wants to cancel the program.' Both are clear live transfers from Resync.</t>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-06-01 18:07, incoming on Retention line: 'My name is Justin on a recorded line. I'm reaching out with Resync. I have a mutual client that's requesting cancellation.' On 2026-06-03 21:18, incoming on Retention line: 'This is Jacob from Resync on a recorded line. I have a mutual client that wants to cancel the program.'</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Johnny Watson, was onboarded and initially set up for a debt consolidation program, but soon after requested cancellation, stating he never enrolled and was unhappy with the process. Multiple live transfers from Resync brought cancellation requests to the Retention team, who worked with Johnny to process his refund and required documents. Several outbound and inbound calls occurred, including document signing and confirmation. Ultimately, the account was cancelled and a refund was processed for Johnny.</t>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Johnny Watson, was transferred in twice by Resync representatives (Justin and Jacob) on the Retention line, both times requesting cancellation of his account. Multiple outbound and inbound calls occurred, including several on the Retention line, with agents discussing cancellation, refund, and document signing. Johnny repeatedly stated he never enrolled and requested a refund, which was ultimately processed after several follow-ups and document completions. The case ended with the customer being refunded and the account cancelled.</t>
         </is>
       </c>
     </row>
@@ -3185,20 +3437,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-20 16:15 incoming on Retention: Caller introduces as Brandon from Aspire Law Group, states he is reaching out for a mutual client's cancellation request, and asks to transfer the client. Line: Retention.</t>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:15 incoming on Retention line: Caller introduces as 'Brandon from Aspire Law Group on a recorded line reaching out to you for a mutual client's cancellation request.'</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Retention line</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Nicholas Pitt, was transferred in via a live call from Aspire Law Group on the Retention line to request cancellation due to a denied secured loan. The Retention agent handled the cancellation request. There were multiple outbound attempts to reach Nicholas, with only one outbound and one inbound Retention call completed. The process included onboarding and follow-up, but ultimately the account moved to cancellation at the customer's request.</t>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>Nicholas Pitt's account had multiple outbound attempts and a few completed calls. The key event was an incoming live transfer on the Retention line from Brandon at Aspire Law Group, who handed Nicholas off for a cancellation request due to a denied secured loan. The client was assisted with cancellation, and there was also an onboarding call earlier. Outbound calls included voicemails and follow-ups, but at least one incoming Retention call was completed.</t>
         </is>
       </c>
     </row>
@@ -3262,24 +3524,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-05, an incoming call on the Onboarding line included Leah Tanner stating, 'I just have this file here, Benjamin m Majama, and his file is ready to go. Are you ready for the account number?' This indicates a partner handoff/transfer.</t>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Leah Tanner (Aspire/Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R35" s="5" t="inlineStr">
+          <t>Leah Tanner</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-05, an incoming call on the Onboarding line began with 'This is Leah Tanner with so I just have this file here, Benjamin m Majama, and his file is ready to go. Are you ready for the account number?' indicating a partner (Leah Tanner) was transferring the client to the onboarding agent.</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>There were two completed incoming calls: one on the Onboarding line where the partner (Leah Tanner) transferred Benjamin to your team, and one on the CS line where the customer called to cancel after a failed consolidation. No completed calls occurred on the Retention line despite numerous outbound attempts and voicemails. The customer ultimately requested cancellation, and the file was terminated without written confirmation.</t>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>There were 26 total calls for this customer, with the majority being outbound attempts (23) and only two completed incoming calls (one on Onboarding, one on CS Team). The initial onboarding was a live transfer from Aspire via Leah Tanner, and the onboarding process was completed. The customer later called the CS Team to cancel after an issue with a truck consolidation, and the file was terminated. No completed calls occurred on the Retention line despite many outbound attempts and voicemails.</t>
         </is>
       </c>
     </row>
@@ -3343,20 +3615,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-15 18:06 and 2026-05-15 18:22, incoming calls on the Retention line began with: 'This is Connor calling from Resync on a recorded line. I have a client on the line, Anthony, who requests cancellation.' and 'This is Daniel speaking on a recorded line from Resync's client care department. I have an Anthony McGriff.'</t>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>"Hello, Talia. This is Connor calling from Resync on a recorded line. I have a client on the line, Anthony, who request cancellation." (Retention line, 2026-05-15 18:06) and "Hey, Talia. This is Daniel speaking on a recorded line from Resync's client care department. I have an Anthony McGriff. He was just transferred over, but the call dropped." (Retention line, 2026-05-15 18:22)</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>Anthony McGriff was live-transferred twice by Resync representatives to the Retention line for cancellation requests. Talia Morgan from compliance handled the calls, confirmed the cancellation, and promised a confirmation email. Numerous outbound attempts and voicemails were made before and after, but the key outcome was the successful processing of Anthony's cancellation request after the live transfer. No retention was achieved; the client insisted on canceling.</t>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>Anthony McGriff was live-transferred twice by Resync representatives (Connor and Daniel) to the Retention line for cancellation assistance. Talia Morgan handled both incoming calls and ultimately processed the cancellation after confirming the client's wishes. Numerous outbound attempts and voicemails were made, but only one outbound call was completed, during which Anthony confirmed his decision to cancel. The account was cancelled as requested, and confirmation was sent.</t>
         </is>
       </c>
     </row>
@@ -3416,20 +3698,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-05, Elena called in on the Onboarding line and introduced herself, stating 'I have Christina Biron with me on the line.' On 2026-05-11, Emily from Resync called in on the Retention line and said, 'Hi, Ryan. This is Emily with Resync. I have a cancellation request for you.'</t>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>Elena (Aspire) via Onboarding line; Emily (Resync) via Retention line</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr"/>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Call #2 (2026-05-11 20:22, incoming on Retention): The incoming caller says, 'Hi, Ryan. This is Emily with Resync. I have a cancellation request for you.'</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>The customer was initially live-transferred by a partner (Aspire) for onboarding, then later live-transferred by Resync for a cancellation request. The customer spoke with a retention agent and insisted on canceling the program, expressing distrust and refusing to discuss further. Numerous outbound attempts were made by agents, but only one incoming retention call was completed. The outcome was a firm cancellation request from the customer, with no retention achieved.</t>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>Cristina Bito was initially onboarded via a live transfer from a partner (Elena) on the Onboarding line. Later, a Resync representative (Emily) live-transferred Cristina to the Retention line for a cancellation request, which was handled by Ryan Henderson. Cristina insisted on canceling her program and did not provide a reason, despite Ryan's attempts to retain her. Multiple outbound attempts and voicemails were made, but only one completed incoming Retention call occurred, resulting in the cancellation process being started.</t>
         </is>
       </c>
     </row>
@@ -3493,24 +3785,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line opened with the caller saying, 'So I have here Janine Platt with me on the line. The file is good to go. Are you ready for the phone number?' This indicates a partner representative was transferring the client.</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>Unknown partner via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R38" s="5" t="inlineStr">
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>The 2026-05-05 incoming Onboarding call opens with the caller saying 'So I have here Janine Platt with me on the line. The file is good to go. Are you ready for the phone number?', indicating a partner representative is live-transferring the client.</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>The customer was initially transferred in by a partner on the Onboarding line and completed onboarding with your agent. Later, the customer requested cancellation, prompting multiple outbound retention calls and voicemails, but no completed incoming calls on the Retention line. The customer expressed financial hardship and insisted on canceling, with agents offering to pause the account or reschedule payments. Ultimately, the customer was not retained, and all retention efforts were outbound only.</t>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>The customer was live-transferred in by a partner rep on the Onboarding line, then completed onboarding and had her first payment scheduled. Later, she requested cancellation after her debts were paid off by her son. Multiple outbound retention calls and voicemails were made, but no completed incoming calls occurred on the Retention line. The account appears to be in the process of cancellation or being placed on hold, with no successful retention conversation completed inbound.</t>
         </is>
       </c>
     </row>
@@ -3574,20 +3868,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>"Hi, Catherine. My name is Jesse. I'm calling from Aspire Law Group customer service. I have here on the line miss Maria Watson who has requested to cancel the program." (2026-05-12 incoming on Retention line)</t>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>"Hi Catherine. My name is Jesse. I'm calling from Aspire Law Group customer service. I have here on the line miss Maria Watson who has requested to cancel the program." (incoming on Retention line)</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Retention line</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>Maria Watson had multiple interactions with the company, including several inbound calls where she repeatedly requested to cancel her contract and expressed frustration about lack of response. A live transfer from Aspire Law Group to the Retention line confirmed her cancellation request. There were also several outbound attempts and completed calls from company agents, including one where cancellation was confirmed. The outcome is that Maria requested cancellation multiple times, was transferred in by a partner (Aspire), and the company acknowledged her cancellation request.</t>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>Maria Watson made multiple calls seeking to cancel her debt management contract, expressing frustration and suspicion about the process. A live transfer from Aspire Law Group brought Maria and a partner rep (Jesse) to the Retention line, where a Better Lending agent attempted to find a Spanish-speaking representative for the cancellation. Several outbound calls and voicemails were made by your agents, and one additional onboarding call involved a partner handoff. Ultimately, Maria's main concern was cancellation, and the process was initiated but required further follow-up.</t>
         </is>
       </c>
     </row>
@@ -3651,24 +3955,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line opened with the caller saying, 'I do have here with me Kathleen Cohen. She is she's all ready. Are you ready for her file number?' indicating a live transfer of the client.</t>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Partner (likely Aspire/Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R40" s="5" t="inlineStr">
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-04 incoming Onboarding line call, the transcript shows: 'I do have here with me Kathleen Cohen. She is she's all ready. Are you ready for her file number?' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live-transferred in via the Onboarding line, where her debt relief plan was set up and explained. Multiple outbound attempts were made by various agents, but there were no completed incoming calls on the Retention line. The customer later expressed a desire to cancel the program and requested no further contact, even threatening legal action if calls continued. Ultimately, the account status is cancellation requested, with no successful retention intervention.</t>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Kathleen Cohen, was live-transferred in via the Onboarding line by a partner representative named Nick. The onboarding process was completed, and Kathleen discussed her debt relief plan. Multiple outbound attempts were made by various agents, but there were no completed incoming calls on the Retention line. The customer later expressed a desire to cancel and requested no further contact, threatening legal action if calls continued.</t>
         </is>
       </c>
     </row>
@@ -3732,20 +4046,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls were completed; all calls were outbound attempts or voicemails. No mention of Aspire or Resync in any transcript or call intro.</t>
-        </is>
-      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; all calls were outbound attempts or voicemails. No Aspire/Resync mention in transcripts.</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>All contact attempts to the customer were outbound, with agents leaving multiple voicemails but never reaching the customer live. There were no completed incoming calls on any line, including Retention. The customer's request for cancellation was not resolved via a live conversation, and no partner transfer or live handoff occurred.</t>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>All contact attempts to Chuck Westerman were outbound, with agents leaving multiple voicemails but never reaching the customer live. There were no completed incoming calls on any line, including Retention, and no evidence of a live transfer from Aspire or Resync. The customer's cancellation request was not resolved via live conversation. The case shows persistent outbound effort but no successful contact.</t>
         </is>
       </c>
     </row>
@@ -3809,24 +4125,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-07 17:11, incoming on CS Team (cs): The agent introduces as 'Tammy Morgan with the compliance department' and, when asked, confirms 'With Resync.' The customer is handed off from Resync to your company to process a cancellation request.</t>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Resync via CS Team (cs) line</t>
-        </is>
-      </c>
-      <c r="R42" s="5" t="inlineStr">
+          <t>Tammy Morgan</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>The incoming call on 2026-05-07 17:11 to the CS Team line opened with: 'This is Tammy Morgan with the compliance department.' When asked, she clarified, 'With Resync.' This indicates the call was from a Resync representative, and the client was already on the line to discuss cancellation.</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Resync via CS Team line</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>Theresa Weidman made several incoming calls to resolve an account issue and ultimately requested cancellation, citing dissatisfaction and a mistaken account inclusion. The only live transfer was from Resync via the CS Team line, where Theresa formally requested to cancel her program. Multiple outbound attempts were made by your agents, but none were completed on the Retention line. The customer was not retained and pursued cancellation after expressing frustration with the process.</t>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>Theresa Weidman made several incoming calls to resolve issues with her account, primarily regarding the inclusion of an unwanted creditor. She ultimately requested cancellation of her program, which was initiated by Ben Harris from Resync. The only live transfer was from a Resync compliance agent to process her cancellation. Numerous outbound attempts were made by your team, but there were no completed incoming calls on the Retention line. The customer was not retained.</t>
         </is>
       </c>
     </row>
@@ -3890,16 +4216,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call had an Aspire or Resync representative, nor any mention of a partner handoff or transfer. The only completed incoming call (Retention line, 2026-06-01) was a direct client call, with Dean Lewis introducing himself as a compliance manager and no mention of Aspire/Resync or a transfer.</t>
-        </is>
-      </c>
+      <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>There were 23 total calls, mostly outbound attempts with only three completed calls: one incoming on the Retention line and two outbound. The only completed incoming call was a direct client call, not a partner transfer. Most outbound calls went to voicemail. The client requested cancellation, and the team made repeated attempts to reach them, but there was no evidence of a live transfer or partner involvement.</t>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates a caller from Aspire or Resync, nor any partner representative handing off or transferring the client. The only completed incoming call (on Retention) was a direct call with no mention of a partner or transfer.</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>The customer received numerous outbound call attempts, mostly resulting in voicemails. Only one incoming call was completed on the Retention line, but it was a direct call with no partner transfer involved. There is no evidence of a live transfer from Aspire or Resync. The overall outcome is that the customer was difficult to reach, with most contact attempts unsuccessful, and the only completed conversations were direct, not partner-transferred.</t>
         </is>
       </c>
     </row>
@@ -3963,16 +4291,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there any mention of a partner company or a handoff/transfer. The only completed incoming call (Retention line, 2026-05-25) was directly from a Better Path Lending accounts manager, not a partner.</t>
-        </is>
-      </c>
+      <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Jesus Portillo, requested cancellation. Numerous outbound calls and voicemails were made by agents, mostly on the Retention line, with only one completed incoming call on the Retention line. In that call, the agent attempted to discuss a contract, but the customer denied any agreement and insisted on cancellation. There is no evidence of a live transfer or partner handoff; all contact was direct between the company and the customer.</t>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary mentions Aspire or Resync, nor any partner representative handing off or transferring the client. The only completed incoming call (on Retention) was from Dean Lewis, an internal accounts manager, not a partner.</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>There were 30 total calls, with 28 outbound attempts and only 3 completed calls (2 outbound, 1 incoming). The only completed incoming call was on the Retention line, where the agent attempted to discuss a loan contract, but the customer denied any involvement and insisted on cancellation. No evidence of a live transfer from Aspire or Resync was found. The customer did not engage with most outreach attempts, and ultimately requested cancellation.</t>
         </is>
       </c>
     </row>
@@ -4036,16 +4366,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript mentions Aspire or Resync, nor does any caller indicate they are a partner handing off or transferring the client. Both completed incoming calls are directly from the customer (Grace Turner) to the Retention line and a follow-up from the same agent, with no evidence of a partner transfer.</t>
-        </is>
-      </c>
+      <c r="P45" s="3" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>Grace Turner repeatedly attempted to contact her original representatives to cancel her transaction but was unsuccessful. She called the Retention line directly and spoke with Katherine Adams, who confirmed the communication issues and explained that the cancellation grace period had expired. Multiple outbound calls and voicemails were made by various agents to follow up, but there were no further completed calls. Ultimately, Grace was not able to cancel due to being outside the allowed period, and her frustration with the lack of communication remained unresolved.</t>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Neither incoming call transcript mentions Aspire or Resync, nor does the caller indicate they are a partner transferring the client. Both calls are direct from the customer to the Retention line and handled by Katherine Adams, a compliance manager with Better Path Lending.</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>Grace Turner called in directly to request cancellation due to lack of communication from her original representatives. Katherine Adams, a compliance manager, handled both completed incoming calls, confirming Grace was outside the cancellation grace period and offering further assistance. No live transfer from Aspire or Resync occurred. Numerous outbound attempts resulted only in voicemails, and the customer was not retained.</t>
         </is>
       </c>
     </row>
@@ -4109,16 +4441,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>Neither incoming call mentions Aspire or Resync, nor does the caller indicate they are a partner transferring a client. The first call is in a foreign language and ends abruptly. The second call is a customer trying to reach someone named Travis, with no mention of a partner handoff.</t>
-        </is>
-      </c>
+      <c r="P46" s="3" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>There were 36 total calls, with the majority being outbound attempts (mostly voicemails) from your agents to the customer. Only three calls were completed, including one on the Retention line. The two completed incoming calls were from the customer directly, not a partner, and involved communication issues or requests to reach a specific person. No evidence of a live transfer or partner handoff was found. The customer's cancellation request status remains unresolved due to lack of successful engagement.</t>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Neither incoming call mentions Aspire or Resync, nor does the caller identify as a partner or state they are transferring a client. The first call is a language barrier, the second is a customer seeking help with no mention of a partner transfer.</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>There were 36 total calls, with the vast majority being outbound attempts that went to voicemail. Only three calls were completed, two on 'other' lines and one on the Retention line. None of the incoming calls were live transfers from Aspire or Resync; the completed Retention call was a direct customer call. The customer requested cancellation, and agents made repeated unsuccessful attempts to reach them.</t>
         </is>
       </c>
     </row>
@@ -4182,20 +4516,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Retention line opened with 'This is Caleb from Aspire Law Group on a recorded line... I do have miss Terry Bell here. She just wants to go ahead and cancel.'</t>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
+          <t>Caleb</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Opening transcript: 'This is Caleb from Aspire Law Group on a recorded line... I do have miss Terry Bell here. She just wants to go ahead and cancel.' Incoming call came in on Retention line.</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Retention line</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr"/>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>There was one completed incoming call on the Retention line, which was a live transfer from Aspire Law Group where the client, Terri Bell, requested cancellation due to misunderstanding the program. All other 28 calls were outbound attempts or voicemails from various agents, with no additional completed conversations. The outcome was that the client was transferred in for cancellation, and no further contact was made despite multiple outbound attempts.</t>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>Aspire Law Group representative Caleb called in on the Retention line to transfer Terri Bell, who wanted to cancel her program due to misunderstanding it as a loan. The call was completed and Talia Morgan from compliance assisted, preparing to transfer Terri to the compliance team. There were numerous outbound attempts and voicemails left by your agents, but only one completed incoming call on the Retention line. The client was not retained and requested cancellation.</t>
         </is>
       </c>
     </row>
@@ -4259,20 +4603,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Retention line opened with: 'Hello, Levi. This is Alexander with Resync. I have Heidi that's requested to cancel.' (2026-05-15 18:17, Retention line).</t>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Retention line: Caller introduced as 'Alexander with Resync. I have Heidi that's requested to cancel.'</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr"/>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>A live transfer from Resync was received on the Retention line, with the partner representative handing off Heidi for a cancellation request. Multiple outbound calls and voicemails followed, with agents discussing cancellation, financial hardship, and postponement of payments. The customer repeatedly requested cancellation due to loss of income, and agents confirmed the account was on hold and no payments would be deducted. There was one completed incoming Retention call and several outbound attempts, with no evidence of retention success.</t>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>Heidi Terrazas was live-transferred in by Alexander from Resync on the Retention line, requesting cancellation and expressing confusion about her enrollment. After the transfer, multiple outbound calls were made by your agents to discuss her situation, confirm her cancellation request, and address her financial hardship due to loss of disability income. The client was informed that no payments would be deducted and her account was placed on hold, with follow-ups scheduled. Ultimately, the client was not retained and the process moved toward cancellation.</t>
         </is>
       </c>
     </row>
@@ -4336,20 +4690,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls with transcribable conversations; no mention of Aspire or Resync in any transcript or call log entry.</t>
-        </is>
-      </c>
+      <c r="P49" s="3" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; all calls were outbound attempts or voicemails, and there is no mention of Aspire or Resync in any transcript or call log.</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>All calls to this customer were outbound attempts, primarily voicemails left by various agents across Retention, CS, and NSF departments. There were no completed incoming calls on any line, including Retention, and no conversations took place. The customer did not answer any calls, and no live transfer from Aspire or Resync occurred. The cancellation request remains unresolved due to lack of contact.</t>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>There were 27 total calls, all of which were outbound attempts or voicemails from various agents. No incoming calls were completed on any line, including the Retention line, and there is no evidence of a live transfer from Aspire or Resync. The customer did not answer any calls, and no conversation took place. The cancellation request remains unresolved due to lack of contact.</t>
         </is>
       </c>
     </row>
@@ -4413,20 +4769,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>Alexander with Resync called in on the Retention line and stated: 'I've got Karen Tushton that's requested to cancel the program due to not being able to afford the payments. Whenever you're ready for the transfer, let me know.'</t>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Alexander with Resync called in on the Retention line and stated, 'This is Alexander with Resync on a recorded line. I've got Karen Tushton that's requested to cancel the program due to not being able to afford the payments. Whenever you're ready for the transfer, let me know.'</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R50" s="2" t="inlineStr"/>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>Karen Touchton's cancellation request was live-transferred by Resync to the Retention line, where the compliance manager discussed her affordability concerns. Multiple outbound attempts were made to follow up, with some completed outbound calls and several voicemails left. The account was set to remain active until June 8, with no payments drafted, pending a final decision. The process involved both inbound and outbound retention efforts, with the main issue being the customer's inability to afford the program.</t>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>Karen Touchton requested cancellation due to unaffordable payments. The only completed incoming call was a live transfer from Resync, where Alexander handed off the client to your agent. Multiple outbound attempts were made, and four outbound calls were completed, including follow-ups about the cancellation process. The account must remain active until June 8, with no payments drafted, and a follow-up is scheduled to finalize the cancellation if Karen's financial situation does not improve.</t>
         </is>
       </c>
     </row>
@@ -4490,16 +4856,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>None of the incoming calls on any line (CS Team or Retention) include an introduction or statement from a representative indicating they are from Aspire or Resync, nor do they mention a partner handing off or transferring the client. All incoming calls are directly from the customer or someone calling on their behalf, asking for specific agents or support.</t>
-        </is>
-      </c>
+      <c r="P51" s="3" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Kenita Crader, made multiple calls to customer support regarding document submission issues and later requested to cancel her debt relief program. Several outbound and inbound calls occurred, including one completed call on the Retention line where the cancellation process was discussed and a payment pause was arranged. Ultimately, the account was placed on hold for thirty days with no payments deducted, and a follow-up was scheduled to confirm the cancellation.</t>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>None of the incoming calls on any line (CS Team or Retention) include an introduction from a representative stating they are from Aspire or Resync, nor do they indicate a partner is transferring the client. All incoming calls are direct from the customer or a person asking for specific agents, with no mention of a partner handoff.</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Kenita Crader, made multiple calls to customer support regarding issues with document submission and ultimately requested to cancel her debt relief program. Several outbound and inbound calls occurred, including one completed call on the Retention line where the agent paused her payments for 30 days pending final cancellation. No live transfer from Aspire or Resync occurred; all calls were direct interactions between the customer and the company’s agents.</t>
         </is>
       </c>
     </row>
@@ -4563,20 +4931,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>None of the incoming calls mention Aspire or Resync, nor do they indicate a partner or representative is transferring the client. All incoming calls are direct from the customer or a family member, requesting to speak with a specific agent (Joey Hackman).</t>
-        </is>
-      </c>
+      <c r="P52" s="3" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="5" t="inlineStr">
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>None of the incoming calls mention Aspire or Resync, nor do the callers identify as a partner representative or indicate a client transfer. All incoming calls are direct from the customer or their spouse, requesting to speak to a specific agent (Joey Heckman) via the CCB (other) line.</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>There were 32 total calls, with 3 completed incoming calls, all on the 'CCB (other)' line, and 28 outbound attempts, mostly resulting in voicemails. No completed calls occurred on the Retention line, and no live transfers from Aspire or Resync were detected. The incoming calls were direct requests from the customer or a family member to speak with agent Joey Hackman, with no evidence of partner handoff or live transfer. The customer's cancellation request was not resolved via a completed retention call.</t>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>There were 32 total calls, with 3 completed incoming calls on the CCB (other) line and no completed calls on the Retention line. All incoming calls were from the customer or their spouse, seeking to reach agent Joey Heckman. Numerous outbound attempts were made by various agents, but none were answered. No live transfer from Aspire or Resync occurred, and no retention conversation was completed.</t>
         </is>
       </c>
     </row>
@@ -4640,20 +5010,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>There are no completed incoming calls on any line where the opening transcript or summary indicates a partner (Aspire/Resync) representative was on the line or transferring the client. The only completed incoming call (2026-05-07 21:04 on CS Team) does not mention Aspire/Resync or a partner transfer in its summary or transcript.</t>
-        </is>
-      </c>
+      <c r="P53" s="3" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="5" t="inlineStr">
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed on the Onboarding, Retention, or CS lines where a partner representative from Aspire or Resync introduced themselves or transferred the client. The only completed incoming call was on the CS Team line and does not mention a partner transfer in the summary.</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>All completed calls were outbound, with no completed incoming calls on the Retention line. The customer, Sheri Kunz, repeatedly expressed confusion and concern about the debt consolidation program, citing identity theft and a preference to cancel. Multiple agents attempted to clarify the situation, provide documentation, and offer to postpone payments, but Sheri remained intent on cancellation. Numerous outbound attempts resulted in voicemails, and ultimately, the deal was cancelled.</t>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>All completed calls were outbound, with no completed incoming calls on the Retention line. The client, Sheri Kunz, repeatedly expressed confusion about the debt consolidation program and ultimately wished to cancel, citing identity theft and existing arrangements with another company. Multiple outbound attempts were made, but the client was not retained and the deal was cancelled. No live transfer from Aspire or Resync was detected.</t>
         </is>
       </c>
     </row>
@@ -4717,24 +5089,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line opened with 'This is Jackson. I have Athena here with me. Her file is good to go. Are you ready for the file number?' indicating a partner (Jackson) was transferring Athena to your company.</t>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>"This is Jackson. I have Athena here with me. Her file is good to go. Are you ready for the file number?" — incoming Onboarding line</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Onboarding line</t>
         </is>
       </c>
-      <c r="R54" s="5" t="inlineStr">
+      <c r="T54" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>Athena Taylor was live transferred by a partner (Aspire) on the Onboarding line, where her onboarding and payment details were confirmed. Multiple outbound attempts were made to reach her on the Retention line, but none were completed; only voicemails were left. There were no completed incoming calls on the Retention line. The only completed call was the initial onboarding transfer, and follow-up efforts did not reach the client directly.</t>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>Athena Taylor was live-transferred in by Jackson from Aspire on the Onboarding line, where her file was confirmed and the onboarding process explained. She was instructed on payment and next steps. Multiple outbound attempts were made to reach her on the Retention line, but none were completed; only voicemails were left. There were no completed incoming calls on the Retention line, and no evidence of cancellation or retention resolution.</t>
         </is>
       </c>
     </row>
@@ -4793,21 +5175,35 @@
       <c r="N55" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>No mention of Aspire or Resync in any incoming call opening transcript. The only incoming calls were from internal company agents (Devon from onboarding, Rick Miller from retention), and there is no indication of a partner handoff or transfer.</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>Jamie Gonzales</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-05 incoming Onboarding call, the opening transcript shows Jamie Gonzales (partner rep) saying, 'So I have here Glynian, and she is my special client. So please, Devon, I need you to take care of my special client, please.' This is a clear live transfer from a partner rep to the onboarding team via the Onboarding line.</t>
+        </is>
+      </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>The customer had two completed incoming calls: one on the Onboarding line and one brief call on the Retention line. There were numerous outbound attempts (17), all resulting in voicemails or no answer, and no completed outbound conversations. No evidence of a partner (Aspire/Resync) live transfer was found. The overall outcome appears to be initial onboarding and attempted retention follow-up, but no successful retention or cancellation conversation.</t>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>Lillian N. Raini was live-transferred in by Jamie Gonzales from Aspire to the onboarding team, where her debt reduction process was explained and her first payment scheduled. Multiple outbound attempts were made by various agents, mostly leaving voicemails, but there were no successful outbound connections. One brief incoming call was completed on the Retention line, but it lasted only 2 seconds and did not result in a substantive conversation. The client was onboarded but did not engage further despite follow-up attempts.</t>
         </is>
       </c>
     </row>
@@ -4871,16 +5267,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>No transcribable conversations; all incoming calls to Onboarding line were no-answer or voicemail with no transcript. No mention of Aspire/Resync or any partner transfer.</t>
-        </is>
-      </c>
+      <c r="P56" s="3" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>There were four incoming calls to the Onboarding line, all of which were either not answered or resulted in a voicemail with no transcript. No completed calls occurred on any line, and there were no outbound call attempts. There is no evidence of a live transfer or partner handoff. The customer's deal status is cancelled, but no direct contact was made.</t>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>All calls were incoming to the Onboarding line but resulted in no answer or voicemail; there were no transcribable conversations or introductions mentioning Aspire, Resync, or a partner transfer.</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>There were four incoming calls to the Onboarding line for Katie Murry, but none were answered or completed—three resulted in no answer and one in voicemail. No outbound calls or attempts were made. There were no completed calls on the Retention line, and no evidence of a live transfer or partner involvement. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -4944,20 +5342,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>The opening transcript of the 2026-05-30 incoming Onboarding call shows Mark (likely from a partner, possibly Resync/Aspire) handing off David to Vera for onboarding, explicitly stating 'She's gonna onboard you to everything. I'm gonna hang up. You'll wait.' This is a clear live transfer. The call came in on the Onboarding line.</t>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>Partner (Mark, likely Resync/Aspire) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr"/>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-30 19:53 incoming Onboarding call, the opening transcript shows Mark (a partner rep) introducing himself and handing off David to Vera for onboarding, saying 'She's gonna onboard you to everything. I'm gonna hang up. You'll wait.' This is a clear live transfer from a partner rep.</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>David was initially onboarded via a live transfer from a partner representative. He later requested cancellation, citing misinformation and being up to date on payments. Multiple retention-line calls confirmed his cancellation request and provided email confirmation. Despite reassurances about credit score impact, David insisted on canceling, and the file was closed. Outbound and inbound calls were made, including voicemails and follow-up confirmations.</t>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>David Vas Nunes was live-transferred in by a Resync rep for onboarding, and his program was set up with a payment plan. Shortly after, David requested cancellation, citing misinformation and being up to date on payments. Multiple calls on the Retention line confirmed his cancellation, and he was reassured about the process and potential credit impacts. The account was ultimately canceled, with confirmation promised via email.</t>
         </is>
       </c>
     </row>
@@ -5021,20 +5429,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line involved a partner representative providing client files and discussing Aspire as the partner. The caller provided file numbers and asked the agent to handle both Francis Welch and Elizabeth Belcher, indicating a live transfer/partner handoff.</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>Partner representative via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr"/>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line; the caller provides client file numbers and confirms handling files for Francis Welch and Elizabeth, indicating a partner handoff/transfer.</t>
+        </is>
+      </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>There were two calls: one brief voicemail and one completed incoming call on the Onboarding line. The completed call involved a partner representative transferring files for both Francis Welch and Elizabeth Belcher, with Aspire mentioned as the debt-relief partner. Payment schedules and program details were discussed, but Elizabeth was not present on the call. Ultimately, the deal was cancelled.</t>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>There were two incoming calls, one of which was a completed live transfer from Aspire on the Onboarding line. The partner representative provided client details for both Francis Welch and Elizabeth Belcher, confirming a handoff. No outbound calls or completed calls on the Retention line occurred. The agent clarified payment schedules and onboarding steps, but ultimately the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -5098,20 +5512,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line involved a partner representative providing client files and discussing Aspire as the partner. The caller provided file numbers and asked the agent to handle both Francis Welch and Elizabeth Belcher, indicating a live transfer/partner handoff.</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>Partner representative via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line; the caller provides client file numbers and confirms handling files for Francis Welch and Elizabeth, indicating a partner handoff/transfer.</t>
+        </is>
+      </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>There were two calls: one brief voicemail and one completed incoming call on the Onboarding line. The completed call involved a partner representative transferring files for both Francis Welch and Elizabeth Belcher, with Aspire mentioned as the debt-relief partner. Payment schedules and program details were discussed, but Elizabeth was not present on the call. Ultimately, the deal was cancelled.</t>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>There were two incoming calls, one of which was a completed live transfer from Aspire on the Onboarding line. The partner representative provided client details for both Francis Welch and Elizabeth Belcher, confirming a handoff. No outbound calls or completed calls on the Retention line occurred. The agent clarified payment schedules and onboarding steps, but ultimately the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -5175,20 +5595,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there an explicit partner handoff or transfer. The incoming calls are from onboarding and account services, but no mention of Aspire/Resync or a partner transfer.</t>
-        </is>
-      </c>
+      <c r="P60" s="3" t="inlineStr"/>
       <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="5" t="inlineStr">
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>None of the incoming calls included an introduction from a representative stating they were from Aspire or Resync, nor did any caller explicitly state they were transferring the client from a partner company. The opening lines on the Onboarding and Retention calls were from internal agents (Cassie, Adam) and the customer or their associate (Sarah), with no mention of Aspire/Resync or a partner transfer.</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>Richard Bosley contacted the company to cancel his debt relief contract due to dissatisfaction with the terms and perceived misinformation about interest rates. He was advised on his right to cancel and directed to the compliance department. Outbound calls were made to confirm his cancellation, and Richard insisted on ending the agreement. The contract was ultimately cancelled, and Richard was told he would receive follow-up communication. No incoming calls were completed on the Retention line.</t>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>Richard Bosley contacted the company to cancel his debt relief contract, expressing dissatisfaction with the program's terms. Multiple calls occurred, including one with an onboarding agent and follow-ups with retention and compliance staff. No live transfer from Aspire or Resync was detected. The contract was ultimately canceled, and Richard was informed that someone would follow up with him. There were outbound attempts and completions, but no completed incoming calls on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -5252,24 +5674,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-29 at 21:25, an incoming call on the Onboarding line opened with Mike introducing Ronald to Cassie, stating, 'This is Mike, and I have Ronald with me on the line...' and 'I will be leaving you with Cassie.' This is a clear partner handoff/transfer.</t>
-        </is>
-      </c>
+      <c r="P61" s="3" t="inlineStr"/>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>Partner agent Mike via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R61" s="5" t="inlineStr">
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-29 21:25, incoming Onboarding line: Mike introduced himself ('This is Mike, and I have Ronald with me on the line... I will be leaving you with Cassie.') and handed off Ronald to Cassie, indicating a partner live transfer.</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep (Mike) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T61" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>Ronald was transferred in by a partner agent (Mike) for onboarding, and later called in again to request cancellation due to affordability issues. Multiple outbound attempts were made by your team, but there were no completed incoming calls on the Retention line. Ultimately, Ronald spoke with a compliance manager on an outbound retention call and confirmed his cancellation request, which was processed. No Aspire/Resync keywords were detected in any transcript.</t>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>Ronald Martinez was live-transferred in by a partner rep (Mike) to the onboarding team, where he completed onboarding steps with Cassie and later Donya. Ronald expressed he could not afford the loan and requested cancellation, which was finalized in an outbound call with the compliance manager. There were multiple outbound attempts and voicemails, but no completed incoming calls on the Retention line. The deal was ultimately cancelled per Ronald's request.</t>
         </is>
       </c>
     </row>
@@ -5333,24 +5761,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-28 incoming call on the Onboarding line, the transcript shows a handoff: '+19493157441: I'll take it from here, Catherine.' The summary confirms Resync was involved and the client was transferred to Better Lending.</t>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-28 21:05 incoming Onboarding line call, the opening transcript shows a partner representative (Catherine) on the line with the client, who then says 'I'll take it from here, Catherine.' This is a clear live transfer.</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R62" s="5" t="inlineStr">
+      <c r="T62" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr">
-        <is>
-          <t>The only completed call was an incoming live transfer from Resync on the Onboarding line, where the onboarding process and payment plan were explained to the client. No completed calls occurred on the Retention line, and two outbound attempts to reach the client were unsuccessful (voicemails left). Ultimately, the deal was cancelled. No retention intervention was completed.</t>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>The client was live-transferred from Resync via the Onboarding line, where the onboarding process was explained and the payment plan was set up. There were no completed calls on the Retention line, and all outbound attempts went to voicemail. The client ultimately cancelled after onboarding, with no further successful contact.</t>
         </is>
       </c>
     </row>
@@ -5414,24 +5852,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>The incoming Onboarding line call opened with the caller saying 'I got Bobby,' indicating a handoff/transfer. The call involved confirming the phone number and details for Bobby, and the process was explained as involving Resync.</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>"I got Bobby." (Onboarding line) — The opening transcript shows a handoff/introduction of the client, indicating a live transfer, and Aspire/Resync keywords were detected in the transcript.</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
         <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R63" s="5" t="inlineStr">
+      <c r="T63" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Bobbi Rowland, was transferred in via a live call from Resync on the Onboarding line, where the program and payment details were explained and confirmed. Subsequent outbound attempts were made, but no completed calls occurred on the Retention line. Ultimately, the customer canceled the program due to concerns about company legitimacy, and the cancellation was processed and confirmed by an agent. No retention intervention was completed, and the customer will receive a cancellation letter.</t>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Bobbi Rowland, was live-transferred in via the Onboarding line, with the partner (Resync) introducing the client for enrollment and confirming payment details. Several outbound attempts were made by your agents, but there were no completed incoming calls on the Retention line. Ultimately, the customer canceled the program after expressing concerns about company legitimacy, and the cancellation was confirmed by your agent. No retention-line conversations were completed; most other calls were voicemails or brief attempts.</t>
         </is>
       </c>
     </row>
@@ -5495,20 +5939,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript contains an introduction from Aspire or Resync, nor any explicit mention of a partner handing off or transferring the client. All introductions are from Better Lending or its agents, and the only onboarding call is from a Better Lending team member.</t>
-        </is>
-      </c>
+      <c r="P64" s="3" t="inlineStr"/>
       <c r="Q64" s="2" t="inlineStr"/>
-      <c r="R64" s="5" t="inlineStr">
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates a caller introducing themselves as being from Aspire or Resync, nor any explicit mention of a partner transferring the client. All introductions are from Better Lending staff or the customer directly.</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr">
-        <is>
-          <t>Evelyn Saguid enrolled in a debt resolution program but quickly requested cancellation, citing issues with her previous provider and a desire to avoid further payments. She made multiple inbound calls to customer service and other lines, expressing frustration with delays and lack of confirmation. Despite several outbound attempts by agents, no completed calls occurred on the Retention line. Ultimately, her cancellation was processed after repeated follow-ups, but the experience was marked by communication issues and customer dissatisfaction.</t>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>Evelyn Saguid enrolled in a debt resolution program but quickly requested cancellation, making multiple calls to Better Lending's customer service and onboarding lines. She repeatedly expressed frustration over delays, lack of confirmation, and poor communication, including being hung up on by an agent. No incoming calls were completed on the Retention line, but there was one completed outbound retention call where her cancellation was confirmed. Ultimately, her deal was cancelled after persistent follow-up.</t>
         </is>
       </c>
     </row>
@@ -5572,20 +6018,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Onboarding line: Jason Todd says, 'This is Jason Todd. I'm here with Renee.' Owen (your agent) responds, 'I'll be taking it from here, Jason.' This is a clear live transfer/hand-off.</t>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Jason Todd via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="inlineStr"/>
+          <t>Jason Todd</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line; opening transcript: '+13343061267: This is Jason Todd. I'm here with Renee.' Jason introduces himself and hands off Renee to Owen, who says 'I'll be taking it from here, Jason.'</t>
+        </is>
+      </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>The only completed call was an incoming live transfer on the Onboarding line, where Jason Todd (likely from a partner such as Resync) handed off Renee Lee to your onboarding agent. Renee was onboarded, had her questions answered, and was given next steps and contact info. There were no completed calls on the Retention line, and no outbound calls or attempts. The deal was ultimately cancelled.</t>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>Renea Lee was live-transferred by Jason Todd from Resync to the onboarding agent Owen Saxe, who explained the program and confirmed details with both Jason and Renee. Renee asked questions about the process and was reassured about creditor actions and prepayment penalties. No calls were completed on the Retention line, and there were no outbound attempts. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -5649,20 +6105,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls mention Aspire or Resync, nor any partner handoff; all completed calls are outbound, and the only incoming call was a brief voicemail with no transcript.</t>
-        </is>
-      </c>
+      <c r="P66" s="3" t="inlineStr"/>
       <c r="Q66" s="2" t="inlineStr"/>
-      <c r="R66" s="5" t="inlineStr">
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; all completed calls were outbound. No transcript or intro lines from Aspire or Resync, and no evidence of a partner transfer in any call.</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr">
-        <is>
-          <t>All completed contact with George McDowell Jr was via outbound calls. The agent reached George on an outbound Retention line call, during which George insisted on canceling his agreement due to dissatisfaction with the debt repayment process. The agent processed the cancellation and confirmed follow-up by email. No incoming Retention line calls were completed, and there was no evidence of a live transfer from Aspire or Resync.</t>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>All completed calls were outbound, with no completed incoming calls on the Retention line. The agent reached George via outbound call, during which George requested to cancel due to dissatisfaction with the debt repayment plan. The agent processed the cancellation as requested. Other calls were voicemails or brief attempts, and there is no evidence of a live transfer or partner involvement.</t>
         </is>
       </c>
     </row>
@@ -5726,20 +6184,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>"Hello, Devon. This is David. I have my customer, Ada, in here." (incoming Onboarding line); "Hello, Dean. This is Andrew from Resync on a recorded line. I have a client requesting to cancel." (incoming Retention line)</t>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Resync via Onboarding line and Resync via Retention line</t>
-        </is>
-      </c>
-      <c r="R67" s="2" t="inlineStr"/>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>"Hello, Dean. This is Andrew from Resync on a recorded line. I have a client requesting to cancel." (incoming on Retention line)</t>
+        </is>
+      </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>Ada Clay was onboarded through a live transfer from Resync, with her payment plan and program details confirmed. Later, another live transfer from Resync on the Retention line was made to request cancellation, as Ada's family would help pay her debts. Despite an outbound retention call attempting to retain her, Ada insisted on canceling, and the cancellation was processed. There were both inbound and outbound calls, with the deal ultimately cancelled.</t>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>Ada Clay was onboarded via a live transfer from Resync, with her initial payment and program details confirmed. Later, Andrew from Resync called in on the Retention line to request a cancellation for Ada, which was processed after confirming her family would help pay off her debts. Outbound calls were made to Ada for follow-up and to finalize the cancellation. The account was ultimately cancelled at Ada's request.</t>
         </is>
       </c>
     </row>
@@ -5803,20 +6271,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls featured an Aspire or Resync representative, nor any explicit partner handoff/transfer. All incoming calls were either voicemails, in-progress with no transcript, or no-answer, and none mentioned Aspire/Resync or a transfer.</t>
-        </is>
-      </c>
+      <c r="P68" s="3" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="5" t="inlineStr">
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, or any partner transfer. All incoming calls were either voicemails, in-progress with no transcript, or no-answer.</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr">
-        <is>
-          <t>The only completed call was an outbound retention call where Marcelle Bobo requested cancellation for both her and her husband's accounts, citing dissatisfaction with the program and concerns about fees and credit impact. The agent confirmed the cancellation process would be started. No incoming retention-line calls were completed, and no live transfers from Aspire or Resync occurred. Other incoming calls were either voicemails or unanswered.</t>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>There were four calls in total: two incoming calls (one voicemail, one in-progress with no transcript), one incoming no-answer, and one completed outbound call from the Retention department. No incoming calls were completed on the Retention line. The completed outbound call resulted in the customer, Marcelle Bobo, confirming her wish to cancel her and her husband's accounts due to dissatisfaction with the program. The agent processed the cancellation as requested.</t>
         </is>
       </c>
     </row>
@@ -5880,20 +6350,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls featured an Aspire or Resync representative, nor any explicit partner handoff/transfer. All incoming calls were either voicemails, in-progress with no transcript, or no-answer, and none mentioned Aspire/Resync or a transfer.</t>
-        </is>
-      </c>
+      <c r="P69" s="3" t="inlineStr"/>
       <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="5" t="inlineStr">
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, or any partner transfer. All incoming calls were either voicemails, in-progress with no transcript, or no-answer.</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S69" s="2" t="inlineStr">
-        <is>
-          <t>The only completed call was an outbound retention call where Marcelle Bobo requested cancellation for both her and her husband's accounts, citing dissatisfaction with the program and concerns about fees and credit impact. The agent confirmed the cancellation process would be started. No incoming retention-line calls were completed, and no live transfers from Aspire or Resync occurred. Other incoming calls were either voicemails or unanswered.</t>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>There were four calls in total: two incoming calls (one voicemail, one in-progress with no transcript), one incoming no-answer, and one completed outbound call from the Retention department. No incoming calls were completed on the Retention line. The completed outbound call resulted in the customer, Marcelle Bobo, confirming her wish to cancel her and her husband's accounts due to dissatisfaction with the program. The agent processed the cancellation as requested.</t>
         </is>
       </c>
     </row>
@@ -5952,29 +6424,23 @@
       <c r="N70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O70" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>Owen Saxe (Onboarding) explains the onboarding process involving two steps: debt reduction by Resync and payoff by Better Lending. The incoming call was on the Onboarding line, and Resync is referenced as part of the process.</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>Onboarding line (Resync referenced)</t>
-        </is>
-      </c>
-      <c r="R70" s="5" t="inlineStr">
-        <is>
-          <t>OB done — no calls on retention line</t>
-        </is>
-      </c>
-      <c r="S70" s="2" t="inlineStr">
-        <is>
-          <t>Gerald Havron had one completed incoming call on the Onboarding line with agent Owen Saxe. During the call, the onboarding process was explained, including Resync's role in debt reduction. No calls were completed on the Retention line, and there were no outbound attempts. The deal status is cancelled, but the only call involved onboarding and process explanation.</t>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>The incoming call on the Onboarding line was initiated by Owen Saxe, an agent from the debt-relief company, not a partner representative. The opening transcript does not mention Aspire or Resync as the caller, nor does it indicate a partner handoff or transfer.</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>There was one completed incoming call on the Onboarding line with agent Owen Saxe, where Gerald Havron was onboarded and discussed the debt relief process. No calls were completed on the Retention line, and there were no outbound calls or attempts. The call involved confirming payment details and explaining the process, but there was no live transfer from a partner company. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -6038,20 +6504,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Retention line opened by Kyle Romaine: 'I do have here Deborah on the line...she wanted to cancel the service, so I just had to connect her over to you.'</t>
-        </is>
-      </c>
+      <c r="P71" s="3" t="inlineStr"/>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>Kyle Romaine via Retention line</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="inlineStr"/>
+          <t>Kyle Romaine</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Retention line: 'This is Kyle Romaine. I do have here Deborah on the line and Deborah Lawrence. She is one of Leanne Anderson's clients. And she mentioned that she wanted to cancel the service, so I just had to connect her over to you.'</t>
+        </is>
+      </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>Deborah Lawrence was transferred in on the Retention line by Kyle Romaine to discuss cancellation. Rick from compliance attempted to retain her by offering to include taxes and lower payments, but Deborah declined and the service was cancelled. Multiple outbound calls were made to Deborah, but all resulted in brief voicemails with no further contact. The account status is cancelled.</t>
+          <t>Retention line</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>Deborah Lawrence was transferred in on the Retention line by Kyle Romaine, who introduced Deborah and explained she wanted to cancel her service. The compliance manager Rick attempted to retain her by offering to include taxes and lower payments, but Deborah declined and her service was cancelled. There were multiple outbound voicemail attempts but no completed outbound calls. The case ended with a confirmed cancellation.</t>
         </is>
       </c>
     </row>
@@ -6115,24 +6587,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Onboarding line: Brian says, 'I have here Teresa Desiderio on the line with me.'</t>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line (Brian)</t>
-        </is>
-      </c>
-      <c r="R72" s="5" t="inlineStr">
-        <is>
-          <t>OB done — no calls on retention line</t>
+          <t>Brian</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>On the incoming Onboarding line, the caller said: 'My name is Brian. I have here Teresa Desiderio on the line with me.' This is a clear partner handoff/transfer.</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Teresa Desiderio was live transferred by Brian (likely from Aspire/Resync) to the onboarding team, where Dana Mohamed explained the debt reduction process and next steps. Teresa expressed frustration about her debt situation, and Dana provided reassurance and instructions. There were no completed calls on the Retention line, and no outbound calls or attempts. Ultimately, the deal was cancelled.</t>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>Teresa Desiderio was live-transferred by Brian from Resync to the onboarding team, where Dana Mohamed explained the debt reduction process and next steps. Teresa expressed frustration about her debt situation, but was reassured and instructed on the program requirements. No calls were completed on the Retention line, and there were no outbound attempts. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -6196,20 +6674,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-25 19:35, incoming on Onboarding: The call opens with 'You have Alexandra from the lending department, and I got Rosa here.' This is a clear live transfer from a partner (Resync) to Better Lending's onboarding team.</t>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-25 19:35, incoming Onboarding line: '+16504653637: You have Alexandra from the lending department, and I got Rosa here.' This is a partner rep (Alexandra) handing off Rosa to Better Lending onboarding.</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr">
-        <is>
-          <t>Rosa Mack was live-transferred in by a partner (Resync) to complete onboarding for a debt resolution program. After onboarding, she made multiple attempts to reach her agent, Alexander Joseph, through various incoming calls. Ultimately, Rosa requested cancellation of her program via a completed incoming call on the Retention line, citing her husband's lack of agreement. The cancellation was processed and confirmed, and subsequent calls involved her requesting that all notices about the program cease.</t>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>Rosa Mack was live-transferred by a Resync representative (Alexandra) to Better Lending for onboarding and was approved for a debt resolution program. Multiple subsequent incoming calls were made by Rosa to reach her agent, but she ultimately requested cancellation via a completed incoming call on the Retention line, which was processed by Dean Lewis. No outbound calls were completed, and the deal was canceled at the client's insistence. Several voicemails and brief calls occurred, mostly related to follow-up and cancellation concerns.</t>
         </is>
       </c>
     </row>
@@ -6273,24 +6761,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-25 18:48, an incoming call on the Onboarding line began with Sarah (partner rep) saying 'I have Peter here on the line. Are you ready for the file number?' and then transferring the client to Cassie from Better Lending.</t>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Partner rep Sarah via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R74" s="5" t="inlineStr">
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-25 incoming Onboarding line call, the caller said: 'This is Sarah. I have Peter here on the line. Are you ready for the file number?' indicating a live transfer from a partner. This call came in on the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T74" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S74" s="2" t="inlineStr">
-        <is>
-          <t>Peter Nero was live-transferred in by a partner rep (Sarah) on the Onboarding line, where the onboarding process was completed and his payment schedule was set up. Multiple outbound attempts were made by the retention team, but no completed incoming calls occurred on the Retention line. Ultimately, Peter requested cancellation, which was confirmed by an outbound retention call. No retention-line inbound calls were completed; the deal was cancelled.</t>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>Peter Nero was live-transferred in by Sarah from Resync on the Onboarding line, where Cassie from Better Lending finalized his onboarding and explained the debt reduction process. Several outbound retention calls were made, but no completed incoming calls occurred on the Retention line. Ultimately, Peter requested cancellation, which was confirmed by Henry Hart during an outbound call. No retention-line inbound calls were completed, and the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -6354,20 +6852,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>"This is Jamie Gonzalez. And I have here Sharon. And when you're ready, tell me to get the file number." (incoming Onboarding line)</t>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
+          <t>Jamie Gonzalez</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-25 16:25 incoming Onboarding line call, the caller introduced themselves as 'Jamie Gonzalez' and said 'I have here Sharon' and provided a file number, clearly indicating a partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Onboarding line</t>
         </is>
       </c>
-      <c r="R75" s="2" t="inlineStr"/>
-      <c r="S75" s="2" t="inlineStr">
-        <is>
-          <t>Sharon Jenkins was live-transferred in by an Aspire representative via the Onboarding line, where she was welcomed and given an overview of the debt reduction process. Later, Sharon called the Retention line to confirm her cancellation and requested email confirmation, which the agent verified had been sent. There were no outbound calls or attempts to Sharon. Ultimately, the account was canceled as requested.</t>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>Sharon Jenkins was live-transferred in by Aspire via the Onboarding line, where she was onboarded and informed about the debt reduction process. Later, Sharon called the Retention line herself to confirm her account cancellation and to request email confirmation, which the agent provided. No outbound calls or attempts were made to Sharon. The account was ultimately cancelled as requested.</t>
         </is>
       </c>
     </row>
@@ -6431,20 +6939,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-25 15:31, an incoming call on the Onboarding line opened with Floyd (likely a partner rep) saying, 'This is Floyd. I'm gonna go with me, mister Jimmy Rogers. Whenever you're ready for the phone number.' Donna (your agent) replied, and Floyd said, 'I'll hand it from here.' This is a clear live transfer handoff.</t>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Partner rep Floyd via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R76" s="2" t="inlineStr"/>
+          <t>Floyd</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-25 15:31, incoming Onboarding line: '+14783943444: This is Floyd. I'm gonna go with me, mister Jimmy Rogers. ... I'll hand it from here.' Floyd introduces himself and explicitly states he is transferring the client to Donna from Better Lending.</t>
+        </is>
+      </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Jimmy Rogers was live-transferred in by a partner rep for onboarding, completed onboarding, but called back the next day to cancel his debt consolidation, stating he could manage his debts himself. He also discussed tax issues and was offered a tax program, but the main debt-relief deal was cancelled after a brief retention call. Multiple outbound attempts and completed calls occurred, including one completed incoming call on the Retention line, but the final outcome was cancellation.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>Jimmie Rogers was onboarded via a live transfer from a partner representative named Floyd to the Better Lending onboarding team. Multiple calls followed, including onboarding, tax-related discussions, and several outbound attempts. Ultimately, Jimmie called in on the Retention line and confirmed his decision to cancel the consolidation loan, despite retention efforts. The account was cancelled and a confirmation was promised.</t>
         </is>
       </c>
     </row>
@@ -6508,20 +7026,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls were completed; the only incoming call was a voicemail with no mention of Aspire or Resync. No transcript evidence of a partner transfer or handoff.</t>
-        </is>
-      </c>
+      <c r="P77" s="3" t="inlineStr"/>
       <c r="Q77" s="2" t="inlineStr"/>
-      <c r="R77" s="5" t="inlineStr">
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call had an Aspire or Resync representative, nor any mention of a partner transfer. All calls were either voicemails or outbound calls to the customer.</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S77" s="2" t="inlineStr">
-        <is>
-          <t>There were three calls: one incoming voicemail on the Retention line, and two outbound calls. The only completed call was an outbound call where Cody requested to cancel his consolidation loan, which was confirmed by the agent. No live transfer or partner handoff occurred, and the deal was cancelled as requested by the customer.</t>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Cody Schulte, was contacted via outbound calls and left a voicemail but did not answer any incoming calls. Ultimately, Cody spoke with Dean Lewis on an outbound call to request cancellation of his consolidation loan, which was processed as requested. No live transfer or partner handoff occurred, and no completed incoming calls were received on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -6585,20 +7105,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>Both completed incoming calls (Onboarding and Retention) began with a partner representative introducing themselves and stating they have the client to transfer. For example, on the Onboarding line: 'I have with me on the line, John, John Martinez, with me.' On the Retention line: 'This is Lana. I have a client here. He want to cancel.'</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>Aspire/Resync via Onboarding line and Retention line</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="inlineStr"/>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-22 22:28 incoming Onboarding line call, the caller says: 'I have with me on the line, John, John Martinez, with me.' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>John Martinez was live-transferred in twice by partner representatives: first for onboarding, then for cancellation. The onboarding call confirmed his understanding of the debt program and set up payments, but a subsequent retention call was made by a partner to cancel his application due to a co-signer backing out. No outbound calls were completed; several outbound attempts and voicemails were left. The final outcome was cancellation, with confirmation to be sent via email.</t>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>John Martinez was live-transferred in by a Resync partner rep on the Onboarding line to start the debt resolution program, with payment details confirmed. Later, a different partner rep (Lana) live-transferred John on the Retention line to cancel the application, as his co-signer withdrew. The cancellation was processed and confirmation was promised via email. Multiple outbound attempts were made, but no outbound calls were completed.</t>
         </is>
       </c>
     </row>
@@ -6662,20 +7188,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-22 at 22:19, an incoming call on the Onboarding line opened with a representative (not the customer) introducing Arthur and stating, 'I have Arthur on the line with me right now... This file is ready. He signed his agreement.' This is a clear partner handoff/live transfer.</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-22 22:19, incoming Onboarding line: The opening transcript includes '+17573395251: Hi, Kathy. How are you doing?... I have Arthur on the line with me right now.' The caller is handing off Arthur to your team, indicating a live transfer.</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
         <is>
           <t>Partner rep via Onboarding line</t>
         </is>
       </c>
-      <c r="R79" s="2" t="inlineStr"/>
-      <c r="S79" s="2" t="inlineStr">
-        <is>
-          <t>Arthur was live-transferred in by a partner rep and completed onboarding. He later called in to cancel due to financial hardship and hospitalization, and despite offers to pause or adjust payments, insisted on cancellation. Multiple outbound attempts were made, and one completed incoming call on the Retention line confirmed his cancellation request. The deal was ultimately cancelled at Arthur's request.</t>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Robertson initially completed onboarding via a live transfer from a partner rep, then later called to cancel his application due to financial hardship and hospitalization. Multiple outbound attempts were made to reach him, and he ultimately completed a call on the Retention line to confirm his cancellation, despite offers to pause the account. The deal was cancelled, and Arthur requested written confirmation.</t>
         </is>
       </c>
     </row>
@@ -6739,20 +7271,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-27 17:11 incoming Retention line call, the caller says: 'This is Ralph calling over with Aspire Law Group. I have a client on the line requesting to cancel.' This is a clear live transfer from Aspire on the Retention line.</t>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
+          <t>Ralph</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Retention line: Caller introduced as 'Ralph calling over with Aspire Law Group. I have a client on the line requesting to cancel.'</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Retention line</t>
         </is>
       </c>
-      <c r="R80" s="2" t="inlineStr"/>
-      <c r="S80" s="2" t="inlineStr">
-        <is>
-          <t>Gerardo's case involved a live transfer from Aspire Law Group to the Retention line, where he requested to cancel his program. The agent discussed options, including postponing payments, but Gerardo ultimately insisted on canceling. Multiple outbound attempts were made, and a final call confirmed his cancellation request, with the agent informing him of the process and possible fees. The deal status is cancelled.</t>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Gerardo Ezqueda, was live-transferred by Ralph from Aspire Law Group on the Retention line to request cancellation. After the transfer, Dean Lewis discussed Gerardo's financial situation and initially offered to postpone payments, but Gerardo insisted on canceling. Multiple outbound attempts were made, and in the final call, Gerardo confirmed his wish to cancel, which was processed with a confirmation to follow. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -6816,20 +7358,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Retention line: The caller says, 'I have here Reginald on the line. We just signed the contract and finished the compliance call, and he wanted to cancel everything.' The caller then transfers Reginald to the compliance manager, indicating a live transfer/handoff.</t>
-        </is>
-      </c>
+      <c r="P81" s="3" t="inlineStr"/>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>Partner representative via Retention line</t>
-        </is>
-      </c>
-      <c r="R81" s="2" t="inlineStr"/>
+          <t>Kelly Morgan</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>Opening transcript on Retention line: '+19855197888: I have here Reginald on the line. We just signed the contract and finished the compliance call, and he wanted to cancel everything.' Caller is handing off the client for cancellation.</t>
+        </is>
+      </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>Reginald Daniels was transferred in by a partner representative immediately after signing the contract, expressing a desire to cancel the debt consolidation program. The compliance manager explained that cancellation could not occur until the account was registered and provided instructions for future cancellation. Multiple outbound attempts were made, but no outbound calls were completed. Ultimately, the deal was cancelled, with only one completed incoming call on the Retention line.</t>
+          <t>Partner rep via Retention line</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>Reginald Daniels was transferred in by a partner representative to the Retention line, expressing a desire to cancel after signing the contract. The compliance manager, Talia Morgan, explained that the account was not yet registered and could not be canceled immediately, but provided instructions for future cancellation. No Aspire or Resync company was named in the transfer. Multiple outbound attempts were made, but no outbound calls were completed and only one incoming call (the transfer) was completed.</t>
         </is>
       </c>
     </row>
@@ -6893,24 +7441,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>The 2026-05-22 19:46 incoming call on the Onboarding line begins with a representative (not the customer) stating, 'I have Christiana here,' and then handing off to Owen from onboarding, indicating a live transfer. The summary also mentions working with Resync.</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
-        <is>
-          <t>Partner rep via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R82" s="5" t="inlineStr">
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-22 19:46 incoming Onboarding call, the transcript shows a handoff: '+16262332457: I have Christiana here. ... So, Christiana, now you have Owen with you. ... So he will take it from here.' This is a clear partner live transfer.</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T82" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S82" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live-transferred in via the Onboarding line, with a partner representative present on the call. After onboarding, the customer expressed inability to afford the program and requested cancellation. Multiple outbound calls were made by retention agents to discuss options, but the customer insisted on canceling due to financial hardship. No completed incoming calls occurred on the Retention line; the account was ultimately canceled as requested.</t>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>Christine was live-transferred in by a Resync partner rep to the Onboarding line, where her debt resolution process was explained. She later called in to the CS Team to request cancellation due to unaffordable payments. Multiple outbound attempts were made by retention agents, but no completed incoming calls occurred on the Retention line. Ultimately, Christine insisted on cancellation, which was processed despite offers of alternative payment options.</t>
         </is>
       </c>
     </row>
@@ -6974,20 +7528,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-22 at 16:05, an incoming call on the Onboarding line began with a representative (Sayan) stating, 'I have missus Tony Buxton here,' and then transferring the client to your agent. On 2026-05-29 at 19:16, an incoming call on the Retention line began with 'This is Caleb from Aspire Law Group on a recorded line,' and he transferred Toni to your agent for cancellation.</t>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>Aspire via Onboarding line and Aspire via Retention line</t>
-        </is>
-      </c>
-      <c r="R83" s="2" t="inlineStr"/>
+          <t>Caleb</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-22 16:05, incoming on Onboarding line: '+16786294858: I have missus Tony Buxton here.' and '+16786294858: You just let me know when you're ready for the phone numb... I'll hand it from here.' This is a clear partner handoff/transfer. On 2026-05-29 19:16, incoming on Retention line: 'This is Caleb from Aspire Law Group on a recorded line... She wants to go ahead and basically cancel today.'</t>
+        </is>
+      </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Toni Buxton was live-transferred twice by Aspire representatives—first to onboarding for program setup, and later to retention for cancellation. Multiple outbound calls were made to discuss tax and debt consolidation options, but Toni ultimately expressed dissatisfaction with the contract and requested cancellation. Despite attempts to address her concerns, Toni insisted on canceling, and the cancellation was confirmed by a supervisor. The case ended with the client opting out of the service.</t>
+          <t>Aspire via Retention line</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>Toni Buxton was transferred in by Aspire on two occasions: first for onboarding, and later for a cancellation request. The client expressed dissatisfaction with the contract and requested to cancel, which was confirmed after discussions with multiple agents. Several outbound calls were made to clarify the program and finalize the cancellation. Ultimately, Toni's deal was cancelled after she remained firm in her decision.</t>
         </is>
       </c>
     </row>
@@ -7051,24 +7615,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-22, an incoming call on the Onboarding line began with Xavier from Better London onboarding team stating, 'I have Revlon with me. Are you ready for the file number?' This indicates a live transfer with the client already on the line, and Aspire was referenced in the call summary.</t>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
+          <t>Xavier Iris</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-22, incoming call on Onboarding line: Xavier Iris introduces himself and says 'I have Revlon with me,' indicating a live transfer with the client already on the line.</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Onboarding line</t>
         </is>
       </c>
-      <c r="R84" s="5" t="inlineStr">
+      <c r="T84" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S84" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live-transferred in by a partner (Aspire) on the Onboarding line, where the debt management program and payment details were explained. Later, the customer called in on the CS Team line to request cancellation due to financial hardship, and the cancellation process was confirmed. Outbound attempts were made, but there were no completed incoming calls on the Retention line. The deal was ultimately cancelled.</t>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>The customer was live-transferred in by Aspire on the Onboarding line, where program details and payment setup were discussed. Subsequent calls included an outbound follow-up to discuss payment postponement and an incoming call from the customer to cancel due to financial hardship. No completed calls occurred on the Retention line. The account was ultimately cancelled after the customer requested to withdraw from the program.</t>
         </is>
       </c>
     </row>
@@ -7132,24 +7706,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr">
-        <is>
-          <t>"+19092240573: Hi, Xavier. This is Zara. I have Joe Bonita on the line." (incoming on Onboarding line)</t>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>Zara via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R85" s="5" t="inlineStr">
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: '+19092240573: I have Joe Bonita on the line.'</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T85" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S85" s="2" t="inlineStr">
-        <is>
-          <t>The customer was transferred in by Zara on the Onboarding line, where the onboarding process and program details were discussed. There were no completed incoming calls on the Retention line, but there was one outbound call attempt and completion from the Onboarding department. Ultimately, the deal was cancelled. No Aspire or Resync keywords were detected in the transcripts.</t>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Jo Bonita Rains, was live-transferred in by a partner rep named Zara on the Onboarding line, where onboarding steps and program details were discussed. There were no completed calls on the Retention line, but there was one outbound call attempt and one completed outbound call for onboarding follow-up. The deal was ultimately cancelled. No Aspire or Resync company was explicitly named in the transcripts.</t>
         </is>
       </c>
     </row>
@@ -7213,20 +7797,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>"And I do have Lisa Villa. She wants to cancel... And thank you for choosing Resync." — Incoming call on Retention line, caller explicitly states they are transferring the client from Resync.</t>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Retention line opened with a representative saying, 'This is Ryan. And I do have Lisa Villa. She wants to cancel.' and later, 'Thank you for choosing Resync.'</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R86" s="2" t="inlineStr"/>
-      <c r="S86" s="2" t="inlineStr">
-        <is>
-          <t>A partner representative from Resync called in on the Retention line to transfer Elisa Villa for a cancellation request due to financial hardship. The agent, Ryan Henderson, handled the cancellation process and confirmed the client's desire to cancel rather than postpone payments. After discussing options, the cancellation was processed and the client was provided with contact information for future needs. There were both an incoming and an outbound completed call, and the deal was ultimately cancelled.</t>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Elisa Villa, was live-transferred in by a Resync representative to the Retention line to request cancellation due to financial hardship. The retention agent, Ryan Henderson, handled the cancellation process and confirmed the reason for cancellation. A follow-up outbound call was made to finalize the cancellation and provide the customer with contact information. The account was ultimately cancelled as requested by the customer.</t>
         </is>
       </c>
     </row>
@@ -7290,24 +7884,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on the Onboarding line: The caller introduces themselves as Catherine from the lending department and says, 'I have Gilbert Martinez on the line.' This is a clear partner handoff/transfer.</t>
+      <c r="P87" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>Catherine (lending department) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R87" s="5" t="inlineStr">
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: Caller says, 'Hi, Devon. This is Catherine, lending department. I have Gilbert Martinez on the line.'</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T87" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S87" s="2" t="inlineStr">
-        <is>
-          <t>Gilbert Martinez was transferred in by a partner (Catherine from the lending department) via a live call on the Onboarding line, where his onboarding and payment dates were finalized. Subsequent outbound calls from Better Lending confirmed Gilbert's enrollment and later addressed his request to cancel the program. No completed incoming calls occurred on the Retention line, and the deal was ultimately cancelled after Gilbert requested to withdraw from the program.</t>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Gilbert Martinez, was live-transferred in by a partner rep named Catherine on the Onboarding line, where onboarding details and payment dates were set up. There were several outbound attempts and completed calls, but no completed incoming calls on the Retention line. Gilbert later requested cancellation during an outbound call, and the agent escalated his request to the cancellation department. The deal was ultimately cancelled, and no retention-line calls were completed.</t>
         </is>
       </c>
     </row>
@@ -7371,20 +7975,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-21, the incoming Onboarding call opened with Devon Smith introducing himself as 'with the family on the onboarding team' and the other party (Leon) stating 'I got Danny and Riley quickly. His first payment is on the June 22 for you to know.' This is a clear live transfer/hand-off scenario, with the partner agent present and transferring the client.</t>
-        </is>
-      </c>
+      <c r="P88" s="3" t="inlineStr"/>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Partner agent (Leon) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R88" s="2" t="inlineStr"/>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-21 20:57, incoming Onboarding line: The call opens with 'This is Devon with the family on the onboarding team.' The other party, Leon, says 'I got Danny and Riley quickly. His first payment is on the June 22 for you to know.' This is a partner handoff/transfer, as Leon is introducing the client and providing details for onboarding.</t>
+        </is>
+      </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>The customer was live-transferred in by a partner agent on the Onboarding line, with payment and program details confirmed. Multiple outbound attempts were made by your team, and one completed outbound call handled account changes. The customer later called in on the Retention line to request cancellation, citing misinformation and lack of confirmation. The agent processed the cancellation and advised the customer would receive compliance follow-up.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>The customer was initially live-transferred in by a partner rep (Leon) on the Onboarding line, where payment and program details were confirmed. Multiple outbound attempts were made by the retention team, and one completed incoming call on the Retention line resulted in the customer requesting cancellation due to dissatisfaction and miscommunication. The program was ultimately cancelled, with the agent promising follow-up from compliance. There were also several voicemails and one completed outbound CS call regarding account changes.</t>
         </is>
       </c>
     </row>
@@ -7448,20 +8058,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P89" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Retention line: 'This is Jacob from Resync on a recorded line. I have a mutual client that wants to cancel the program. It should be for David Johns.'</t>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
+          <t>Jacob</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>The first incoming call on the Retention line opened with: 'This is Jacob from Resync on a recorded line. I have a mutual client that wants to cancel the program.' This is a clear live transfer from Resync, coming in on the Retention line.</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R89" s="2" t="inlineStr"/>
-      <c r="S89" s="2" t="inlineStr">
-        <is>
-          <t>David Johns was transferred in by Jacob from Resync on the Retention line to request cancellation of his program. Max Francis handled the call, discussed the client's concerns, and initiated the cancellation process, sending required documents for signature. Multiple outbound attempts and voicemails were made, but only one outbound call was completed. Ultimately, the client proceeded with cancellation after expressing dissatisfaction with the program.</t>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>David Johns was transferred in by Jacob from Resync via a live transfer on the Retention line to request cancellation of his debt-relief program. Two completed incoming calls on the Retention line occurred, during which David expressed dissatisfaction and requested cancellation, citing confusion about the nature of the program. The agent (Max Francis) worked to process the cancellation and sent David a document to sign. Numerous outbound attempts and voicemails were made, but the deal ultimately resulted in cancellation.</t>
         </is>
       </c>
     </row>
@@ -7525,20 +8145,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P90" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls included any mention of Aspire or Resync, nor was there any indication of a partner representative transferring the client. All incoming calls were voicemails with no transcribable conversations.</t>
-        </is>
-      </c>
+      <c r="P90" s="3" t="inlineStr"/>
       <c r="Q90" s="2" t="inlineStr"/>
-      <c r="R90" s="5" t="inlineStr">
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript mentions Aspire or Resync, nor any indication of a partner transfer. All incoming calls were voicemails with no transcribable conversation.</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S90" s="2" t="inlineStr">
-        <is>
-          <t>There were a total of five calls, all of which resulted in voicemails with no completed conversations. Two outbound attempts were made to reach the customer, but no contact was established. No incoming calls were completed on the Retention line. The deal was ultimately cancelled, and there was no evidence of a live transfer or partner handoff.</t>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>There were a total of five calls, all resulting in voicemails with no completed conversations. Two outbound attempts were made, but none were answered. No incoming calls were completed on the Retention line, and there is no evidence of a live transfer or partner involvement. The customer ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -7602,24 +8224,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P91" s="2" t="inlineStr">
-        <is>
-          <t>Julian Morris (partner rep) called in on the Onboarding line and stated, 'I have here Mary on the line,' indicating a live transfer. The call included both Julian and Mary, with Dana Mohamed from onboarding department receiving the transfer.</t>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>Julian Morris (Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R91" s="5" t="inlineStr">
-        <is>
-          <t>OB done — no calls on retention line</t>
+          <t>Julian Morris</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>"I have here Mary on the line" from Julian Morris on the incoming Onboarding line; Julian is introducing the client for a handoff.</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>Mary Scott was live-transferred by a Resync representative (Julian Morris) to the onboarding department, where Dana Mohamed explained the debt reduction program and scheduled her first payment. There were no outbound calls or completed calls on the Retention line. The deal status is cancelled, but the only call was an onboarding live transfer with no further follow-up or retention activity.</t>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>Mary Scott was live-transferred in by Julian Morris from Resync on the Onboarding line. The call focused on onboarding Mary into the debt relief program, explaining the process, and setting up her first payment. There were no outbound or retention-line calls. Ultimately, the deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -7683,20 +8311,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P92" s="2" t="inlineStr">
-        <is>
-          <t>The opening transcript of the 2026-05-20 incoming call on the Onboarding line includes: 'This is Leah, and I have Sylvia here with me... she's all good to go. Now Sylvia, they'll take care of everything. So she's all yours, Donna.' This is a clear live transfer from a partner handing off the client.</t>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>Partner representative (Leah) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R92" s="2" t="inlineStr"/>
+          <t>Leah</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-20 incoming Onboarding line call, the transcript opens with: 'This is Leah, and I have Sylvia here with me... she's all good to go. Now Sylvia, they'll take care of everything. So she's all yours, Donna.' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>Sylvia Ramos was live-transferred by a partner representative to the onboarding team, where her enrollment and program details were confirmed. Later, Sylvia called customer support to follow up on a cancellation notice after ending her program; the agent confirmed her cancellation and explained the notice would be sent by email. No completed calls occurred on the Retention line, and there were no outbound call attempts. The client was ultimately canceled and received confirmation of this status.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>Sylvia Ramos was live-transferred in by a partner rep (Leah) to the onboarding team, where her enrollment and next steps were confirmed. Later, Sylvia called customer support to confirm her program cancellation and to request a cancellation notice, which the agent assured would be sent by email. There were no completed calls on the Retention line, and no outbound attempts. The account status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -7760,20 +8398,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P93" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-20, incoming Onboarding line: '+13343548248: I have Michael here with me. Are you ready for the file number?' and '+13343548248: We got Vera here. I told you she is my favorite. So now I make sure you're in great hands.' This is a clear live transfer from a partner handing off the client.</t>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>Partner (likely Aspire/Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R93" s="2" t="inlineStr"/>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-20, an incoming call on the Onboarding line opened with 'This is Vera.' and 'I have Michael here with me. Are you ready for the file number?' indicating a partner rep (Vera) transferring Michael Lambert. On 2026-05-27, an incoming call on the Retention line opened with 'This is Emily with Freesync. I have a cancellation request for you.' Both are clear live transfers.</t>
+        </is>
+      </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>Michael Lambert was live-transferred in by a partner for onboarding, where he expressed concerns about the program. Later, a partner (Emily from Freesync) live-transferred him on the Retention line to request cancellation, which was confirmed by your agents. Michael called back to Retention to ensure cancellation, citing lack of written confirmation and a preference to handle payments himself. Multiple outbound attempts were made but only voicemails were left; ultimately, the deal was cancelled.</t>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>Michael Lambert was initially onboarded via a live transfer from a partner rep. Later, a partner rep (Emily from Freesync/Resync) called in to request cancellation, which was confirmed by your agent. Michael also called in himself to the Retention line to ensure his cancellation was processed, expressing concerns about the program and preferring to handle payments himself. No outbound calls were completed; all outbound attempts went to voicemail. The account was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -7837,24 +8485,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P94" s="2" t="inlineStr">
-        <is>
-          <t>"We have Robert here. So are you ready for the phone number?... He's gonna take it from here, Robert." — incoming Onboarding line. This is a clear live transfer with the client already on the line.</t>
-        </is>
-      </c>
-      <c r="Q94" s="2" t="inlineStr">
-        <is>
-          <t>Unknown partner via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R94" s="5" t="inlineStr">
-        <is>
-          <t>OB done — no calls on retention line</t>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-20 21:52 incoming Onboarding line call, the transcript shows the caller says 'We have Robert here. So are you ready for the phone number?... He's gonna take it from here, Robert.' This is a clear handoff/transfer.</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>Robert Lundgren was live-transferred in via the Onboarding line by a partner representative, then discussed the debt consolidation program with an agent. Later, he called the CS Team to request cancellation after discussing with his wife, expressing concerns about the program. There were no completed calls on the Retention line and no outbound attempts. The deal was ultimately cancelled.</t>
+          <t>Partner transfer via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>Robert Lundgren was transferred in by a partner on the Onboarding line, where the debt consolidation program was explained and he was reassured about the process. Later, Robert called the CS Team to discuss backing out of the program after talking with his wife, expressing concerns about the process and potential credit impact. No calls were completed on the Retention line, and no outbound attempts were made. Ultimately, Robert decided to cancel his enrollment.</t>
         </is>
       </c>
     </row>
@@ -7918,20 +8568,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P95" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-27 14:25, an incoming call on the Retention line opened with: 'Hello, Levi. This is Connor calling from Resync on a recorded line... I have mister Levi here on the line ready to assist you with your request.' This is a clear live transfer from Resync.</t>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-27 14:25, incoming on Retention line: 'Hello, Levi. This is Connor calling from Resync on a recorded line... I have mister Levi here on the line ready to assist you with your request.' Clearly a live transfer from Resync.</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R95" s="2" t="inlineStr"/>
-      <c r="S95" s="2" t="inlineStr">
-        <is>
-          <t>Scott Robinson had multiple interactions with the company, including onboarding, support, and retention. A live transfer from Resync led to a cancellation request, which was confirmed and processed after several follow-up calls. There were both inbound and outbound calls on the Retention line, including voicemails and confirmations. Ultimately, the account was cancelled per the client's request, with final confirmation provided.</t>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>Scott Robinson had multiple interactions with the company, including onboarding, support, and retention calls. The key event was a live transfer from Resync, where the client requested cancellation, which was confirmed and processed by the retention team. Several outbound and inbound calls occurred on the Retention line, including follow-ups and confirmation of cancellation. The account was ultimately cancelled as requested by the client.</t>
         </is>
       </c>
     </row>
@@ -7995,24 +8655,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P96" s="2" t="inlineStr">
-        <is>
-          <t>The incoming Onboarding call opened with a partner representative on the line: '+14236051275: Rosita, I have here Owen. He's on the line. They're going to take good care of you.' This indicates a live transfer from a partner.</t>
-        </is>
-      </c>
-      <c r="Q96" s="2" t="inlineStr">
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>"+14236051275: Rosita, I have here Owen. He's on the line. They're going to take good care of you. Alright?" — Incoming Onboarding line. The caller is handing off Rosita to Owen, indicating a live transfer.</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
         <is>
           <t>Aspire via Onboarding line</t>
         </is>
       </c>
-      <c r="R96" s="5" t="inlineStr">
+      <c r="T96" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S96" s="2" t="inlineStr">
-        <is>
-          <t>Rosita Delgado was live-transferred in by Aspire on the Onboarding line, where she completed her onboarding call and had her program details explained. No completed calls occurred on the Retention line, and there was one outbound attempt from the CS Team that resulted in voicemail. The deal was ultimately cancelled, and no further successful contact was made after onboarding. Multiple voicemails were left on the CS Team line, but no additional conversations took place.</t>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>Rosita Delgado was live-transferred in by a partner (Aspire) on the Onboarding line, where she was welcomed and onboarded by Owen. She expressed concerns about the debt relief process, which Owen addressed, and her first payment was scheduled. No completed calls occurred on the Retention line, and one outbound attempt was made but only reached voicemail. Ultimately, her deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -8076,20 +8742,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P97" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript shows a representative from Aspire or Resync, or any explicit partner handoff/transfer. The only incoming completed call (CCB) was from Faye David at Better Pest Funding, not Aspire/Resync, and was a message request for Amy.</t>
-        </is>
-      </c>
+      <c r="P97" s="3" t="inlineStr"/>
       <c r="Q97" s="2" t="inlineStr"/>
-      <c r="R97" s="5" t="inlineStr">
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript shows a representative from Aspire or Resync, or any explicit partner handoff/transfer. All incoming calls were either voicemails or the customer calling in directly to leave a message.</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S97" s="2" t="inlineStr">
-        <is>
-          <t>All completed calls were outbound, with no completed incoming calls on the Retention line. Martha Lowe was repeatedly contacted by agents regarding her debt consolidation program but firmly requested cancellation and no further contact. She stated she would handle her debts independently and disputed the program's value. The deal was ultimately cancelled, and Martha requested to be removed from the call list.</t>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>Martha Lowe attempted to contact the company to leave a message for her agent, but there were no live transfers or incoming calls from partner companies. All completed calls were outbound, where Martha repeatedly stated her desire to cancel and not be contacted further. The customer was firm in her decision to cancel the debt consolidation program, and the deal was ultimately cancelled. No completed incoming calls occurred on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -8153,20 +8821,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-19 23:33 incoming Onboarding line call, the caller (+12525616877) said: 'It's Joey. I do have live on file here with me... So, Lavrin, you do have here Devon on the line now... They're going to take care from here.' This is a clear live transfer from a partner (likely Resync) via the Onboarding line.</t>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
+          <t>Joey</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-19 incoming Onboarding line call, the caller (+12525616877) says: 'It's Joey. I do have live on file here with me... So, Lavrin, you do have here Devon on the line now. He's the best. They're going to take care from here. You're in great hands. Devon, they're all yours.' This is a clear live transfer handoff.</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live-transferred in from a partner (Resync) to the Onboarding line, where the onboarding process and program details were explained. Shortly after, the customer called in to cancel, stating her daughter would pay her bills instead, and the agent confirmed the cancellation and promised a supervisor callback. No completed calls occurred on the Retention line, and there were no outbound attempts. The deal was ultimately cancelled.</t>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>The client was live-transferred in from Resync via the Onboarding line, where onboarding steps and program details were discussed and the first payment scheduled. The following day, the client called in directly to cancel, stating her daughter would pay her bills instead, and the agent confirmed the cancellation and promised a supervisor callback. No calls were completed on the Retention line, and there were no outbound attempts. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -8230,24 +8908,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P99" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-19 22:52 incoming on Onboarding: Liano from the lending department says, 'Valerie Smith, she's here with us already on the line,' and introduces the client to Mohamed Mosad for handoff. This is a clear live transfer from a partner (Resync mentioned in call summary).</t>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
+          <t>Liano</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-19 22:52, incoming on Onboarding: Liano from the lending department says 'Valerie Smith, she's here with us already on the line' and introduces her to Mohamed Mosad for a handoff. This is a clear live transfer from a partner rep.</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R99" s="5" t="inlineStr">
+      <c r="T99" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S99" s="2" t="inlineStr">
-        <is>
-          <t>Valerie Smith was live-transferred in by a partner (Resync) and onboarded, but soon after requested cancellation due to dissatisfaction with the service and communication issues. Multiple inbound and outbound calls occurred, but no completed calls were handled on the Retention line. Ultimately, the cancellation was processed and confirmed, with Valerie requesting written confirmation by email.</t>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>Valery Smith was live transferred in by a Resync partner rep to the Onboarding team, where she was onboarded and informed about the debt reduction process. Multiple subsequent calls show Valery attempting to reach her assigned agent, expressing frustration with communication and ultimately requesting cancellation. There were several outbound attempts but no completed incoming calls on the Retention line. The account was ultimately cancelled, and Valery requested confirmation of the cancellation.</t>
         </is>
       </c>
     </row>
@@ -8311,20 +8999,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-19 21:28, incoming Onboarding line: '+15712370411: I have mister Maldonado on the line right now, and his phone number is 115088148.' This is a clear live transfer from a partner handing off the client.</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr">
-        <is>
-          <t>Partner (unknown, likely Aspire) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R100" s="2" t="inlineStr"/>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>The 2026-05-19 21:28 incoming call on the Onboarding line begins with '+15712370411: I have mister Maldonado on the line right now, and his phone number is 115088148.' This is a partner representative handing off the client.</t>
+        </is>
+      </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>Juan Maldonado was live-transferred in by a partner (likely Aspire) and onboarded into the debt management program. He later had issues with the service, leading to multiple outbound attempts and a completed inbound call on the NSF line. Ultimately, Juan called the Retention line to request immediate cancellation due to dissatisfaction and confusion about the program, which was processed by the agent. The account was closed, and confirmation was promised.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>Juan Maldonado was live-transferred in by a partner rep on the Onboarding line and completed onboarding with Xavier Lookman. He later had issues with the service, leading to several outbound attempts and a completed incoming call with NSF. Ultimately, Juan called the Retention line and requested immediate cancellation, which was processed by Dean Lewis. The account was cancelled, and confirmation was promised.</t>
         </is>
       </c>
     </row>
@@ -8388,20 +9082,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P101" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there any mention of a partner handoff or transfer. The only completed incoming call was from 'Liam with Better Lending onboarding team' on the Onboarding line, which does not match the partner transfer criteria.</t>
-        </is>
-      </c>
+      <c r="P101" s="3" t="inlineStr"/>
       <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="5" t="inlineStr">
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, nor any explicit partner handoff/transfer. The only incoming completed call was from 'Liam with Better Lending onboarding team' on the Onboarding line, which is not Aspire or Resync.</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S101" s="2" t="inlineStr">
-        <is>
-          <t>Robbie Parras was onboarded via an incoming call from the Better Lending team, where account setup and program details were discussed. Multiple outbound calls were made by various agents to discuss tax and debt relief, but most resulted in voicemails or brief conversations. Robbie requested cancellation during an outbound retention call, and the agent processed the cancellation after discussing the risks and benefits. No completed incoming calls occurred on the Retention line, and the deal was ultimately cancelled.</t>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>Robbie Parras was onboarded via an incoming call from Better Lending's own onboarding team. Multiple outbound calls were made by various agents regarding tax and debt issues, with several voicemails left. A completed outbound retention call resulted in Robbie insisting on cancellation, which was confirmed by the agent. No live transfers from Aspire or Resync occurred, and no completed incoming calls were received on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -8465,20 +9161,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P102" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line opened with 'This is Donna of your carding team,' and referenced Resync as the negotiating party, indicating a partner handoff.</t>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
+          <t>Donna</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>The incoming call on the Onboarding line opened with 'This is Donna of your carding team,' indicating a partner representative was on the line to facilitate a handoff.</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R102" s="2" t="inlineStr"/>
-      <c r="S102" s="2" t="inlineStr">
-        <is>
-          <t>Todd Fiske had one completed incoming call on the Onboarding line, facilitated by Donna from the carding team, who referenced Resync and explained the debt reduction process. No calls were completed on the Retention line, and there were no outbound attempts. The outcome was that Todd was onboarded with a scheduled payment, but the deal status is now cancelled.</t>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>Todd Fiske had one completed incoming call on the Onboarding line, where Donna from Resync explained the debt reduction process and confirmed the file details. No calls were completed on the Retention line, and there were no outbound attempts. The customer was onboarded for a payment scheduled for May 29, but the deal status is now cancelled.</t>
         </is>
       </c>
     </row>
@@ -8542,20 +9248,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P103" s="2" t="inlineStr">
-        <is>
-          <t>In the 2026-05-18 21:21 incoming Onboarding call, the transcript shows Daniel (likely from Aspire/Resync or a partner) calling in and handing off Gail to Xavier Lookman from Better Lending, saying 'I got it from here. Thank you, Daniel.' This is a classic live transfer.</t>
+      <c r="P103" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>Partner (Daniel) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R103" s="2" t="inlineStr"/>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-18 21:21 incoming Onboarding line call, Daniel (the incoming caller) says 'May I have Gail?' and provides the client's phone number, then Xavier (your agent) says 'I got it from here. Thank you, Daniel.' This is a clear handoff/transfer from a partner rep.</t>
+        </is>
+      </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>Gail Pettigrew Butler was live-transferred in by a partner (Daniel) to the Better Lending onboarding team, where her onboarding and payment schedule were explained. She later called the CS Team with questions about applying for new credit while enrolled, and was reassured this would not interfere with her plan. No calls were completed on the Retention line, and there were no outbound attempts. Ultimately, the deal was cancelled.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T103" s="5" t="inlineStr">
+        <is>
+          <t>OB done — no calls on retention line</t>
+        </is>
+      </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>Gail Pettigrew Butler was live-transferred in by a partner rep (Daniel) on the Onboarding line, where the onboarding process and payment plan were explained. A subsequent incoming call to the CS Team addressed questions about applying for new credit. There were no completed calls on the Retention line and no outbound attempts. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -8619,24 +9339,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P104" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line opened with 'This is Lawson Pierce. I have Kim O'Donnell here. She her file is good to go.' This indicates a partner representative (Lawson Pierce) was transferring the client.</t>
+      <c r="P104" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Lawson Pierce via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R104" s="5" t="inlineStr">
+          <t>Lawson Pierce</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>Opening transcript on Onboarding line: '+19493106824: This is Lawson Pierce. I have Kim O'Donnell here.' Lawson Pierce is handing off Kim to your agent, indicating a live transfer.</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T104" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S104" s="2" t="inlineStr">
-        <is>
-          <t>Kim O'Donnell was live transferred by Lawson Pierce to the onboarding team, where the onboarding process and program details were explained. There were no completed incoming calls on the Retention line, but an outbound onboarding call was completed to confirm payment details and next steps. The customer was successfully onboarded, but the deal status is now marked as cancelled.</t>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>Kim O'Donnell was transferred in by Lawson Pierce on the Onboarding line, where the onboarding process and program details were explained. There were no completed incoming calls on the Retention line, but there was one outbound call to the customer confirming payment details and next steps. No Aspire or Resync partner was explicitly mentioned in any transcript. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -8700,16 +9430,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P105" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls with a representative mentioning Aspire/Resync or indicating a live transfer; only a brief voicemail on the Compliance BL line.</t>
-        </is>
-      </c>
+      <c r="P105" s="3" t="inlineStr"/>
       <c r="Q105" s="2" t="inlineStr"/>
-      <c r="R105" s="2" t="inlineStr"/>
-      <c r="S105" s="2" t="inlineStr">
-        <is>
-          <t>There was only one incoming call, which went to voicemail on the Compliance BL line and had no transcribable conversation. No completed calls occurred on any line, and there were no outbound attempts. The customer did not interact with an agent, and the deal status is cancelled.</t>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript shows a representative from Aspire or Resync, nor any mention of a partner transfer. The only call was an incoming voicemail on the Compliance BL line with no transcribable conversation.</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>There was only one incoming call, which went to voicemail on the Compliance BL line and had no transcribable content. No live conversations occurred, and there were no outbound call attempts. The customer did not interact with an agent, and the deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -8773,24 +9505,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P106" s="2" t="inlineStr">
-        <is>
-          <t>"+12522029314: Hey. This is Zara. I have Denise with me on the line." (Onboarding line, incoming call, 2026-05-18 19:29). Zara is a partner rep transferring the client.</t>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>"This is Vera. ... I have Denise with me on the line." (Onboarding line, incoming call, #1)</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Onboarding line</t>
         </is>
       </c>
-      <c r="R106" s="5" t="inlineStr">
+      <c r="T106" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S106" s="2" t="inlineStr">
-        <is>
-          <t>Denise Coleman was live-transferred in by Aspire on the Onboarding line and completed onboarding for a debt-relief program. Multiple subsequent calls were made to customer service regarding payment status, creditor notifications, and confusion about the program. Denise ultimately requested cancellation due to ongoing creditor pressure and dissatisfaction with the timeline. No completed incoming calls occurred on the Retention line, and the deal was cancelled.</t>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>Denise Coleman was live-transferred in by Aspire (Zara) on the Onboarding line, where her onboarding and payment process were explained. Multiple subsequent incoming calls on the CS Team line involved Denise seeking clarification about creditor notifications, payment timelines, and ultimately requesting cancellation due to creditor pressure. No completed incoming calls occurred on the Retention line, though there were outbound attempts and one completed outbound Retention call. Denise ultimately chose to cancel her enrollment due to concerns about creditor actions and program timelines.</t>
         </is>
       </c>
     </row>
@@ -8854,24 +9596,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P107" s="2" t="inlineStr">
-        <is>
-          <t>In the 2026-05-17 00:12 incoming Onboarding call, David (likely from Aspire/Resync) says, 'This is David... I'm ready for the file ID whenever you are... Please take good care of him,' clearly handing off Carlos to the Better Lending onboarding agent.</t>
-        </is>
-      </c>
+      <c r="P107" s="3" t="inlineStr"/>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R107" s="5" t="inlineStr">
+          <t>David</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-17 00:12, incoming on Onboarding line: David (partner rep) says, 'This is David. How are you doing today?... This is Carlos. Please take get good care of him.' This is a clear live transfer from a partner handing off the client.</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep David via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T107" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S107" s="2" t="inlineStr">
-        <is>
-          <t>Carlos was live-transferred by a partner (David, likely from Aspire/Resync) to the Better Lending onboarding team, where his onboarding was initiated. After further discussion in an outbound call, Carlos decided the program was not suitable and called back to cancel. No completed calls occurred on the Retention line, and the cancellation was confirmed on an incoming Onboarding call. No payments were processed, and Carlos stopped his scheduled payment with his bank.</t>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>Carlos was live-transferred in by a partner rep (David) to the onboarding team, where his file was handed off and the onboarding process began. After an outbound onboarding call to discuss the program, Carlos decided to cancel, calling back inbound to the onboarding line to request cancellation. No completed calls occurred on the Retention line. The deal was ultimately cancelled per Carlos's request.</t>
         </is>
       </c>
     </row>
@@ -8935,24 +9683,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P108" s="2" t="inlineStr">
-        <is>
-          <t>Cassie (partner rep) on the Onboarding line says, 'I have Ingrid with me on the line. Are you ready for her phone number?' and hands off the client to Mohamed from Allego Boarding Team.</t>
+      <c r="P108" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>Cassie (partner rep) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R108" s="5" t="inlineStr">
-        <is>
-          <t>OB done — no calls on retention line</t>
+          <t>Cassie</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>"This is Cassie. I have Ingrid with me on the line. Are you ready for her phone number?" on the Onboarding line. Cassie is handing off Ingrid to the Allego/Better Lending team, indicating a live transfer.</t>
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>The only completed call was an incoming live transfer on the Onboarding line, where Cassie from a partner company transferred Ingrid to the Allego Boarding Team for onboarding. No completed calls occurred on the Retention line, and there were no outbound attempts. Ingrid was onboarded, her payment plan was confirmed, but the deal ultimately ended in cancellation.</t>
+          <t>Partner rep (Cassie) via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>The only completed call was an incoming live transfer on the Onboarding line, where Cassie handed Ingrid off to the Allego/Better Lending team for onboarding. No outbound calls were made, and no completed calls occurred on the Retention line. Ingrid's deal was ultimately cancelled, but there is no evidence of a retention or cancellation discussion in the available call logs.</t>
         </is>
       </c>
     </row>
@@ -9016,20 +9770,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P109" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-16 17:56 incoming Onboarding call, the transcript shows: '+14787142524: I got miss Monica here. ... You're in good hands.' This indicates a partner representative (Charlie) is handing off Monica to the onboarding team on the Onboarding line.</t>
+      <c r="P109" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>Partner rep (Charlie) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R109" s="2" t="inlineStr"/>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-27 20:19, an incoming call on the Retention line began with: 'Hello, Levi. This is Samuel on a recorded line... I have a client with me. She requested to cancel.' This is a clear live transfer from a partner rep handing off the client.</t>
+        </is>
+      </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>Monica Williams was initially live-transferred by a partner rep to the onboarding team to start her debt resolution process. Later, a partner rep (Samuel) live-transferred Monica to the Retention line to request cancellation, which was processed after confirming her husband would handle their finances. Multiple outbound and inbound calls occurred, including voicemails and follow-ups, with the final outcome being a confirmed cancellation of Monica's program. Monica was informed about possible cancellation fees and will receive confirmation via email.</t>
+          <t>Retention line</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>Monica Williams was initially onboarded via a live transfer from a partner, and her debt resolution plan was set up with payments scheduled. Later, a partner rep named Samuel called in on the Retention line to transfer Monica for a cancellation request, which was processed by Levi Miller. Outbound calls were made to Monica to confirm her cancellation and discuss her options, but she ultimately chose to cancel, citing her husband's decision to handle their finances. The account was marked as cancelled, and Monica was informed she would receive confirmation via email.</t>
         </is>
       </c>
     </row>
@@ -9093,20 +9857,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P110" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates a caller from Aspire or Resync, or any explicit partner handoff/transfer. All incoming calls are either voicemails or have no transcribable conversation.</t>
-        </is>
-      </c>
+      <c r="P110" s="3" t="inlineStr"/>
       <c r="Q110" s="2" t="inlineStr"/>
-      <c r="R110" s="5" t="inlineStr">
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript mentions Aspire or Resync, nor any explicit partner transfer. No opening lines indicate a live transfer.</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S110" s="2" t="inlineStr">
-        <is>
-          <t>There were a total of five calls for this customer, all of which were either voicemails or had no completed conversations. Three outbound attempts were made by the agent, all resulting in voicemail. No incoming calls were completed on the Retention line, and there is no evidence of a live transfer from Aspire or Resync. The deal status is cancelled, and there was no successful contact with the customer.</t>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>There were five total calls for this customer, all either brief voicemails or incomplete. Three outbound attempts were made, all resulting in voicemail. No completed incoming calls occurred on the Retention line, and no live transfer from Aspire or Resync was detected. The customer's deal status is cancelled, with no evidence of successful contact.</t>
         </is>
       </c>
     </row>
@@ -9170,24 +9936,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P111" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-15, an incoming call on the Onboarding line opened with: 'I have Jerry with me here. You ready for the file number?' and 'So, Jerry, I have Vera on the line now. She's gonna take it from here.' This is a clear live transfer from a partner representative handing off the client.</t>
+      <c r="P111" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>"This is Damien. I have Jerry with me here. You ready for the file number?" (incoming Onboarding line, 2026-05-15 21:34)</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
           <t>Partner rep via Onboarding line</t>
         </is>
       </c>
-      <c r="R111" s="5" t="inlineStr">
+      <c r="T111" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S111" s="2" t="inlineStr">
-        <is>
-          <t>Jerry and Marsha Craft contacted the company to cancel their loan and resolve a refund for a payment withdrawn after cancellation. Multiple incoming calls were made to customer support and onboarding, but none were completed on the Retention line. The refund process was discussed and initiated, with agents providing updates and contact numbers for Aspire. The deal was ultimately cancelled, and the clients were awaiting their refund.</t>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Jerry L Kraft, was initially live-transferred in by a partner rep named Damien on the Onboarding line, after which onboarding was completed. Multiple subsequent incoming calls were made by Jerry and Marsha Craft to the CS Team regarding a $360.31 charge after their loan was canceled, with agents confirming the cancellation and providing refund instructions. There were no completed incoming calls on the Retention line, and outbound attempts were made but only one was completed. Ultimately, the deal was canceled and the customer was awaiting a refund.</t>
         </is>
       </c>
     </row>
@@ -9251,20 +10027,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P112" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Onboarding line: The caller (Elena) says, 'I have Chiyon with me' and provides the client's information to Xavier, indicating a live transfer/hand-off.</t>
+      <c r="P112" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Elena via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R112" s="2" t="inlineStr"/>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: opening transcript shows Elena says 'I have Chiyon with me' and hands off to Xavier, indicating a partner transfer.</t>
+        </is>
+      </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>The customer, Chihyung Chang, was transferred in via a live call on the Onboarding line by Elena, who handed off the client to agent Xavier Lookman. The call focused on explaining the debt management process and confirming payment details, with the customer expressing understanding. There were no completed calls on the Retention line and no outbound attempts. The deal status is cancelled.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Chiyung Chang, was transferred in via the Onboarding line by Elena, who handed off the client to Xavier Lookman. The call focused on explaining the debt management process and confirming payment details. No Aspire or Resync company was mentioned, but the call was clearly a partner transfer. There were no completed calls on the Retention line, and the deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -9328,20 +10114,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P113" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, nor any mention of a partner transferring the client. All incoming calls are directly from the customer (Bessie/Betsy Wilson).</t>
-        </is>
-      </c>
+      <c r="P113" s="3" t="inlineStr"/>
       <c r="Q113" s="2" t="inlineStr"/>
-      <c r="R113" s="5" t="inlineStr">
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, nor any explicit partner handoff/transfer. All incoming calls are directly from Bessie Wilson herself.</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S113" s="2" t="inlineStr">
-        <is>
-          <t>Bessie Wilson called in to cancel her application, citing concerns from a family member and enrollment with another debt consolidation company. The company made outbound attempts and handled incoming calls on the Onboarding and CS lines, but there were no completed calls on the Retention line. Ultimately, the cancellation was confirmed and Bessie expressed gratitude. No live transfer or partner handoff occurred.</t>
+      <c r="U113" s="2" t="inlineStr">
+        <is>
+          <t>Bessie Wilson called in to cancel her application after concerns raised by a family member. The agent attempted to reassure her, but she insisted on canceling. She later called to confirm the cancellation, which was completed and confirmed by the CS agent. No live transfer or partner handoff occurred, and there were no completed incoming calls on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -9405,24 +10193,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P114" s="2" t="inlineStr">
-        <is>
-          <t>The 2026-05-15 18:53 incoming call on the Onboarding line includes a handoff: the incoming caller says, 'I'll be taking it from here, and don't worry. Todd is in good hands,' and the transcript shows a partner representative transferring the client. The summary and transcript mention Aspire and a transfer.</t>
-        </is>
-      </c>
-      <c r="Q114" s="2" t="inlineStr">
+      <c r="P114" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: '+12083000520: I'm gonna give you the file number... I'll be taking it from here, and don't worry. Todd is in good hands.' The caller is clearly handing off the client to Better Lending, indicating a live transfer.</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
         <is>
           <t>Aspire via Onboarding line</t>
         </is>
       </c>
-      <c r="R114" s="5" t="inlineStr">
+      <c r="T114" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S114" s="2" t="inlineStr">
-        <is>
-          <t>Todd Searle was live-transferred in by Aspire on the Onboarding line. After onboarding, he had several outbound calls with agents to discuss his debt relief plan and business funding needs. Ultimately, Todd requested to cancel his program, and the cancellation was processed with confirmation and a refund timeline provided. No completed incoming calls occurred on the Retention line; all retention interactions were outbound.</t>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
+          <t>Todd Searle was live-transferred from Aspire to Better Lending via the Onboarding line. After onboarding, Todd discussed his debt relief plan and later explored loan options with an agent, but ultimately requested to cancel his program. The cancellation was confirmed on an outbound retention call, with a refund process explained. No completed incoming calls occurred on the Retention line; all retention interactions were outbound.</t>
         </is>
       </c>
     </row>
@@ -9486,20 +10280,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P115" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call included an introduction from Aspire or Resync, nor did any caller indicate they were a partner handing off the client. The only completed incoming call (CS Team) was initiated directly by the customer, Bernie Schumacher.</t>
-        </is>
-      </c>
+      <c r="P115" s="3" t="inlineStr"/>
       <c r="Q115" s="2" t="inlineStr"/>
-      <c r="R115" s="5" t="inlineStr">
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, or that the call was a partner live transfer. The only completed incoming call was directly from the customer (Bernie Schumacher) to the CS Team line.</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr"/>
+      <c r="T115" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S115" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Bernd Schumacher, called in directly to request cancellation of his loan payoff program, stating the payment plan was not suitable. The agent confirmed the cancellation request and discussed next steps. Multiple outbound attempts and voicemails were made, but no calls were completed on the Retention line. The deal was ultimately cancelled after the customer's request.</t>
+      <c r="U115" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Bernd Schumacher, called in directly to request cancellation of his loan payoff program, stating the payment plan was not suitable. The agent confirmed the cancellation request and discussed next steps. There were several outbound attempts and voicemails left by agents, but no completed calls occurred on the Retention line. The deal was ultimately cancelled per the customer's request.</t>
         </is>
       </c>
     </row>
@@ -9563,20 +10359,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P116" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Retention line: Ethan (partner rep) transferred the client to Adam, stating, 'You can transfer the client over. I'll be able to help.' and 'I just transferred you over, and Adam will be able to assist you further in this call.'</t>
-        </is>
-      </c>
+      <c r="P116" s="3" t="inlineStr"/>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>Partner rep Ethan via Retention line</t>
-        </is>
-      </c>
-      <c r="R116" s="2" t="inlineStr"/>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Retention line: Ethan introduced himself and transferred the client to Adam, saying 'You can transfer the client over' and 'I just transferred you over, and Adam will be able to assist you further in this call.'</t>
+        </is>
+      </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>A partner representative (Ethan) live-transferred David Stout to the Retention line, where Adam handled the call. The client discussed confusion over a loan offer from Aspire, received clarification, but ultimately chose to cancel due to dissatisfaction and financial concerns. There was one completed outbound call and one completed incoming call on Retention; voicemails were left on other lines. The deal was cancelled.</t>
+          <t>Retention line</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
+          <t>The customer, David Stout, was transferred in via a live call on the Retention line by a representative named Ethan, who handed the client off to Adam for further assistance. There was one completed incoming call on Retention and one completed outbound call, with additional outbound attempts and voicemails. During the calls, the client expressed confusion and dissatisfaction with loan terms, ultimately deciding to cancel the deal due to financial concerns and unclear communication.</t>
         </is>
       </c>
     </row>
@@ -9636,24 +10438,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P117" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-14, an incoming call on the Onboarding line opened with: 'This is Floyd in here, and I got with you mister Felix Gonzalez Corveto. Tell me when you're ready for the file number.' This is a clear live transfer from a partner (Resync) to the onboarding agent.</t>
+      <c r="P117" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
+          <t>Floyd</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-14, an incoming call on the Onboarding line opened with 'This is Floyd in here, and I got with you mister Felix Gonzalez Corveto.' Floyd was clearly transferring Felix to Donna from Better Lending, and mentioned the file number and that Donna would take it from here. The transcript also references Resync as the partner company negotiating with creditors.</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R117" s="5" t="inlineStr">
+      <c r="T117" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S117" s="2" t="inlineStr">
-        <is>
-          <t>Felix was live-transferred in by Resync for onboarding, where his program and payment plan were explained. He later requested cancellation due to personal and financial concerns, with multiple calls discussing removing accounts and qualifying for the program. Ultimately, Felix insisted on canceling, and the agent confirmed the cancellation would be processed with no payments taken. No completed incoming calls occurred on the Retention line; all retention interactions were via outbound or other lines.</t>
+      <c r="U117" s="2" t="inlineStr">
+        <is>
+          <t>Felix was transferred in via Resync for onboarding, where his payment plan and program details were discussed. Multiple outbound and inbound calls followed, mostly on the Retention line, as Felix considered cancellation and discussed qualifying debts. Ultimately, Felix requested cancellation due to personal issues, and the agent confirmed the cancellation would be processed with no payments deducted. No completed incoming calls occurred on the Retention line; all retention calls were outbound or in-progress, and the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -9717,24 +10529,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P118" s="2" t="inlineStr">
-        <is>
-          <t>Owen Saxe from onboarding says, 'I'll be taking it from here. Thank you, Marcus.' This indicates a live transfer from a partner (likely Aspire or Resync) on the Onboarding line.</t>
-        </is>
-      </c>
+      <c r="P118" s="3" t="inlineStr"/>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R118" s="5" t="inlineStr">
-        <is>
-          <t>OB done — no calls on retention line</t>
+          <t>Marcus</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-14 20:31 incoming call on the Onboarding line, the transcript shows a handoff: '+19493157441: I'll be taking it from here. Thank you, Marcus.' This indicates a partner representative (Marcus) was transferring the client.</t>
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>The customer, Dereje Aychiluhim, was live-transferred in via the Onboarding line, with the partner representative present at the start of the call. The onboarding agent explained the debt relief process and scheduled the first payment. No completed calls occurred on the Retention line, and there were no outbound attempts. Ultimately, the deal status is cancelled.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Dereje Aychiluhim, was transferred in via a live call on the Onboarding line, where onboarding agent Owen Saxe explained the debt management process and scheduled the first payment. There were no completed calls on the Retention line, and no outbound calls or attempts were made. The deal status is cancelled, but the only completed call involved onboarding and initial program setup, with no evidence of retention intervention.</t>
         </is>
       </c>
     </row>
@@ -9793,25 +10607,23 @@
       <c r="N119" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O119" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P119" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-18 18:04 incoming Retention line call, the caller says: 'I have here Rosie with me. She's basically in the process... So she's actually looking just to basically change her mind about the process. Alright? So I'll leave right now. You can take care of the device from now.' This is a clear live transfer/handoff.</t>
-        </is>
-      </c>
-      <c r="Q119" s="2" t="inlineStr">
-        <is>
-          <t>Partner representative via Retention line</t>
-        </is>
-      </c>
-      <c r="R119" s="2" t="inlineStr"/>
-      <c r="S119" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Rosie Todorov, called in with a partner representative who handed her off to the Retention team for a cancellation request due to financial hardship. The Retention agent processed the cancellation after confirming no penalties would apply and offered to help retain the client, but Rosie declined. There were no outbound calls or attempts, and the process was completed via incoming calls. No Aspire or Resync partner was mentioned by name, but a live transfer did occur.</t>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P119" s="3" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr"/>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>No incoming caller identified themselves as being from Aspire or Resync, nor did any caller explicitly state they were transferring the client from a partner company. The Retention call was initiated by the client (Rosie) herself, with no mention of Aspire/Resync or a partner transfer.</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr"/>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr">
+        <is>
+          <t>Rosie Todorov called in directly to request a cancellation due to financial hardship. The agent offered to help her skip a payment, but Rosie declined and the cancellation was processed with no penalties. There were no outbound calls or attempts, and no evidence of a live transfer from Aspire or Resync. The case was resolved through direct client contact on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -9875,16 +10687,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P120" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call included an Aspire or Resync mention, nor was there any indication of a partner handoff. The only call was an unanswered inbound call to the CS Team line.</t>
-        </is>
-      </c>
+      <c r="P120" s="3" t="inlineStr"/>
       <c r="Q120" s="2" t="inlineStr"/>
-      <c r="R120" s="2" t="inlineStr"/>
-      <c r="S120" s="2" t="inlineStr">
-        <is>
-          <t>There was a single incoming call attempt to the CS Team line, but the call was not answered and no conversation took place. No outbound calls were made to the customer. No evidence of a live transfer or partner handoff was found. The deal status is cancelled, but no further call activity occurred.</t>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript contains Aspire/Resync mention or a partner handoff; only one incoming call (CS Team) was a no-answer.</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr"/>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr">
+        <is>
+          <t>There was only one incoming call to the CS Team, which was not answered and had no conversation. No outbound or completed calls occurred, and there were no live transfers or partner handoffs. The customer's deal status is cancelled, but no engagement or resolution happened via phone.</t>
         </is>
       </c>
     </row>
@@ -9948,20 +10762,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P121" s="2" t="inlineStr">
-        <is>
-          <t>"This is Adam Jose with Randall Osborne. Are you ready for the file number?" (incoming on Onboarding line)</t>
+      <c r="P121" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>Aspire via Onboarding line (Adam Jose)</t>
-        </is>
-      </c>
-      <c r="R121" s="2" t="inlineStr"/>
+          <t>Adam Jose</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line opened with '+12706063744: This is Adam Jose with Randall Osborne. Are you ready for the file number?' indicating a partner rep is transferring the client.</t>
+        </is>
+      </c>
       <c r="S121" s="2" t="inlineStr">
         <is>
-          <t>The customer, Randall Osborne, was live transferred by Adam Jose from Aspire to the Better Lending onboarding team via the Onboarding line. The onboarding agent, Donya Alnasharty, explained the debt-relief process, confirmed Randall’s understanding, and provided contact details for future support. No calls were completed on the Retention line, and the deal status is cancelled.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Randall Osborne, was transferred in by a partner representative (Adam Jose) on the Onboarding line for program enrollment. The onboarding agent welcomed Randall, explained the debt relief process, and confirmed program details. No calls were completed on the Retention line, and there were no outbound attempts. The deal status is cancelled, but the only completed call was an onboarding live transfer.</t>
         </is>
       </c>
     </row>
@@ -10025,20 +10849,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P122" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates a partner (Aspire/Resync) or any live transfer; all incoming calls were voicemails or had no transcribable content.</t>
-        </is>
-      </c>
+      <c r="P122" s="3" t="inlineStr"/>
       <c r="Q122" s="2" t="inlineStr"/>
-      <c r="R122" s="5" t="inlineStr">
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates a partner representative from Aspire or Resync, or any mention of a live transfer. All incoming calls were either voicemails or had no transcribable conversation.</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr"/>
+      <c r="T122" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S122" s="2" t="inlineStr">
-        <is>
-          <t>The company made multiple outbound attempts to reach Cindy Ellett, leaving several voicemails. Two outbound calls were completed, but there were no completed incoming calls on the Retention line. No live transfer or partner handoff occurred. Ultimately, the deal was cancelled.</t>
+      <c r="U122" s="2" t="inlineStr">
+        <is>
+          <t>There were a total of 12 calls, with 10 outbound attempts and 2 completed outbound calls. No completed incoming calls occurred on the Retention line, and there is no evidence of a live transfer from Aspire or Resync. Most calls resulted in voicemails or brief interactions, and the deal status is marked as cancelled.</t>
         </is>
       </c>
     </row>
@@ -10102,20 +10928,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P123" s="2" t="inlineStr">
-        <is>
-          <t>"This is Daniel, and I have Gloria here." (Onboarding line, 2026-05-13 16:04) — Daniel is handing off the client, indicating a live transfer from a partner.</t>
+      <c r="P123" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>Partner (Daniel) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R123" s="2" t="inlineStr"/>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-13 16:04, incoming on Onboarding line: '+14085070424: This is Daniel, and I have Gloria here.' This is a partner representative handing off the client for onboarding, indicating a live transfer.</t>
+        </is>
+      </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>Gloria Miranda was live-transferred by a partner (Daniel) for onboarding, where her debt management program was explained. Shortly after, Gloria called the Retention line to cancel her enrollment, citing a change of mind after discussing with her daughter. The cancellation was processed and confirmed by Henry Hart, with no payments withdrawn. Outbound follow-up confirmed the cancellation and that Gloria received her confirmation email.</t>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr">
+        <is>
+          <t>Gloria Miranda was live-transferred from Resync for onboarding and completed the process with a Better Lending agent. Shortly after, she called in on the Retention line to request cancellation, which was processed without issue. Outbound attempts were made, and a follow-up confirmed her cancellation and that no payments would be withdrawn. The client was not retained and did not proceed with the program.</t>
         </is>
       </c>
     </row>
@@ -10174,21 +11010,35 @@
       <c r="N124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O124" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P124" s="2" t="inlineStr">
-        <is>
-          <t>No incoming caller identified themselves as from Aspire or Resync, nor did any incoming caller explicitly state they were a partner handing off/transferring the client. The Onboarding and Retention calls were handled by internal agents (Vera Grayson, Ryan Henderson) and the opening lines do not mention Aspire/Resync or a partner transfer.</t>
-        </is>
-      </c>
-      <c r="Q124" s="2" t="inlineStr"/>
-      <c r="R124" s="2" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P124" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-13 incoming Onboarding line call, the caller (+15053213634) says, 'This is Leon here with the lending department. I got Jessica here with me. The file is Jessica and Barrett, by the way.' This is a partner representative handing off the client to your company on the Onboarding line.</t>
+        </is>
+      </c>
       <c r="S124" s="2" t="inlineStr">
         <is>
-          <t>The customer had two completed incoming calls: one with onboarding to discuss program details and one with retention to request cancellation. The retention agent attempted to retain the client by offering lower payments, but the customer insisted on canceling both accounts. Outbound attempts were made but not completed. The deal was ultimately cancelled as requested by the customer.</t>
+          <t>Partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr">
+        <is>
+          <t>The customer (Barrett Chadwell) and a co-applicant (Jessica) were onboarded via a live transfer from a partner rep named Leon on the Onboarding line. Later, Jessica called in on the Retention line and requested to cancel both accounts due to affordability issues; the cancellation was processed by Ryan Henderson. There were no completed outbound calls, but there were two outbound attempts and one brief voicemail. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -10247,21 +11097,35 @@
       <c r="N125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O125" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P125" s="2" t="inlineStr">
-        <is>
-          <t>No incoming caller identified themselves as from Aspire or Resync, nor did any incoming caller explicitly state they were a partner handing off/transferring the client. The Onboarding and Retention calls were handled by internal agents (Vera Grayson, Ryan Henderson) and the opening lines do not mention Aspire/Resync or a partner transfer.</t>
-        </is>
-      </c>
-      <c r="Q125" s="2" t="inlineStr"/>
-      <c r="R125" s="2" t="inlineStr"/>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P125" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-13 incoming Onboarding line call, the caller (+15053213634) says, 'This is Leon here with the lending department. I got Jessica here with me. The file is Jessica and Barrett, by the way.' This is a partner representative handing off the client to your company on the Onboarding line.</t>
+        </is>
+      </c>
       <c r="S125" s="2" t="inlineStr">
         <is>
-          <t>The customer had two completed incoming calls: one with onboarding to discuss program details and one with retention to request cancellation. The retention agent attempted to retain the client by offering lower payments, but the customer insisted on canceling both accounts. Outbound attempts were made but not completed. The deal was ultimately cancelled as requested by the customer.</t>
+          <t>Partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr">
+        <is>
+          <t>The customer (Barrett Chadwell) and a co-applicant (Jessica) were onboarded via a live transfer from a partner rep named Leon on the Onboarding line. Later, Jessica called in on the Retention line and requested to cancel both accounts due to affordability issues; the cancellation was processed by Ryan Henderson. There were no completed outbound calls, but there were two outbound attempts and one brief voicemail. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -10325,16 +11189,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P126" s="2" t="inlineStr">
-        <is>
-          <t>No mention of Aspire or Resync in any incoming call transcript or greeting. The only completed incoming call on the Retention line was initiated by the customer, Laura Mims, who referenced being transferred by Jonathan Underwood (an agent), not a partner company.</t>
-        </is>
-      </c>
+      <c r="P126" s="3" t="inlineStr"/>
       <c r="Q126" s="2" t="inlineStr"/>
-      <c r="R126" s="2" t="inlineStr"/>
-      <c r="S126" s="2" t="inlineStr">
-        <is>
-          <t>Laura Mims called in on the Retention line to request cancellation due to upcoming surgery. The agent offered to postpone, but Laura insisted on canceling. There were no live transfers from Aspire or Resync; all calls were either direct from the customer or outbound attempts from agents. The deal was ultimately cancelled after the customer's request.</t>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript mentions Aspire or Resync, nor does any incoming caller identify as a partner or state they are transferring the client. The only completed incoming call is from the client herself, Laura Mims, who says she was transferred by Jonathan Underwood but does not indicate this was a partner live transfer.</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr"/>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr">
+        <is>
+          <t>Laura Mims called in on the Retention line to request cancellation of her contract due to upcoming surgery. The agent offered to postpone, but Laura insisted on canceling. The agent agreed to follow up to finalize the cancellation. There were several voicemails and outbound attempts, but no live transfers or partner involvement were detected.</t>
         </is>
       </c>
     </row>
@@ -10398,24 +11264,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P127" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-12, an incoming call on the Onboarding line opened with a representative (Gabriella) stating, 'I have Kirk here. Are you ready?... I'll just give her your file number, and then I'll transfer you with her.' This indicates a live transfer from a partner.</t>
-        </is>
-      </c>
-      <c r="Q127" s="2" t="inlineStr">
-        <is>
-          <t>Partner rep (Gabriella) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R127" s="5" t="inlineStr">
+      <c r="P127" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr"/>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-12, the incoming call on the Onboarding line opened with: '+16156912637: I have Kirk here. Are you ready?... I'll just give her your file number, and then I'll transfer you with her.' This indicates a partner representative was handing off the client.</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>Partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T127" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S127" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live-transferred in by a partner rep on the Onboarding line and completed onboarding. Later, the customer attempted to cancel, with several inbound and outbound calls handled by the CS Team, but no completed calls occurred on the Retention line. Ultimately, the account was confirmed canceled by a CS agent. Multiple voicemails and missed calls occurred, and the customer was not retained.</t>
+      <c r="U127" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Kirk Shelton, was live-transferred in on the Onboarding line by a partner rep, then onboarded to the program. Over the following weeks, Kirk called customer support several times, mainly to inquire about or request cancellation. No completed calls occurred on the Retention line, but there were multiple outbound attempts and one completed outbound call. Ultimately, the account was confirmed canceled by a CS agent.</t>
         </is>
       </c>
     </row>
@@ -10474,21 +11346,35 @@
       <c r="N128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O128" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P128" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary mentions Aspire or Resync, nor does any incoming caller explicitly state they are a partner handing off or transferring the client. The Onboarding line call was from 'Elena', but there is no indication she is from Aspire/Resync or a partner company.</t>
-        </is>
-      </c>
-      <c r="Q128" s="2" t="inlineStr"/>
-      <c r="R128" s="2" t="inlineStr"/>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P128" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>The 2026-05-12 18:04 incoming Onboarding call begins with Elena (not a company agent) stating, 'I have Meredith Martin. Ready for the phone number?' and providing the client details to Xavier Lookman, indicating a partner handoff/transfer.</t>
+        </is>
+      </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>Meredith Martin was onboarded through an incoming call with Elena and agent Xavier, where her program and payment schedule were set up. She later requested to postpone her payment due to financial difficulties. Ultimately, Meredith called the Retention line and then confirmed her cancellation in a follow-up outbound call, citing bankruptcy and her husband's illness. No evidence of a live transfer from Aspire or Resync was found, and the account was cancelled after several outbound and inbound interactions.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr">
+        <is>
+          <t>Meredith Martin was transferred in by a partner rep (Elena) on the Onboarding line, then onboarded and scheduled for her first payment. Multiple outbound calls followed, including support for payment postponement due to financial hardship. Meredith later called in on the Retention line and ultimately requested cancellation due to bankruptcy and personal circumstances. The account was cancelled, and no further payments were scheduled.</t>
         </is>
       </c>
     </row>
@@ -10552,20 +11438,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P129" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-12, an incoming call on the Onboarding line included a handoff where the caller (likely from Aspire) said, 'I'll take it from here,' and the agent Dana Mohamed introduced herself as from Better Lending onboarding. On 2026-05-22, an incoming call on the Retention line began with 'This is Lucas calling from Aspire Law Group. So, Sally, I have a client here with me,' clearly indicating a live transfer from Aspire.</t>
+      <c r="P129" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>Aspire via Onboarding line and Aspire via Retention line</t>
-        </is>
-      </c>
-      <c r="R129" s="2" t="inlineStr"/>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:07 incoming on Retention: 'This is Lucas calling from Aspire Law Group. So, Sally, I have a client here with me...' (Retention line).</t>
+        </is>
+      </c>
       <c r="S129" s="2" t="inlineStr">
         <is>
-          <t>The customer was live-transferred in twice: first for onboarding via Aspire, and later for cancellation via Aspire Law Group on the Retention line. After the cancellation request, agents confirmed the client wanted to cancel due to family assistance and processed the cancellation, with follow-up outbound calls to confirm and document the outcome. The deal was ultimately cancelled, and the customer declined to keep the loan as a backup. Multiple outbound attempts were made, and voicemails were left, but there was one completed incoming Retention call.</t>
+          <t>Aspire via Retention line</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Flossie Church, was initially onboarded via a live transfer from Aspire on the Onboarding line. Later, Aspire (Lucas) called in on the Retention line to transfer Flossie for cancellation, which was completed by Talia Morgan. Multiple outbound attempts were made by agents to follow up, and the customer confirmed cancellation, stating she had family help and no longer needed the program. The deal was ultimately cancelled, with confirmation provided to the customer.</t>
         </is>
       </c>
     </row>
@@ -10629,24 +11525,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P130" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-12 01:46, incoming call on the Onboarding line: Owen from onboarding says, 'Thank you, Sarah,' and Sarah says, 'You're welcome,' indicating a handoff/transfer from Sarah (likely a partner rep) to Owen. The transcript shows Sarah on the line with the client and then handing off to Owen, which matches the definition of a live transfer. 'Resync' is also mentioned in the onboarding summary.</t>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-12 01:46, incoming on Onboarding: Opening transcript shows 'Hi. This is Owen from the onboarding.' Owen then says, 'I'll be taking it from here. Thank you, Sarah.' This indicates Sarah (likely from Resync) transferred Alex to Owen for onboarding, confirming a live transfer. The process was explained as involving Resync reducing debt.</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R130" s="5" t="inlineStr">
+      <c r="T130" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S130" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Alex, was live transferred in via a partner (Resync) and completed onboarding, expressing concerns about credit but proceeding. Multiple outbound attempts were made by agents, but there were no completed incoming calls on the Retention line. Alex repeatedly requested cancellation and to stop payments, with several completed inbound calls to CS but not Retention. Ultimately, Alex's deal was cancelled after discussions about his options and inability to proceed with payments.</t>
+      <c r="U130" s="2" t="inlineStr">
+        <is>
+          <t>Alex was live-transferred from Resync to the onboarding team, where the debt relief process was explained and he agreed to proceed. Multiple subsequent calls involved Alex requesting cancellation and trying to stop a scheduled payment, with several inbound and outbound attempts but no completed incoming calls on the Retention line. Ultimately, Alex's deal was cancelled after discussions with support and retention agents, and no payment was processed.</t>
         </is>
       </c>
     </row>
@@ -10710,20 +11616,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P131" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls detected; only one outbound call was made by Levi Miller. No mention of Aspire or Resync, and no handoff/transfer occurred.</t>
-        </is>
-      </c>
+      <c r="P131" s="3" t="inlineStr"/>
       <c r="Q131" s="2" t="inlineStr"/>
-      <c r="R131" s="5" t="inlineStr">
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls; only one outbound call made by Levi Miller. No mention of Aspire or Resync, and no partner transfer occurred.</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr"/>
+      <c r="T131" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S131" s="2" t="inlineStr">
-        <is>
-          <t>There was one outbound call made by agent Levi Miller to the customer. During the call, the agent confirmed the cancellation of the customer's file and informed him that a confirmation email would be sent. The customer thanked the agent for the assistance. No incoming or retention line calls occurred.</t>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>There was only one outbound call to the customer, Derek Horton, made by Levi Miller. During this call, Levi confirmed the file would be canceled and the customer expressed appreciation. No incoming calls were received on the Retention line or any other line, and there were no live transfers or partner involvement.</t>
         </is>
       </c>
     </row>
@@ -10782,25 +11690,35 @@
       <c r="N132" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O132" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P132" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls had a representative identify as being from Aspire or Resync, nor did any incoming caller explicitly state they were transferring or handing off the client. The opening lines of the incoming Onboarding and CS Team calls show direct client contact, not a partner handoff.</t>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr"/>
-      <c r="R132" s="5" t="inlineStr">
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-12 00:19, an incoming call on the Onboarding line included the caller saying, 'I have Donnie here,' and providing client details, indicating a handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T132" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S132" s="2" t="inlineStr">
-        <is>
-          <t>Johnny Smith completed onboarding and began the debt relief process, but experienced issues with payment processing and creditor notifications. Multiple outbound attempts were made to reach him, with only two outbound calls completed. No completed incoming calls occurred on the Retention line. Ultimately, Johnny requested to cancel his program during an outbound call with the Retention department, and the cancellation was confirmed.</t>
+      <c r="U132" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Johnny Smith, was onboarded via a partner handoff on the Onboarding line. Multiple outbound attempts were made regarding payment issues, but no completed incoming calls occurred on the Retention line. Johnny called in to the CS Team to check on creditor notifications and later requested cancellation during an outbound Retention call. The account was ultimately cancelled after Johnny insisted on ending the program.</t>
         </is>
       </c>
     </row>
@@ -10859,29 +11777,27 @@
       <c r="N133" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O133" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P133" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-12 00:11 incoming Onboarding call, the caller said: 'Owen, I got Susan right here with me on the line. I want you to take good care of her, ma'am.' This indicates a live transfer from a partner (Aspire mentioned in summary) via the Onboarding line.</t>
-        </is>
-      </c>
-      <c r="Q133" s="2" t="inlineStr">
-        <is>
-          <t>Aspire via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R133" s="5" t="inlineStr">
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P133" s="3" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr"/>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript mentions Aspire or Resync, nor does any caller clearly identify as a partner handing off or transferring the client. The opening lines are from 'Landlords Lending' and 'Better Starts Lending Company,' not Aspire/Resync.</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr"/>
+      <c r="T133" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S133" s="2" t="inlineStr">
-        <is>
-          <t>Susan was live-transferred by an Aspire partner representative to the Onboarding team, where her debt management program was explained and initiated. No completed calls occurred on the Retention line, and there was one outbound attempt that resulted in a voicemail. Additional incoming calls were handled by other departments, but none resulted in retention activity. Ultimately, Susan's deal was cancelled.</t>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Susan Dangleman, called in seeking information about a debt consolidation loan and referenced a previous sign-up. All completed calls were incoming, with none on the Retention line and no outbound calls completed. There is no evidence of a live transfer from Aspire or Resync. The case ended with the deal cancelled, and the only outbound attempt resulted in a voicemail.</t>
         </is>
       </c>
     </row>
@@ -10945,24 +11861,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P134" s="2" t="inlineStr">
-        <is>
-          <t>"So I have Denise here with me... They're taking they're gonna be taking it from here... They're all yours." (incoming Onboarding line, 2026-05-11 22:13)</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr">
-        <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R134" s="5" t="inlineStr">
+      <c r="P134" s="3" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr"/>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-11 22:13 incoming Onboarding call, the caller said, 'So I have Denise here with me... They're taking they're gonna be taking it from here... They're all yours.' This is a clear handoff/transfer of the client to our company, indicating a live transfer. The call came in on the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>Partner transfer via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T134" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S134" s="2" t="inlineStr">
-        <is>
-          <t>Denise Adams was live-transferred in by a partner (Aspire/Resync) on the Onboarding line, where her account was set up and program terms were explained. Subsequent calls included onboarding support and multiple outbound attempts from the Retention line, but no completed incoming calls on Retention. Denise ultimately requested cancellation, citing dissatisfaction and feeling misled, and her cancellation was processed after several outbound retention attempts. The deal was cancelled, with no retention save achieved.</t>
+      <c r="U134" s="2" t="inlineStr">
+        <is>
+          <t>Denise Adams was transferred in via a partner handoff on the Onboarding line, then completed onboarding and discussed her debt consolidation options. Multiple outbound calls were made, including attempts to reach her on the Retention line, but no completed incoming Retention calls occurred. Denise ultimately canceled her enrollment, expressing dissatisfaction and threatening legal action if the cancellation was not processed. The deal status is cancelled, and no retention was achieved.</t>
         </is>
       </c>
     </row>
@@ -11026,20 +11944,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P135" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-11 21:48, the incoming call on the Onboarding line began with the partner representative saying, 'This is Kyle, and I do have Jennifer on the line. Whenever you're ready for the file numbers.' This is a clear live transfer from a partner.</t>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
-          <t>Partner (Kyle) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R135" s="2" t="inlineStr"/>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-11 21:48, incoming Onboarding line: '+14144678750: This is Kyle, and I do have Jennifer on the line. Whenever you're ready for the file numbers.' This is a partner (Kyle) handing off the client to your onboarding agent.</t>
+        </is>
+      </c>
       <c r="S135" s="2" t="inlineStr">
         <is>
-          <t>The customer was live-transferred in by a partner (Kyle) for onboarding, where the debt relief program was explained and initial steps were set up. Subsequently, the customer and her husband decided to cancel, leading to multiple outbound and inbound calls, including one completed incoming call on the Retention line to confirm cancellation. The account was ultimately cancelled after the customer's repeated requests and confirmation with agents. Several outbound attempts were made to follow up, and the customer expressed frustration at ongoing calls after cancellation.</t>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
+          <t>The customer was live-transferred in by Aspire on the Onboarding line, where the onboarding process and debt program were explained. Multiple outbound retention calls were made after the customer submitted a cancellation request, and one completed incoming call on the Retention line confirmed the cancellation. The customer insisted on canceling due to her husband's wishes, and the cancellation was processed. Several voicemails and follow-up calls occurred, but ultimately the account was cancelled as requested.</t>
         </is>
       </c>
     </row>
@@ -11103,20 +12031,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P136" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-11 21:48, the incoming call on the Onboarding line began with the partner representative saying, 'This is Kyle, and I do have Jennifer on the line. Whenever you're ready for the file numbers.' This is a clear live transfer from a partner.</t>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>Partner (Kyle) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R136" s="2" t="inlineStr"/>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-11 21:48, incoming Onboarding line: '+14144678750: This is Kyle, and I do have Jennifer on the line. Whenever you're ready for the file numbers.' This is a partner (Kyle) handing off the client to your onboarding agent.</t>
+        </is>
+      </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>The customer was live-transferred in by a partner (Kyle) for onboarding, where the debt relief program was explained and initial steps were set up. Subsequently, the customer and her husband decided to cancel, leading to multiple outbound and inbound calls, including one completed incoming call on the Retention line to confirm cancellation. The account was ultimately cancelled after the customer's repeated requests and confirmation with agents. Several outbound attempts were made to follow up, and the customer expressed frustration at ongoing calls after cancellation.</t>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr">
+        <is>
+          <t>The customer was live-transferred in by Aspire on the Onboarding line, where the onboarding process and debt program were explained. Multiple outbound retention calls were made after the customer submitted a cancellation request, and one completed incoming call on the Retention line confirmed the cancellation. The customer insisted on canceling due to her husband's wishes, and the cancellation was processed. Several voicemails and follow-up calls occurred, but ultimately the account was cancelled as requested.</t>
         </is>
       </c>
     </row>
@@ -11180,24 +12118,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P137" s="2" t="inlineStr">
-        <is>
-          <t>Opening transcript of 2026-05-11 21:29 incoming Onboarding call: The caller (Iris) is transferring Patricia to Owen from onboarding, with explicit handoff language: 'I'll be taking it from you. Thank you, Iris.' This is a live transfer from a partner (Iris) to onboarding.</t>
+      <c r="P137" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
         <is>
+          <t>Iris</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-11 21:29, an incoming call on the Onboarding line opened with: '+19493157441: This is Owen from the onboarding.' Shortly after, '+16154198137: This is Iris.' and '+19493157441: I'll be taking it from you. Thank you, Iris.' This indicates a partner rep (Iris) was on the line handing off Patricia to Owen.</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Onboarding line</t>
         </is>
       </c>
-      <c r="R137" s="5" t="inlineStr">
+      <c r="T137" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S137" s="2" t="inlineStr">
-        <is>
-          <t>Patricia was live-transferred in by a partner (Aspire) to the onboarding team, where her debt relief program was explained and initial steps were taken. She later called customer service to reach a specific representative, but no incoming retention-line calls were completed. Multiple outbound attempts were made by retention agents, and Patricia ultimately decided to cancel after clarifying program details and feeling misled. No payments were processed, and her cancellation was confirmed.</t>
+      <c r="U137" s="2" t="inlineStr">
+        <is>
+          <t>Patricia Patton was live-transferred by an Aspire representative (Iris) to the onboarding team, where her debt relief program was explained and set up. Several outbound calls were made to Patricia, including from retention, but there were no completed incoming calls on the Retention line. Patricia expressed confusion about the program, ultimately deciding to cancel after consulting her lawyer. The account was cancelled, and no payments were taken.</t>
         </is>
       </c>
     </row>
@@ -11261,24 +12209,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P138" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-11, an incoming call on the Onboarding line opened with: 'I have Derek on the line. Are you ready for the file number?' indicating a partner representative was transferring the client.</t>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>Unknown partner via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R138" s="5" t="inlineStr">
+          <t>Gabriela</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>"I have Derek on the line. Are you ready for the file number?" from Gabriela on the incoming Onboarding line (2026-05-11 19:32), indicating a partner is handing off the client.</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T138" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S138" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Derrick Ellis, was transferred in by a partner representative for onboarding and discussed his financial situation and program details. Subsequent calls included an incoming call to the CS Team where the customer requested cancellation due to affordability, and another brief incoming call from a lending company. There were multiple outbound attempts to reach the customer on the Retention line, but no completed incoming calls on that line. Ultimately, the deal was cancelled.</t>
+      <c r="U138" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Derrick Ellis, was transferred in by a partner rep (Gabriela) on the Onboarding line for initial onboarding and discussion of the debt program. Several calls followed, including incoming calls to CS and another department, but no completed calls occurred on the Retention line. Outbound attempts to reach the customer on Retention were unsuccessful. Ultimately, the deal was cancelled after the customer expressed affordability concerns and declined further loan offers.</t>
         </is>
       </c>
     </row>
@@ -11342,20 +12300,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P139" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-15, incoming on Retention line: Alexander with Resync says, 'I have Johnny Drake that's requested to cancel... Whenever you're ready for the transfer, let me know.' This is a clear live transfer from Resync via the Retention line.</t>
+      <c r="P139" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
         <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:34 incoming on Retention: 'This is Alexander with Resync on a recorded line. I have Johnny Drake that's requested to cancel... Whenever you're ready for the transfer, let me know.' (Retention line)</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R139" s="2" t="inlineStr"/>
-      <c r="S139" s="2" t="inlineStr">
-        <is>
-          <t>Johnny Drake was live-transferred in by Resync to request cancellation, which was handled by the compliance manager. He also called in himself to the CS Team to confirm cancellation and request a refund for a payment taken in error. Multiple outbound attempts were made, and a Resync supervisor later confirmed the cancellation process and sent required documents. The account was ultimately cancelled, with refund and closure steps initiated.</t>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr">
+        <is>
+          <t>Johnny Drake was live-transferred in by Alexander from Resync to request cancellation, which was handled by Talia Morgan. Johnny also called in directly to request cancellation and a refund due to an unwanted payment, and was transferred to accounting for follow-up. Multiple outbound attempts and voicemails occurred, and a Resync supervisor later confirmed the cancellation process and next steps. The account was ultimately cancelled, with no retention saves.</t>
         </is>
       </c>
     </row>
@@ -11419,20 +12387,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P140" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-10, the incoming Onboarding call opens with '+15612946881: Rose, this is Jamie Gonzales. I have here Michelin. Are you ready for the file number?' indicating a partner (likely Aspire/Resync) is transferring the client to Better Lending via the Onboarding line.</t>
-        </is>
-      </c>
+      <c r="P140" s="3" t="inlineStr"/>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R140" s="2" t="inlineStr"/>
+          <t>Jamie Gonzales</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-10 00:12, incoming on Onboarding line: '+15612946881: Rose, this is Jamie Gonzales. I have here Michelin. Are you ready for the file number?' This is a partner (Jamie Gonzales) handing off the client to the onboarding agent.</t>
+        </is>
+      </c>
       <c r="S140" s="2" t="inlineStr">
         <is>
-          <t>The customer was live-transferred in by a partner (Aspire/Resync) and onboarded. Multiple completed incoming calls occurred on the Retention line, where the customer discussed their account, program details, and ultimately confirmed cancellation. There were numerous outbound attempts and voicemails, but the customer did connect with agents several times. The account was ultimately canceled and the customer received confirmation.</t>
+          <t>Partner rep via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Micheline Malerbranche, was live-transferred in by a partner rep (Jamie Gonzales) on the Onboarding line and completed onboarding for a debt relief program. Multiple inbound calls were later completed on the Retention line, where the customer discussed account details, confusion about the program, and ultimately confirmed cancellation. Numerous outbound attempts and voicemails were made by agents, but the account was ultimately canceled and the customer received confirmation.</t>
         </is>
       </c>
     </row>
@@ -11496,20 +12470,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P141" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls had a representative mention Aspire or Resync, nor did any indicate a partner was transferring the client. All incoming calls were voicemails, no-answers, or had no transcribable conversation.</t>
-        </is>
-      </c>
+      <c r="P141" s="3" t="inlineStr"/>
       <c r="Q141" s="2" t="inlineStr"/>
-      <c r="R141" s="5" t="inlineStr">
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, or any partner transfer; all incoming calls were voicemails, no-answers, or had no transcribable conversation.</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr"/>
+      <c r="T141" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S141" s="2" t="inlineStr">
-        <is>
-          <t>There were a total of 12 calls, all involving the CS Team, with 6 outbound attempts made to the customer. All incoming calls resulted in voicemails or no answers, and no completed conversations occurred. No live transfers from Aspire or Resync were detected. The deal was ultimately cancelled, and no retention-line calls were completed.</t>
+      <c r="U141" s="2" t="inlineStr">
+        <is>
+          <t>There were a total of 12 calls, all either outbound attempts or incomplete inbound calls (voicemails, no-answers, or no conversation). No completed calls occurred on the Retention line, and no live transfers from Aspire or Resync were detected. Multiple outbound voicemails were left by agents, but there was no successful contact with the customer. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -11573,20 +12549,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P142" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-11 16:19, incoming on Retention line: 'This is Landon speaking on a recorded line from Resync... I have Maureen with Linda Line here... I'm just transferring her over.'</t>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
+          <t>Landon</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>"Hello, Michael. This is Landon speaking on a recorded line from Resync. ... I have Maureen with Linda Line here. The client requested to cancel since last Friday. ... I'm just transferring her over." (Retention line, 2026-05-11 16:19)</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R142" s="2" t="inlineStr"/>
-      <c r="S142" s="2" t="inlineStr">
-        <is>
-          <t>Maureen Redding had several interactions with the company, including onboarding and multiple retention calls. There was a clear live transfer from Resync on the Retention line, where the client was handed off to discuss her cancellation request. Ultimately, Maureen insisted on canceling her contract, and the agent agreed to process the cancellation after requesting email confirmation. Outbound attempts and voicemails were also made, but the main outcome was the client's cancellation.</t>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr">
+        <is>
+          <t>Maureen Redding had multiple interactions with the company, including onboarding and several calls regarding her account. The most significant event was a live transfer from Landon at Resync on the Retention line, where Maureen requested cancellation. The company confirmed the cancellation after discussing the process and requesting email confirmation. Outbound and inbound calls were made, with three completed on the Retention line, ultimately resulting in the client's cancellation.</t>
         </is>
       </c>
     </row>
@@ -11650,24 +12636,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P143" s="2" t="inlineStr">
-        <is>
-          <t>The 2026-05-08 21:55 incoming call on the Onboarding line began with a representative ('Liam') stating 'I have here Helen' and handing off the client to the Better Lending onboarding agent, indicating a live transfer from a partner.</t>
-        </is>
-      </c>
-      <c r="Q143" s="2" t="inlineStr">
-        <is>
-          <t>Partner rep via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R143" s="5" t="inlineStr">
+      <c r="P143" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr"/>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>Opening transcript of 2026-05-08 21:55 incoming Onboarding call: '+13215075483: Hi, Liam. I have here Helen. ... So I have here Helen. Her file is good to go.' This is a partner rep handing off the client on the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T143" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S143" s="2" t="inlineStr">
-        <is>
-          <t>Helen was live-transferred in by a partner rep for onboarding, where her file was confirmed and the debt-relief process explained. Subsequent calls included Helen requesting and confirming cancellation, with agents promising email confirmation within five to seven business days. There were several outbound attempts and voicemails, but no completed incoming calls on the Retention line. The deal was ultimately cancelled as requested by Helen.</t>
+      <c r="U143" s="2" t="inlineStr">
+        <is>
+          <t>Helen was live-transferred in by a Resync partner rep on the Onboarding line, where her file was confirmed and onboarding steps were explained. Several outbound attempts were made, but no completed calls occurred on the Retention line. Helen later called in to the CS Team to request and confirm her cancellation, and was assured she would receive a confirmation email. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -11727,24 +12719,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P144" s="2" t="inlineStr">
-        <is>
-          <t>Both incoming calls on the Onboarding line involved Floyd, a partner representative, transferring Carla Nash to Devon Smith. Floyd explicitly states he is with Carla Nash and hands her off to Devon, indicating a live transfer from a partner (Aspire/Resync).</t>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R144" s="5" t="inlineStr">
+          <t>Floyd</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>On both incoming Onboarding calls, the caller Floyd introduces himself as present with Miss Carla Nash and hands her off to Devon Smith from the onboarding team, indicating a live transfer. The first call includes: 'This is Floyd, and I got with me miss Carla Nash.' The second call includes: 'Just to be honest, Floyd, I'm back again with miss Nash right now.' Both came in on the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T144" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S144" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Karla Nash, was transferred in via a partner (Aspire/Resync) on the Onboarding line for initial setup and program explanation. After onboarding, an outbound call from the Retention team reached her, during which she requested cancellation due to concerns about her credit cards and credit score. The agent confirmed the cancellation, assured no further payments would be deducted, and agreed to send a confirmation letter and place her on a do not call list. No completed incoming calls occurred on the Retention line.</t>
+      <c r="U144" s="2" t="inlineStr">
+        <is>
+          <t>Karla Nash was live-transferred in by Floyd from Aspire to the onboarding team, where her debt management process was explained and her first payment scheduled. Later, an outbound call from Retention confirmed her desire to cancel the program due to credit concerns and her finding another loan. The agent processed her cancellation, assured her no further payments would be taken, and agreed to send a confirmation letter and add her to the do-not-call list. No incoming calls were completed on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -11808,20 +12810,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P145" s="2" t="inlineStr">
-        <is>
-          <t>Incoming Onboarding call: Julian Morris introduces himself and states, 'So I have here, okay, Linda Jean with me,' clearly indicating a live transfer of the client. Incoming Retention call: Nolan from Resync says, 'This is Nolan from Resync on a recorded line. So I have a client on the line who wants to cancel the program,' confirming a partner handoff.</t>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>Julian Morris via Onboarding line; Nolan from Resync via Retention line</t>
-        </is>
-      </c>
-      <c r="R145" s="2" t="inlineStr"/>
+          <t>Nolan</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-23 16:25, incoming on Retention: 'This is Nolan from Resync on a recorded line...I have a client on the line who wants to cancel the program.'</t>
+        </is>
+      </c>
       <c r="S145" s="2" t="inlineStr">
         <is>
-          <t>Linda Jean was transferred in by partner representatives (Julian from Aspire/Resync and Nolan from Resync) for onboarding and cancellation assistance. She completed onboarding and later requested cancellation due to financial and account issues, including IRS concerns and a Chase account problem. Retention agents discussed possible postponement, but Linda insisted on cancellation and acknowledged potential fees. The deal was ultimately cancelled after several completed calls, including both inbound and outbound attempts.</t>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr">
+        <is>
+          <t>Linda Jean was initially onboarded via a live transfer from a partner rep (Julian Morris) on the Onboarding line. Later, a Resync rep (Nolan) live-transferred Linda Jean to the Retention line to process her cancellation request. Multiple calls occurred on the Retention line, including both inbound and outbound, where Linda confirmed her desire to cancel due to banking and tax issues. The account was ultimately cancelled, with Linda acknowledging possible cancellation fees.</t>
         </is>
       </c>
     </row>
@@ -11885,24 +12897,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P146" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-07 incoming Onboarding line call, the transcript shows: '+18314025314: I have with me Aaron Waters on the line. Whenever you're ready, I can give you the phone number.' This indicates a partner/third party was handing off the client.</t>
-        </is>
-      </c>
+      <c r="P146" s="3" t="inlineStr"/>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>Partner/third party via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R146" s="5" t="inlineStr">
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-07 23:13 incoming Onboarding call, the transcript shows a representative (Jonathan) on the line with Aaron Waters, introducing Aaron to Devon from the onboarding team and facilitating the handoff. This is a clear partner handoff/transfer, though the partner company is not named.</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T146" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S146" s="2" t="inlineStr">
-        <is>
-          <t>Aaron Waters was initially onboarded via a live transfer from a partner or third party. He later called in to the CS Team to cancel his enrollment, expressing concerns about credit impact and requesting confirmation of cancellation. An outbound call was made to him to coordinate with accounting, and a final incoming CS Team call confirmed his cancellation and that no payments would be withdrawn. No completed calls occurred on the Retention line.</t>
+      <c r="U146" s="2" t="inlineStr">
+        <is>
+          <t>Aaron Waters was live-transferred in by a partner rep (Jonathan) to the onboarding team to start a debt resolution program. Aaron later called in to cancel, expressing concerns about credit impact and requesting confirmation of cancellation. No incoming calls were completed on the Retention line, but there was one outbound attempt. Ultimately, Aaron's enrollment was cancelled and he was reassured that no payments would be withdrawn.</t>
         </is>
       </c>
     </row>
@@ -11966,20 +12984,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P147" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-18, an incoming call on the Retention line began with 'This is Caleb from Aspire Law Group on a recorded line... I have miss Sasha here. She just wants to go ahead and opt out today.'</t>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
         <is>
+          <t>Caleb</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:01 incoming on Retention: Caller says, 'Hi, Samuel. This is Caleb from Aspire Law Group on a recorded line...I have miss Sasha or Sasha here. She just wants to go ahead and opt out today.' Call came in on the Retention line.</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Retention line</t>
         </is>
       </c>
-      <c r="R147" s="2" t="inlineStr"/>
-      <c r="S147" s="2" t="inlineStr">
-        <is>
-          <t>The customer was initially onboarded via a live transfer from a partner representative (Ray) on the Onboarding line. Later, Aspire Law Group called in on the Retention line to transfer Sasha for a cancellation request. After the transfer, the agent confirmed Sasha's identity and processed her cancellation after discussing her reasons for leaving. Outbound attempts were made but only one outbound call was completed, and the deal was ultimately cancelled.</t>
+      <c r="T147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Sacha Vanosten, was onboarded via a live transfer from a partner (Ray) on the Onboarding line, and later transferred again by Caleb from Aspire on the Retention line to process a cancellation. Multiple outbound attempts were made, but only one outbound call was completed after the live transfer, during which the agent confirmed the cancellation after discussing alternatives. Ultimately, the customer was cancelled and will receive confirmation by email.</t>
         </is>
       </c>
     </row>
@@ -12043,20 +13071,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P148" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls; only a single outbound call attempt to voicemail on the Retention line. No mention of Aspire/Resync or any partner transfer.</t>
-        </is>
-      </c>
+      <c r="P148" s="3" t="inlineStr"/>
       <c r="Q148" s="2" t="inlineStr"/>
-      <c r="R148" s="5" t="inlineStr">
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls; only one outbound voicemail attempt on the Retention line. No mention of Aspire or Resync.</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr"/>
+      <c r="T148" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S148" s="2" t="inlineStr">
-        <is>
-          <t>There was only one outbound call attempt made to the customer on the Retention line, which reached voicemail and was not completed. No incoming calls were received, and there is no evidence of a live transfer or partner involvement. The deal status is cancelled, and no further contact was made.</t>
+      <c r="U148" s="2" t="inlineStr">
+        <is>
+          <t>There was one outbound call attempt to the customer on the Retention line, which resulted in a brief voicemail and no completed conversation. No incoming calls were received, and there is no evidence of a live transfer or partner involvement. The deal status is marked as cancelled.</t>
         </is>
       </c>
     </row>
@@ -12120,20 +13150,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P149" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line began with Jason Powell introducing himself and providing the file ID for Pamela Garcia, indicating a live transfer from a partner (likely Aspire/Resync).</t>
+      <c r="P149" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R149" s="2" t="inlineStr"/>
+          <t>Jason Powell</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>The incoming call on the Onboarding line begins with 'This is Jason Powell' and the partner rep provides the file ID for Pamela Garcia, indicating a handoff/transfer.</t>
+        </is>
+      </c>
       <c r="S149" s="2" t="inlineStr">
         <is>
-          <t>Pamela Garcia was live-transferred in by Jason Powell (Aspire/Resync) to the onboarding team. The agent, Vera Grayson, confirmed client details and explained the debt relief process, addressing Pamela's concerns about credit impact and payment schedules. No calls were completed on the Retention line, and the deal status is cancelled.</t>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr">
+        <is>
+          <t>Pamela Garcia was transferred in by Jason Powell from Resync on the Onboarding line. The onboarding agent, Vera Grayson, explained the debt relief process and addressed Pamela's concerns about creditor payments and credit score impact. Pamela clarified she did not need a graduation loan. The deal was ultimately cancelled, and there were no outbound or retention-line calls for this customer.</t>
         </is>
       </c>
     </row>
@@ -12197,24 +13237,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P150" s="2" t="inlineStr">
-        <is>
-          <t>The 2026-05-07 incoming Onboarding call opens with 'This is Leon from Better Lending onboarding team' and 'I have my office here. Her file is good to go.' The transcript shows a partner representative (Leon/Better Lending) transferring Maria Lopez to your company for onboarding, mentioning Resync and the handoff process. This is a live transfer from a partner.</t>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>Better Lending/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R150" s="5" t="inlineStr">
+          <t>Mohamed Mosad</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-07 21:10, the incoming Onboarding call opened with Mohamed Mosad from Better Lending onboarding Lawson Pierce, stating that Resync will work on reducing debt and Better Lending will handle payoff. The call references a partner handoff and mentions Resync as the partner company.</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T150" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S150" s="2" t="inlineStr">
-        <is>
-          <t>Maria Lopez was transferred in via a live onboarding call from Better Lending/Resync, enrolled in a debt management program, but soon requested cancellation due to family concerns and dissatisfaction. Multiple inbound calls to the CS Team followed, with Maria repeatedly seeking cancellation and expressing frustration with transfers and wait times. No completed incoming calls occurred on the Retention line, despite several outbound attempts. Ultimately, Maria's deal was cancelled, and she was not retained.</t>
+      <c r="U150" s="2" t="inlineStr">
+        <is>
+          <t>Maria Lopez was onboarded via a live transfer from Resync, with Mohamed Mosad handling the initial setup. Maria later called multiple times to request cancellation, citing family and financial reasons, and was assisted by several agents, including Spanish-speaking staff. Despite several outbound attempts and completed calls on the CS Team line, there were no completed incoming calls on the Retention line. Ultimately, Maria's program was cancelled after she confirmed her decision to discontinue.</t>
         </is>
       </c>
     </row>
@@ -12278,20 +13328,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P151" s="2" t="inlineStr">
-        <is>
-          <t>The opening transcript of the 2026-05-22 incoming Retention call shows Grant from the client care of Freesync explicitly stating, 'I have a mutual client that requested to cancel,' and transferring Christine to Talia Morgan. This is a clear live transfer from a partner (Freesync/Resync) on the Retention line.</t>
+      <c r="P151" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>Resync via Retention line</t>
-        </is>
-      </c>
-      <c r="R151" s="2" t="inlineStr"/>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Retention line opened with Grant from client care of Freesync stating, 'I have a mutual client that requested to cancel.'</t>
+        </is>
+      </c>
       <c r="S151" s="2" t="inlineStr">
         <is>
-          <t>Christine Bradich was initially onboarded via a live transfer from a partner on the Onboarding line, with her debt management plan set up. Later, a live transfer from Resync on the Retention line brought her cancellation request due to family issues, which was handled by Talia Morgan. Despite offers to pause payments, Christine insisted on cancellation, and the agent agreed to process it. Outbound calls were made for follow-up, including a voicemail, but the account was ultimately cancelled.</t>
+          <t>Freesync via Retention line</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr">
+        <is>
+          <t>Christine Bradich's case involved a cancellation request due to family issues. A partner representative, Grant from Freesync, live-transferred Christine to the Retention line, where Talia Morgan handled the cancellation process. Talia confirmed the cancellation after discussing options with Christine. Outbound attempts were made, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -12355,20 +13415,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P152" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-07, the incoming Onboarding line call opened with: 'Devon, this is Wesley. I have James here on the line. His file is good to go. You ready for the number?' This is a clear live transfer from a partner handing off the client.</t>
+      <c r="P152" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R152" s="2" t="inlineStr"/>
+          <t>Wesley</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-07 01:33, the incoming Onboarding call opened with: 'Devon, this is Wesley. I have James here on the line. His file is good to go. You ready for the number?' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
       <c r="S152" s="2" t="inlineStr">
         <is>
-          <t>James Newcomb was live-transferred in by a partner (Wesley) and onboarded. He later called in to the CS Team to request cancellation due to concerns about account closures and credit impact. Multiple outbound attempts were made, and there was one completed incoming call on the Retention line, where a transfer was attempted but ultimately the cancellation was processed. The deal was cancelled and the customer was not retained.</t>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>James Newcomb was live-transferred in by a Resync partner rep (Wesley) to the onboarding team. He later called in to the CS line to request cancellation due to concerns about account charge-offs and credit impact. Multiple outbound attempts were made, and one completed outbound call confirmed his decision to cancel. The case was ultimately cancelled, with final confirmation and removal from call lists.</t>
         </is>
       </c>
     </row>
@@ -12432,20 +13502,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P153" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Retention line: Nicholas says, 'This is Nicholas on a recorded line calling from Resync who have a mutual client that wants to be canceled.'</t>
+      <c r="P153" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
         <is>
+          <t>Nicholas</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Retention line: Caller introduced as 'Nicholas on a recorded line calling from Resync who have a mutual client that wants to be canceled.'</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R153" s="2" t="inlineStr"/>
-      <c r="S153" s="2" t="inlineStr">
-        <is>
-          <t>Ricardo was contacted by an agent to discuss tax debt relief options but could not afford the services. The next day, a Resync representative called in on the Retention line to request cancellation on Ricardo's behalf due to new financial difficulties. The cancellation process was initiated and confirmed, with Ricardo requesting written confirmation. The account was set to be canceled, and a confirmation email was promised.</t>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr">
+        <is>
+          <t>Ricardo was contacted by an agent regarding tax debt relief options but could not afford the services. The next day, a partner representative from Resync called in on the Retention line to request cancellation on Ricardo's behalf due to financial hardship. The cancellation process was initiated and confirmed by your agent, with a follow-up outbound call to Ricardo to finalize and confirm the cancellation. The account was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -12509,24 +13589,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P154" s="2" t="inlineStr">
-        <is>
-          <t>"This is George. I got Cricket here. Her file is already in front of me... So, Cricket, I'm gonna leave you here." (incoming Onboarding line)</t>
+      <c r="P154" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
         <is>
-          <t>George (partner rep) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R154" s="5" t="inlineStr">
+          <t>George</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>Opening transcript of the 2026-05-06 incoming Onboarding call: 'This is George. I got Cricket here. Her file is already in front of me.' George hands off Cricket to Vera from onboarding, indicating a partner transfer. Came in on Onboarding line.</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>Partner transfer via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T154" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S154" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live-transferred in by George for onboarding, completed the onboarding process, and later called multiple times about a cancellation and refund issue. There were several incoming calls, but none were completed on the Retention line, despite outbound attempts. Ultimately, the customer canceled the program and was awaiting a refund, with customer service confirming the refund timeline. The deal ended as cancelled, with the customer expressing frustration over communication and refund delays.</t>
+      <c r="U154" s="2" t="inlineStr">
+        <is>
+          <t>Crickett Schacht was transferred in by a partner representative (George) for onboarding, where her debt management plan was set up. She later called multiple times to cancel her account and request a refund after a payment was processed post-cancellation. No completed incoming calls occurred on the Retention line, but outbound attempts were made. The account was ultimately cancelled, and the customer was informed about the refund timeline.</t>
         </is>
       </c>
     </row>
@@ -12590,20 +13680,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P155" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-07 17:50, incoming on Retention line: 'Hi, Henry. This is Ethan from Aspire Law Group on a recorded line. I have a client with me on the line. It's for Lawrence Hart. He called in to cancel out with the program.'</t>
+      <c r="P155" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
         <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-07 17:50, incoming call on Retention line: 'Hi, Henry. This is Ethan from Aspire Law Group on a recorded line. I have a client with me on the line. It's for Lawrence Hart. He called in to cancel out with the program.'</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Retention line</t>
         </is>
       </c>
-      <c r="R155" s="2" t="inlineStr"/>
-      <c r="S155" s="2" t="inlineStr">
-        <is>
-          <t>Lawrence Hart was transferred in by Aspire on both the Onboarding and Retention lines, with the Retention call specifically for a cancellation request. Multiple outbound calls and voicemails were made to the client, and two completed outbound calls occurred after the live transfer. Ultimately, the client expressed dissatisfaction and confusion, leading to a cancellation of the program. The process and payment plan were explained, but the client chose not to proceed.</t>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence Hart was initially onboarded via a live transfer from a partner (Aspire) and later called in to cancel his program, again via a live transfer from Aspire on the Retention line. Multiple outbound attempts were made by agents, but only a few calls were completed, including one on the Retention line where the cancellation was processed. The client expressed concerns about communication and the process, ultimately resulting in cancellation of the deal.</t>
         </is>
       </c>
     </row>
@@ -12667,20 +13767,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P156" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-06 02:44, an incoming call on the Onboarding line opened with a representative saying, 'That's Margaret Bernard. She's with me on the line here. She's ready to go. I'll be taking it from here.' This is a clear live transfer handoff. Additionally, on 2026-05-29 22:10, the Retention line call summary states Michael Belfort is on a call with Connor from Resync, who transfers Margaret to Michael.</t>
+      <c r="P156" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line (2026-05-06), Resync via Retention line (2026-05-29)</t>
-        </is>
-      </c>
-      <c r="R156" s="2" t="inlineStr"/>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 02:44 incoming Onboarding: '+13362553891: She's with me on the line here.' and 2026-05-29 22:10 incoming Retention: 'Michael Belfort is on a call with Connor from Resync regarding a customer issue... Connor transfers Margaret to Michael.' Both are clear live transfers. The 05-29 call came in on the Retention line.</t>
+        </is>
+      </c>
       <c r="S156" s="2" t="inlineStr">
         <is>
-          <t>Margaret Bernard was live-transferred in by a partner (Aspire/Resync) and completed onboarding, but soon requested to cancel her contract due to concerns about her credit score and a preference to work with her credit union. Multiple inbound calls were made to customer service and retention, including a live transfer from Resync to Retention, to process her cancellation and refund. Ultimately, her account was canceled and she was provided information about her refund, with several follow-ups to confirm the status.</t>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr">
+        <is>
+          <t>Margaret Bernard had multiple interactions regarding onboarding, program cancellation, and refund requests. There were two clear live transfers, including one from Resync (Connor) to the Retention line to resolve a refund issue. Margaret repeatedly requested cancellation and a refund, which was confirmed and processed by several agents. Ultimately, her account was canceled and she was awaiting her refund, with no retention success.</t>
         </is>
       </c>
     </row>
@@ -12744,24 +13854,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P157" s="2" t="inlineStr">
-        <is>
-          <t>The incoming Onboarding call opened with a representative on the line saying, 'I have here Anthony. His file is good to go... Sorry. It's not Anthony. It's Raymond, actually.' This indicates a live transfer/handoff from a partner (likely Aspire, as referenced in the onboarding summary).</t>
-        </is>
-      </c>
-      <c r="Q157" s="2" t="inlineStr">
-        <is>
-          <t>Aspire via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R157" s="5" t="inlineStr">
+      <c r="P157" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr"/>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-06 incoming Onboarding call, the opening transcript shows a partner rep on the line: '+16099025978: I have here Anthony. His file is good to go... Sorry. It's not Anthony. It's Raymond, actually.' This indicates a live transfer with the client already on the line, coming in via the Onboarding line.</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T157" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S157" s="2" t="inlineStr">
-        <is>
-          <t>Raymond Johnson was live-transferred in by a partner (Aspire) to the onboarding team, where his onboarding process and payment schedule were explained. Numerous outbound attempts were made by your agents, mostly leaving voicemails, but there were no completed incoming calls on the Retention line. Ultimately, the deal was cancelled, and there was no successful retention contact with the customer.</t>
+      <c r="U157" s="2" t="inlineStr">
+        <is>
+          <t>Raymond Johnson was live-transferred in on the Onboarding line, where the onboarding process and payment schedule were explained. The call included a partner representative handing off the client to your agent. Multiple outbound attempts were made to reach Raymond, mostly via the Retention line, but none were completed and all resulted in voicemails. No completed incoming calls occurred on the Retention line, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -12820,21 +13936,31 @@
       <c r="N158" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O158" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P158" s="2" t="inlineStr">
-        <is>
-          <t>Neither incoming call mentions Aspire or Resync, nor does any representative indicate they are a partner handing off the client. The Onboarding call appears to be a direct transfer from another agent (Bruce), but there is no mention of Aspire/Resync or an external partner. The Retention call is a direct call from the customer.</t>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr"/>
-      <c r="R158" s="2" t="inlineStr"/>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-05 incoming Onboarding line call, the caller said: 'I have Theresa here with me. Are you ready for the file ID?' and then handed off the client to Vera Grayson. This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
       <c r="S158" s="2" t="inlineStr">
         <is>
-          <t>Teresa Musick completed two incoming calls: one with onboarding to set up her debt relief plan and one with retention to request cancellation. The onboarding call involved a handoff from another internal agent (Bruce), but not from Aspire/Resync. Teresa decided to cancel her loan consolidation because her mother will pay off her debts. The cancellation was confirmed by the agent, and Teresa will receive written confirmation via email.</t>
+          <t>Partner transfer via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr">
+        <is>
+          <t>Teresa Musick was live-transferred in on the Onboarding line by a partner representative, then completed onboarding with Vera Grayson. The next day, Teresa called the Retention line to cancel her loan consolidation, stating her mother would pay off her debts. Michael Belfort confirmed the cancellation and promised written confirmation. No outbound calls were made to Teresa.</t>
         </is>
       </c>
     </row>
@@ -12898,24 +14024,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P159" s="2" t="inlineStr">
-        <is>
-          <t>"So I have Irene on the other line here. She's already ready to go. Let me give you the file number here." — Incoming Onboarding line, 2026-05-05 23:02. Caller is handing off the client to your agent.</t>
-        </is>
-      </c>
-      <c r="Q159" s="2" t="inlineStr">
-        <is>
-          <t>Partner/unknown rep via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R159" s="5" t="inlineStr">
+      <c r="P159" s="3" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr"/>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-05 23:02, incoming call on Onboarding line: '+16616188677: So I have Irene on the other line here. She's already ready to go. Let me give you the file number here.' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T159" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S159" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Irene, was live-transferred in by a partner/unknown rep for onboarding, where she expressed concerns about the debt resolution process. Multiple outbound attempts were made, but no completed incoming calls occurred on the Retention line. Irene later called in to cancel after realizing the program was for debt consolidation, not a personal loan. Her cancellation was processed, and she received confirmation that her account was closed with no further deductions.</t>
+      <c r="U159" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Irene Ephriam, was onboarded via a live transfer from an unidentified partner. Multiple outbound attempts were made, but no completed calls occurred on the Retention line. Irene later called in to cancel, expressing she wanted a loan, not debt consolidation. Her cancellation was processed and confirmed, with follow-up to ensure no further deductions. The deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -12979,20 +14107,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P160" s="2" t="inlineStr">
-        <is>
-          <t>No incoming caller identified themselves as from Aspire or Resync, nor did any incoming call mention a partner handoff or transfer. Both completed incoming calls (Onboarding and CS Team) were handled by internal agents (Donya Alnasharty and Levi Miller) and did not reference Aspire/Resync or a partner transfer in their greetings or transcripts.</t>
-        </is>
-      </c>
+      <c r="P160" s="3" t="inlineStr"/>
       <c r="Q160" s="2" t="inlineStr"/>
-      <c r="R160" s="5" t="inlineStr">
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>Neither incoming call featured an Aspire or Resync representative, nor did the callers identify as a partner handing off the client. The Onboarding call was handled by Donya Alnasharty from the onboarding team, and the CS Team call was handled by Levi Miller from Better Best Lending's compliance team. No mention of Aspire or Resync in any transcript.</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr"/>
+      <c r="T160" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S160" s="2" t="inlineStr">
-        <is>
-          <t>There were two completed incoming calls: one with onboarding and one with the CS team, both handled internally with no partner transfer. The customer, Kyle Pasley, expressed concerns about contract discrepancies and requested a callback from a supervisor. Despite 23 outbound attempts (mostly voicemails) to reach the customer via the Retention line, there were zero completed incoming calls on Retention. Ultimately, the deal was cancelled.</t>
+      <c r="U160" s="2" t="inlineStr">
+        <is>
+          <t>There were two completed incoming calls: one with the onboarding team to set up the account, and one with the CS team regarding contract concerns. No completed calls came in on the Retention line, despite 23 outbound attempts (mostly voicemails) to reach the customer. The customer ultimately cancelled, and there is no evidence of a live transfer from Aspire or Resync.</t>
         </is>
       </c>
     </row>
@@ -13056,20 +14186,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P161" s="2" t="inlineStr">
-        <is>
-          <t>"This is Devon from the onboarding team." ... '+16507718284: This is Marcus, and I have Robert Hunt here with us on the line, and the file is good to go.' (2026-05-05 incoming Onboarding line). Also, on 2026-05-21 incoming Retention line: '+16693337644: This is Adam Maxwell. I'm account services manager with Better Path Lending and the affiliate with Resync. I actually had a file here for you.'</t>
+      <c r="P161" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
         <is>
-          <t>Aspire via Onboarding line; Resync via Retention line</t>
-        </is>
-      </c>
-      <c r="R161" s="2" t="inlineStr"/>
+          <t>Marcus</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>"This is Marcus, and I have Robert Hunt here with us on the line, and the file is good to go." (incoming Onboarding line, 2026-05-05)</t>
+        </is>
+      </c>
       <c r="S161" s="2" t="inlineStr">
         <is>
-          <t>Robert Hunt was live transferred in by both Aspire (via the Onboarding line) and Resync (via the Retention line), with agents confirming the handoff and presence of the client. Multiple inbound and outbound calls occurred, including several customer support and retention discussions about legal notices, payment plans, and bankruptcy. Ultimately, Robert decided to cancel his loan after filing for bankruptcy, despite agents offering to delay payments or discuss alternatives. The deal was cancelled after the client insisted on ending the program.</t>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr">
+        <is>
+          <t>Robert Hunt was live-transferred from Aspire by Marcus on the Onboarding line to begin his debt relief process. Several subsequent inbound calls were made by Robert to the CS Team regarding legal documents and confusion about the process, with Aspire mentioned as the partner. One completed incoming call occurred on the Retention line, where a Resync affiliate (Adam Maxwell) was involved, followed by outbound retention calls discussing loan consolidation and ultimately, Robert's cancellation of the program after filing for bankruptcy. The account ended in cancellation after multiple support and retention interactions.</t>
         </is>
       </c>
     </row>
@@ -13133,24 +14273,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P162" s="2" t="inlineStr">
-        <is>
-          <t>The opening transcript of the 2026-05-05 incoming Onboarding call shows a handoff: '+19493157441: I'll take it from here. Thank you.' This indicates a partner (likely Aspire or Resync) was on the line to transfer Olivia to your agent, consistent with a live transfer.</t>
-        </is>
-      </c>
-      <c r="Q162" s="2" t="inlineStr">
-        <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R162" s="5" t="inlineStr">
+      <c r="P162" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr"/>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-05 incoming Onboarding line call, the transcript shows a handoff: '+19493157441: I'll take it from here. Thank you.' The initial caller provides a file number and then hands the call over, indicating a live transfer from a partner.</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T162" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S162" s="2" t="inlineStr">
-        <is>
-          <t>Olivia was live-transferred in via the Onboarding line, completed onboarding, and was informed about the debt resolution process. Multiple outbound attempts were made by your agents, but no completed incoming calls occurred on the Retention line. Olivia requested cancellation soon after starting the plan, citing a family member's offer to pay off her debts, and the account was ultimately cancelled. No retention-line inbound calls were completed; all retention efforts were outbound.</t>
+      <c r="U162" s="2" t="inlineStr">
+        <is>
+          <t>Olivia Hause was live-transferred in on the Onboarding line, completed onboarding, and was informed about the debt resolution process. Multiple outbound retention calls were made after Olivia requested cancellation, but there were no completed incoming calls on the Retention line. Olivia ultimately cancelled her plan, citing a family member paying off her debts. Most outbound attempts reached voicemail or were not answered.</t>
         </is>
       </c>
     </row>
@@ -13214,20 +14360,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P163" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-05, the incoming Onboarding line call opened with: 'This is Henry Hart. I have Robert Ransom here. His file is good to go.' This is a clear live transfer from a partner (Aspire/Resync) handing off the client.</t>
-        </is>
-      </c>
+      <c r="P163" s="3" t="inlineStr"/>
       <c r="Q163" s="2" t="inlineStr">
         <is>
-          <t>Aspire/Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R163" s="2" t="inlineStr"/>
+          <t>Henry Hart</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-05 17:01, an incoming call on the Onboarding line opened with: 'This is Henry Hart. I have Robert Ransom here. His file is good to go.' This is a clear partner handoff/transfer.</t>
+        </is>
+      </c>
       <c r="S163" s="2" t="inlineStr">
         <is>
-          <t>Robert Ransom was live transferred in by a partner (Aspire/Resync) and onboarded. He soon requested cancellation, calling multiple times to confirm it and to ensure no payments would be taken. Several incoming calls were made to the Retention line, where agents confirmed and finalized the cancellation, and promised email confirmation. No outbound calls were completed; all key actions occurred via incoming calls, and the deal was ultimately cancelled as requested.</t>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr">
+        <is>
+          <t>Robert Ransom was live-transferred in by Henry Hart on the Onboarding line to begin the debt relief process. Multiple subsequent incoming calls, including three on the Retention line, were made by Robert to confirm and follow up on his cancellation request. The client repeatedly sought confirmation and paperwork for the cancellation, which was eventually finalized and confirmed by the agent, with assurances that no further payments would be taken. No outbound calls to the customer were completed, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -13291,16 +14443,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P164" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript indicates the caller is from Aspire or Resync, nor does any caller explicitly state they are transferring or handing off the client from a partner. All incoming calls are either directly from the customer or from representatives of BetterPath/Better Back/Better Pass Lending.</t>
-        </is>
-      </c>
+      <c r="P164" s="3" t="inlineStr"/>
       <c r="Q164" s="2" t="inlineStr"/>
-      <c r="R164" s="2" t="inlineStr"/>
-      <c r="S164" s="2" t="inlineStr">
-        <is>
-          <t>Larry Linton contacted the company to cancel his debt consolidation plan, citing that he received a settlement check and would handle his finances independently. Multiple calls occurred, including two completed incoming calls on the Retention line and one outbound call confirming the cancellation. No evidence of a partner live transfer was found. The cancellation was processed, and Larry was assured he would receive confirmation within 48 hours.</t>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>No incoming caller identified themselves as from Aspire or Resync, nor did any incoming caller state they were transferring or handing off a client. All incoming calls were directly from the customer or from agents representing BetterPath/Better Back/Better Pass Lending.</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr"/>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>Larry Linton contacted the company multiple times regarding his debt consolidation plan, ultimately deciding to cancel after receiving a settlement check and opting to handle his finances independently. The Retention team processed his cancellation and confirmed no payments would be deducted. There were both inbound and outbound calls, including voicemails and follow-ups, but no evidence of a live transfer from Aspire or Resync. The deal was cancelled and Larry was assured of a confirmation email.</t>
         </is>
       </c>
     </row>
@@ -13360,20 +14514,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P165" s="2" t="inlineStr">
+      <c r="P165" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr"/>
+      <c r="R165" s="2" t="inlineStr">
         <is>
           <t>"We have Edward in call here right now." Incoming call on Onboarding line.</t>
         </is>
       </c>
-      <c r="Q165" s="2" t="inlineStr">
+      <c r="S165" s="2" t="inlineStr">
         <is>
           <t>Resync via Onboarding line</t>
         </is>
       </c>
-      <c r="R165" s="2" t="inlineStr"/>
-      <c r="S165" s="2" t="inlineStr">
-        <is>
-          <t>Edward Samonte was transferred in via a live call from Resync on the Onboarding line, where agent Dana Mohamed took over the call. The onboarding process was explained, including payment instructions and the involvement of Resync and Better Lending. Edward confirmed his first payment date and banking details. No calls were completed on the Retention line, and there were no outbound calls or attempts.</t>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>Edward Samonte was live-transferred in by a Resync representative on the Onboarding line, where Dana Mohamed completed the onboarding process and confirmed payment details. There were no calls on the Retention line and no outbound attempts. The deal was ultimately cancelled, but the only call was an inbound onboarding handoff from Resync.</t>
         </is>
       </c>
     </row>
@@ -13437,24 +14597,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P166" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-04 incoming Onboarding call, Jason Todd says, 'So are you ready for the file?' and 'So right now, I'm gonna be leaving you with Carmen,' clearly indicating a live transfer/hand-off to Donna on the onboarding team via the Onboarding line.</t>
-        </is>
-      </c>
+      <c r="P166" s="3" t="inlineStr"/>
       <c r="Q166" s="2" t="inlineStr">
         <is>
-          <t>Jason Todd via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R166" s="5" t="inlineStr">
+          <t>Jason Todd</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>Opening transcript on Onboarding line: '+14075339548: This is Jason Todd. ... Right now, I'm just I was done with Carmen. ... So are you ready for the file? ... So right now, I'm gonna be leaving you with Carmen.' Incoming caller (Jason Todd) is handing off the client to onboarding.</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T166" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S166" s="2" t="inlineStr">
-        <is>
-          <t>Carmen was live-transferred by Jason Todd to the onboarding team, where her onboarding was completed and the program explained. Later, Carmen called in to leave a message for Jason Todd, initially indicating she wanted to withdraw but then deciding to stay with her current program and promising to notify customer service. Two outbound retention calls were attempted but only reached voicemail. Ultimately, the deal was cancelled with no completed retention-line calls.</t>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Carmen Rivera Oconnor, was live-transferred to the onboarding team by Jason Todd, who handed off her file and left her on the line for onboarding. Carmen discussed her previous negative experiences and was reassured about the new program. Later, Carmen called in to leave a message stating she wanted to withdraw from the program but then changed her mind and decided to stay with her current program. No completed calls occurred on the Retention line, and two outbound retention attempts resulted in voicemails. Ultimately, the deal was cancelled.</t>
         </is>
       </c>
     </row>
@@ -13518,24 +14684,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P167" s="2" t="inlineStr">
-        <is>
-          <t>The incoming Onboarding call opens with Ellie introducing herself and stating, 'I have with me Patricia Mullings,' and offering the customer ID to the agent. This is a clear live transfer/hand-off from a partner representative.</t>
-        </is>
-      </c>
+      <c r="P167" s="3" t="inlineStr"/>
       <c r="Q167" s="2" t="inlineStr">
         <is>
-          <t>Partner rep (Ellie) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R167" s="5" t="inlineStr">
+          <t>Ellie</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-04 19:33 incoming Onboarding call, Ellie introduces herself and says, 'I have with me Patricia Mullings. Would you like me to tell you the customer ID?' indicating a live transfer/hand-off.</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T167" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S167" s="2" t="inlineStr">
-        <is>
-          <t>Patricia Mullings was live-transferred in by a partner rep (Ellie) on the Onboarding line, where her onboarding was completed and her customer ID was confirmed. An outbound call followed, explaining the debt management process and payment schedule, with instructions to contact support if needed. No completed calls occurred on the Retention line, and the deal was ultimately cancelled.</t>
+      <c r="U167" s="2" t="inlineStr">
+        <is>
+          <t>Patricia Mullings was live-transferred in by Ellie on the Onboarding line, and then completed an onboarding call with Vera Grayson. There were no completed incoming calls on the Retention line, but there was one outbound call attempt and completion. The deal was ultimately cancelled. The process included onboarding and discussion of the debt management program, but no retention intervention occurred.</t>
         </is>
       </c>
     </row>
@@ -13599,20 +14771,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P168" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-04 incoming Onboarding line call, Xavier Lookman says: 'I believe you were with Daniel Cruz. Correct? He transferred you to me.' This indicates a live transfer from a partner/agent (Daniel Cruz) to the onboarding team.</t>
+      <c r="P168" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t>Daniel Cruz via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R168" s="2" t="inlineStr"/>
+          <t>Daniel Cruz</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-04 16:11, incoming on Onboarding: Xavier Lookman said, 'I believe you were with Daniel Cruz. Correct? He transferred you to me.' and explained Aspire's process, indicating a partner handoff.</t>
+        </is>
+      </c>
       <c r="S168" s="2" t="inlineStr">
         <is>
-          <t>The customer was live-transferred in by Daniel Cruz to the onboarding team, where the onboarding process and debt relief steps were explained. Multiple calls followed, including two completed incoming calls on the Retention line, where the customer (and a relative) requested cancellation and confirmed the process. Outbound attempts were made for follow-up and confirmation, but ultimately the customer chose to cancel the program. No retention was achieved, and the deal was closed as cancelled.</t>
+          <t>Aspire via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>Irene Pierce was live-transferred from Aspire (Daniel Cruz) to the onboarding team, where her debt-relief process was explained and her first payment scheduled. Multiple retention-line calls followed, including two completed incoming calls where Irene (and Audrey) requested cancellation, which was confirmed by the agent. Outbound attempts were made for follow-up, but ultimately the account was cancelled as requested. No payments were processed, and the client was not retained.</t>
         </is>
       </c>
     </row>
@@ -13676,20 +14858,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P169" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls included any mention of Aspire or Resync, nor did any incoming call transcript indicate a partner handoff or transfer. All completed calls were outbound, and all incoming calls to the Retention line were voicemails with 0s duration.</t>
-        </is>
-      </c>
+      <c r="P169" s="3" t="inlineStr"/>
       <c r="Q169" s="2" t="inlineStr"/>
-      <c r="R169" s="5" t="inlineStr">
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; all completed calls were outbound. No transcript or log entry shows an incoming caller introducing themselves as from Aspire or Resync, or as a partner transfer. All mentions of Aspire/Resync are absent.</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr"/>
+      <c r="T169" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S169" s="2" t="inlineStr">
-        <is>
-          <t>All completed calls were outbound attempts by company agents, with no completed incoming calls on the Retention line. The customer, Graylin Robinson, was reached twice by outbound calls, during which he stated he wanted to cancel due to unemployment and inability to pay. The agent offered a refund and to pause deductions, but ultimately the deal was cancelled. Most other calls were outbound voicemails or unanswered attempts.</t>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>The company made numerous outbound attempts to reach Mr. Robinson, leaving multiple voicemails. Only two outbound calls were completed, both on the Retention line, where Mr. Robinson explained he wished to cancel due to unemployment and health issues. No completed incoming calls occurred, and there is no evidence of a live transfer from Aspire or Resync. The account was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -13753,20 +14937,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P170" s="2" t="inlineStr">
-        <is>
-          <t>The only completed incoming call was on the Onboarding line, but the opening transcript shows Mason introducing himself as from the onboarding team and does not mention Aspire, Resync, or indicate a partner transfer. There is no evidence of a partner handoff or live transfer.</t>
-        </is>
-      </c>
+      <c r="P170" s="3" t="inlineStr"/>
       <c r="Q170" s="2" t="inlineStr"/>
-      <c r="R170" s="5" t="inlineStr">
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>The completed incoming call on the Onboarding line was answered by Mason from the onboarding team, who did not introduce themselves as being from Aspire or Resync, nor did they indicate they were transferring the client from a partner. The transcript shows a direct greeting and onboarding process, not a partner handoff.</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr"/>
+      <c r="T170" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S170" s="2" t="inlineStr">
-        <is>
-          <t>There were four total calls for this customer: two incoming (one completed, one no-answer) and two outbound (both voicemails). The only completed call was an incoming Onboarding call where the agent explained the debt relief process and Aspire's role, but there was no partner transfer. No calls were completed on the Retention line, and all outbound attempts went to voicemail. The customer ultimately did not proceed and the deal was cancelled.</t>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>There were four calls total: two outbound attempts (one each from Onboarding and Retention, both resulting in brief voicemails), one missed incoming call, and one completed incoming call on the Onboarding line. The completed call was a standard onboarding conversation with Mason, not a partner transfer. No completed calls occurred on the Retention line. The customer ultimately cancelled, and there is no evidence of a live transfer from Aspire or Resync.</t>
         </is>
       </c>
     </row>
@@ -13830,20 +15016,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P171" s="2" t="inlineStr">
-        <is>
-          <t>There were no incoming calls where a partner (Aspire or Resync) representative called in to transfer the client. All calls were outbound attempts or voicemails, except for one completed outbound call. No incoming call transcript shows a partner handoff or transfer.</t>
-        </is>
-      </c>
+      <c r="P171" s="3" t="inlineStr"/>
       <c r="Q171" s="2" t="inlineStr"/>
-      <c r="R171" s="5" t="inlineStr">
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; all completed calls were outbound. No incoming call transcript shows a partner representative introducing themselves or transferring the client.</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr"/>
+      <c r="T171" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S171" s="2" t="inlineStr">
-        <is>
-          <t>All calls to the customer were outbound, with most resulting in brief voicemails and only one completed outbound conversation. There were no completed incoming calls on the Retention line. The only completed call confirmed that the customer had already canceled their program with Resync, and the agent acknowledged the recent cancellation. The account status is cancelled.</t>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>All calls to this customer were outbound, with only one completed call and the rest being voicemails. The completed call confirmed that the customer had already canceled their program with Resync, and the agent apologized for the delay in processing. No incoming calls were completed on the Retention line. The deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -13907,16 +15095,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P172" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary mentions Aspire or Resync, nor any explicit partner handoff/transfer. Both completed incoming calls on 'CCB (other)' are from Better Pass Lending or a direct customer, not a partner transfer.</t>
-        </is>
-      </c>
+      <c r="P172" s="3" t="inlineStr"/>
       <c r="Q172" s="2" t="inlineStr"/>
-      <c r="R172" s="2" t="inlineStr"/>
-      <c r="S172" s="2" t="inlineStr">
-        <is>
-          <t>The customer (Samuel Vargas) had two completed incoming calls on the 'CCB (other)' line, one from Abby at Better Pass Lending and one from a caller wanting to cancel a claim related to Javier Gonzalez. There was one completed incoming call on the Retention line, but no outbound calls were completed—only two outbound attempts resulted in voicemails. Ultimately, the customer’s deal was cancelled, and there is no evidence of a live transfer from Aspire or Resync.</t>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call was introduced by a representative from Aspire or Resync, nor did any caller explicitly state they were transferring or handing off the client. The only named company was 'Better Pass Lending' (call #1), and the other incoming call (call #2) was a direct customer inquiry about cancellation.</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr"/>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Samuel Vargas, had three completed calls: two incoming on the 'CCB (other)' line and one on the Retention line. The first call was from Abby at Better Pass Lending, but no clear action was taken. The second call was a direct request to cancel a claim, which was processed by the agent. There were two outbound attempts from the Retention line, both resulting in voicemails. Ultimately, the deal was cancelled, and there is no evidence of a live transfer from Aspire or Resync.</t>
         </is>
       </c>
     </row>
@@ -13980,20 +15170,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P173" s="2" t="inlineStr">
-        <is>
-          <t>There were no incoming calls where the caller identified as being from Aspire or Resync, nor any explicit mention of a partner transferring the client on an inbound line. The only mention of Aspire was during an outbound call initiated by the company's agent.</t>
-        </is>
-      </c>
+      <c r="P173" s="3" t="inlineStr"/>
       <c r="Q173" s="2" t="inlineStr"/>
-      <c r="R173" s="5" t="inlineStr">
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call was completed; the only completed call was outbound from our agent to the client. The only incoming call was a voicemail with no conversation.</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr"/>
+      <c r="T173" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S173" s="2" t="inlineStr">
-        <is>
-          <t>Multiple outbound attempts were made to reach the customer, with voicemails left. One outbound call was completed, during which the agent spoke with Jacob Zander from Aspire about the client's desire to cancel. The client confirmed they wanted to cancel due to dissatisfaction with the debt consolidation offer. No incoming retention-line calls were completed, and the deal was ultimately cancelled.</t>
+      <c r="U173" s="2" t="inlineStr">
+        <is>
+          <t>There were four calls in total: three outbound attempts (two voicemails, one completed) and one incoming voicemail with no conversation. The only completed call was an outbound call where the client confirmed they wanted to cancel due to dissatisfaction with the debt consolidation offer. No live transfer from Aspire or Resync occurred, and no completed incoming calls were received on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -14057,20 +15249,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P174" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls were completed; all calls were outbound attempts with voicemails, and there are no transcripts indicating a partner transfer or mention of Aspire/Resync.</t>
-        </is>
-      </c>
+      <c r="P174" s="3" t="inlineStr"/>
       <c r="Q174" s="2" t="inlineStr"/>
-      <c r="R174" s="5" t="inlineStr">
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; all calls were outbound attempts or voicemails, and no Aspire/Resync keywords or partner transfer intros were detected.</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr"/>
+      <c r="T174" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S174" s="2" t="inlineStr">
-        <is>
-          <t>All 27 calls to the customer were outbound attempts, resulting only in voicemails or brief messages. There were no completed incoming calls on any line, including Retention. No live conversations or partner transfers occurred. The customer did not answer, and the deal was ultimately cancelled.</t>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>All 27 calls to Latanya Turner were outbound attempts, primarily voicemails left by various agents on the Retention and NSF lines. No incoming calls were completed, and there were no live transfers or mentions of Aspire or Resync. The customer did not answer any calls, and the deal was ultimately cancelled.</t>
         </is>
       </c>
     </row>
@@ -14130,20 +15324,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P175" s="2" t="inlineStr">
-        <is>
-          <t>All calls were outbound attempts or voicemails from company agents; there were no incoming calls, and no mention of Aspire or Resync in any transcript.</t>
-        </is>
-      </c>
+      <c r="P175" s="3" t="inlineStr"/>
       <c r="Q175" s="2" t="inlineStr"/>
-      <c r="R175" s="5" t="inlineStr">
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>All calls were outbound attempts or voicemails; there were no completed incoming calls and no mention of Aspire or Resync in any transcript.</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr"/>
+      <c r="T175" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S175" s="2" t="inlineStr">
-        <is>
-          <t>All contact attempts to Kaiya Brooks were outbound calls, mostly resulting in voicemails or no answer. There were no completed incoming calls on any line, including Retention. The customer did not engage in any conversations, and the deal status is marked as cancelled.</t>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>All contact attempts to Kaiya Brooks were outbound calls, primarily resulting in voicemails or no answer. There were no completed incoming calls, including none on the Retention line, and no evidence of a live transfer from Aspire or Resync. The deal status is cancelled, and no conversation with the customer was completed.</t>
         </is>
       </c>
     </row>
@@ -14207,14 +15403,16 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P176" s="2" t="inlineStr"/>
+      <c r="P176" s="3" t="inlineStr"/>
       <c r="Q176" s="2" t="inlineStr"/>
-      <c r="R176" s="6" t="inlineStr">
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr"/>
+      <c r="T176" s="6" t="inlineStr">
         <is>
           <t>No calls found</t>
         </is>
       </c>
-      <c r="S176" s="2" t="inlineStr">
+      <c r="U176" s="2" t="inlineStr">
         <is>
           <t>No calls found for this number in the phone system.</t>
         </is>
@@ -14280,16 +15478,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P177" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there any mention of a partner transferring the client. All incoming calls are directly from the customer.</t>
-        </is>
-      </c>
+      <c r="P177" s="3" t="inlineStr"/>
       <c r="Q177" s="2" t="inlineStr"/>
-      <c r="R177" s="2" t="inlineStr"/>
-      <c r="S177" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Tina Nosky, made multiple requests to cancel her account, resulting in several completed calls with the Retention department. Agents confirmed the cancellation process, addressed confusion about account status, and assured no further payments would be taken. Numerous outbound attempts were made, but only one outbound call was completed. Ultimately, the account was confirmed as canceled, and the customer was not retained.</t>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary indicates a representative from Aspire or Resync, nor any mention of a partner transfer or handoff. All incoming calls are directly from the customer.</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr"/>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Tina Nosky, made multiple attempts to cancel her debt relief account, resulting in several outbound voicemails and three completed calls (two inbound on the Retention line). In the first retention call, Tina initiated cancellation, and the agent explained the process. A follow-up call confirmed the account was closed and addressed confusing text messages. One outbound call further confirmed Tina's intent to cancel, and the agent promised final confirmation. The account was ultimately cancelled, with no evidence of any live transfer from Aspire or Resync.</t>
         </is>
       </c>
     </row>
@@ -14353,20 +15553,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P178" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls were completed; the only call was an outbound call made by agent Henry Hart. No mention of Aspire or Resync, and no evidence of a partner transfer.</t>
-        </is>
-      </c>
+      <c r="P178" s="3" t="inlineStr"/>
       <c r="Q178" s="2" t="inlineStr"/>
-      <c r="R178" s="5" t="inlineStr">
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; the only call was an outbound call from Henry Hart to Denise Bradley. No mention of Aspire or Resync, and no evidence of a partner transfer.</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr"/>
+      <c r="T178" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S178" s="2" t="inlineStr">
-        <is>
-          <t>The only call was an outbound call from Henry Hart to Denise Bradley, during which Denise requested to withdraw from the debt consolidation program due to personal and financial hardships. The agent confirmed the cancellation and provided information about possible future options. There were no incoming calls, live transfers, or calls completed on the Retention line.</t>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>The only call was an outbound call from Henry Hart to Denise Bradley. Denise withdrew her application for the debt consolidation program due to personal and financial hardships. The agent confirmed the cancellation and provided information for future contact. No incoming or retention-line calls occurred.</t>
         </is>
       </c>
     </row>
@@ -14430,20 +15632,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P179" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Retention line: Marcus from Resync called in and stated, 'This is Marcus with Resync. We do have a client, a mutual client that requests cancellation.' He then transferred Mary Hoffman to Talia Morgan for further assistance.</t>
+      <c r="P179" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
         <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-21 16:06 incoming Retention line call, the caller introduced themselves as 'Marcus with Resync' and stated, 'We do have a client, a mutual client that requests cancellation,' then transferred Mary Hoffman to Talia Morgan.</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R179" s="2" t="inlineStr"/>
-      <c r="S179" s="2" t="inlineStr">
-        <is>
-          <t>Mary Hoffman's case involved multiple outbound attempts and a single completed incoming call on the Retention line, which was a live transfer from Resync regarding her cancellation request. After the transfer, agents discussed her desire to cancel due to financial hardship and previous scams. Despite offers to postpone payments or split them, Mary insisted on canceling and planned to change her bank account to prevent further withdrawals. The outcome was a confirmed cancellation after several follow-up calls and voicemails.</t>
+      <c r="T179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>Mary Hoffman was live-transferred by Marcus from Resync to the Retention line, requesting cancellation. Multiple outbound calls were made by your agents to discuss her cancellation and financial situation, but Mary insisted on canceling due to financial hardship and prior scams. The cancellation was ultimately processed, with agents explaining the process and possible fees. The case ended with the client's program canceled and no further retention achieved.</t>
         </is>
       </c>
     </row>
@@ -14498,25 +15710,23 @@
       <c r="N180" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O180" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P180" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on 'Katherine RT OB' (retention_ob) line, opening transcript: Caller (Mrs. Gomez) states she wants to remove herself from the 'resync repayment program' after consulting an attorney. Katherine Adams responds as the agent. The mention of 'resync' and the context of the call indicate a partner handoff or transfer from Resync.</t>
-        </is>
-      </c>
-      <c r="Q180" s="2" t="inlineStr">
-        <is>
-          <t>Resync via Katherine RT OB (retention_ob) line</t>
-        </is>
-      </c>
-      <c r="R180" s="2" t="inlineStr"/>
-      <c r="S180" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Yenislecdys Gomez, made multiple calls seeking clarification about her debt program, including requests to speak with specific agents. She expressed confusion about the program terms and ultimately decided to cancel after consulting an attorney and discussing her concerns with agents. The cancellation was confirmed by Kevin Michael, who assured her a notification would be sent. Several outbound attempts were made, and at least one completed incoming call occurred on the Retention line.</t>
+      <c r="O180" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P180" s="3" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript contains an introduction from a representative stating they are from Aspire or Resync, nor any explicit mention of a partner transferring the client. All incoming calls are either direct from the client or lack any partner handoff language.</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr"/>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Yenislecdys Gomez, made several attempts to reach her agent and ultimately spoke with Katherine Adams on the Retention line regarding confusion about her debt program and a desire to cancel. Katherine clarified the program terms, offered to delay payments, and assisted with account changes. The customer later confirmed her intent to cancel after consulting an attorney, and the cancellation was finalized by Kevin Michael, who sent a confirmation. No live transfer from Aspire or Resync occurred; all calls were direct or outbound follow-ups.</t>
         </is>
       </c>
     </row>
@@ -14580,20 +15790,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P181" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary indicates the caller was from Aspire or Resync, nor is there evidence of a partner handoff/transfer. The incoming calls are from customers or internal lines.</t>
-        </is>
-      </c>
+      <c r="P181" s="3" t="inlineStr"/>
       <c r="Q181" s="2" t="inlineStr"/>
-      <c r="R181" s="5" t="inlineStr">
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>No incoming caller identified themselves as from Aspire or Resync, nor was there any mention of a partner transfer or handoff in the opening lines of any incoming call. All incoming calls appear to be direct customer or agent follow-ups.</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="inlineStr"/>
+      <c r="T181" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S181" s="2" t="inlineStr">
-        <is>
-          <t>Multiple outbound attempts were made to reach Richard Holcombe, with only one outbound call completed. There were two incoming calls, but none were completed on the Retention line. The customer expressed disinterest in continuing with the debt program and ultimately cancelled. No evidence of a live transfer from Aspire or Resync was found, and the case was closed without retention.</t>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>Richard Holcombe received several outbound calls regarding his debt program, but only one completed incoming call occurred, and it was not on the Retention line. No evidence of a live transfer from Aspire or Resync was found. The customer expressed disinterest in continuing with the program and ultimately cancelled. Most calls were outbound attempts or voicemails, with no successful retention intervention.</t>
         </is>
       </c>
     </row>
@@ -14657,20 +15869,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P182" s="2" t="inlineStr">
-        <is>
-          <t>Opening transcript of 2026-06-01 23:37 incoming Retention call: 'This is Jacob from Aspire Law Group... I have a mutual client, a Denise... I just authenticated the client and transferred the call.' Call came in on the Retention line.</t>
+      <c r="P182" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
         <is>
+          <t>Jacob</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-06-01 23:37 incoming Retention line call, the caller introduced themselves as 'Jacob from Aspire Law Group' and stated, 'I have a mutual client, a Denise,' and 'I just authenticated the client and transferred the call.'</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Retention line</t>
         </is>
       </c>
-      <c r="R182" s="2" t="inlineStr"/>
-      <c r="S182" s="2" t="inlineStr">
-        <is>
-          <t>Denise's case involved two completed incoming calls on the Retention line, both related to her cancellation and refund request. The first call was a live transfer from Jacob at Aspire Law Group, who handed Denise off to Michael Belfort for assistance. The second call continued the discussion, with Denise expressing frustration about a withdrawal after her cancellation attempt; Michael processed her refund and confirmed cancellation. No outbound calls were answered, only brief voicemails were left. The outcome was a confirmed cancellation and refund for Denise.</t>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr">
+        <is>
+          <t>Denise Goulet was live-transferred by Jacob from Aspire to Michael Belfort on the Retention line to discuss a refund after cancellation. Two completed incoming calls occurred on the Retention line; the first was the live transfer, and the second was a follow-up with Denise and a third party, Tim, to resolve her refund and confirm cancellation. No outbound calls were answered; both outbound attempts went to voicemail. The case ended with Denise's cancellation confirmed and a refund processed.</t>
         </is>
       </c>
     </row>
@@ -14730,16 +15952,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P183" s="2" t="inlineStr">
-        <is>
-          <t>No mention of Aspire or Resync, and no indication that the incoming call was a partner handoff or transfer. The call opened with the agent introducing herself as from Better Path Lending and speaking directly to the client.</t>
-        </is>
-      </c>
+      <c r="P183" s="3" t="inlineStr"/>
       <c r="Q183" s="2" t="inlineStr"/>
-      <c r="R183" s="2" t="inlineStr"/>
-      <c r="S183" s="2" t="inlineStr">
-        <is>
-          <t>Brenda Evans received one completed incoming call on the Retention line, where she expressed her desire to cancel her debt consolidation program due to lack of communication and trust. The agent attempted to address her concerns, but Brenda remained firm about cancellation and mentioned involving her lawyer. There was also one outbound call attempt from the CS team that resulted in a brief voicemail. The deal status is cancelled.</t>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>No mention of Aspire or Resync, and no indication of a partner representative handing off the client in the opening transcript of the only incoming call (Retention line). The call was initiated by a Better Path Lending agent directly to the client.</t>
+        </is>
+      </c>
+      <c r="S183" s="2" t="inlineStr"/>
+      <c r="T183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="inlineStr">
+        <is>
+          <t>Brenda Evans received one completed incoming call on the Retention line from a Better Path Lending agent, where she expressed her desire to cancel her debt consolidation program due to trust issues and lack of communication. The agent attempted to address her concerns, but Brenda insisted on involving her lawyer. There was also one brief outbound call attempt that resulted in voicemail. Ultimately, Brenda's deal status is cancelled.</t>
         </is>
       </c>
     </row>
@@ -14803,16 +16027,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P184" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Retention line featured a representative named Kevin from 'client care,' but there was no mention of Aspire or Resync, nor was there an explicit statement that this was a partner handoff or live transfer from those companies.</t>
-        </is>
-      </c>
+      <c r="P184" s="3" t="inlineStr"/>
       <c r="Q184" s="2" t="inlineStr"/>
-      <c r="R184" s="2" t="inlineStr"/>
-      <c r="S184" s="2" t="inlineStr">
-        <is>
-          <t>Frank Saliture called in to cancel his debt relief program, expressing concerns about affordability and not recalling enrollment. The call was handled by Henry Hart, who discussed Frank's options and attempted to lower his payment, but Frank still decided to cancel. There was one completed incoming call on the Retention line and one outbound follow-up, with no evidence of a partner live transfer. The deal was ultimately cancelled.</t>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>No incoming caller identified themselves as from Aspire or Resync, nor did they explicitly state they were a partner transferring the client. The incoming call was from 'Kevin with client care', but no Aspire/Resync mention.</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr"/>
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr">
+        <is>
+          <t>Frank Saliture had one incoming and one outgoing call, both on the Retention line. The incoming call was facilitated by a 'client care' representative named Kevin, who transferred Frank to Henry Hart for cancellation assistance, but there was no mention of Aspire or Resync. Frank expressed financial concerns and ultimately decided to cancel his program. The agent provided information about refunds and encouraged Frank to reach out if he reconsidered.</t>
         </is>
       </c>
     </row>
@@ -14876,20 +16102,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P185" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls were completed; all completed calls were outbound. No transcripts or summaries mention an incoming call from Aspire, Resync, or a partner representative handing off the client.</t>
-        </is>
-      </c>
+      <c r="P185" s="3" t="inlineStr"/>
       <c r="Q185" s="2" t="inlineStr"/>
-      <c r="R185" s="5" t="inlineStr">
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; all calls were outbound. No transcripts mention Aspire or Resync, and no incoming call introductions indicate a partner transfer.</t>
+        </is>
+      </c>
+      <c r="S185" s="2" t="inlineStr"/>
+      <c r="T185" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S185" s="2" t="inlineStr">
-        <is>
-          <t>All completed calls to Noel Crockett were outbound, with no completed incoming calls on the Retention line. The customer expressed dissatisfaction with the program, requested cancellation, and repeatedly asked for confirmation that her account was closed. Agents discussed cancellation policies, attempted to resolve her concerns, and confirmed her request to cancel. Ultimately, the customer was not retained and requested no further contact.</t>
+      <c r="U185" s="2" t="inlineStr">
+        <is>
+          <t>All calls to Noel Crockett were outbound, with no completed incoming calls on the Retention line. The customer requested cancellation multiple times, and agents confirmed the cancellation process. There were several voicemail attempts and completed outbound conversations, but no evidence of a live transfer from Aspire or Resync. The account was ultimately cancelled per the customer's request.</t>
         </is>
       </c>
     </row>
@@ -14953,16 +16181,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P186" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript mentions Aspire or Resync, nor does any caller identify as a partner handing off the client. The only partner mentioned is 'Colton with the Sky Law Group,' which is not Aspire or Resync.</t>
-        </is>
-      </c>
+      <c r="P186" s="3" t="inlineStr"/>
       <c r="Q186" s="2" t="inlineStr"/>
-      <c r="R186" s="2" t="inlineStr"/>
-      <c r="S186" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Timothy Langenberg, had multiple interactions with the retention team, including two completed incoming calls and one completed outbound call. The main issue was dissatisfaction with the program's timeline for debt payoff, leading to a cancellation request. The calls involved a representative from Sky Law Group assisting with the cancellation, but there were no Aspire or Resync live transfers. Ultimately, the client canceled due to unmet expectations and concerns about payment timing.</t>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>The incoming call on the Retention line was from Colton at Sky Law Group, not Aspire or Resync, and there is no mention of a partner handoff from Aspire or Resync in the transcript or summary.</t>
+        </is>
+      </c>
+      <c r="S186" s="2" t="inlineStr"/>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Timothy Langenberg, had multiple interactions primarily on the Retention line, including two completed incoming calls and several outbound attempts. The main incoming call was from a representative at Sky Law Group requesting cancellation due to dissatisfaction with the program's speed. There is no evidence of a live transfer from Aspire or Resync. Ultimately, the deal was cancelled after the customer's concerns were discussed.</t>
         </is>
       </c>
     </row>
@@ -15022,20 +16252,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P187" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls; only one outbound call attempt (voicemail) on the Retention line. No Aspire/Resync mention.</t>
-        </is>
-      </c>
+      <c r="P187" s="3" t="inlineStr"/>
       <c r="Q187" s="2" t="inlineStr"/>
-      <c r="R187" s="5" t="inlineStr">
+      <c r="R187" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls; only one outbound call (voicemail) on the Retention line. No mention of Aspire or Resync.</t>
+        </is>
+      </c>
+      <c r="S187" s="2" t="inlineStr"/>
+      <c r="T187" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S187" s="2" t="inlineStr">
-        <is>
-          <t>There was a single outbound call attempt to the customer on the Retention line, which went to voicemail and was not answered. No incoming calls were completed, and there is no evidence of a live transfer or partner handoff. The deal status is cancelled, and no conversation with the customer took place.</t>
+      <c r="U187" s="2" t="inlineStr">
+        <is>
+          <t>There was a single outbound call attempt to the customer on the Retention line, which resulted in a voicemail and no completed conversation. No incoming calls were received, and there is no evidence of a live transfer or partner involvement. The deal status is cancelled, and no further contact was made.</t>
         </is>
       </c>
     </row>
@@ -15099,16 +16331,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P188" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Retention line was from 'Kevin with client care,' but there is no mention of Aspire or Resync, nor is there any indication that Kevin is from a partner company handing off the client. The transcript only references internal staff.</t>
-        </is>
-      </c>
+      <c r="P188" s="3" t="inlineStr"/>
       <c r="Q188" s="2" t="inlineStr"/>
-      <c r="R188" s="2" t="inlineStr"/>
-      <c r="S188" s="2" t="inlineStr">
-        <is>
-          <t>Calvin Berryhill contacted the company to cancel his program, believing it was a loan rather than debt consolidation. An internal client care representative transferred the call to a compliance agent, who confirmed Calvin's wish to cancel. The agent then called Calvin back to clarify the situation, but Calvin remained dissatisfied and insisted on cancellation. The account was ultimately cancelled, and no payments were taken.</t>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>The incoming call on the Retention line was a transfer from 'Kevin with client care,' but there is no mention or indication that Kevin is from Aspire or Resync, nor is there any explicit statement that this is a partner handoff from those companies.</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr"/>
+      <c r="T188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Calvin Berryhill, was transferred in by a representative named Kevin from client care, requesting cancellation of his program. There was one completed incoming call on the Retention line and one outbound follow-up by Ryan Henderson, during which Calvin confirmed his desire to cancel, citing dissatisfaction and misunderstanding about the program. No Aspire or Resync partner was involved in the transfer. The account was cancelled as requested.</t>
         </is>
       </c>
     </row>
@@ -15168,20 +16402,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P189" s="2" t="inlineStr">
-        <is>
-          <t>All completed calls were outbound from company agents to the customer; there were no completed incoming calls where a partner (Aspire/Resync) or representative transferred or handed off the client. No incoming call transcript shows a partner introduction or transfer.</t>
-        </is>
-      </c>
+      <c r="P189" s="3" t="inlineStr"/>
       <c r="Q189" s="2" t="inlineStr"/>
-      <c r="R189" s="5" t="inlineStr">
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; all completed calls were outbound. No transcript evidence of an incoming call where a partner (Aspire or Resync) transferred the client.</t>
+        </is>
+      </c>
+      <c r="S189" s="2" t="inlineStr"/>
+      <c r="T189" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S189" s="2" t="inlineStr">
-        <is>
-          <t>All contact attempts to Gloria Mciver were outbound, with no completed incoming calls on the Retention line. Agents discussed program details, clarified confusion about Aspire and Better Way, and addressed cancellation requests. Gloria ultimately insisted on canceling her enrollment, and the deal was marked as cancelled. Multiple voicemails were left, and no live transfer from Aspire or Resync occurred.</t>
+      <c r="U189" s="2" t="inlineStr">
+        <is>
+          <t>All completed calls were outbound attempts to reach Gloria Mciver, with no completed incoming calls on the Retention line. Agents discussed program details, clarified confusion about the debt consolidation process, and addressed cancellation requests. Gloria ultimately insisted on canceling her enrollment, and the deal status is marked as cancelled. Multiple voicemails were left, but no live transfer or partner handoff occurred.</t>
         </is>
       </c>
     </row>
@@ -15241,20 +16477,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P190" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary mentions Aspire, Resync, or a partner transfer. The only incoming call was from the customer returning a missed call.</t>
-        </is>
-      </c>
+      <c r="P190" s="3" t="inlineStr"/>
       <c r="Q190" s="2" t="inlineStr"/>
-      <c r="R190" s="5" t="inlineStr">
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call had a representative mention Aspire or Resync, nor did any incoming caller indicate they were a partner transferring the client. The only incoming call was from the customer returning a missed call.</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr"/>
+      <c r="T190" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S190" s="2" t="inlineStr">
-        <is>
-          <t>The customer, Vilmar Are, requested to cancel their program due to credit concerns and unaffordable payments. An outbound retention call was completed to process the cancellation, and the agent explained the implications. Later, the customer called back after missing a call, and was informed that the cancellation had already been finalized. No live transfer or partner handoff occurred, and the account was successfully cancelled.</t>
+      <c r="U190" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Vilmar Are, initiated cancellation due to concerns about credit impact and unaffordable payments. An outbound Retention call completed the cancellation and provided information. The only incoming call was the customer returning a missed call, confirming the cancellation was finalized. No live transfer or partner involvement occurred, and no completed incoming calls came in on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -15318,20 +16556,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P191" s="2" t="inlineStr">
+      <c r="P191" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr">
         <is>
           <t>"This is Emily with Resync. I just have a cancellation request for you." — incoming on Retention line (retention_in)</t>
         </is>
       </c>
-      <c r="Q191" s="2" t="inlineStr">
+      <c r="S191" s="2" t="inlineStr">
         <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R191" s="2" t="inlineStr"/>
-      <c r="S191" s="2" t="inlineStr">
-        <is>
-          <t>The customer was transferred in by a Resync representative on the Retention line to request a cancellation, citing being misled about the program. The compliance manager confirmed the cancellation and discussed related account details with the customer. Multiple outbound attempts were made before and after, but only one incoming Retention call was completed. The case ended with the customer's cancellation being processed and confirmation promised.</t>
+      <c r="T191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="inlineStr">
+        <is>
+          <t>The customer was live-transferred in by Emily from Resync on the Retention line for a cancellation request, citing being misled about the program. The compliance manager, Henry, confirmed the cancellation and discussed related account and payment issues with Alan. Multiple outbound calls and voicemails were made by your agents before and after the transfer, but only one completed incoming retention call occurred. Ultimately, the customer's deal was cancelled and confirmation was provided.</t>
         </is>
       </c>
     </row>
@@ -15391,16 +16639,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P192" s="2" t="inlineStr">
-        <is>
-          <t>Neither incoming completed call (Rika NSF or Retention) includes any greeting or introduction from an Aspire or Resync representative, nor do they mention being a partner transferring the client. The Retention call opens with 'This is Michael with Better Lending,' not Aspire/Resync, and the other incoming call is a direct conversation between Rika Hart and Jennifer with no transfer or partner handoff.</t>
-        </is>
-      </c>
+      <c r="P192" s="3" t="inlineStr"/>
       <c r="Q192" s="2" t="inlineStr"/>
-      <c r="R192" s="2" t="inlineStr"/>
-      <c r="S192" s="2" t="inlineStr">
-        <is>
-          <t>Jennifer Blackmon had multiple outbound call attempts from agents, mostly resulting in voicemails. She spoke with Rika Hart about payment issues and disputed charges, then called in to confirm her desire to cancel the account. Michael Belfort from Better Lending handled her cancellation request on the Retention line, confirmed the account would be canceled, and promised a confirmation email. The account was ultimately canceled after Jennifer insisted and threatened legal action.</t>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call was from an Aspire or Resync representative, nor did any incoming caller introduce themselves as transferring the client from Aspire or Resync. All incoming calls were either directly from the customer or from Better Lending's own agents (e.g., Michael Belfort on Retention).</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr"/>
+      <c r="T192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>Multiple outbound attempts were made to Jennifer regarding a missed payment, with only one outbound and two incoming calls completed. The only completed incoming Retention call was handled by Michael Belfort from Better Lending, not a partner transfer. Jennifer insisted on canceling her account due to payment issues and ultimately her account was canceled after she threatened legal action. No live transfer from Aspire or Resync occurred; all partner mentions were from outbound calls.</t>
         </is>
       </c>
     </row>
@@ -15464,14 +16714,16 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P193" s="2" t="inlineStr"/>
+      <c r="P193" s="3" t="inlineStr"/>
       <c r="Q193" s="2" t="inlineStr"/>
-      <c r="R193" s="6" t="inlineStr">
+      <c r="R193" s="2" t="inlineStr"/>
+      <c r="S193" s="2" t="inlineStr"/>
+      <c r="T193" s="6" t="inlineStr">
         <is>
           <t>No calls found</t>
         </is>
       </c>
-      <c r="S193" s="2" t="inlineStr">
+      <c r="U193" s="2" t="inlineStr">
         <is>
           <t>No calls found for this number in the phone system.</t>
         </is>
@@ -15537,20 +16789,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P194" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls had transcribable conversations or any mention of Aspire/Resync or a partner transfer; all calls were either outbound voicemails or an incoming call that went to voicemail.</t>
-        </is>
-      </c>
+      <c r="P194" s="3" t="inlineStr"/>
       <c r="Q194" s="2" t="inlineStr"/>
-      <c r="R194" s="5" t="inlineStr">
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript mentions Aspire or Resync, and no incoming call involved a partner representative handing off the client. All calls were outbound voicemails or an unanswered incoming call.</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr"/>
+      <c r="T194" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S194" s="2" t="inlineStr">
-        <is>
-          <t>All calls were either outbound attempts that resulted in voicemail or a single incoming call to the Retention line that also went to voicemail. There were no completed conversations with the customer. No evidence of a live transfer or partner handoff was found. The customer's deal status is cancelled, and no retention was achieved.</t>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>There were a total of six calls, all of which were either outbound attempts that reached voicemail or an unanswered incoming call. No completed conversations occurred, and no live transfers from Aspire or Resync were detected. The customer's deal status is cancelled, with no successful contact made on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -15614,20 +16868,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P195" s="2" t="inlineStr">
-        <is>
-          <t>Call #1: Incoming on Retention line. The caller introduced herself as 'Emily with Resync' and stated, 'I just have a cancellation request for you.' This is a clear partner handoff/transfer.</t>
+      <c r="P195" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
         <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>Call #1: Incoming on Retention line. Caller says, 'This is Emily with Resync. I just have a cancellation request for you.'</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
           <t>Resync via Retention line</t>
         </is>
       </c>
-      <c r="R195" s="2" t="inlineStr"/>
-      <c r="S195" s="2" t="inlineStr">
-        <is>
-          <t>Both calls were incoming on the Retention line. The first was a live transfer from Resync requesting cancellation, which was handled by Rick. The second call was a direct inquiry from the customer, Esteban, who confirmed his desire to cancel the consolidation loan service. Both calls resulted in the processing of the cancellation, with confirmation to be sent via email. No outbound calls or attempts were made.</t>
+      <c r="T195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Esteban Escobedo, had two completed incoming calls on the Retention line. The first was a live transfer from Emily at Resync, who requested cancellation on the client's behalf and handed the call off to your agent. The second call was a direct incoming call from the client to discuss and confirm the cancellation. No outbound calls or attempts were made. The account was ultimately cancelled as requested.</t>
         </is>
       </c>
     </row>
@@ -15691,14 +16955,16 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P196" s="2" t="inlineStr"/>
+      <c r="P196" s="3" t="inlineStr"/>
       <c r="Q196" s="2" t="inlineStr"/>
-      <c r="R196" s="6" t="inlineStr">
+      <c r="R196" s="2" t="inlineStr"/>
+      <c r="S196" s="2" t="inlineStr"/>
+      <c r="T196" s="6" t="inlineStr">
         <is>
           <t>No calls found</t>
         </is>
       </c>
-      <c r="S196" s="2" t="inlineStr">
+      <c r="U196" s="2" t="inlineStr">
         <is>
           <t>No calls found for this number in the phone system.</t>
         </is>
@@ -15764,20 +17030,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P197" s="2" t="inlineStr">
-        <is>
-          <t>No incoming call transcript or summary mentions Aspire or Resync, nor any explicit partner handoff/transfer. All incoming calls are directly from the customer or unrelated parties.</t>
-        </is>
-      </c>
+      <c r="P197" s="3" t="inlineStr"/>
       <c r="Q197" s="2" t="inlineStr"/>
-      <c r="R197" s="5" t="inlineStr">
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary mentions Aspire or Resync, nor any partner representative handing off or transferring the client. All incoming calls are direct from the customer.</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr"/>
+      <c r="T197" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S197" s="2" t="inlineStr">
-        <is>
-          <t>There were several incoming calls, but none on the Retention line and none involved a partner transfer. Outbound attempts were made, with one completed outbound Retention call where the customer confirmed cancellation after discussing options. No live transfer from Aspire or Resync occurred; the customer independently requested cancellation, which was processed and confirmed.</t>
+      <c r="U197" s="2" t="inlineStr">
+        <is>
+          <t>The customer made several incoming calls directly to the company, requesting to speak with Ben Harris after being disconnected. No live transfer from Aspire or Resync occurred. An outbound retention call was completed, during which the customer confirmed cancellation of their application, as her brother would pay off her debt. The cancellation was finalized and a confirmation email was promised.</t>
         </is>
       </c>
     </row>
@@ -15841,24 +17109,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P198" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the CS Team line opened with Talia Morgan stating, 'This is Talia Morgan with Resync, and this is about the debt consolidation program that you have with us.'</t>
+      <c r="P198" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
         <is>
+          <t>Talia Morgan</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-07 incoming call to the CS Team line, the agent introduced herself as 'Talia Morgan with Resync, and this is about the debt consolidation program that you have with us.'</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
           <t>Resync via CS Team line</t>
         </is>
       </c>
-      <c r="R198" s="5" t="inlineStr">
+      <c r="T198" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S198" s="2" t="inlineStr">
-        <is>
-          <t>Deborah Devincentz canceled her debt consolidation program, stating she had already paid off her credit cards and no longer needed the service. There were multiple outbound retention calls, but no completed incoming calls on the Retention line. The only completed incoming call was on the CS Team line, where a Resync representative confirmed receipt of Deborah's cancellation request. Ultimately, the deal was canceled and no retention was achieved.</t>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>Deborah Devincentz had several outbound retention calls and one completed incoming call on the CS Team line. The incoming call was a live transfer from Resync, where the agent confirmed Deborah's cancellation request and discussed her reasons for leaving the program. No completed calls occurred on the Retention line, and the deal was ultimately cancelled as Deborah had already paid off her credit cards and no longer needed the service.</t>
         </is>
       </c>
     </row>
@@ -15922,16 +17200,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P199" s="2" t="inlineStr">
-        <is>
-          <t>No mention of Aspire or Resync in the incoming retention call transcript. The caller was the customer, Luis Sarango, not a partner representative. The opening lines show Luis called in directly after receiving a voicemail.</t>
-        </is>
-      </c>
+      <c r="P199" s="3" t="inlineStr"/>
       <c r="Q199" s="2" t="inlineStr"/>
-      <c r="R199" s="2" t="inlineStr"/>
-      <c r="S199" s="2" t="inlineStr">
-        <is>
-          <t>Luis Sarango received two outbound retention calls, both resulting in voicemails. He then called in directly to the Retention line to request cancellation, citing family support and a new debt management option. The agent discussed alternatives but Luis remained firm on cancellation, requesting an email summary. No partner live transfer occurred; the deal was cancelled after the direct customer call.</t>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>No mention of Aspire or Resync, and the incoming caller was the client himself (Luis Sarango), not a partner representative. The opening transcript shows a direct client call on the Retention line.</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr"/>
+      <c r="T199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="inlineStr">
+        <is>
+          <t>Luis Sarango received two outbound voicemail attempts from the Retention department and then called back directly on the Retention line. He requested cancellation, citing alternative debt management options with family assistance. The agent discussed options but Luis remained firm on his decision to cancel, requesting a summary email. No partner transfer or live call from Aspire or Resync occurred.</t>
         </is>
       </c>
     </row>
@@ -15990,29 +17270,27 @@
       <c r="N200" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O200" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P200" s="2" t="inlineStr">
-        <is>
-          <t>The incoming completed call on the Onboarding line (2026-05-23) opened with Dana from the onboarding team welcoming Iris, the client, and referencing the Resync partner process. The transcript and summary indicate the client was handed off and the Resync process was explained, showing a partner transfer.</t>
-        </is>
-      </c>
-      <c r="Q200" s="2" t="inlineStr">
-        <is>
-          <t>Resync via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R200" s="5" t="inlineStr">
+      <c r="O200" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P200" s="3" t="inlineStr"/>
+      <c r="Q200" s="2" t="inlineStr"/>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript shows a representative from Aspire or Resync, nor any explicit mention of a partner transferring the client. The only completed incoming call (Onboarding line) is from Dana with the onboarding team, not a partner rep.</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="inlineStr"/>
+      <c r="T200" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S200" s="2" t="inlineStr">
-        <is>
-          <t>The customer was transferred in via the Onboarding line, with the Resync process explained and initial payment arrangements confirmed. Multiple outbound calls were made by retention agents, but no completed incoming calls occurred on the Retention line. The customer ultimately chose to handle their debt directly with creditors, declining further assistance from the company. Several outbound attempts resulted in voicemails or brief conversations, but no retention was achieved.</t>
+      <c r="U200" s="2" t="inlineStr">
+        <is>
+          <t>The customer had several outbound attempts and two completed outbound calls, but no completed incoming calls on the Retention line. The only completed incoming call was with the onboarding team, where the process and payment schedule were explained. Outbound calls involved discussing debt arrangements, but the customer chose to handle creditors directly and declined further assistance. No live transfer from Aspire or Resync occurred.</t>
         </is>
       </c>
     </row>
@@ -16076,24 +17354,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P201" s="2" t="inlineStr">
-        <is>
-          <t>On the 2026-05-22 incoming Onboarding line call, the opening transcript shows: '+18158142724: This is Sarah assist you. Can I have Allison with me?' and 'Are you ready for the file number?' indicating a partner representative (Sarah) is transferring the client (Allison) to Better Lending for onboarding. This is a live transfer.</t>
+      <c r="P201" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
         <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>On the 2026-05-22 incoming Onboarding line call, the opening transcript includes: '+18158142724: This is Sarah assist you. Can I have Allison with me?' and 'Go ahead with the file number.' This indicates a partner rep (Sarah) is live-transferring Allison to Better Lending, and Aspire is mentioned as the initial debt reduction provider in the call summary.</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
           <t>Aspire via Onboarding line</t>
         </is>
       </c>
-      <c r="R201" s="5" t="inlineStr">
+      <c r="T201" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S201" s="2" t="inlineStr">
-        <is>
-          <t>Allison Schroeder was live-transferred by an Aspire representative to Better Lending for onboarding, where her debt reduction process and payment schedule were set up. Multiple outbound calls and voicemails were made by retention agents, but there were no completed incoming calls on the Retention line. The client did not connect with Retention, and the only completed inbound call was the initial onboarding transfer. No cancellation or retention resolution occurred.</t>
+      <c r="U201" s="2" t="inlineStr">
+        <is>
+          <t>Allison Schroeder was live-transferred in by a partner rep from Aspire on the Onboarding line, where she completed her onboarding and was set up for a debt reduction program. Multiple outbound attempts were made by retention agents, but there were no completed incoming calls on the Retention line. The client did not answer any retention calls, and only onboarding was completed. No cancellation or retention resolution occurred; the account remains in 'Forth Hold' status.</t>
         </is>
       </c>
     </row>
@@ -16157,20 +17445,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P202" s="2" t="inlineStr">
-        <is>
-          <t>No mention of Aspire or Resync in any incoming call transcript. The only incoming call (Onboarding line) was from someone referencing a file for Brian Adams, but there is no indication this was a partner handoff or live transfer from Aspire/Resync.</t>
-        </is>
-      </c>
+      <c r="P202" s="3" t="inlineStr"/>
       <c r="Q202" s="2" t="inlineStr"/>
-      <c r="R202" s="5" t="inlineStr">
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>No incoming call transcript or summary mentions Aspire or Resync, nor does any incoming caller explicitly state they are a partner or are transferring a client. The only incoming call (Onboarding line) is from a caller discussing a file for Brian Adams, but there is no indication this is a partner handoff or live transfer.</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr"/>
+      <c r="T202" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S202" s="2" t="inlineStr">
-        <is>
-          <t>There was one completed incoming call on the Onboarding line, where a file was discussed, but no evidence of a partner live transfer. The majority of calls were outbound attempts, mostly resulting in voicemails, with only one outbound call completed. No completed incoming calls occurred on the Retention line. The customer did not connect with the Retention team, and most outreach attempts were unsuccessful.</t>
+      <c r="U202" s="2" t="inlineStr">
+        <is>
+          <t>There were 20 total calls, with 19 outbound attempts and only 1 completed incoming call (on the Onboarding line). No completed calls occurred on the Retention line, despite multiple outbound attempts and voicemails from various agents. The only completed calls were an onboarding discussion and a follow-up about a graduation loan. There is no evidence of a live transfer, cancellation, or retention interaction; the customer was not reached on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -16234,24 +17524,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P203" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-15 15:23, an incoming call on the Onboarding line opened with a representative saying, 'I got Don Mace here with me. Ready with the file number?' and then handed off to the Better Lending onboarding team, indicating a live transfer from a partner.</t>
+      <c r="P203" s="3" t="inlineStr">
+        <is>
+          <t>Aspire</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
         <is>
-          <t>Aspire via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R203" s="5" t="inlineStr">
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-15 15:23, incoming on Onboarding line: The caller says, 'I got Don Mace here with me. Ready with the file number?' and then hands off to the Better Lending onboarding agent, indicating a live transfer. The partner did not state Aspire or Resync by name.</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t>Partner via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T203" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S203" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live transferred in from Aspire via the Onboarding line and began the onboarding process for debt reduction. Multiple outbound attempts were made to reach the customer, with only a few completed outbound calls and no completed incoming calls on the Retention line. The customer later attempted to cancel due to financial hardship, as discussed in an incoming NSF call, but did not connect with Retention directly. The case remains unresolved with cancellation requested but not confirmed.</t>
+      <c r="U203" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Mace was live-transferred in by a partner rep to the onboarding team, where her debt reduction process was explained and scheduled. Multiple outbound attempts were made, with only a few completed outbound calls and one completed incoming call on the NSF line. Dawn later called back to confirm cancellation of her Aspire debt consolidation, citing affordability issues. No completed calls occurred on the Retention line.</t>
         </is>
       </c>
     </row>
@@ -16315,20 +17615,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P204" s="2" t="inlineStr">
-        <is>
-          <t>No incoming calls mention Aspire or Resync, nor any partner handoff/transfer. All completed calls are outbound; all incoming calls are voicemails or in-progress with no evidence of a live transfer.</t>
-        </is>
-      </c>
+      <c r="P204" s="3" t="inlineStr"/>
       <c r="Q204" s="2" t="inlineStr"/>
-      <c r="R204" s="5" t="inlineStr">
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls had an agent introduce themselves as from Aspire or Resync, nor did any incoming call mention a partner transfer. All completed calls were outbound, and the only incoming calls were either voicemails or in-progress with no transcript evidence of a live transfer.</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr"/>
+      <c r="T204" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S204" s="2" t="inlineStr">
-        <is>
-          <t>All completed calls to this customer were outbound, with agents leaving messages or providing updates, but no incoming calls were completed on the Retention line. There were numerous outbound attempts, mostly resulting in voicemails. No evidence of a live transfer or partner handoff was found, and the customer did not connect on any inbound Retention call.</t>
+      <c r="U204" s="2" t="inlineStr">
+        <is>
+          <t>All completed calls to Stephanie Paige were outbound attempts by your agents, with no completed incoming calls on the Retention line. Most calls resulted in voicemails or brief messages, and there is no evidence of a live transfer from Aspire or Resync. The customer did not answer or return calls, and no cancellation or retention conversation was completed.</t>
         </is>
       </c>
     </row>
@@ -16392,24 +17694,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P205" s="2" t="inlineStr">
-        <is>
-          <t>The incoming call on the Onboarding line began with Donna from the onboarding team greeting Melina, who then said, 'So I have Denise on the line. Let me provide you with the file number.' Melina then stated, 'I will leave the call now to care of the customer,' indicating a live transfer/hand-off.</t>
-        </is>
-      </c>
-      <c r="Q205" s="2" t="inlineStr">
-        <is>
-          <t>Melina via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R205" s="5" t="inlineStr">
+      <c r="P205" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr"/>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: '+12487039036: So I have Denise on the line. Let me provide you with the file number.' and '+12487039036: I will leave the call now to care of the customer.' clearly indicates a partner representative transferring the client.</t>
+        </is>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T205" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S205" s="2" t="inlineStr">
-        <is>
-          <t>There was one completed incoming call, which was a live transfer from Melina via the Onboarding line, where the onboarding process and debt program were explained to the customer. All other calls were outbound attempts or voicemails, including several to the Retention line, but no completed incoming calls on Retention. No Aspire or Resync partner was mentioned. The customer was onboarded, but there was no further live contact; all subsequent outreach attempts were unsuccessful.</t>
+      <c r="U205" s="2" t="inlineStr">
+        <is>
+          <t>There were 19 total calls, with 17 outbound attempts and only one completed incoming call on the Onboarding line. The completed call was a partner handoff, but the partner company was not named. No completed calls occurred on the Retention line, and all outbound attempts resulted in voicemails. The customer was onboarded but did not answer any retention calls.</t>
         </is>
       </c>
     </row>
@@ -16473,24 +17781,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P206" s="2" t="inlineStr">
-        <is>
-          <t>On 2026-05-05, an incoming call on the Onboarding line began with the caller saying, 'I have here Tony Daniels. Are you ready for the phone number?' indicating a partner was transferring the client. Additionally, the agent later referenced Aspire and Resync as partners in the process.</t>
-        </is>
-      </c>
-      <c r="Q206" s="2" t="inlineStr">
-        <is>
-          <t>Partner (Aspire/Resync) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R206" s="5" t="inlineStr">
+      <c r="P206" s="3" t="inlineStr"/>
+      <c r="Q206" s="2" t="inlineStr"/>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>On 2026-05-05, incoming Onboarding line: '+14807037854: I have here Tony Daniels. Are you ready for the phone number?' indicates a partner representative is handing off the client.</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T206" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S206" s="2" t="inlineStr">
-        <is>
-          <t>The customer was live-transferred in by a partner (Aspire/Resync) on the Onboarding line and began the onboarding process, confirming a first payment date. Later, the customer expressed concerns about multiple debt programs and considered canceling, leading to several retention outbound attempts and two completed incoming calls on the retention line. The customer was reassured about no immediate payments and was advised to clarify her situation with other creditors. No completed incoming calls occurred on the Retention line itself; most retention activity was outbound or on other lines.</t>
+      <c r="U206" s="2" t="inlineStr">
+        <is>
+          <t>The customer, Toni Daniels, was live-transferred in via the Onboarding line by a partner rep, then onboarded and scheduled for a first payment. Later, Toni expressed concerns about multiple debt payments and considered canceling, leading to several outbound retention attempts and two completed incoming retention calls. The retention agent clarified program details and offered to postpone payments while Toni resolved her situation. No completed incoming calls occurred on the Retention line; most retention contact was via outbound calls and voicemails.</t>
         </is>
       </c>
     </row>
@@ -16554,20 +17864,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P207" s="2" t="inlineStr">
-        <is>
-          <t>"Hi, Rick. This is Emily with Resync. I have a cancellation request for you." (2026-05-14 incoming on Retention line); also, 2026-05-04 incoming Onboarding line: "I have William Hill with me. Are you ready for the file number?"</t>
+      <c r="P207" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
         <is>
-          <t>Resync via Onboarding line (2026-05-04) and Resync via Retention line (2026-05-14)</t>
-        </is>
-      </c>
-      <c r="R207" s="2" t="inlineStr"/>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 22:34 incoming on Onboarding: The incoming caller says, 'This is Bruce. I have William Hill with me. Are you ready for the file number?' indicating a live transfer from a partner. The call came in on the Onboarding line.</t>
+        </is>
+      </c>
       <c r="S207" s="2" t="inlineStr">
         <is>
-          <t>The customer was live-transferred in twice: once for onboarding (from Resync) and once for a cancellation request (from Resync). After the cancellation request, the agent explained the account would remain active until June 15 with no further payments, and a refund would be processed. Multiple outbound attempts were made, with only one additional outbound call completed and many voicemails left. The customer was not retained, and the process moved toward cancellation and refund.</t>
+          <t>Resync via Onboarding line</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr">
+        <is>
+          <t>The customer was live-transferred in by Bruce from Resync for onboarding, and Vera Grayson completed the setup and explained the process. Later, Emily from Resync live-transferred a cancellation request to the Retention line, where Rick handled the cancellation and refund arrangements. There were multiple outbound attempts and follow-ups, including a completed outbound call to discuss the account status and refund, but the customer was not always available. Ultimately, the account was set to remain active until June 15 with a refund processed.</t>
         </is>
       </c>
     </row>
@@ -16631,20 +17951,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P208" s="2" t="inlineStr">
-        <is>
-          <t>"Hello, Talia. This is Connor calling from Resync on a recorded line... I have Anthony here on the line. He's following up on his cancellation. Thank you, Talia. Transferring 321." (Retention line); also, Onboarding call opened with a handoff: 'I have here Anthony on the line. His file is good to go. So are you ready for the phone number?' (Onboarding line)</t>
+      <c r="P208" s="3" t="inlineStr">
+        <is>
+          <t>Resync</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
         <is>
-          <t>Resync via Retention line; partner handoff via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R208" s="2" t="inlineStr"/>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 19:53 incoming on Retention: 'This is Connor calling from Resync on a recorded line... I have Anthony here on the line. He's following up on his cancellation.'</t>
+        </is>
+      </c>
       <c r="S208" s="2" t="inlineStr">
         <is>
-          <t>Anthony was live-transferred in twice: once via Onboarding for initial setup (with Resync mentioned as a partner), and once via Retention from Resync regarding a cancellation. He discussed removing a debt and ultimately requested cancellation and a refund, which was confirmed as in process. Multiple outbound attempts were made, but there was one completed inbound Retention call and one completed outbound Retention call. The account is on hold pending refund and cancellation resolution.</t>
+          <t>Resync via Retention line</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr"/>
+      <c r="U208" s="2" t="inlineStr">
+        <is>
+          <t>Anthony Dzurka had multiple interactions, including a live transfer from Resync (Connor) to the Retention line regarding a cancellation request. The customer discussed removing a debt and ultimately requested cancellation and a refund, which was being processed. There were several outbound attempts and voicemails, but at least one completed incoming call on the Retention line. The case involved onboarding, program changes, and a pending refund.</t>
         </is>
       </c>
     </row>
@@ -16708,24 +18038,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P209" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call on Onboarding line: Max said, 'I had a client on the line, but it seems that the call dropped with her. Let me just give you the file number.' This indicates a partner (Max) was transferring or handing off a client.</t>
-        </is>
-      </c>
+      <c r="P209" s="3" t="inlineStr"/>
       <c r="Q209" s="2" t="inlineStr">
         <is>
-          <t>Max (partner) via Onboarding line</t>
-        </is>
-      </c>
-      <c r="R209" s="5" t="inlineStr">
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call on Onboarding line: Max (partner rep) said, 'I had a client on the line, but it seems that the call dropped with her.' This indicates a partner was handing off/transferring the client.</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding line</t>
+        </is>
+      </c>
+      <c r="T209" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S209" s="2" t="inlineStr">
-        <is>
-          <t>The customer was transferred in via a live call from a partner (Max) on the Onboarding line. Multiple outbound attempts were made, with three completed outbound calls discussing the customer's desire to cancel their program. No completed incoming calls occurred on the Retention line, and the customer ultimately confirmed their wish to cancel after comparing programs. Most other calls were voicemails or brief attempts with no further live contact.</t>
+      <c r="U209" s="2" t="inlineStr">
+        <is>
+          <t>There were multiple outbound attempts to reach the customer, with three outbound calls completed. No completed incoming calls occurred on the Retention line. The only live transfer was an incoming call on the Onboarding line, where a partner rep (Max) attempted to transfer the client after a dropped call. The customer repeatedly requested cancellation, and ultimately confirmed cancellation with a compliance agent from Resync on an outbound call.</t>
         </is>
       </c>
     </row>
@@ -16789,25 +18125,27 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P210" s="2" t="inlineStr">
-        <is>
-          <t>All calls were outbound attempts with no completed incoming calls. No mention of Aspire or Resync, and no evidence of a live transfer or partner handoff in any call transcript or log.</t>
-        </is>
-      </c>
+      <c r="P210" s="3" t="inlineStr"/>
       <c r="Q210" s="2" t="inlineStr"/>
-      <c r="R210" s="5" t="inlineStr">
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>No incoming calls were completed; all calls were outbound attempts with only brief voicemails left. No mention of Aspire or Resync, and no evidence of a partner transfer in any transcript or call log.</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr"/>
+      <c r="T210" s="5" t="inlineStr">
         <is>
           <t>OB done — no calls on retention line</t>
         </is>
       </c>
-      <c r="S210" s="2" t="inlineStr">
-        <is>
-          <t>All 20 calls to Frank Miller were outbound attempts, each resulting in brief voicemails with no completed conversations. There were no completed incoming calls on any line, including Retention. No live transfers or partner handoffs occurred, and the customer did not answer or return any calls. No progress was made on the account due to lack of contact.</t>
+      <c r="U210" s="2" t="inlineStr">
+        <is>
+          <t>All 20 calls to Frank Miller were outbound attempts, each resulting in brief voicemails with no completed conversations. There were no completed incoming calls on any line, including Retention. No evidence of a live transfer or partner handoff was found. The customer was not reached, and no progress was made on the account.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S210"/>
+  <autoFilter ref="A1:U210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>